--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -4667,19 +4667,19 @@
         <v>313</v>
       </c>
       <c r="B5" s="34">
-        <v>-397923</v>
+        <v>-190250</v>
       </c>
       <c r="C5" s="34">
-        <v>-79576</v>
+        <v>128096</v>
       </c>
       <c r="D5" s="34">
-        <v>1227043</v>
+        <v>1434716</v>
       </c>
       <c r="E5" s="34">
-        <v>3344538</v>
+        <v>3552210</v>
       </c>
       <c r="F5" s="34">
-        <v>5791669</v>
+        <v>5999341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4747,19 +4747,19 @@
         <v>317</v>
       </c>
       <c r="B9" s="29">
-        <v>-397923</v>
+        <v>-190250</v>
       </c>
       <c r="C9" s="29">
-        <v>-79576</v>
+        <v>128096</v>
       </c>
       <c r="D9" s="29">
-        <v>1227043</v>
+        <v>1434716</v>
       </c>
       <c r="E9" s="29">
-        <v>3344538</v>
+        <v>3552210</v>
       </c>
       <c r="F9" s="29">
-        <v>5791669</v>
+        <v>5999341</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,19 +4847,19 @@
         <v>323</v>
       </c>
       <c r="B17" s="25">
-        <v>-876284</v>
+        <v>-668611</v>
       </c>
       <c r="C17" s="25">
-        <v>-535021</v>
+        <v>-327348</v>
       </c>
       <c r="D17" s="25">
-        <v>795868</v>
+        <v>1003541</v>
       </c>
       <c r="E17" s="25">
-        <v>2939065</v>
+        <v>3146738</v>
       </c>
       <c r="F17" s="25">
-        <v>5413416</v>
+        <v>5621089</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4869,17 +4869,17 @@
       <c r="B19" s="35">
         <v>0</v>
       </c>
-      <c r="C19" s="36">
-        <v>1</v>
+      <c r="C19" s="35">
+        <v>0</v>
       </c>
       <c r="D19" s="35">
         <v>0</v>
       </c>
-      <c r="E19" s="35">
-        <v>0</v>
-      </c>
-      <c r="F19" s="35">
-        <v>0</v>
+      <c r="E19" s="36">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="36">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -5021,19 +5021,19 @@
         <v>330</v>
       </c>
       <c r="B10" s="24">
-        <v>-397923</v>
+        <v>-190250</v>
       </c>
       <c r="C10" s="24">
-        <v>-79576</v>
+        <v>128096</v>
       </c>
       <c r="D10" s="24">
-        <v>1227043</v>
+        <v>1434716</v>
       </c>
       <c r="E10" s="24">
-        <v>3344538</v>
+        <v>3552210</v>
       </c>
       <c r="F10" s="24">
-        <v>5791669</v>
+        <v>5999341</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5041,19 +5041,19 @@
         <v>331</v>
       </c>
       <c r="B11" s="21">
-        <v>-90</v>
+        <v>-43</v>
       </c>
       <c r="C11" s="21">
-        <v>-13</v>
+        <v>21</v>
       </c>
       <c r="D11" s="21">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E11" s="21">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="F11" s="21">
-        <v>707</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5061,19 +5061,19 @@
         <v>332</v>
       </c>
       <c r="B12" s="28">
-        <v>-2.9</v>
+        <v>-1.4</v>
       </c>
       <c r="C12" s="28">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D12" s="28">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="E12" s="28">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="F12" s="28">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6411,19 +6411,19 @@
         <v>370</v>
       </c>
       <c r="D16" s="24">
-        <v>-397923</v>
+        <v>-190250</v>
       </c>
       <c r="E16" s="24">
-        <v>-79576</v>
+        <v>128096</v>
       </c>
       <c r="F16" s="24">
-        <v>1227043</v>
+        <v>1434716</v>
       </c>
       <c r="G16" s="24">
-        <v>3344538</v>
+        <v>3552210</v>
       </c>
       <c r="H16" s="24">
-        <v>5791669</v>
+        <v>5999341</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -357,7 +357,7 @@
     <t>CSP Startup Grant</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -612,10 +612,10 @@
     <t>Special Education Funding (Public Funding)</t>
   </si>
   <si>
-    <t>CSP Startup Grant (Grants &amp; Contributions)</t>
-  </si>
-  <si>
-    <t>Annual Fundraising (Grants &amp; Contributions)</t>
+    <t>CSP Startup Grant (Philanthropy)</t>
+  </si>
+  <si>
+    <t>Annual Fundraising (Philanthropy)</t>
   </si>
   <si>
     <t>Food Service Revenue (Other Revenue)</t>
@@ -1172,7 +1172,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1216,7 +1216,7 @@
     <font>
       <i/>
       <color rgb="FF999999"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1234,7 +1234,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1252,12 +1252,6 @@
     <font>
       <b/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1332,7 +1326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1387,7 +1381,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5607,7 +5600,7 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="12" t="s">
         <v>358</v>
       </c>
     </row>
@@ -5715,19 +5708,19 @@
       <c r="A10" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>-5.68</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="42">
         <v>8.19</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="42">
         <v>28.03</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="42">
         <v>44</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <v>50.52</v>
       </c>
     </row>
@@ -5762,7 +5755,7 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="12" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5870,19 +5863,19 @@
       <c r="A20" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="42">
         <v>-5.68</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="42">
         <v>8.19</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>28.03</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="42">
         <v>44</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="42">
         <v>50.52</v>
       </c>
     </row>
@@ -5917,7 +5910,7 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="12" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6025,19 +6018,19 @@
       <c r="A30" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B30" s="43">
+      <c r="B30" s="42">
         <v>-6.97</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="42">
         <v>5.62</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="42">
         <v>24.12</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="42">
         <v>39.01</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="42">
         <v>45.04</v>
       </c>
     </row>
@@ -6072,7 +6065,7 @@
       <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="12" t="s">
         <v>365</v>
       </c>
     </row>
@@ -6180,19 +6173,19 @@
       <c r="A40" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B40" s="43">
+      <c r="B40" s="42">
         <v>-7.32</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="42">
         <v>5.52</v>
       </c>
-      <c r="D40" s="43">
+      <c r="D40" s="42">
         <v>24.44</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="42">
         <v>39.67</v>
       </c>
-      <c r="F40" s="43">
+      <c r="F40" s="42">
         <v>45.83</v>
       </c>
     </row>
@@ -6330,19 +6323,19 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6468,19 +6461,19 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6508,19 +6501,19 @@
       <c r="A22" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="42">
         <v>-5.68</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="42">
         <v>8.19</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="42">
         <v>28.03</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="42">
         <v>44</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="42">
         <v>50.52</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="378">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -813,6 +813,9 @@
     <t xml:space="preserve">    Janitorial</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Occupancy / Facility</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Marketing &amp; Recruitment</t>
   </si>
   <si>
@@ -828,6 +831,9 @@
     <t xml:space="preserve">    Transportation</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Administrative / General</t>
+  </si>
+  <si>
     <t>Total Operating Expenses</t>
   </si>
   <si>
@@ -1014,6 +1020,9 @@
     <t>CASH FLOW &amp; DEBT</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
     <t>CFADS (Rev - Pers - OpEx)</t>
   </si>
   <si>
@@ -1108,9 +1117,6 @@
   </si>
   <si>
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
-  </si>
-  <si>
-    <t>Revenue</t>
   </si>
   <si>
     <t>SLOW RAMP</t>
@@ -2226,18 +2232,23 @@
         <v>196</v>
       </c>
       <c r="B13" s="25">
+        <f>SUM(B7:B12)</f>
         <v>1546000</v>
       </c>
       <c r="C13" s="25">
+        <f>SUM(C7:C12)</f>
         <v>2564700</v>
       </c>
       <c r="D13" s="25">
+        <f>SUM(D7:D12)</f>
         <v>3893503</v>
       </c>
       <c r="E13" s="25">
+        <f>SUM(E7:E12)</f>
         <v>4977371</v>
       </c>
       <c r="F13" s="25">
+        <f>SUM(F7:F12)</f>
         <v>5458718</v>
       </c>
     </row>
@@ -2390,18 +2401,23 @@
         <v>232</v>
       </c>
       <c r="B8" s="29">
+        <f>SUM(B5:B7)</f>
         <v>510600</v>
       </c>
       <c r="C8" s="29">
+        <f>SUM(C5:C7)</f>
         <v>631102</v>
       </c>
       <c r="D8" s="29">
+        <f>SUM(D5:D7)</f>
         <v>650035</v>
       </c>
       <c r="E8" s="29">
+        <f>SUM(E5:E7)</f>
         <v>669536</v>
       </c>
       <c r="F8" s="29">
+        <f>SUM(F5:F7)</f>
         <v>689622</v>
       </c>
     </row>
@@ -2480,18 +2496,23 @@
         <v>236</v>
       </c>
       <c r="B13" s="29">
+        <f>SUM(B10:B12)</f>
         <v>307473</v>
       </c>
       <c r="C13" s="29">
+        <f>SUM(C10:C12)</f>
         <v>380037</v>
       </c>
       <c r="D13" s="29">
+        <f>SUM(D10:D12)</f>
         <v>391438</v>
       </c>
       <c r="E13" s="29">
+        <f>SUM(E10:E12)</f>
         <v>403181</v>
       </c>
       <c r="F13" s="29">
+        <f>SUM(F10:F12)</f>
         <v>415277</v>
       </c>
     </row>
@@ -2530,18 +2551,23 @@
         <v>238</v>
       </c>
       <c r="B16" s="29">
+        <f>SUM(B15:B15)</f>
         <v>62173</v>
       </c>
       <c r="C16" s="29">
+        <f>SUM(C15:C15)</f>
         <v>76846</v>
       </c>
       <c r="D16" s="29">
+        <f>SUM(D15:D15)</f>
         <v>79151</v>
       </c>
       <c r="E16" s="29">
+        <f>SUM(E15:E15)</f>
         <v>81526</v>
       </c>
       <c r="F16" s="29">
+        <f>SUM(F15:F15)</f>
         <v>83971</v>
       </c>
     </row>
@@ -2580,18 +2606,23 @@
         <v>240</v>
       </c>
       <c r="B19" s="29">
+        <f>SUM(B18:B18)</f>
         <v>62173</v>
       </c>
       <c r="C19" s="29">
+        <f>SUM(C18:C18)</f>
         <v>76846</v>
       </c>
       <c r="D19" s="29">
+        <f>SUM(D18:D18)</f>
         <v>79151</v>
       </c>
       <c r="E19" s="29">
+        <f>SUM(E18:E18)</f>
         <v>81526</v>
       </c>
       <c r="F19" s="29">
+        <f>SUM(F18:F18)</f>
         <v>83971</v>
       </c>
     </row>
@@ -2630,18 +2661,23 @@
         <v>242</v>
       </c>
       <c r="B22" s="29">
+        <f>SUM(B21:B21)</f>
         <v>84012</v>
       </c>
       <c r="C22" s="29">
+        <f>SUM(C21:C21)</f>
         <v>103838</v>
       </c>
       <c r="D22" s="29">
+        <f>SUM(D21:D21)</f>
         <v>106954</v>
       </c>
       <c r="E22" s="29">
+        <f>SUM(E21:E21)</f>
         <v>110162</v>
       </c>
       <c r="F22" s="29">
+        <f>SUM(F21:F21)</f>
         <v>113467</v>
       </c>
     </row>
@@ -2650,18 +2686,23 @@
         <v>243</v>
       </c>
       <c r="B24" s="25">
+        <f>B8+B13+B16+B19+B22</f>
         <v>1026431</v>
       </c>
       <c r="C24" s="25">
+        <f>C8+C13+C16+C19+C22</f>
         <v>1268669</v>
       </c>
       <c r="D24" s="25">
+        <f>D8+D13+D16+D19+D22</f>
         <v>1306729</v>
       </c>
       <c r="E24" s="25">
+        <f>E8+E13+E16+E19+E22</f>
         <v>1345931</v>
       </c>
       <c r="F24" s="25">
+        <f>F8+F13+F16+F19+F22</f>
         <v>1386309</v>
       </c>
     </row>
@@ -2682,7 +2723,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2854,18 +2895,23 @@
         <v>252</v>
       </c>
       <c r="B11" s="29">
+        <f>SUM(B5:B10)</f>
         <v>1288333</v>
       </c>
       <c r="C11" s="29">
+        <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
       <c r="D11" s="29">
+        <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
       <c r="E11" s="29">
+        <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
       <c r="F11" s="29">
+        <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
     </row>
@@ -3064,18 +3110,23 @@
         <v>200</v>
       </c>
       <c r="B23" s="29">
+        <f>SUM(B14:B22)</f>
         <v>1026431</v>
       </c>
       <c r="C23" s="29">
+        <f>SUM(C14:C22)</f>
         <v>1268669</v>
       </c>
       <c r="D23" s="29">
+        <f>SUM(D14:D22)</f>
         <v>1306729</v>
       </c>
       <c r="E23" s="29">
+        <f>SUM(E14:E22)</f>
         <v>1345931</v>
       </c>
       <c r="F23" s="29">
+        <f>SUM(F14:F22)</f>
         <v>1386309</v>
       </c>
     </row>
@@ -3224,29 +3275,34 @@
         <v>20259</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="29">
+        <f>SUM(B31:B34)</f>
+        <v>235000</v>
+      </c>
+      <c r="C35" s="29">
+        <f>SUM(C31:C34)</f>
+        <v>290460</v>
+      </c>
+      <c r="D35" s="29">
+        <f>SUM(D31:D34)</f>
+        <v>299174</v>
+      </c>
+      <c r="E35" s="29">
+        <f>SUM(E31:E34)</f>
+        <v>308149</v>
+      </c>
+      <c r="F35" s="29">
+        <f>SUM(F31:F34)</f>
+        <v>317393</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B36" s="24">
-        <v>20833</v>
-      </c>
-      <c r="C36" s="24">
-        <v>25750</v>
-      </c>
-      <c r="D36" s="24">
-        <v>26523</v>
-      </c>
-      <c r="E36" s="24">
-        <v>27318</v>
-      </c>
-      <c r="F36" s="24">
-        <v>28138</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3254,19 +3310,19 @@
         <v>261</v>
       </c>
       <c r="B37" s="24">
-        <v>12500</v>
+        <v>20833</v>
       </c>
       <c r="C37" s="24">
-        <v>15450</v>
+        <v>25750</v>
       </c>
       <c r="D37" s="24">
-        <v>15914</v>
+        <v>26523</v>
       </c>
       <c r="E37" s="24">
-        <v>16391</v>
+        <v>27318</v>
       </c>
       <c r="F37" s="24">
-        <v>16883</v>
+        <v>28138</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3274,19 +3330,19 @@
         <v>262</v>
       </c>
       <c r="B38" s="24">
-        <v>16667</v>
+        <v>12500</v>
       </c>
       <c r="C38" s="24">
-        <v>20600</v>
+        <v>15450</v>
       </c>
       <c r="D38" s="24">
-        <v>21218</v>
+        <v>15914</v>
       </c>
       <c r="E38" s="24">
-        <v>21855</v>
+        <v>16391</v>
       </c>
       <c r="F38" s="24">
-        <v>22510</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3294,19 +3350,19 @@
         <v>263</v>
       </c>
       <c r="B39" s="24">
-        <v>80000</v>
+        <v>16667</v>
       </c>
       <c r="C39" s="24">
-        <v>164800</v>
+        <v>20600</v>
       </c>
       <c r="D39" s="24">
-        <v>254616</v>
+        <v>21218</v>
       </c>
       <c r="E39" s="24">
-        <v>327818</v>
+        <v>21855</v>
       </c>
       <c r="F39" s="24">
-        <v>360163</v>
+        <v>22510</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3314,128 +3370,183 @@
         <v>264</v>
       </c>
       <c r="B40" s="24">
+        <v>80000</v>
+      </c>
+      <c r="C40" s="24">
+        <v>164800</v>
+      </c>
+      <c r="D40" s="24">
+        <v>254616</v>
+      </c>
+      <c r="E40" s="24">
+        <v>327818</v>
+      </c>
+      <c r="F40" s="24">
+        <v>360163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" s="24">
         <v>60000</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C41" s="24">
         <v>123600</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D41" s="24">
         <v>190962</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E41" s="24">
         <v>245864</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F41" s="24">
         <v>270122</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B41" s="29">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B42" s="29">
+        <f>SUM(B37:B41)</f>
+        <v>190000</v>
+      </c>
+      <c r="C42" s="29">
+        <f>SUM(C37:C41)</f>
+        <v>350200</v>
+      </c>
+      <c r="D42" s="29">
+        <f>SUM(D37:D41)</f>
+        <v>509232</v>
+      </c>
+      <c r="E42" s="29">
+        <f>SUM(E37:E41)</f>
+        <v>639245</v>
+      </c>
+      <c r="F42" s="29">
+        <f>SUM(F37:F41)</f>
+        <v>697815</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B43" s="29">
+        <f>B27+B29+B35+B42</f>
         <v>545000</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C43" s="29">
+        <f>C27+C29+C35+C42</f>
         <v>887860</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D43" s="29">
+        <f>D27+D29+D35+D42</f>
         <v>1190330</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E43" s="29">
+        <f>E27+E29+E35+E42</f>
         <v>1439121</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F43" s="29">
+        <f>F27+F29+F35+F42</f>
         <v>1555453</v>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B44" s="24">
-        <v>49825</v>
-      </c>
-      <c r="C44" s="24">
-        <v>49825</v>
-      </c>
-      <c r="D44" s="24">
-        <v>49825</v>
-      </c>
-      <c r="E44" s="24">
-        <v>49825</v>
-      </c>
-      <c r="F44" s="24">
-        <v>49825</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+    <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B45" s="24">
-        <v>75000</v>
-      </c>
-      <c r="C45" s="24">
-        <v>25000</v>
-      </c>
-      <c r="D45" s="24">
-        <v>30000</v>
-      </c>
-      <c r="E45" s="24">
-        <v>15000</v>
-      </c>
-      <c r="F45" s="24">
-        <v>10000</v>
-      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>269</v>
       </c>
       <c r="B46" s="24">
+        <v>49825</v>
+      </c>
+      <c r="C46" s="24">
+        <v>49825</v>
+      </c>
+      <c r="D46" s="24">
+        <v>49825</v>
+      </c>
+      <c r="E46" s="24">
+        <v>49825</v>
+      </c>
+      <c r="F46" s="24">
+        <v>49825</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" s="24">
+        <v>75000</v>
+      </c>
+      <c r="C47" s="24">
+        <v>25000</v>
+      </c>
+      <c r="D47" s="24">
+        <v>30000</v>
+      </c>
+      <c r="E47" s="24">
+        <v>15000</v>
+      </c>
+      <c r="F47" s="24">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B48" s="24">
         <v>40000</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C48" s="24">
         <v>15000</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D48" s="24">
         <v>10000</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E48" s="24">
         <v>10000</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F48" s="24">
         <v>10000</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B47" s="29">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="29">
+        <f>SUM(B46:B48)</f>
         <v>164825</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C49" s="29">
+        <f>SUM(C46:C48)</f>
         <v>89825</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D49" s="29">
+        <f>SUM(D46:D48)</f>
         <v>89825</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E49" s="29">
+        <f>SUM(E46:E48)</f>
         <v>74825</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F49" s="29">
+        <f>SUM(F46:F48)</f>
         <v>69825</v>
       </c>
     </row>
@@ -3465,7 +3576,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3498,18 +3609,23 @@
         <v>252</v>
       </c>
       <c r="B4" s="27">
+        <f>'Budget Detail'!B11</f>
         <v>1288333</v>
       </c>
       <c r="C4" s="27">
+        <f>'Budget Detail'!C11</f>
         <v>2564700</v>
       </c>
       <c r="D4" s="27">
+        <f>'Budget Detail'!D11</f>
         <v>3893503</v>
       </c>
       <c r="E4" s="27">
+        <f>'Budget Detail'!E11</f>
         <v>4977371</v>
       </c>
       <c r="F4" s="27">
+        <f>'Budget Detail'!F11</f>
         <v>5458718</v>
       </c>
     </row>
@@ -3518,84 +3634,104 @@
         <v>200</v>
       </c>
       <c r="B5" s="27">
+        <f>'Budget Detail'!B23</f>
         <v>1026431</v>
       </c>
       <c r="C5" s="27">
+        <f>'Budget Detail'!C23</f>
         <v>1268669</v>
       </c>
       <c r="D5" s="27">
+        <f>'Budget Detail'!D23</f>
         <v>1306729</v>
       </c>
       <c r="E5" s="27">
+        <f>'Budget Detail'!E23</f>
         <v>1345931</v>
       </c>
       <c r="F5" s="27">
+        <f>'Budget Detail'!F23</f>
         <v>1386309</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B6" s="27">
+        <f>'Budget Detail'!B43</f>
         <v>545000</v>
       </c>
       <c r="C6" s="27">
+        <f>'Budget Detail'!C43</f>
         <v>887860</v>
       </c>
       <c r="D6" s="27">
+        <f>'Budget Detail'!D43</f>
         <v>1190330</v>
       </c>
       <c r="E6" s="27">
+        <f>'Budget Detail'!E43</f>
         <v>1439121</v>
       </c>
       <c r="F6" s="27">
+        <f>'Budget Detail'!F43</f>
         <v>1555453</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B7" s="27">
+        <f>'Budget Detail'!B49</f>
         <v>164825</v>
       </c>
       <c r="C7" s="27">
+        <f>'Budget Detail'!C49</f>
         <v>89825</v>
       </c>
       <c r="D7" s="27">
+        <f>'Budget Detail'!D49</f>
         <v>89825</v>
       </c>
       <c r="E7" s="27">
+        <f>'Budget Detail'!E49</f>
         <v>74825</v>
       </c>
       <c r="F7" s="27">
+        <f>'Budget Detail'!F49</f>
         <v>69825</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B8" s="29">
+        <f>SUM(B5:B7)</f>
         <v>1736256</v>
       </c>
       <c r="C8" s="29">
+        <f>SUM(C5:C7)</f>
         <v>2246354</v>
       </c>
       <c r="D8" s="29">
+        <f>SUM(D5:D7)</f>
         <v>2586884</v>
       </c>
       <c r="E8" s="29">
+        <f>SUM(E5:E7)</f>
         <v>2859877</v>
       </c>
       <c r="F8" s="29">
+        <f>SUM(F5:F7)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3605,47 +3741,57 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B11" s="25">
+        <f>B4-B8</f>
         <v>-447923</v>
       </c>
       <c r="C11" s="25">
+        <f>C4-C8</f>
         <v>318346</v>
       </c>
       <c r="D11" s="25">
+        <f>D4-D8</f>
         <v>1306619</v>
       </c>
       <c r="E11" s="25">
+        <f>E4-E8</f>
         <v>2117494</v>
       </c>
       <c r="F11" s="25">
+        <f>F4-F8</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B12" s="23">
-        <v>-0.34767595489354136</v>
+        <f>IF(B4=0,0,B11/B4)</f>
+        <v>-0.34767595</v>
       </c>
       <c r="C12" s="23">
-        <v>0.12412616281780338</v>
+        <f>IF(C4=0,0,C11/C4)</f>
+        <v>0.12412616</v>
       </c>
       <c r="D12" s="23">
-        <v>0.33558969879535744</v>
+        <f>IF(D4=0,0,D11/D4)</f>
+        <v>0.3355897</v>
       </c>
       <c r="E12" s="23">
-        <v>0.42542423416409325</v>
+        <f>IF(E4=0,0,E11/E4)</f>
+        <v>0.42542423</v>
       </c>
       <c r="F12" s="23">
-        <v>0.44829778198663</v>
+        <f>IF(F4=0,0,F11/F4)</f>
+        <v>0.44829778</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B13" s="24">
         <v>-447923</v>
@@ -3685,7 +3831,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B15" s="24">
         <v>14469</v>
@@ -3730,7 +3876,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3751,43 +3897,43 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3854,7 +4000,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3872,7 +4018,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B7" s="24">
         <v>102643</v>
@@ -3916,7 +4062,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B8" s="24">
         <v>54500</v>
@@ -3960,7 +4106,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B9" s="24">
         <v>13735</v>
@@ -4004,7 +4150,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4022,7 +4168,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B12" s="27">
         <v>170878</v>
@@ -4066,7 +4212,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B13" s="27">
         <v>-16278</v>
@@ -4110,7 +4256,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B14" s="32">
         <v>-16278</v>
@@ -4154,7 +4300,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4169,7 +4315,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B18" s="32">
         <v>-190250</v>
@@ -4177,7 +4323,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B19" s="24">
         <v>-190250</v>
@@ -4209,7 +4355,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4267,19 +4413,9 @@
         <v>5458718</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4289,7 +4425,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B8" s="27">
         <v>1026431</v>
@@ -4309,7 +4445,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B9" s="27">
         <v>545000</v>
@@ -4329,7 +4465,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B10" s="27">
         <v>164825</v>
@@ -4349,37 +4485,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B11" s="29">
+        <f>SUM(B8:B10)</f>
         <v>1736256</v>
       </c>
       <c r="C11" s="29">
+        <f>SUM(C8:C10)</f>
         <v>2246354</v>
       </c>
       <c r="D11" s="29">
+        <f>SUM(D8:D10)</f>
         <v>2586884</v>
       </c>
       <c r="E11" s="29">
+        <f>SUM(E8:E10)</f>
         <v>2859877</v>
       </c>
       <c r="F11" s="29">
+        <f>SUM(F8:F10)</f>
         <v>3011587</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4389,42 +4520,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B14" s="25">
+        <f>B5-B11</f>
         <v>-447923</v>
       </c>
       <c r="C14" s="25">
+        <f>C5-C11</f>
         <v>318346</v>
       </c>
       <c r="D14" s="25">
+        <f>D5-D11</f>
         <v>1306619</v>
       </c>
       <c r="E14" s="25">
+        <f>E5-E11</f>
         <v>2117494</v>
       </c>
       <c r="F14" s="25">
+        <f>F5-F11</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B15" s="23">
-        <v>-0.34767595489354136</v>
+        <f>IF(B5=0,0,B14/B5)</f>
+        <v>-0.34767595</v>
       </c>
       <c r="C15" s="23">
-        <v>0.12412616281780338</v>
+        <f>IF(C5=0,0,C14/C5)</f>
+        <v>0.12412616</v>
       </c>
       <c r="D15" s="23">
-        <v>0.33558969879535744</v>
+        <f>IF(D5=0,0,D14/D5)</f>
+        <v>0.3355897</v>
       </c>
       <c r="E15" s="23">
-        <v>0.42542423416409325</v>
+        <f>IF(E5=0,0,E14/E5)</f>
+        <v>0.42542423</v>
       </c>
       <c r="F15" s="23">
-        <v>0.44829778198663</v>
+        <f>IF(F5=0,0,F14/F5)</f>
+        <v>0.44829778</v>
       </c>
     </row>
   </sheetData>
@@ -4493,7 +4634,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B5" s="24">
         <v>500000</v>
@@ -4513,7 +4654,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B6" s="24">
         <v>28186</v>
@@ -4533,7 +4674,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B7" s="24">
         <v>21639</v>
@@ -4553,7 +4694,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B8" s="27">
         <v>49825</v>
@@ -4573,7 +4714,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B9" s="32">
         <v>478361</v>
@@ -4617,7 +4758,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4647,7 +4788,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4657,7 +4798,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="34">
         <v>-190250</v>
@@ -4677,7 +4818,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B6" s="24">
         <v>0</v>
@@ -4697,7 +4838,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B7" s="24">
         <v>0</v>
@@ -4717,7 +4858,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B8" s="24">
         <v>0</v>
@@ -4737,7 +4878,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B9" s="29">
         <v>-190250</v>
@@ -4757,7 +4898,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4767,7 +4908,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B12" s="24">
         <v>0</v>
@@ -4787,7 +4928,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B13" s="24">
         <v>478361</v>
@@ -4807,7 +4948,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B14" s="29">
         <v>478361</v>
@@ -4827,7 +4968,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4837,7 +4978,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B17" s="25">
         <v>-668611</v>
@@ -4857,7 +4998,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B19" s="35">
         <v>0</v>
@@ -4892,7 +5033,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4901,7 +5042,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4931,7 +5072,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4941,22 +5082,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B5" s="24">
-        <v>-283098</v>
+        <v>1288333</v>
       </c>
       <c r="C5" s="24">
-        <v>408171</v>
+        <v>2564700</v>
       </c>
       <c r="D5" s="24">
-        <v>1396444</v>
+        <v>3893503</v>
       </c>
       <c r="E5" s="24">
-        <v>2192319</v>
+        <v>4977371</v>
       </c>
       <c r="F5" s="24">
-        <v>2516956</v>
+        <v>5458718</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4964,309 +5105,329 @@
         <v>296</v>
       </c>
       <c r="B6" s="24">
+        <v>1026431</v>
+      </c>
+      <c r="C6" s="24">
+        <v>1268669</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1306729</v>
+      </c>
+      <c r="E6" s="24">
+        <v>1345931</v>
+      </c>
+      <c r="F6" s="24">
+        <v>1386309</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="24">
+        <v>545000</v>
+      </c>
+      <c r="C7" s="24">
+        <v>887860</v>
+      </c>
+      <c r="D7" s="24">
+        <v>1190330</v>
+      </c>
+      <c r="E7" s="24">
+        <v>1439121</v>
+      </c>
+      <c r="F7" s="24">
+        <v>1555453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="27">
+        <f>B5-B6-B7</f>
+        <v>-283098</v>
+      </c>
+      <c r="C8" s="27">
+        <f>C5-C6-C7</f>
+        <v>408171</v>
+      </c>
+      <c r="D8" s="27">
+        <f>D5-D6-D7</f>
+        <v>1396444</v>
+      </c>
+      <c r="E8" s="27">
+        <f>E5-E6-E7</f>
+        <v>2192319</v>
+      </c>
+      <c r="F8" s="27">
+        <f>F5-F6-F7</f>
+        <v>2516956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" s="24">
         <v>49825</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C9" s="24">
         <v>49825</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D9" s="24">
         <v>49825</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E9" s="24">
         <v>49825</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F9" s="24">
         <v>49825</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B7" s="37">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="37">
+        <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-5.68</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C10" s="37">
+        <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>8.19</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D10" s="37">
+        <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>28.03</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E10" s="37">
+        <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>44</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F10" s="37">
+        <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>50.52</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="24">
-        <v>-190250</v>
-      </c>
-      <c r="C10" s="24">
-        <v>128096</v>
-      </c>
-      <c r="D10" s="24">
-        <v>1434716</v>
-      </c>
-      <c r="E10" s="24">
-        <v>3552210</v>
-      </c>
-      <c r="F10" s="24">
-        <v>5999341</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B11" s="21">
-        <v>-43</v>
-      </c>
-      <c r="C11" s="21">
-        <v>21</v>
-      </c>
-      <c r="D11" s="21">
-        <v>206</v>
-      </c>
-      <c r="E11" s="21">
-        <v>457</v>
-      </c>
-      <c r="F11" s="21">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="B12" s="28">
-        <v>-1.4</v>
-      </c>
-      <c r="C12" s="28">
-        <v>0.7</v>
-      </c>
-      <c r="D12" s="28">
-        <v>6.8</v>
-      </c>
-      <c r="E12" s="28">
-        <v>15</v>
-      </c>
-      <c r="F12" s="28">
-        <v>24.1</v>
-      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.75</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.9375</v>
-      </c>
-      <c r="F13" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B13" s="24">
+        <v>-190250</v>
+      </c>
+      <c r="C13" s="24">
+        <v>128096</v>
+      </c>
+      <c r="D13" s="24">
+        <v>1434716</v>
+      </c>
+      <c r="E13" s="24">
+        <v>3552210</v>
+      </c>
+      <c r="F13" s="24">
+        <v>5999341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B14" s="21">
+        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
+        <v>-43</v>
+      </c>
+      <c r="C14" s="21">
+        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
+        <v>21</v>
+      </c>
+      <c r="D14" s="21">
+        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
+        <v>206</v>
+      </c>
+      <c r="E14" s="21">
+        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
+        <v>457</v>
+      </c>
+      <c r="F14" s="21">
+        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="28">
+        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
+        <v>-1.4</v>
+      </c>
+      <c r="C15" s="28">
+        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
+        <v>0.7</v>
+      </c>
+      <c r="D15" s="28">
+        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
+        <v>6.8</v>
+      </c>
+      <c r="E15" s="28">
+        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
+        <v>15</v>
+      </c>
+      <c r="F15" s="28">
+        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
+        <v>24.1</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="E16" s="23">
+        <v>0.9375</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B19" s="24">
         <v>10736</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C19" s="24">
         <v>12824</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D19" s="24">
         <v>12978</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E19" s="24">
         <v>13273</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F19" s="24">
         <v>13647</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B17" s="24">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="24">
         <v>1076256</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C20" s="24">
         <v>1318494</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D20" s="24">
         <v>1356554</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E20" s="24">
         <v>1395756</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F20" s="24">
         <v>1436134</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="24">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" s="24">
         <v>4542</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C21" s="24">
         <v>4439</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D21" s="24">
         <v>3968</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E21" s="24">
         <v>3838</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F21" s="24">
         <v>3889</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B19" s="38">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" s="38">
         <v>174</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C22" s="38">
         <v>158</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D22" s="38">
         <v>151</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E22" s="38">
         <v>148</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F22" s="38">
         <v>148</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="C22" s="40" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="F22" s="40" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>339</v>
-      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="B25" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>339</v>
-      </c>
       <c r="D25" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5274,19 +5435,79 @@
         <v>344</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>339</v>
+        <v>342</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>343</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>340</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -5327,13 +5548,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E3" s="41" t="s">
         <v>100</v>
@@ -5347,7 +5568,7 @@
         <v>500000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E4" s="24">
         <v>400000</v>
@@ -5361,7 +5582,7 @@
         <v>100000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E5" s="24">
         <v>75000</v>
@@ -5369,13 +5590,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B6" s="24">
         <v>50000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E6" s="24">
         <v>40000</v>
@@ -5383,7 +5604,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E7" s="24">
         <v>60000</v>
@@ -5391,7 +5612,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E8" s="24">
         <v>75000</v>
@@ -5399,13 +5620,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B10" s="25">
         <v>650000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E10" s="25">
         <v>650000</v>
@@ -5413,7 +5634,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B11" s="35">
         <v>0</v>
@@ -5581,7 +5802,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5591,7 +5812,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5601,7 +5822,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5626,7 +5847,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="B6" s="24">
         <v>1288333</v>
@@ -5646,7 +5867,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B7" s="24">
         <v>1621256</v>
@@ -5666,7 +5887,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B8" s="25">
         <v>-332923</v>
@@ -5686,7 +5907,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B9" s="23">
         <v>-0.2584133416981985</v>
@@ -5706,7 +5927,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B10" s="42">
         <v>-5.68</v>
@@ -5726,7 +5947,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B11" s="21">
         <v>174</v>
@@ -5746,7 +5967,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5756,7 +5977,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5781,7 +6002,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="B16" s="24">
         <v>1288333</v>
@@ -5801,7 +6022,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B17" s="24">
         <v>1621256</v>
@@ -5821,7 +6042,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B18" s="25">
         <v>-332923</v>
@@ -5841,7 +6062,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B19" s="23">
         <v>-0.2584133416981985</v>
@@ -5861,7 +6082,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B20" s="42">
         <v>-5.68</v>
@@ -5881,7 +6102,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B21" s="21">
         <v>131</v>
@@ -5901,7 +6122,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5911,7 +6132,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5936,7 +6157,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="B26" s="24">
         <v>1223917</v>
@@ -5956,7 +6177,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B27" s="24">
         <v>1621256</v>
@@ -5976,7 +6197,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B28" s="25">
         <v>-397339</v>
@@ -5996,7 +6217,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B29" s="23">
         <v>-0.3246456228402091</v>
@@ -6016,7 +6237,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B30" s="42">
         <v>-6.97</v>
@@ -6036,7 +6257,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B31" s="21">
         <v>191</v>
@@ -6056,7 +6277,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6066,7 +6287,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6091,7 +6312,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="B36" s="24">
         <v>1288333</v>
@@ -6111,7 +6332,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B37" s="24">
         <v>1703006</v>
@@ -6131,7 +6352,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B38" s="25">
         <v>-414673</v>
@@ -6151,7 +6372,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B39" s="23">
         <v>-0.32186741673054003</v>
@@ -6171,7 +6392,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B40" s="42">
         <v>-7.32</v>
@@ -6191,7 +6412,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B41" s="21">
         <v>196</v>
@@ -6237,7 +6458,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6271,7 +6492,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6295,7 +6516,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6303,7 +6524,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6341,7 +6562,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="D13" s="24">
         <v>1288333</v>
@@ -6361,7 +6582,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D14" s="24">
         <v>1621256</v>
@@ -6381,7 +6602,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D15" s="24">
         <v>-447923</v>
@@ -6401,7 +6622,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D16" s="24">
         <v>-190250</v>
@@ -6421,7 +6642,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D17" s="24">
         <v>478361</v>
@@ -6441,7 +6662,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6479,7 +6700,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D21" s="23">
         <v>-0.34767595489354136</v>
@@ -6499,7 +6720,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D22" s="42">
         <v>-5.68</v>
@@ -6539,7 +6760,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D24" s="21">
         <v>120</v>
@@ -6559,7 +6780,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7925,18 +8146,23 @@
         <v>196</v>
       </c>
       <c r="B11" s="25">
+        <f>SUM(B5:B10)</f>
         <v>1546000</v>
       </c>
       <c r="C11" s="25">
+        <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
       <c r="D11" s="25">
+        <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
       <c r="E11" s="25">
+        <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
       <c r="F11" s="25">
+        <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
     </row>
@@ -8389,18 +8615,23 @@
         <v>205</v>
       </c>
       <c r="B6" s="29">
+        <f>SUM(B5:B5)</f>
         <v>84000</v>
       </c>
       <c r="C6" s="29">
+        <f>SUM(C5:C5)</f>
         <v>144200</v>
       </c>
       <c r="D6" s="29">
+        <f>SUM(D5:D5)</f>
         <v>222789</v>
       </c>
       <c r="E6" s="29">
+        <f>SUM(E5:E5)</f>
         <v>286841</v>
       </c>
       <c r="F6" s="29">
+        <f>SUM(F5:F5)</f>
         <v>315142</v>
       </c>
     </row>
@@ -8439,18 +8670,23 @@
         <v>207</v>
       </c>
       <c r="B9" s="29">
+        <f>SUM(B8:B8)</f>
         <v>60000</v>
       </c>
       <c r="C9" s="29">
+        <f>SUM(C8:C8)</f>
         <v>103000</v>
       </c>
       <c r="D9" s="29">
+        <f>SUM(D8:D8)</f>
         <v>159135</v>
       </c>
       <c r="E9" s="29">
+        <f>SUM(E8:E8)</f>
         <v>204886</v>
       </c>
       <c r="F9" s="29">
+        <f>SUM(F8:F8)</f>
         <v>225102</v>
       </c>
     </row>
@@ -8549,18 +8785,23 @@
         <v>212</v>
       </c>
       <c r="B15" s="29">
+        <f>SUM(B11:B14)</f>
         <v>282000</v>
       </c>
       <c r="C15" s="29">
+        <f>SUM(C11:C14)</f>
         <v>290460</v>
       </c>
       <c r="D15" s="29">
+        <f>SUM(D11:D14)</f>
         <v>299174</v>
       </c>
       <c r="E15" s="29">
+        <f>SUM(E11:E14)</f>
         <v>308149</v>
       </c>
       <c r="F15" s="29">
+        <f>SUM(F11:F14)</f>
         <v>317393</v>
       </c>
     </row>
@@ -8679,18 +8920,23 @@
         <v>218</v>
       </c>
       <c r="B22" s="29">
+        <f>SUM(B17:B21)</f>
         <v>228000</v>
       </c>
       <c r="C22" s="29">
+        <f>SUM(C17:C21)</f>
         <v>350200</v>
       </c>
       <c r="D22" s="29">
+        <f>SUM(D17:D21)</f>
         <v>509232</v>
       </c>
       <c r="E22" s="29">
+        <f>SUM(E17:E21)</f>
         <v>639245</v>
       </c>
       <c r="F22" s="29">
+        <f>SUM(F17:F21)</f>
         <v>697815</v>
       </c>
     </row>
@@ -8699,18 +8945,23 @@
         <v>219</v>
       </c>
       <c r="B24" s="25">
+        <f>B6+B9+B15+B22</f>
         <v>654000</v>
       </c>
       <c r="C24" s="25">
+        <f>C6+C9+C15+C22</f>
         <v>887860</v>
       </c>
       <c r="D24" s="25">
+        <f>D6+D9+D15+D22</f>
         <v>1190330</v>
       </c>
       <c r="E24" s="25">
+        <f>E6+E9+E15+E22</f>
         <v>1439121</v>
       </c>
       <c r="F24" s="25">
+        <f>F6+F9+F15+F22</f>
         <v>1555453</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -216,7 +216,7 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
-    <t>CONFIDENTIAL — Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
+    <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
     <t>How to Use This Workbook</t>
@@ -225,10 +225,10 @@
     <t>Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas — do not edit.</t>
+    <t>Yellow cells are editable inputs - change these to update your model.</t>
+  </si>
+  <si>
+    <t>Gray cells contain formulas - do not edit.</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -279,7 +279,7 @@
     <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — Assumptions</t>
+    <t>Civic Scholars Charter - Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells are formulas.</t>
@@ -594,7 +594,7 @@
     <t>Enrollment Growth Rate</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Tuition &amp; Funding Drivers</t>
@@ -765,7 +765,7 @@
     <t>TOTAL PERSONNEL</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — Budget Detail</t>
+    <t>Civic Scholars Charter - Budget Detail</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -852,7 +852,7 @@
     <t>Total Capital &amp; Debt</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — Budget Summary</t>
+    <t>Civic Scholars Charter - Budget Summary</t>
   </si>
   <si>
     <t>Total Capital &amp; Debt Service</t>
@@ -876,7 +876,7 @@
     <t>Cost per Student</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — Year 1 Monthly Cash Flow</t>
+    <t>Civic Scholars Charter - Year 1 Monthly Cash Flow</t>
   </si>
   <si>
     <t>July</t>
@@ -948,7 +948,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — 5-Year Operating Statement</t>
+    <t>Civic Scholars Charter - 5-Year Operating Statement</t>
   </si>
   <si>
     <t>Capital &amp; Debt Service</t>
@@ -972,7 +972,7 @@
     <t>Ending Balance</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — Balance Sheet</t>
+    <t>Civic Scholars Charter - Balance Sheet</t>
   </si>
   <si>
     <t>ASSETS</t>
@@ -1137,7 +1137,7 @@
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +15%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot — Loan Committee Summary</t>
+    <t>Underwriting Snapshot - Loan Committee Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1164,7 +1164,7 @@
     <t>Enrollment</t>
   </si>
   <si>
-    <t>Prepared by SchoolStack Budget — budget.schoolstack.ai</t>
+    <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -1116,25 +1116,25 @@
     <t>BASE CASE</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>SLOW RAMP</t>
   </si>
   <si>
-    <t>Enrollment: -25%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: -25%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>FUNDING CUT</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: -5%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: -5%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>COST OVERRUN</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +15%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +15%</t>
   </si>
   <si>
     <t>Underwriting Snapshot - Loan Committee Summary</t>
@@ -6005,19 +6005,19 @@
         <v>329</v>
       </c>
       <c r="B16" s="24">
-        <v>1288333</v>
+        <v>966250</v>
       </c>
       <c r="C16" s="24">
-        <v>2564700</v>
+        <v>1923525</v>
       </c>
       <c r="D16" s="24">
-        <v>3893503</v>
+        <v>2920127</v>
       </c>
       <c r="E16" s="24">
-        <v>4977371</v>
+        <v>3733029</v>
       </c>
       <c r="F16" s="24">
-        <v>5458718</v>
+        <v>4094038</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6045,19 +6045,19 @@
         <v>277</v>
       </c>
       <c r="B18" s="25">
-        <v>-332923</v>
+        <v>-655006</v>
       </c>
       <c r="C18" s="25">
-        <v>358346</v>
+        <v>-282829</v>
       </c>
       <c r="D18" s="25">
-        <v>1346619</v>
+        <v>373244</v>
       </c>
       <c r="E18" s="25">
-        <v>2142494</v>
+        <v>898152</v>
       </c>
       <c r="F18" s="25">
-        <v>2467131</v>
+        <v>1102452</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6065,19 +6065,19 @@
         <v>278</v>
       </c>
       <c r="B19" s="23">
-        <v>-0.2584133416981985</v>
+        <v>-0.677884455597598</v>
       </c>
       <c r="C19" s="23">
-        <v>0.1397225288645145</v>
+        <v>-0.14703662818064733</v>
       </c>
       <c r="D19" s="23">
-        <v>0.3458632236905482</v>
+        <v>0.12781763158739762</v>
       </c>
       <c r="E19" s="23">
-        <v>0.43044696555461553</v>
+        <v>0.2405959540728207</v>
       </c>
       <c r="F19" s="23">
-        <v>0.4519616461017463</v>
+        <v>0.26928219480232835</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6085,19 +6085,19 @@
         <v>331</v>
       </c>
       <c r="B20" s="42">
-        <v>-5.68</v>
+        <v>-12.15</v>
       </c>
       <c r="C20" s="42">
-        <v>8.19</v>
+        <v>-4.68</v>
       </c>
       <c r="D20" s="42">
-        <v>28.03</v>
+        <v>8.49</v>
       </c>
       <c r="E20" s="42">
-        <v>44</v>
+        <v>19.03</v>
       </c>
       <c r="F20" s="42">
-        <v>50.52</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6105,19 +6105,19 @@
         <v>339</v>
       </c>
       <c r="B21" s="21">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="C21" s="21">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="D21" s="21">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="E21" s="21">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F21" s="21">
-        <v>111</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -5876,13 +5876,13 @@
         <v>2206354</v>
       </c>
       <c r="D7" s="24">
-        <v>2546884</v>
+        <v>2547075</v>
       </c>
       <c r="E7" s="24">
-        <v>2834877</v>
+        <v>2834845</v>
       </c>
       <c r="F7" s="24">
-        <v>2991587</v>
+        <v>2991057</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5896,13 +5896,13 @@
         <v>358346</v>
       </c>
       <c r="D8" s="25">
-        <v>1346619</v>
+        <v>1346428</v>
       </c>
       <c r="E8" s="25">
-        <v>2142494</v>
+        <v>2142527</v>
       </c>
       <c r="F8" s="25">
-        <v>2467131</v>
+        <v>2467660</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5916,13 +5916,13 @@
         <v>0.1397225288645145</v>
       </c>
       <c r="D9" s="23">
-        <v>0.3458632236905482</v>
+        <v>0.34581401350630037</v>
       </c>
       <c r="E9" s="23">
-        <v>0.43044696555461553</v>
+        <v>0.43045348043904746</v>
       </c>
       <c r="F9" s="23">
-        <v>0.4519616461017463</v>
+        <v>0.45205860522041197</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5936,13 +5936,13 @@
         <v>8.19</v>
       </c>
       <c r="D10" s="42">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="E10" s="42">
         <v>44</v>
       </c>
       <c r="F10" s="42">
-        <v>50.52</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6031,13 +6031,13 @@
         <v>2206354</v>
       </c>
       <c r="D17" s="24">
-        <v>2546884</v>
+        <v>2547075</v>
       </c>
       <c r="E17" s="24">
-        <v>2834877</v>
+        <v>2834845</v>
       </c>
       <c r="F17" s="24">
-        <v>2991587</v>
+        <v>2991057</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6051,13 +6051,13 @@
         <v>-282829</v>
       </c>
       <c r="D18" s="25">
-        <v>373244</v>
+        <v>373052</v>
       </c>
       <c r="E18" s="25">
-        <v>898152</v>
+        <v>898184</v>
       </c>
       <c r="F18" s="25">
-        <v>1102452</v>
+        <v>1102981</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6071,13 +6071,13 @@
         <v>-0.14703662818064733</v>
       </c>
       <c r="D19" s="23">
-        <v>0.12781763158739762</v>
+        <v>0.12775201800840047</v>
       </c>
       <c r="E19" s="23">
-        <v>0.2405959540728207</v>
+        <v>0.24060464058539663</v>
       </c>
       <c r="F19" s="23">
-        <v>0.26928219480232835</v>
+        <v>0.2694114736272159</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6097,7 +6097,7 @@
         <v>19.03</v>
       </c>
       <c r="F20" s="42">
-        <v>23.13</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6186,13 +6186,13 @@
         <v>2206354</v>
       </c>
       <c r="D27" s="24">
-        <v>2546884</v>
+        <v>2547075</v>
       </c>
       <c r="E27" s="24">
-        <v>2834877</v>
+        <v>2834845</v>
       </c>
       <c r="F27" s="24">
-        <v>2991587</v>
+        <v>2991057</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6206,13 +6206,13 @@
         <v>230111</v>
       </c>
       <c r="D28" s="25">
-        <v>1151944</v>
+        <v>1151753</v>
       </c>
       <c r="E28" s="25">
-        <v>1893626</v>
+        <v>1893658</v>
       </c>
       <c r="F28" s="25">
-        <v>2194195</v>
+        <v>2194724</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -6226,13 +6226,13 @@
         <v>0.09444476722580472</v>
       </c>
       <c r="D29" s="23">
-        <v>0.31143497230584016</v>
+        <v>0.31138317211189503</v>
       </c>
       <c r="E29" s="23">
-        <v>0.40047049005748997</v>
+        <v>0.4004773478305762</v>
       </c>
       <c r="F29" s="23">
-        <v>0.4231175222123644</v>
+        <v>0.4232195844425388</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6252,7 +6252,7 @@
         <v>39.01</v>
       </c>
       <c r="F30" s="42">
-        <v>45.04</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,19 +6335,19 @@
         <v>275</v>
       </c>
       <c r="B37" s="24">
-        <v>1703006</v>
+        <v>1667756</v>
       </c>
       <c r="C37" s="24">
-        <v>2339533</v>
+        <v>2295964</v>
       </c>
       <c r="D37" s="24">
-        <v>2725433</v>
+        <v>2680778</v>
       </c>
       <c r="E37" s="24">
-        <v>3050745</v>
+        <v>3004485</v>
       </c>
       <c r="F37" s="24">
-        <v>3224905</v>
+        <v>3176687</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,19 +6355,19 @@
         <v>277</v>
       </c>
       <c r="B38" s="25">
-        <v>-414673</v>
+        <v>-379423</v>
       </c>
       <c r="C38" s="25">
-        <v>225167</v>
+        <v>268736</v>
       </c>
       <c r="D38" s="25">
-        <v>1168070</v>
+        <v>1212725</v>
       </c>
       <c r="E38" s="25">
-        <v>1926626</v>
+        <v>1972886</v>
       </c>
       <c r="F38" s="25">
-        <v>2233813</v>
+        <v>2282031</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,19 +6375,19 @@
         <v>278</v>
       </c>
       <c r="B39" s="23">
-        <v>-0.32186741673054003</v>
+        <v>-0.2945064852945763</v>
       </c>
       <c r="C39" s="23">
-        <v>0.08779481802114118</v>
+        <v>0.10478276982836991</v>
       </c>
       <c r="D39" s="23">
-        <v>0.3000049130638453</v>
+        <v>0.31147392182022743</v>
       </c>
       <c r="E39" s="23">
-        <v>0.3870770423932544</v>
+        <v>0.3963710635426523</v>
       </c>
       <c r="F39" s="23">
-        <v>0.4092193780605092</v>
+        <v>0.4180525145535826</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,19 +6395,19 @@
         <v>331</v>
       </c>
       <c r="B40" s="42">
-        <v>-7.32</v>
+        <v>-6.62</v>
       </c>
       <c r="C40" s="42">
-        <v>5.52</v>
+        <v>6.39</v>
       </c>
       <c r="D40" s="42">
-        <v>24.44</v>
+        <v>25.34</v>
       </c>
       <c r="E40" s="42">
-        <v>39.67</v>
+        <v>40.6</v>
       </c>
       <c r="F40" s="42">
-        <v>45.83</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -6415,19 +6415,19 @@
         <v>339</v>
       </c>
       <c r="B41" s="21">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C41" s="21">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D41" s="21">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E41" s="21">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F41" s="21">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="379">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -517,6 +517,9 @@
   </si>
   <si>
     <t>Salary Escalation Rate</t>
+  </si>
+  <si>
+    <t>Derived from tuition escalation rate</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
@@ -1178,7 +1181,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1246,6 +1249,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1332,7 +1341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1361,6 +1370,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1376,14 +1386,14 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2049,7 +2059,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2081,25 +2091,25 @@
       <c r="A4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>120</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>200</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>300</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>375</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>400</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2111,19 +2121,19 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>1140000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>1957000</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>3023565</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>3892840</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>4276933</v>
       </c>
     </row>
@@ -2131,19 +2141,19 @@
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>96000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>164800</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>254616</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>327818</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>360163</v>
       </c>
     </row>
@@ -2151,19 +2161,19 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>144000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>247200</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>381924</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>491727</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>540244</v>
       </c>
     </row>
@@ -2171,19 +2181,19 @@
       <c r="A10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <v>100000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>103000</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>106090</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>109273</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>112551</v>
       </c>
     </row>
@@ -2191,19 +2201,19 @@
       <c r="A11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <v>30000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>30900</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>31827</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>32782</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>33765</v>
       </c>
     </row>
@@ -2211,64 +2221,64 @@
       <c r="A12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <v>36000</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>61800</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>95481</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>122932</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>135061</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="25">
+        <v>197</v>
+      </c>
+      <c r="B13" s="26">
         <f>SUM(B7:B12)</f>
         <v>1546000</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>SUM(C7:C12)</f>
         <v>2564700</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>SUM(D7:D12)</f>
         <v>3893503</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>SUM(E7:E12)</f>
         <v>4977371</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>SUM(F7:F12)</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" s="24">
+        <v>228</v>
+      </c>
+      <c r="B15" s="25">
         <v>12883</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>12824</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>12978</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>13273</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>13647</v>
       </c>
     </row>
@@ -2298,7 +2308,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2338,85 +2348,85 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="24">
+        <v>230</v>
+      </c>
+      <c r="B5" s="25">
         <v>352690</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>435925</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>449003</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>462473</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>476347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="24">
+        <v>231</v>
+      </c>
+      <c r="B6" s="25">
         <v>62173</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>76846</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>79151</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>81526</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="24">
+        <v>232</v>
+      </c>
+      <c r="B7" s="25">
         <v>95738</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>118332</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>121881</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>125538</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>129304</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="29">
+        <v>233</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>510600</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>631102</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>650035</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>669536</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>689622</v>
       </c>
@@ -2433,85 +2443,85 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="24">
+        <v>234</v>
+      </c>
+      <c r="B10" s="25">
         <v>124346</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>153691</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>158302</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>163051</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>167943</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="24">
+        <v>235</v>
+      </c>
+      <c r="B11" s="25">
         <v>101738</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>125748</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>129520</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>133406</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>137408</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="24">
+        <v>236</v>
+      </c>
+      <c r="B12" s="25">
         <v>81390</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>100598</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>103616</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>106724</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>109926</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B13" s="29">
+        <v>237</v>
+      </c>
+      <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
         <v>307473</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>SUM(C10:C12)</f>
         <v>380037</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>SUM(D10:D12)</f>
         <v>391438</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>SUM(E10:E12)</f>
         <v>403181</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>SUM(F10:F12)</f>
         <v>415277</v>
       </c>
@@ -2528,45 +2538,45 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B15" s="24">
+        <v>238</v>
+      </c>
+      <c r="B15" s="25">
         <v>62173</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>76846</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>79151</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>81526</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" s="29">
+        <v>239</v>
+      </c>
+      <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
         <v>62173</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>SUM(C15:C15)</f>
         <v>76846</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>SUM(D15:D15)</f>
         <v>79151</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>SUM(E15:E15)</f>
         <v>81526</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>SUM(F15:F15)</f>
         <v>83971</v>
       </c>
@@ -2583,45 +2593,45 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="24">
+        <v>240</v>
+      </c>
+      <c r="B18" s="25">
         <v>62173</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>76846</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>79151</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>81526</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="29">
+        <v>241</v>
+      </c>
+      <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
         <v>62173</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>SUM(C18:C18)</f>
         <v>76846</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>SUM(D18:D18)</f>
         <v>79151</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>SUM(E18:E18)</f>
         <v>81526</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>SUM(F18:F18)</f>
         <v>83971</v>
       </c>
@@ -2638,70 +2648,70 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="24">
+        <v>242</v>
+      </c>
+      <c r="B21" s="25">
         <v>84012</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>103838</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>106954</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>110162</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>113467</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B22" s="29">
+        <v>243</v>
+      </c>
+      <c r="B22" s="30">
         <f>SUM(B21:B21)</f>
         <v>84012</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>SUM(C21:C21)</f>
         <v>103838</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>SUM(D21:D21)</f>
         <v>106954</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>SUM(E21:E21)</f>
         <v>110162</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>SUM(F21:F21)</f>
         <v>113467</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="B24" s="25">
+        <v>244</v>
+      </c>
+      <c r="B24" s="26">
         <f>B8+B13+B16+B19+B22</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>C8+C13+C16+C19+C22</f>
         <v>1268669</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="26">
         <f>D8+D13+D16+D19+D22</f>
         <v>1306729</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>E8+E13+E16+E19+E22</f>
         <v>1345931</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>F8+F13+F16+F19+F22</f>
         <v>1386309</v>
       </c>
@@ -2732,7 +2742,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2762,7 +2772,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2772,152 +2782,152 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" s="24">
+        <v>247</v>
+      </c>
+      <c r="B5" s="25">
         <v>950000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>1957000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>3023565</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>3892840</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>4276933</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="24">
+        <v>248</v>
+      </c>
+      <c r="B6" s="25">
         <v>80000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>164800</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>254616</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>327818</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>360163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B7" s="24">
+        <v>249</v>
+      </c>
+      <c r="B7" s="25">
         <v>120000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>247200</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>381924</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>491727</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>540244</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="24">
+        <v>250</v>
+      </c>
+      <c r="B8" s="25">
         <v>83333</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>103000</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>106090</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>109273</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>112551</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B9" s="24">
+        <v>251</v>
+      </c>
+      <c r="B9" s="25">
         <v>25000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>30900</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>31827</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>32782</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="24">
+        <v>252</v>
+      </c>
+      <c r="B10" s="25">
         <v>30000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>61800</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>95481</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>122932</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>135061</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B11" s="29">
+        <v>253</v>
+      </c>
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1288333</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2927,205 +2937,205 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="24">
+        <v>234</v>
+      </c>
+      <c r="B14" s="25">
         <v>124346</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>153691</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>158302</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>163051</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>167943</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B15" s="24">
+        <v>235</v>
+      </c>
+      <c r="B15" s="25">
         <v>101738</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>125748</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>129520</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>133406</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>137408</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="24">
+        <v>236</v>
+      </c>
+      <c r="B16" s="25">
         <v>81390</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>100598</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>103616</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>106724</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>109926</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B17" s="24">
+        <v>230</v>
+      </c>
+      <c r="B17" s="25">
         <v>352690</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>435925</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>449003</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>462473</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>476347</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B18" s="24">
+        <v>231</v>
+      </c>
+      <c r="B18" s="25">
         <v>62173</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>76846</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>79151</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>81526</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B19" s="24">
+        <v>232</v>
+      </c>
+      <c r="B19" s="25">
         <v>95738</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>118332</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>121881</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>125538</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>129304</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="24">
+        <v>240</v>
+      </c>
+      <c r="B20" s="25">
         <v>62173</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>76846</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>79151</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>81526</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="24">
+        <v>242</v>
+      </c>
+      <c r="B21" s="25">
         <v>84012</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>103838</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>106954</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>110162</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>113467</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="24">
+        <v>238</v>
+      </c>
+      <c r="B22" s="25">
         <v>62173</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="25">
         <v>76846</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <v>79151</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <v>81526</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="25">
         <v>83971</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B23" s="29">
+        <v>201</v>
+      </c>
+      <c r="B23" s="30">
         <f>SUM(B14:B22)</f>
         <v>1026431</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <f>SUM(C14:C22)</f>
         <v>1268669</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <f>SUM(D14:D22)</f>
         <v>1306729</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <f>SUM(E14:E22)</f>
         <v>1345931</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <f>SUM(F14:F22)</f>
         <v>1386309</v>
       </c>
@@ -3141,323 +3151,323 @@
       <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="32" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B27" s="24">
+        <v>255</v>
+      </c>
+      <c r="B27" s="25">
         <v>70000</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>144200</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <v>222789</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <v>286841</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <v>315142</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B29" s="24">
+        <v>256</v>
+      </c>
+      <c r="B29" s="25">
         <v>50000</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <v>103000</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="25">
         <v>159135</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <v>204886</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="25">
         <v>225102</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="32" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B31" s="24">
+        <v>257</v>
+      </c>
+      <c r="B31" s="25">
         <v>180000</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <v>222480</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>229154</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <v>236029</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <v>243110</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B32" s="24">
+        <v>258</v>
+      </c>
+      <c r="B32" s="25">
         <v>25000</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="25">
         <v>30900</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="25">
         <v>31827</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <v>32782</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B33" s="24">
+        <v>259</v>
+      </c>
+      <c r="B33" s="25">
         <v>15000</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="25">
         <v>18540</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="25">
         <v>19096</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <v>19669</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B34" s="24">
+        <v>260</v>
+      </c>
+      <c r="B34" s="25">
         <v>15000</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="25">
         <v>18540</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="25">
         <v>19096</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <v>19669</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B35" s="29">
+        <v>261</v>
+      </c>
+      <c r="B35" s="30">
         <f>SUM(B31:B34)</f>
         <v>235000</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <f>SUM(C31:C34)</f>
         <v>290460</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="30">
         <f>SUM(D31:D34)</f>
         <v>299174</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="30">
         <f>SUM(E31:E34)</f>
         <v>308149</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="30">
         <f>SUM(F31:F34)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="32" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B37" s="24">
+        <v>262</v>
+      </c>
+      <c r="B37" s="25">
         <v>20833</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="25">
         <v>25750</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="25">
         <v>26523</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <v>27318</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="25">
         <v>28138</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B38" s="24">
+        <v>263</v>
+      </c>
+      <c r="B38" s="25">
         <v>12500</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="25">
         <v>15450</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="25">
         <v>15914</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="25">
         <v>16391</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="25">
         <v>16883</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B39" s="24">
+        <v>264</v>
+      </c>
+      <c r="B39" s="25">
         <v>16667</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="25">
         <v>20600</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="25">
         <v>21218</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="25">
         <v>21855</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="25">
         <v>22510</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B40" s="24">
+        <v>265</v>
+      </c>
+      <c r="B40" s="25">
         <v>80000</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="25">
         <v>164800</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="25">
         <v>254616</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="25">
         <v>327818</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="25">
         <v>360163</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B41" s="24">
+        <v>266</v>
+      </c>
+      <c r="B41" s="25">
         <v>60000</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="25">
         <v>123600</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="25">
         <v>190962</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="25">
         <v>245864</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="25">
         <v>270122</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B42" s="29">
+        <v>267</v>
+      </c>
+      <c r="B42" s="30">
         <f>SUM(B37:B41)</f>
         <v>190000</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <f>SUM(C37:C41)</f>
         <v>350200</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <f>SUM(D37:D41)</f>
         <v>509232</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <f>SUM(E37:E41)</f>
         <v>639245</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="30">
         <f>SUM(F37:F41)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B43" s="29">
+        <v>268</v>
+      </c>
+      <c r="B43" s="30">
         <f>B27+B29+B35+B42</f>
         <v>545000</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <f>C27+C29+C35+C42</f>
         <v>887860</v>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="30">
         <f>D27+D29+D35+D42</f>
         <v>1190330</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="30">
         <f>E27+E29+E35+E42</f>
         <v>1439121</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="30">
         <f>F27+F29+F35+F42</f>
         <v>1555453</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -3467,85 +3477,85 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B46" s="24">
+        <v>270</v>
+      </c>
+      <c r="B46" s="25">
         <v>49825</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="25">
         <v>49825</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="25">
         <v>49825</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="25">
         <v>49825</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="25">
         <v>49825</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B47" s="24">
+        <v>271</v>
+      </c>
+      <c r="B47" s="25">
         <v>75000</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="25">
         <v>25000</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="25">
         <v>30000</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="25">
         <v>15000</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="25">
         <v>10000</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B48" s="24">
+        <v>272</v>
+      </c>
+      <c r="B48" s="25">
         <v>40000</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="25">
         <v>15000</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="25">
         <v>10000</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="25">
         <v>10000</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="25">
         <v>10000</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B49" s="29">
+        <v>273</v>
+      </c>
+      <c r="B49" s="30">
         <f>SUM(B46:B48)</f>
         <v>164825</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="30">
         <f>SUM(C46:C48)</f>
         <v>89825</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="30">
         <f>SUM(D46:D48)</f>
         <v>89825</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="30">
         <f>SUM(E46:E48)</f>
         <v>74825</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="30">
         <f>SUM(F46:F48)</f>
         <v>69825</v>
       </c>
@@ -3576,7 +3586,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3606,132 +3616,132 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="27">
+        <v>253</v>
+      </c>
+      <c r="B4" s="28">
         <f>'Budget Detail'!B11</f>
         <v>1288333</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <f>'Budget Detail'!C11</f>
         <v>2564700</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="28">
         <f>'Budget Detail'!D11</f>
         <v>3893503</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <f>'Budget Detail'!E11</f>
         <v>4977371</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <f>'Budget Detail'!F11</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="27">
+        <v>201</v>
+      </c>
+      <c r="B5" s="28">
         <f>'Budget Detail'!B23</f>
         <v>1026431</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>'Budget Detail'!C23</f>
         <v>1268669</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>'Budget Detail'!D23</f>
         <v>1306729</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>'Budget Detail'!E23</f>
         <v>1345931</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>'Budget Detail'!F23</f>
         <v>1386309</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="27">
+        <v>268</v>
+      </c>
+      <c r="B6" s="28">
         <f>'Budget Detail'!B43</f>
         <v>545000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>'Budget Detail'!C43</f>
         <v>887860</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>'Budget Detail'!D43</f>
         <v>1190330</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>'Budget Detail'!E43</f>
         <v>1439121</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>'Budget Detail'!F43</f>
         <v>1555453</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="27">
+        <v>275</v>
+      </c>
+      <c r="B7" s="28">
         <f>'Budget Detail'!B49</f>
         <v>164825</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>'Budget Detail'!C49</f>
         <v>89825</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>'Budget Detail'!D49</f>
         <v>89825</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>'Budget Detail'!E49</f>
         <v>74825</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>'Budget Detail'!F49</f>
         <v>69825</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="29">
+        <v>276</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>1736256</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>2246354</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>2586884</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>2859877</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3741,111 +3751,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B11" s="25">
+        <v>278</v>
+      </c>
+      <c r="B11" s="26">
         <f>B4-B8</f>
         <v>-447923</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>C4-C8</f>
         <v>318346</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>D4-D8</f>
         <v>1306619</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>E4-E8</f>
         <v>2117494</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>F4-F8</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" s="23">
+        <v>279</v>
+      </c>
+      <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.44829778</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" s="24">
+        <v>280</v>
+      </c>
+      <c r="B13" s="25">
         <v>-447923</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>-129576</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>1177043</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>3294538</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>5741669</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="24">
+        <v>228</v>
+      </c>
+      <c r="B14" s="25">
         <v>10736</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>12824</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>12978</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>13273</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>13647</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" s="24">
+        <v>281</v>
+      </c>
+      <c r="B15" s="25">
         <v>14469</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>11232</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>8623</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>7626</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>7529</v>
       </c>
     </row>
@@ -3876,7 +3886,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3897,48 +3907,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3956,51 +3966,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="29">
+        <v>253</v>
+      </c>
+      <c r="B4" s="30">
         <v>154600</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>154600</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>154600</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>154600</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>154600</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <v>154600</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="30">
         <v>154600</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="30">
         <v>154600</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="30">
         <v>154600</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>154600</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="30">
         <v>0</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="30">
         <v>0</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="30">
         <v>1546000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4018,139 +4028,139 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="24">
+        <v>297</v>
+      </c>
+      <c r="B7" s="25">
         <v>102643</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>102643</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>102643</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>102643</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>102643</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>102643</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <v>102643</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <v>102643</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <v>102643</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="25">
         <v>102643</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="25">
         <v>0</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="25">
         <v>0</v>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="25">
         <v>1026431</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B8" s="24">
+        <v>298</v>
+      </c>
+      <c r="B8" s="25">
         <v>54500</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>54500</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>54500</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>54500</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>54500</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <v>54500</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <v>54500</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <v>54500</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <v>54500</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <v>54500</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="25">
         <v>0</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="25">
         <v>0</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="25">
         <v>545000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="24">
+        <v>299</v>
+      </c>
+      <c r="B9" s="25">
         <v>13735</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>13735</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>13735</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>13735</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>13735</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <v>13735</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="25">
         <v>13735</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="25">
         <v>13735</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="25">
         <v>13735</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="25">
         <v>13735</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="25">
         <v>13735</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="25">
         <v>13735</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="25">
         <v>164825</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4168,164 +4178,164 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B12" s="27">
+        <v>276</v>
+      </c>
+      <c r="B12" s="28">
         <v>170878</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <v>170878</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <v>170878</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <v>170878</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <v>170878</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="28">
         <v>170878</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="28">
         <v>170878</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="28">
         <v>170878</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="28">
         <v>170878</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="28">
         <v>170878</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="28">
         <v>13735</v>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="28">
         <v>13735</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="28">
         <v>1736250</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B13" s="27">
+        <v>301</v>
+      </c>
+      <c r="B13" s="28">
         <v>-16278</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <v>-16278</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <v>-16278</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <v>-16278</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <v>-16278</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <v>-16278</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="28">
         <v>-16278</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <v>-16278</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="28">
         <v>-16278</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="28">
         <v>-16278</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="28">
         <v>-13735</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="28">
         <v>-13735</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="28">
         <v>-190250</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B14" s="32">
+        <v>302</v>
+      </c>
+      <c r="B14" s="33">
         <v>-16278</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <v>-32556</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <v>-48834</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <v>-65112</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>-81390</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <v>-97668</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <v>-113946</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="33">
         <v>-130224</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="33">
         <v>-146502</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="33">
         <v>-162780</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="33">
         <v>-176515</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="33">
         <v>-190250</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="26">
         <v>-190250</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="24">
+        <v>165</v>
+      </c>
+      <c r="B17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B18" s="32">
+        <v>304</v>
+      </c>
+      <c r="B18" s="33">
         <v>-190250</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B19" s="24">
+        <v>305</v>
+      </c>
+      <c r="B19" s="25">
         <v>-190250</v>
       </c>
     </row>
@@ -4355,7 +4365,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4385,7 +4395,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4394,28 +4404,28 @@
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="30">
         <v>1288333</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>2564700</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3893503</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>4977371</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>5458718</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4425,92 +4435,92 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" s="27">
+        <v>297</v>
+      </c>
+      <c r="B8" s="28">
         <v>1026431</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>1268669</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>1306729</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>1345931</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>1386309</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="27">
+        <v>298</v>
+      </c>
+      <c r="B9" s="28">
         <v>545000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>887860</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>1190330</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <v>1439121</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <v>1555453</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B10" s="27">
+        <v>307</v>
+      </c>
+      <c r="B10" s="28">
         <v>164825</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <v>89825</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <v>89825</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <v>74825</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <v>69825</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
         <v>1736256</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>SUM(C8:C10)</f>
         <v>2246354</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>SUM(D8:D10)</f>
         <v>2586884</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>SUM(E8:E10)</f>
         <v>2859877</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>SUM(F8:F10)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4519,51 +4529,51 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="26">
         <f>B5-B11</f>
         <v>-447923</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>C5-C11</f>
         <v>318346</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>D5-D11</f>
         <v>1306619</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>E5-E11</f>
         <v>2117494</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>F5-F11</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="23">
+        <v>279</v>
+      </c>
+      <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.44829778</v>
       </c>
@@ -4634,101 +4644,101 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="24">
+        <v>309</v>
+      </c>
+      <c r="B5" s="25">
         <v>500000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>478361</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>455444</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>431175</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>405473</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B6" s="24">
+        <v>310</v>
+      </c>
+      <c r="B6" s="25">
         <v>28186</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>26908</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>25555</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>24122</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>22605</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B7" s="24">
+        <v>311</v>
+      </c>
+      <c r="B7" s="25">
         <v>21639</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>22917</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>24270</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>25702</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>27220</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B8" s="27">
+        <v>312</v>
+      </c>
+      <c r="B8" s="28">
         <v>49825</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>49825</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>49825</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>49825</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>49825</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B9" s="32">
+        <v>313</v>
+      </c>
+      <c r="B9" s="33">
         <v>478361</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>455444</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>431175</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>405473</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>378253</v>
       </c>
     </row>
@@ -4758,7 +4768,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4788,7 +4798,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4798,107 +4808,107 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="34">
+        <v>316</v>
+      </c>
+      <c r="B5" s="35">
         <v>-190250</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>128096</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>1434716</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>3552210</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>5999341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="24">
+        <v>317</v>
+      </c>
+      <c r="B6" s="25">
         <v>0</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>0</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B7" s="24">
+        <v>318</v>
+      </c>
+      <c r="B7" s="25">
         <v>0</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>0</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>0</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>0</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B8" s="24">
+        <v>319</v>
+      </c>
+      <c r="B8" s="25">
         <v>0</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>0</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B9" s="29">
+        <v>320</v>
+      </c>
+      <c r="B9" s="30">
         <v>-190250</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>128096</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>1434716</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>3552210</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>5999341</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4908,67 +4918,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B12" s="24">
+        <v>322</v>
+      </c>
+      <c r="B12" s="25">
         <v>0</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>0</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>0</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B13" s="24">
+        <v>323</v>
+      </c>
+      <c r="B13" s="25">
         <v>478361</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>455444</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>431175</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>405473</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>378253</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B14" s="29">
+        <v>324</v>
+      </c>
+      <c r="B14" s="30">
         <v>478361</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>455444</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>431175</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>405473</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>378253</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4978,41 +4988,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B17" s="25">
+        <v>326</v>
+      </c>
+      <c r="B17" s="26">
         <v>-668611</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>-327348</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>1003541</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>3146738</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>5621089</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B19" s="35">
+        <v>327</v>
+      </c>
+      <c r="B19" s="36">
         <v>0</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="36">
         <v>0</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <v>0</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <v>-1</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <v>-1</v>
       </c>
     </row>
@@ -5042,7 +5052,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5072,7 +5082,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5082,137 +5092,137 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="24">
+        <v>330</v>
+      </c>
+      <c r="B5" s="25">
         <v>1288333</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>2564700</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>3893503</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>4977371</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>5458718</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B6" s="24">
+        <v>297</v>
+      </c>
+      <c r="B6" s="25">
         <v>1026431</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>1268669</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>1306729</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>1345931</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>1386309</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B7" s="24">
+        <v>298</v>
+      </c>
+      <c r="B7" s="25">
         <v>545000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>887860</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>1190330</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>1439121</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>1555453</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8" s="27">
+        <v>331</v>
+      </c>
+      <c r="B8" s="28">
         <f>B5-B6-B7</f>
         <v>-283098</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>C5-C6-C7</f>
         <v>408171</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>D5-D6-D7</f>
         <v>1396444</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>E5-E6-E7</f>
         <v>2192319</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>F5-F6-F7</f>
         <v>2516956</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="24">
+        <v>299</v>
+      </c>
+      <c r="B9" s="25">
         <v>49825</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>49825</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>49825</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>49825</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>49825</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B10" s="37">
+        <v>332</v>
+      </c>
+      <c r="B10" s="38">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-5.68</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="38">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>8.19</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>28.03</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="38">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>44</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="38">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>50.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5222,97 +5232,97 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B13" s="24">
+        <v>334</v>
+      </c>
+      <c r="B13" s="25">
         <v>-190250</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>128096</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>1434716</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>3552210</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>5999341</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B14" s="21">
+        <v>335</v>
+      </c>
+      <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>-43</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>21</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>206</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>457</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>732</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B15" s="28">
+        <v>336</v>
+      </c>
+      <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>-1.4</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>0.7</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>6.8</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>15</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>24.1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B16" s="23">
+        <v>186</v>
+      </c>
+      <c r="B16" s="24">
         <v>0.3</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <v>0.5</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <v>0.75</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <v>0.9375</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5322,87 +5332,87 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="24">
+        <v>228</v>
+      </c>
+      <c r="B19" s="25">
         <v>10736</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>12824</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>12978</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>13273</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>13647</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B20" s="24">
+        <v>338</v>
+      </c>
+      <c r="B20" s="25">
         <v>1076256</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>1318494</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>1356554</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>1395756</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <v>1436134</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B21" s="24">
+        <v>339</v>
+      </c>
+      <c r="B21" s="25">
         <v>4542</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>4439</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>3968</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>3838</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>3889</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B22" s="38">
+        <v>340</v>
+      </c>
+      <c r="B22" s="39">
         <v>174</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="39">
         <v>158</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="39">
         <v>151</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="39">
         <v>148</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="39">
         <v>148</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5412,102 +5422,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B25" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="B25" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="D25" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>343</v>
+      <c r="C25" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="C26" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>343</v>
+      <c r="D26" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>342</v>
+        <v>346</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="D28" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="B28" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="E28" s="40" t="s">
+      <c r="C28" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="F28" s="40" t="s">
-        <v>343</v>
+      <c r="D28" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="D29" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="B29" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="C29" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="F29" s="40" t="s">
-        <v>343</v>
+      <c r="D29" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -5547,16 +5557,16 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>348</v>
-      </c>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>349</v>
-      </c>
-      <c r="E3" s="41" t="s">
+      <c r="D3" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5564,13 +5574,13 @@
       <c r="A4" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="25">
         <v>500000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="E4" s="24">
+        <v>351</v>
+      </c>
+      <c r="E4" s="25">
         <v>400000</v>
       </c>
     </row>
@@ -5578,65 +5588,65 @@
       <c r="A5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <v>100000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E5" s="24">
+        <v>352</v>
+      </c>
+      <c r="E5" s="25">
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="24">
+        <v>353</v>
+      </c>
+      <c r="B6" s="25">
         <v>50000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="E6" s="24">
+        <v>354</v>
+      </c>
+      <c r="E6" s="25">
         <v>40000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="E7" s="24">
+        <v>355</v>
+      </c>
+      <c r="E7" s="25">
         <v>60000</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="E8" s="24">
+        <v>356</v>
+      </c>
+      <c r="E8" s="25">
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B10" s="25">
+        <v>357</v>
+      </c>
+      <c r="B10" s="26">
         <v>650000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E10" s="25">
+        <v>358</v>
+      </c>
+      <c r="E10" s="26">
         <v>650000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B11" s="35">
+        <v>359</v>
+      </c>
+      <c r="B11" s="36">
         <v>0</v>
       </c>
     </row>
@@ -5802,7 +5812,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5812,7 +5822,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5822,7 +5832,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5847,127 +5857,127 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B6" s="24">
+        <v>330</v>
+      </c>
+      <c r="B6" s="25">
         <v>1288333</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>2564700</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>3893503</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>4977371</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>5458718</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="24">
+        <v>276</v>
+      </c>
+      <c r="B7" s="25">
         <v>1621256</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>2206354</v>
       </c>
-      <c r="D7" s="24">
-        <v>2547075</v>
-      </c>
-      <c r="E7" s="24">
-        <v>2834845</v>
-      </c>
-      <c r="F7" s="24">
-        <v>2991057</v>
+      <c r="D7" s="25">
+        <v>2546884</v>
+      </c>
+      <c r="E7" s="25">
+        <v>2834877</v>
+      </c>
+      <c r="F7" s="25">
+        <v>2991587</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="25">
+        <v>278</v>
+      </c>
+      <c r="B8" s="26">
         <v>-332923</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>358346</v>
       </c>
-      <c r="D8" s="25">
-        <v>1346428</v>
-      </c>
-      <c r="E8" s="25">
-        <v>2142527</v>
-      </c>
-      <c r="F8" s="25">
-        <v>2467660</v>
+      <c r="D8" s="26">
+        <v>1346619</v>
+      </c>
+      <c r="E8" s="26">
+        <v>2142494</v>
+      </c>
+      <c r="F8" s="26">
+        <v>2467131</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B9" s="23">
+        <v>279</v>
+      </c>
+      <c r="B9" s="24">
         <v>-0.2584133416981985</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <v>0.1397225288645145</v>
       </c>
-      <c r="D9" s="23">
-        <v>0.34581401350630037</v>
-      </c>
-      <c r="E9" s="23">
-        <v>0.43045348043904746</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0.45205860522041197</v>
+      <c r="D9" s="24">
+        <v>0.3458632236905482</v>
+      </c>
+      <c r="E9" s="24">
+        <v>0.43044696555461553</v>
+      </c>
+      <c r="F9" s="24">
+        <v>0.4519616461017463</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B10" s="42">
+        <v>332</v>
+      </c>
+      <c r="B10" s="43">
         <v>-5.68</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="43">
         <v>8.19</v>
       </c>
-      <c r="D10" s="42">
-        <v>28.02</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="D10" s="43">
+        <v>28.03</v>
+      </c>
+      <c r="E10" s="43">
         <v>44</v>
       </c>
-      <c r="F10" s="42">
-        <v>50.53</v>
+      <c r="F10" s="43">
+        <v>50.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B11" s="21">
+        <v>340</v>
+      </c>
+      <c r="B11" s="22">
         <v>174</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <v>158</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <v>151</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <v>148</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>148</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5977,7 +5987,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6002,127 +6012,127 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B16" s="24">
+        <v>330</v>
+      </c>
+      <c r="B16" s="25">
         <v>966250</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>1923525</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>2920127</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>3733029</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>4094038</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="24">
+        <v>276</v>
+      </c>
+      <c r="B17" s="25">
         <v>1621256</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>2206354</v>
       </c>
-      <c r="D17" s="24">
-        <v>2547075</v>
-      </c>
-      <c r="E17" s="24">
-        <v>2834845</v>
-      </c>
-      <c r="F17" s="24">
-        <v>2991057</v>
+      <c r="D17" s="25">
+        <v>2546884</v>
+      </c>
+      <c r="E17" s="25">
+        <v>2834877</v>
+      </c>
+      <c r="F17" s="25">
+        <v>2991587</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="25">
+        <v>278</v>
+      </c>
+      <c r="B18" s="26">
         <v>-655006</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>-282829</v>
       </c>
-      <c r="D18" s="25">
-        <v>373052</v>
-      </c>
-      <c r="E18" s="25">
-        <v>898184</v>
-      </c>
-      <c r="F18" s="25">
-        <v>1102981</v>
+      <c r="D18" s="26">
+        <v>373244</v>
+      </c>
+      <c r="E18" s="26">
+        <v>898152</v>
+      </c>
+      <c r="F18" s="26">
+        <v>1102452</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="23">
+        <v>279</v>
+      </c>
+      <c r="B19" s="24">
         <v>-0.677884455597598</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <v>-0.14703662818064733</v>
       </c>
-      <c r="D19" s="23">
-        <v>0.12775201800840047</v>
-      </c>
-      <c r="E19" s="23">
-        <v>0.24060464058539663</v>
-      </c>
-      <c r="F19" s="23">
-        <v>0.2694114736272159</v>
+      <c r="D19" s="24">
+        <v>0.12781763158739762</v>
+      </c>
+      <c r="E19" s="24">
+        <v>0.2405959540728207</v>
+      </c>
+      <c r="F19" s="24">
+        <v>0.26928219480232835</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B20" s="42">
+        <v>332</v>
+      </c>
+      <c r="B20" s="43">
         <v>-12.15</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="43">
         <v>-4.68</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="43">
         <v>8.49</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="43">
         <v>19.03</v>
       </c>
-      <c r="F20" s="42">
-        <v>23.14</v>
+      <c r="F20" s="43">
+        <v>23.13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B21" s="21">
+        <v>340</v>
+      </c>
+      <c r="B21" s="22">
         <v>230</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <v>191</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>177</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="22">
         <v>171</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="22">
         <v>170</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6132,7 +6142,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6157,127 +6167,127 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B26" s="24">
+        <v>330</v>
+      </c>
+      <c r="B26" s="25">
         <v>1223917</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <v>2436465</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <v>3698828</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <v>4728503</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="25">
         <v>5185782</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B27" s="24">
+        <v>276</v>
+      </c>
+      <c r="B27" s="25">
         <v>1621256</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>2206354</v>
       </c>
-      <c r="D27" s="24">
-        <v>2547075</v>
-      </c>
-      <c r="E27" s="24">
-        <v>2834845</v>
-      </c>
-      <c r="F27" s="24">
-        <v>2991057</v>
+      <c r="D27" s="25">
+        <v>2546884</v>
+      </c>
+      <c r="E27" s="25">
+        <v>2834877</v>
+      </c>
+      <c r="F27" s="25">
+        <v>2991587</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="25">
+        <v>278</v>
+      </c>
+      <c r="B28" s="26">
         <v>-397339</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <v>230111</v>
       </c>
-      <c r="D28" s="25">
-        <v>1151753</v>
-      </c>
-      <c r="E28" s="25">
-        <v>1893658</v>
-      </c>
-      <c r="F28" s="25">
-        <v>2194724</v>
+      <c r="D28" s="26">
+        <v>1151944</v>
+      </c>
+      <c r="E28" s="26">
+        <v>1893626</v>
+      </c>
+      <c r="F28" s="26">
+        <v>2194195</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B29" s="23">
+        <v>279</v>
+      </c>
+      <c r="B29" s="24">
         <v>-0.3246456228402091</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <v>0.09444476722580472</v>
       </c>
-      <c r="D29" s="23">
-        <v>0.31138317211189503</v>
-      </c>
-      <c r="E29" s="23">
-        <v>0.4004773478305762</v>
-      </c>
-      <c r="F29" s="23">
-        <v>0.4232195844425388</v>
+      <c r="D29" s="24">
+        <v>0.31143497230584016</v>
+      </c>
+      <c r="E29" s="24">
+        <v>0.40047049005748997</v>
+      </c>
+      <c r="F29" s="24">
+        <v>0.4231175222123644</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B30" s="42">
+        <v>332</v>
+      </c>
+      <c r="B30" s="43">
         <v>-6.97</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="43">
         <v>5.62</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="43">
         <v>24.12</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="43">
         <v>39.01</v>
       </c>
-      <c r="F30" s="42">
-        <v>45.05</v>
+      <c r="F30" s="43">
+        <v>45.04</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B31" s="21">
+        <v>340</v>
+      </c>
+      <c r="B31" s="22">
         <v>191</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="22">
         <v>171</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="22">
         <v>163</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>160</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="22">
         <v>159</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6287,7 +6297,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6312,121 +6322,121 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B36" s="24">
+        <v>330</v>
+      </c>
+      <c r="B36" s="25">
         <v>1288333</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="25">
         <v>2564700</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="25">
         <v>3893503</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <v>4977371</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="25">
         <v>5458718</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B37" s="24">
+        <v>276</v>
+      </c>
+      <c r="B37" s="25">
         <v>1667756</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="25">
         <v>2295964</v>
       </c>
-      <c r="D37" s="24">
-        <v>2680778</v>
-      </c>
-      <c r="E37" s="24">
-        <v>3004485</v>
-      </c>
-      <c r="F37" s="24">
-        <v>3176687</v>
+      <c r="D37" s="25">
+        <v>2680557</v>
+      </c>
+      <c r="E37" s="25">
+        <v>3004523</v>
+      </c>
+      <c r="F37" s="25">
+        <v>3177296</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B38" s="25">
+        <v>278</v>
+      </c>
+      <c r="B38" s="26">
         <v>-379423</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="26">
         <v>268736</v>
       </c>
-      <c r="D38" s="25">
-        <v>1212725</v>
-      </c>
-      <c r="E38" s="25">
-        <v>1972886</v>
-      </c>
-      <c r="F38" s="25">
-        <v>2282031</v>
+      <c r="D38" s="26">
+        <v>1212946</v>
+      </c>
+      <c r="E38" s="26">
+        <v>1972849</v>
+      </c>
+      <c r="F38" s="26">
+        <v>2281422</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B39" s="23">
+        <v>279</v>
+      </c>
+      <c r="B39" s="24">
         <v>-0.2945064852945763</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="24">
         <v>0.10478276982836991</v>
       </c>
-      <c r="D39" s="23">
-        <v>0.31147392182022743</v>
-      </c>
-      <c r="E39" s="23">
-        <v>0.3963710635426523</v>
-      </c>
-      <c r="F39" s="23">
-        <v>0.4180525145535826</v>
+      <c r="D39" s="24">
+        <v>0.31153079862242844</v>
+      </c>
+      <c r="E39" s="24">
+        <v>0.3963635407467121</v>
+      </c>
+      <c r="F39" s="24">
+        <v>0.4179410275450453</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B40" s="42">
+        <v>332</v>
+      </c>
+      <c r="B40" s="43">
         <v>-6.62</v>
       </c>
-      <c r="C40" s="42">
+      <c r="C40" s="43">
         <v>6.39</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D40" s="43">
         <v>25.34</v>
       </c>
-      <c r="E40" s="42">
+      <c r="E40" s="43">
         <v>40.6</v>
       </c>
-      <c r="F40" s="42">
-        <v>46.8</v>
+      <c r="F40" s="43">
+        <v>46.79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B41" s="21">
+        <v>340</v>
+      </c>
+      <c r="B41" s="22">
         <v>186</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <v>167</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <v>159</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="22">
         <v>156</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="22">
         <v>155</v>
       </c>
     </row>
@@ -6458,7 +6468,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6492,7 +6502,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6516,7 +6526,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6524,7 +6534,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6544,125 +6554,125 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="D13" s="24">
+        <v>330</v>
+      </c>
+      <c r="D13" s="25">
         <v>1288333</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>2564700</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>3893503</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <v>4977371</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <v>5458718</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" s="24">
+        <v>276</v>
+      </c>
+      <c r="D14" s="25">
         <v>1621256</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>2206354</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>2546884</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="25">
         <v>2834877</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="25">
         <v>2991587</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" s="24">
+        <v>278</v>
+      </c>
+      <c r="D15" s="25">
         <v>-447923</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>318346</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>1306619</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="25">
         <v>2117494</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="25">
         <v>2447131</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D16" s="24">
+        <v>373</v>
+      </c>
+      <c r="D16" s="25">
         <v>-190250</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>128096</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>1434716</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="25">
         <v>3552210</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="25">
         <v>5999341</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="D17" s="24">
+        <v>374</v>
+      </c>
+      <c r="D17" s="25">
         <v>478361</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>455444</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>431175</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="25">
         <v>405473</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="25">
         <v>378253</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6682,105 +6692,105 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D21" s="23">
+        <v>376</v>
+      </c>
+      <c r="D21" s="24">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0.12412616281780338</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <v>0.33558969879535744</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <v>0.42542423416409325</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <v>0.44829778198663</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="D22" s="42">
+        <v>332</v>
+      </c>
+      <c r="D22" s="43">
         <v>-5.68</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="43">
         <v>8.19</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="43">
         <v>28.03</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="43">
         <v>44</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="43">
         <v>50.52</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" s="23">
+        <v>186</v>
+      </c>
+      <c r="D23" s="24">
         <v>0.3</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0.5</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <v>0.75</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="24">
         <v>0.9375</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D24" s="21">
+        <v>377</v>
+      </c>
+      <c r="D24" s="22">
         <v>120</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="22">
         <v>200</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="22">
         <v>300</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="22">
         <v>375</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="22">
         <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7642,25 +7652,31 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>161</v>
       </c>
       <c r="B61" s="18">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61" s="20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B62" s="18">
         <v>0.03</v>
       </c>
+      <c r="C62" s="20" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B63" s="19">
         <v>0.8333333333333334</v>
@@ -7668,7 +7684,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B64" s="17">
         <v>0</v>
@@ -7676,10 +7692,10 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -7714,10 +7730,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7738,10 +7754,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7754,7 +7770,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7765,31 +7781,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7797,31 +7813,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -7881,7 +7897,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7893,19 +7909,19 @@
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <v>120</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>200</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>300</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>375</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>400</v>
       </c>
     </row>
@@ -7913,47 +7929,47 @@
       <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="22">
+        <v>186</v>
+      </c>
+      <c r="B8" s="23">
         <v>0.3</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <v>0.5</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <v>0.75</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <v>0.9375</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" s="23">
+        <v>188</v>
+      </c>
+      <c r="C10" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <v>0.5</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <v>0.25</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <v>0.06666666666666667</v>
       </c>
     </row>
@@ -7983,7 +7999,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8013,7 +8029,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8023,145 +8039,145 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="24">
+        <v>191</v>
+      </c>
+      <c r="B5" s="25">
         <v>1140000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>1957000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>3023565</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>3892840</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>4276933</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="24">
+        <v>192</v>
+      </c>
+      <c r="B6" s="25">
         <v>96000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>164800</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>254616</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>327818</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>360163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="24">
+        <v>193</v>
+      </c>
+      <c r="B7" s="25">
         <v>144000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>247200</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>381924</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>491727</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>540244</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="24">
+        <v>194</v>
+      </c>
+      <c r="B8" s="25">
         <v>100000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>103000</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>106090</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>109273</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>112551</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="24">
+        <v>195</v>
+      </c>
+      <c r="B9" s="25">
         <v>30000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>30900</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>31827</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>32782</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="24">
+        <v>196</v>
+      </c>
+      <c r="B10" s="25">
         <v>36000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>61800</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>95481</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>122932</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>135061</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="25">
+        <v>197</v>
+      </c>
+      <c r="B11" s="26">
         <f>SUM(B5:B10)</f>
         <v>1546000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
@@ -8216,7 +8232,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>118</v>
@@ -8225,7 +8241,7 @@
         <v>119</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8235,19 +8251,19 @@
       <c r="B4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>1</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>110000</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="24">
         <v>0.28</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="28">
         <v>149215</v>
       </c>
     </row>
@@ -8258,19 +8274,19 @@
       <c r="B5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>90000</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <v>0.28</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="28">
         <v>122085</v>
       </c>
     </row>
@@ -8281,19 +8297,19 @@
       <c r="B6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>1</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>72000</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="24">
         <v>0.28</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <v>97668</v>
       </c>
     </row>
@@ -8304,19 +8320,19 @@
       <c r="B7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <v>6</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>52000</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <v>0.28</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <v>423228</v>
       </c>
     </row>
@@ -8327,19 +8343,19 @@
       <c r="B8" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>1</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>55000</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>0.28</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <v>74608</v>
       </c>
     </row>
@@ -8350,19 +8366,19 @@
       <c r="B9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>3</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>30000</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <v>0.2</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="28">
         <v>114885</v>
       </c>
     </row>
@@ -8373,19 +8389,19 @@
       <c r="B10" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>1</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>55000</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <v>0.28</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <v>74608</v>
       </c>
     </row>
@@ -8396,19 +8412,19 @@
       <c r="B11" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>2</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>38000</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <v>0.25</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="28">
         <v>100814</v>
       </c>
     </row>
@@ -8419,25 +8435,25 @@
       <c r="B12" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>1</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>55000</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <v>0.28</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="28">
         <v>74608</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -8468,61 +8484,61 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B16" s="25">
+        <v>201</v>
+      </c>
+      <c r="B16" s="26">
         <v>1026431</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>1268669</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>1306729</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>1345931</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>1386309</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="23">
+        <v>202</v>
+      </c>
+      <c r="B17" s="24">
         <v>0.6639270698576973</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="24">
         <v>0.49466566265060247</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <v>0.3356178474114441</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <v>0.27040998902305163</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="24">
         <v>0.25396237113402065</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B18" s="28">
+        <v>203</v>
+      </c>
+      <c r="B18" s="29">
         <v>7.1</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <v>11.8</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <v>17.6</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <v>22.1</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <v>23.5</v>
       </c>
     </row>
@@ -8552,7 +8568,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8592,45 +8608,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="24">
+        <v>205</v>
+      </c>
+      <c r="B5" s="25">
         <v>84000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>144200</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>222789</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>286841</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>315142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="29">
+        <v>206</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
         <v>84000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>SUM(C5:C5)</f>
         <v>144200</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>SUM(D5:D5)</f>
         <v>222789</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>SUM(E5:E5)</f>
         <v>286841</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>SUM(F5:F5)</f>
         <v>315142</v>
       </c>
@@ -8647,45 +8663,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="24">
+        <v>207</v>
+      </c>
+      <c r="B8" s="25">
         <v>60000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>103000</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>159135</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>204886</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>225102</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="29">
+        <v>208</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>103000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>159135</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>204886</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>225102</v>
       </c>
@@ -8702,105 +8718,105 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B11" s="24">
+        <v>209</v>
+      </c>
+      <c r="B11" s="25">
         <v>216000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>222480</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>229154</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>236029</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>243110</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B12" s="24">
+        <v>210</v>
+      </c>
+      <c r="B12" s="25">
         <v>30000</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>30900</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>31827</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>32782</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="24">
+        <v>211</v>
+      </c>
+      <c r="B13" s="25">
         <v>18000</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>18540</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>19096</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>19669</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="24">
+        <v>212</v>
+      </c>
+      <c r="B14" s="25">
         <v>18000</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>18540</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>19096</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>19669</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="29">
+        <v>213</v>
+      </c>
+      <c r="B15" s="30">
         <f>SUM(B11:B14)</f>
         <v>282000</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>SUM(C11:C14)</f>
         <v>290460</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>SUM(D11:D14)</f>
         <v>299174</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>SUM(E11:E14)</f>
         <v>308149</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>SUM(F11:F14)</f>
         <v>317393</v>
       </c>
@@ -8817,150 +8833,150 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="24">
+        <v>214</v>
+      </c>
+      <c r="B17" s="25">
         <v>25000</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>25750</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>26523</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>27318</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>28138</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="24">
+        <v>215</v>
+      </c>
+      <c r="B18" s="25">
         <v>15000</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>15450</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>15914</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>16391</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>16883</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B19" s="24">
+        <v>216</v>
+      </c>
+      <c r="B19" s="25">
         <v>20000</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>20600</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>21218</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>21855</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>22510</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" s="24">
+        <v>217</v>
+      </c>
+      <c r="B20" s="25">
         <v>96000</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>164800</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>254616</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>327818</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <v>360163</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B21" s="24">
+        <v>218</v>
+      </c>
+      <c r="B21" s="25">
         <v>72000</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>123600</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>190962</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>245864</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>270122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B22" s="29">
+        <v>219</v>
+      </c>
+      <c r="B22" s="30">
         <f>SUM(B17:B21)</f>
         <v>228000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>SUM(C17:C21)</f>
         <v>350200</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>SUM(D17:D21)</f>
         <v>509232</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>SUM(E17:E21)</f>
         <v>639245</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>SUM(F17:F21)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="25">
+        <v>220</v>
+      </c>
+      <c r="B24" s="26">
         <f>B6+B9+B15+B22</f>
         <v>654000</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>C6+C9+C15+C22</f>
         <v>887860</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="26">
         <f>D6+D9+D15+D22</f>
         <v>1190330</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>E6+E9+E15+E22</f>
         <v>1439121</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>F6+F9+F15+F22</f>
         <v>1555453</v>
       </c>
@@ -8992,7 +9008,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -9017,7 +9033,7 @@
         <v>154</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -9030,13 +9046,13 @@
       <c r="C4" s="17">
         <v>500000</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="24">
         <v>0.0575</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="22">
         <v>15</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <v>49825</v>
       </c>
     </row>
@@ -9045,18 +9061,18 @@
         <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C5" s="17">
         <v>75000</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="24">
         <v>0</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="22">
         <v>0</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <v>75000</v>
       </c>
     </row>
@@ -9065,34 +9081,34 @@
         <v>159</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C6" s="17">
         <v>40000</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="24">
         <v>0</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <v>0</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>40000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F8" s="25">
+        <v>224</v>
+      </c>
+      <c r="F8" s="26">
         <v>49825</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F9" s="29">
+        <v>225</v>
+      </c>
+      <c r="F9" s="30">
         <v>500000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="380">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -519,10 +519,13 @@
     <t>Salary Escalation Rate</t>
   </si>
   <si>
-    <t>Derived from tuition escalation rate</t>
+    <t>Salary input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
+  </si>
+  <si>
+    <t>Cost inflation input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Year 1 Proration Factor</t>
@@ -2059,7 +2062,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2109,7 +2112,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2239,7 +2242,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="26">
         <f>SUM(B7:B12)</f>
@@ -2264,7 +2267,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B15" s="25">
         <v>12883</v>
@@ -2308,7 +2311,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2348,7 +2351,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B5" s="25">
         <v>352690</v>
@@ -2368,7 +2371,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B6" s="25">
         <v>62173</v>
@@ -2388,7 +2391,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B7" s="25">
         <v>95738</v>
@@ -2408,7 +2411,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -2443,7 +2446,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B10" s="25">
         <v>124346</v>
@@ -2463,7 +2466,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B11" s="25">
         <v>101738</v>
@@ -2483,7 +2486,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B12" s="25">
         <v>81390</v>
@@ -2503,7 +2506,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
@@ -2538,7 +2541,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="25">
         <v>62173</v>
@@ -2558,7 +2561,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
@@ -2593,7 +2596,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -2613,7 +2616,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
@@ -2648,7 +2651,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B21:B21)</f>
@@ -2693,7 +2696,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" s="26">
         <f>B8+B13+B16+B19+B22</f>
@@ -2742,7 +2745,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2772,7 +2775,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2782,7 +2785,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B5" s="25">
         <v>950000</v>
@@ -2802,7 +2805,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B6" s="25">
         <v>80000</v>
@@ -2822,7 +2825,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B7" s="25">
         <v>120000</v>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B8" s="25">
         <v>83333</v>
@@ -2862,7 +2865,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B9" s="25">
         <v>25000</v>
@@ -2882,7 +2885,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B10" s="25">
         <v>30000</v>
@@ -2902,7 +2905,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
@@ -2927,7 +2930,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2937,7 +2940,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B14" s="25">
         <v>124346</v>
@@ -2957,7 +2960,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B15" s="25">
         <v>101738</v>
@@ -2977,7 +2980,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B16" s="25">
         <v>81390</v>
@@ -2997,7 +3000,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B17" s="25">
         <v>352690</v>
@@ -3017,7 +3020,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -3037,7 +3040,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B19" s="25">
         <v>95738</v>
@@ -3057,7 +3060,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B20" s="25">
         <v>62173</v>
@@ -3077,7 +3080,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -3097,7 +3100,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" s="25">
         <v>62173</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B23" s="30">
         <f>SUM(B14:B22)</f>
@@ -3157,7 +3160,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B27" s="25">
         <v>70000</v>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="25">
         <v>50000</v>
@@ -3207,7 +3210,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" s="25">
         <v>180000</v>
@@ -3227,7 +3230,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B32" s="25">
         <v>25000</v>
@@ -3247,7 +3250,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B33" s="25">
         <v>15000</v>
@@ -3267,7 +3270,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B34" s="25">
         <v>15000</v>
@@ -3287,7 +3290,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B35" s="30">
         <f>SUM(B31:B34)</f>
@@ -3317,7 +3320,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" s="25">
         <v>20833</v>
@@ -3337,7 +3340,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" s="25">
         <v>12500</v>
@@ -3357,7 +3360,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" s="25">
         <v>16667</v>
@@ -3377,7 +3380,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B40" s="25">
         <v>80000</v>
@@ -3397,7 +3400,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B41" s="25">
         <v>60000</v>
@@ -3417,7 +3420,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B42" s="30">
         <f>SUM(B37:B41)</f>
@@ -3442,7 +3445,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B43" s="30">
         <f>B27+B29+B35+B42</f>
@@ -3467,7 +3470,7 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -3477,7 +3480,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B46" s="25">
         <v>49825</v>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B47" s="25">
         <v>75000</v>
@@ -3517,7 +3520,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B48" s="25">
         <v>40000</v>
@@ -3537,7 +3540,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B49" s="30">
         <f>SUM(B46:B48)</f>
@@ -3586,7 +3589,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3616,7 +3619,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B4" s="28">
         <f>'Budget Detail'!B11</f>
@@ -3641,7 +3644,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B5" s="28">
         <f>'Budget Detail'!B23</f>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B6" s="28">
         <f>'Budget Detail'!B43</f>
@@ -3691,7 +3694,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B7" s="28">
         <f>'Budget Detail'!B49</f>
@@ -3716,7 +3719,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -3741,7 +3744,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3751,7 +3754,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
@@ -3776,7 +3779,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3801,7 +3804,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B13" s="25">
         <v>-447923</v>
@@ -3821,7 +3824,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B14" s="25">
         <v>10736</v>
@@ -3841,7 +3844,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B15" s="25">
         <v>14469</v>
@@ -3886,7 +3889,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3907,48 +3910,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3966,7 +3969,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B4" s="30">
         <v>154600</v>
@@ -4010,7 +4013,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4028,7 +4031,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B7" s="25">
         <v>102643</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B8" s="25">
         <v>54500</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B9" s="25">
         <v>13735</v>
@@ -4160,7 +4163,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4178,7 +4181,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B12" s="28">
         <v>170878</v>
@@ -4222,7 +4225,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" s="28">
         <v>-16278</v>
@@ -4266,7 +4269,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B14" s="33">
         <v>-16278</v>
@@ -4310,14 +4313,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17" s="25">
         <v>0</v>
@@ -4325,7 +4328,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" s="33">
         <v>-190250</v>
@@ -4333,7 +4336,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B19" s="25">
         <v>-190250</v>
@@ -4365,7 +4368,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4395,7 +4398,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4405,7 +4408,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -4425,7 +4428,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4435,7 +4438,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B8" s="28">
         <v>1026431</v>
@@ -4455,7 +4458,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B9" s="28">
         <v>545000</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" s="28">
         <v>164825</v>
@@ -4495,7 +4498,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4530,7 +4533,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
@@ -4555,7 +4558,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4644,7 +4647,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B5" s="25">
         <v>500000</v>
@@ -4664,7 +4667,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B6" s="25">
         <v>28186</v>
@@ -4684,7 +4687,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B7" s="25">
         <v>21639</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B8" s="28">
         <v>49825</v>
@@ -4724,7 +4727,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B9" s="33">
         <v>478361</v>
@@ -4768,7 +4771,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4798,7 +4801,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4808,7 +4811,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B5" s="35">
         <v>-190250</v>
@@ -4828,7 +4831,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -4848,7 +4851,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B7" s="25">
         <v>0</v>
@@ -4868,7 +4871,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -4888,7 +4891,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B9" s="30">
         <v>-190250</v>
@@ -4908,7 +4911,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4918,7 +4921,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4938,7 +4941,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B13" s="25">
         <v>478361</v>
@@ -4958,7 +4961,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B14" s="30">
         <v>478361</v>
@@ -4978,7 +4981,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4988,7 +4991,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B17" s="26">
         <v>-668611</v>
@@ -5008,7 +5011,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B19" s="36">
         <v>0</v>
@@ -5052,7 +5055,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5082,7 +5085,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B5" s="25">
         <v>1288333</v>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B6" s="25">
         <v>1026431</v>
@@ -5132,7 +5135,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B7" s="25">
         <v>545000</v>
@@ -5152,7 +5155,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
@@ -5177,7 +5180,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B9" s="25">
         <v>49825</v>
@@ -5197,7 +5200,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B10" s="38">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5222,7 +5225,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5232,7 +5235,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B13" s="25">
         <v>-190250</v>
@@ -5252,7 +5255,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5277,7 +5280,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="24">
         <v>0.3</v>
@@ -5322,7 +5325,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5332,7 +5335,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" s="25">
         <v>10736</v>
@@ -5352,7 +5355,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B20" s="25">
         <v>1076256</v>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B21" s="25">
         <v>4542</v>
@@ -5392,7 +5395,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B22" s="39">
         <v>174</v>
@@ -5412,7 +5415,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5422,102 +5425,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="C26" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>344</v>
-      </c>
       <c r="D26" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -5558,13 +5561,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>100</v>
@@ -5578,7 +5581,7 @@
         <v>500000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E4" s="25">
         <v>400000</v>
@@ -5592,7 +5595,7 @@
         <v>100000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E5" s="25">
         <v>75000</v>
@@ -5600,13 +5603,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B6" s="25">
         <v>50000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E6" s="25">
         <v>40000</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E7" s="25">
         <v>60000</v>
@@ -5622,7 +5625,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E8" s="25">
         <v>75000</v>
@@ -5630,13 +5633,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B10" s="26">
         <v>650000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E10" s="26">
         <v>650000</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B11" s="36">
         <v>0</v>
@@ -5812,7 +5815,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5822,7 +5825,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5832,7 +5835,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5857,7 +5860,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B6" s="25">
         <v>1288333</v>
@@ -5877,7 +5880,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B7" s="25">
         <v>1621256</v>
@@ -5897,7 +5900,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B8" s="26">
         <v>-332923</v>
@@ -5917,7 +5920,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B9" s="24">
         <v>-0.2584133416981985</v>
@@ -5937,7 +5940,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B10" s="43">
         <v>-5.68</v>
@@ -5957,7 +5960,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B11" s="22">
         <v>174</v>
@@ -5977,7 +5980,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6012,7 +6015,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B16" s="25">
         <v>966250</v>
@@ -6032,7 +6035,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B17" s="25">
         <v>1621256</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B18" s="26">
         <v>-655006</v>
@@ -6072,7 +6075,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B19" s="24">
         <v>-0.677884455597598</v>
@@ -6092,7 +6095,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B20" s="43">
         <v>-12.15</v>
@@ -6112,7 +6115,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B21" s="22">
         <v>230</v>
@@ -6132,7 +6135,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6142,7 +6145,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6167,7 +6170,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B26" s="25">
         <v>1223917</v>
@@ -6187,7 +6190,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B27" s="25">
         <v>1621256</v>
@@ -6207,7 +6210,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" s="26">
         <v>-397339</v>
@@ -6227,7 +6230,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" s="24">
         <v>-0.3246456228402091</v>
@@ -6247,7 +6250,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B30" s="43">
         <v>-6.97</v>
@@ -6267,7 +6270,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B31" s="22">
         <v>191</v>
@@ -6287,7 +6290,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6297,7 +6300,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6322,7 +6325,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B36" s="25">
         <v>1288333</v>
@@ -6342,7 +6345,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B37" s="25">
         <v>1667756</v>
@@ -6362,7 +6365,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B38" s="26">
         <v>-379423</v>
@@ -6382,7 +6385,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B39" s="24">
         <v>-0.2945064852945763</v>
@@ -6402,7 +6405,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" s="43">
         <v>-6.62</v>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B41" s="22">
         <v>186</v>
@@ -6468,7 +6471,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6526,7 +6529,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6534,7 +6537,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6572,7 +6575,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D13" s="25">
         <v>1288333</v>
@@ -6592,7 +6595,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D14" s="25">
         <v>1621256</v>
@@ -6612,7 +6615,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D15" s="25">
         <v>-447923</v>
@@ -6632,7 +6635,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D16" s="25">
         <v>-190250</v>
@@ -6652,7 +6655,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D17" s="25">
         <v>478361</v>
@@ -6672,7 +6675,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6710,7 +6713,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D21" s="24">
         <v>-0.34767595489354136</v>
@@ -6730,7 +6733,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D22" s="43">
         <v>-5.68</v>
@@ -6750,7 +6753,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D23" s="24">
         <v>0.3</v>
@@ -6770,7 +6773,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D24" s="22">
         <v>120</v>
@@ -6790,7 +6793,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7671,12 +7674,12 @@
         <v>0.03</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B63" s="19">
         <v>0.8333333333333334</v>
@@ -7684,7 +7687,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="17">
         <v>0</v>
@@ -7692,10 +7695,10 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -7730,10 +7733,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7754,10 +7757,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7770,7 +7773,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7781,31 +7784,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7813,31 +7816,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -7897,7 +7900,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7935,7 +7938,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" s="23">
         <v>0.3</v>
@@ -7955,10 +7958,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C10" s="24">
         <v>0.6666666666666666</v>
@@ -7999,7 +8002,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8029,7 +8032,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8039,7 +8042,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" s="25">
         <v>1140000</v>
@@ -8059,7 +8062,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B6" s="25">
         <v>96000</v>
@@ -8079,7 +8082,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" s="25">
         <v>144000</v>
@@ -8099,7 +8102,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B8" s="25">
         <v>100000</v>
@@ -8119,7 +8122,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B9" s="25">
         <v>30000</v>
@@ -8139,7 +8142,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B10" s="25">
         <v>36000</v>
@@ -8159,7 +8162,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B11" s="26">
         <f>SUM(B5:B10)</f>
@@ -8232,7 +8235,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>118</v>
@@ -8241,7 +8244,7 @@
         <v>119</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8453,7 +8456,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -8484,7 +8487,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" s="26">
         <v>1026431</v>
@@ -8504,7 +8507,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" s="24">
         <v>0.6639270698576973</v>
@@ -8524,7 +8527,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B18" s="29">
         <v>7.1</v>
@@ -8568,7 +8571,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8608,7 +8611,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="25">
         <v>84000</v>
@@ -8628,7 +8631,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -8663,7 +8666,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="25">
         <v>60000</v>
@@ -8683,7 +8686,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -8718,7 +8721,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B11" s="25">
         <v>216000</v>
@@ -8738,7 +8741,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B12" s="25">
         <v>30000</v>
@@ -8758,7 +8761,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B13" s="25">
         <v>18000</v>
@@ -8778,7 +8781,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B14" s="25">
         <v>18000</v>
@@ -8798,7 +8801,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B15" s="30">
         <f>SUM(B11:B14)</f>
@@ -8833,7 +8836,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B17" s="25">
         <v>25000</v>
@@ -8853,7 +8856,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" s="25">
         <v>15000</v>
@@ -8873,7 +8876,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" s="25">
         <v>20000</v>
@@ -8893,7 +8896,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" s="25">
         <v>96000</v>
@@ -8913,7 +8916,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B21" s="25">
         <v>72000</v>
@@ -8933,7 +8936,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B17:B21)</f>
@@ -8958,7 +8961,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B24" s="26">
         <f>B6+B9+B15+B22</f>
@@ -9008,7 +9011,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -9033,7 +9036,7 @@
         <v>154</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -9061,7 +9064,7 @@
         <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C5" s="17">
         <v>75000</v>
@@ -9081,7 +9084,7 @@
         <v>159</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C6" s="17">
         <v>40000</v>
@@ -9098,7 +9101,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F8" s="26">
         <v>49825</v>
@@ -9106,7 +9109,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F9" s="30">
         <v>500000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -26,7 +26,7 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>Stage</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="391">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -222,13 +222,13 @@
     <t>How to Use This Workbook</t>
   </si>
   <si>
-    <t>Color Legend</t>
-  </si>
-  <si>
-    <t>Yellow cells are editable inputs - change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas - do not edit.</t>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Yellow cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -258,6 +258,24 @@
     <t>Tabs 18-21: Analysis &amp; underwriting</t>
   </si>
   <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
+  </si>
+  <si>
+    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
+  </si>
+  <si>
+    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+  </si>
+  <si>
     <t>Tips</t>
   </si>
   <si>
@@ -961,6 +979,21 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>LOAN TERMS</t>
+  </si>
+  <si>
+    <t>Loan Name</t>
+  </si>
+  <si>
+    <t>Annual Rate</t>
+  </si>
+  <si>
+    <t>Term (Years)</t>
+  </si>
+  <si>
+    <t>AMORTIZATION: Facility Improvement Loan</t>
   </si>
   <si>
     <t>Beginning Balance</t>
@@ -1344,7 +1377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1388,6 +1421,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2062,7 +2098,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2075,24 +2111,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B4" s="31">
         <v>120</v>
@@ -2112,7 +2148,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2122,7 +2158,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="25">
         <v>1140000</v>
@@ -2142,7 +2178,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B8" s="25">
         <v>96000</v>
@@ -2162,7 +2198,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="25">
         <v>144000</v>
@@ -2182,7 +2218,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B10" s="25">
         <v>100000</v>
@@ -2202,7 +2238,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" s="25">
         <v>30000</v>
@@ -2222,7 +2258,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B12" s="25">
         <v>36000</v>
@@ -2242,7 +2278,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B13" s="26">
         <f>SUM(B7:B12)</f>
@@ -2267,7 +2303,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B15" s="25">
         <v>12883</v>
@@ -2311,7 +2347,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2324,24 +2360,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2351,7 +2387,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B5" s="25">
         <v>352690</v>
@@ -2371,7 +2407,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B6" s="25">
         <v>62173</v>
@@ -2391,7 +2427,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B7" s="25">
         <v>95738</v>
@@ -2411,7 +2447,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -2436,7 +2472,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2446,7 +2482,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B10" s="25">
         <v>124346</v>
@@ -2466,7 +2502,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B11" s="25">
         <v>101738</v>
@@ -2486,7 +2522,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B12" s="25">
         <v>81390</v>
@@ -2506,7 +2542,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
@@ -2531,7 +2567,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2541,7 +2577,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B15" s="25">
         <v>62173</v>
@@ -2561,7 +2597,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
@@ -2586,7 +2622,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2596,7 +2632,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -2616,7 +2652,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
@@ -2641,7 +2677,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2651,7 +2687,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -2671,7 +2707,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B21:B21)</f>
@@ -2696,7 +2732,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B24" s="26">
         <f>B8+B13+B16+B19+B22</f>
@@ -2745,7 +2781,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2758,24 +2794,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2785,7 +2821,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B5" s="25">
         <v>950000</v>
@@ -2805,7 +2841,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B6" s="25">
         <v>80000</v>
@@ -2825,7 +2861,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B7" s="25">
         <v>120000</v>
@@ -2845,7 +2881,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B8" s="25">
         <v>83333</v>
@@ -2865,7 +2901,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B9" s="25">
         <v>25000</v>
@@ -2885,7 +2921,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B10" s="25">
         <v>30000</v>
@@ -2905,7 +2941,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
@@ -2930,7 +2966,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2940,7 +2976,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B14" s="25">
         <v>124346</v>
@@ -2960,7 +2996,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B15" s="25">
         <v>101738</v>
@@ -2980,7 +3016,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B16" s="25">
         <v>81390</v>
@@ -3000,7 +3036,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B17" s="25">
         <v>352690</v>
@@ -3020,7 +3056,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -3040,7 +3076,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B19" s="25">
         <v>95738</v>
@@ -3060,7 +3096,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B20" s="25">
         <v>62173</v>
@@ -3080,7 +3116,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -3100,7 +3136,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B22" s="25">
         <v>62173</v>
@@ -3120,7 +3156,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B23" s="30">
         <f>SUM(B14:B22)</f>
@@ -3145,7 +3181,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -3155,12 +3191,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B27" s="25">
         <v>70000</v>
@@ -3180,12 +3216,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B29" s="25">
         <v>50000</v>
@@ -3205,12 +3241,12 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="32" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B31" s="25">
         <v>180000</v>
@@ -3230,7 +3266,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B32" s="25">
         <v>25000</v>
@@ -3250,7 +3286,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B33" s="25">
         <v>15000</v>
@@ -3270,7 +3306,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B34" s="25">
         <v>15000</v>
@@ -3290,7 +3326,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B35" s="30">
         <f>SUM(B31:B34)</f>
@@ -3315,12 +3351,12 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="32" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B37" s="25">
         <v>20833</v>
@@ -3340,7 +3376,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B38" s="25">
         <v>12500</v>
@@ -3360,7 +3396,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B39" s="25">
         <v>16667</v>
@@ -3380,7 +3416,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B40" s="25">
         <v>80000</v>
@@ -3400,7 +3436,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B41" s="25">
         <v>60000</v>
@@ -3420,7 +3456,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B42" s="30">
         <f>SUM(B37:B41)</f>
@@ -3445,7 +3481,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B43" s="30">
         <f>B27+B29+B35+B42</f>
@@ -3470,7 +3506,7 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -3480,7 +3516,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B46" s="25">
         <v>49825</v>
@@ -3500,7 +3536,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B47" s="25">
         <v>75000</v>
@@ -3520,7 +3556,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B48" s="25">
         <v>40000</v>
@@ -3540,7 +3576,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B49" s="30">
         <f>SUM(B46:B48)</f>
@@ -3589,7 +3625,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3602,24 +3638,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B4" s="28">
         <f>'Budget Detail'!B11</f>
@@ -3644,7 +3680,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B5" s="28">
         <f>'Budget Detail'!B23</f>
@@ -3669,7 +3705,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B6" s="28">
         <f>'Budget Detail'!B43</f>
@@ -3694,7 +3730,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B7" s="28">
         <f>'Budget Detail'!B49</f>
@@ -3719,7 +3755,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -3744,7 +3780,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3754,7 +3790,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
@@ -3779,7 +3815,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3804,7 +3840,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B13" s="25">
         <v>-447923</v>
@@ -3824,7 +3860,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B14" s="25">
         <v>10736</v>
@@ -3844,7 +3880,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B15" s="25">
         <v>14469</v>
@@ -3889,7 +3925,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3910,48 +3946,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3969,7 +4005,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B4" s="30">
         <v>154600</v>
@@ -4013,7 +4049,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4031,7 +4067,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B7" s="25">
         <v>102643</v>
@@ -4075,7 +4111,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B8" s="25">
         <v>54500</v>
@@ -4119,7 +4155,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B9" s="25">
         <v>13735</v>
@@ -4163,7 +4199,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4181,7 +4217,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B12" s="28">
         <v>170878</v>
@@ -4225,7 +4261,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B13" s="28">
         <v>-16278</v>
@@ -4269,7 +4305,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B14" s="33">
         <v>-16278</v>
@@ -4313,14 +4349,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B17" s="25">
         <v>0</v>
@@ -4328,7 +4364,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B18" s="33">
         <v>-190250</v>
@@ -4336,7 +4372,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B19" s="25">
         <v>-190250</v>
@@ -4368,7 +4404,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4381,24 +4417,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4408,7 +4444,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -4428,7 +4464,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4438,7 +4474,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B8" s="28">
         <v>1026431</v>
@@ -4458,7 +4494,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B9" s="28">
         <v>545000</v>
@@ -4478,7 +4514,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B10" s="28">
         <v>164825</v>
@@ -4498,7 +4534,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -4523,7 +4559,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4533,7 +4569,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
@@ -4558,7 +4594,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4598,7 +4634,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4620,24 +4656,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>155</v>
+        <v>316</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4645,103 +4681,173 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B5" s="25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="17">
         <v>500000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C6" s="18">
+        <v>0.0575</v>
+      </c>
+      <c r="D6" s="14">
+        <v>15</v>
+      </c>
+      <c r="E6" s="25">
+        <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
+        <v>49825</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="25">
+        <f>B6</f>
+        <v>500000</v>
+      </c>
+      <c r="C9" s="25">
+        <f>B13</f>
         <v>478361</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D9" s="25">
+        <f>C13</f>
         <v>455444</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E9" s="25">
+        <f>D13</f>
         <v>431175</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F9" s="25">
+        <f>E13</f>
         <v>405473</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B6" s="25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="25">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>28186</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C10" s="25">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>26908</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D10" s="25">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>25555</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E10" s="25">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>24122</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F10" s="25">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>22605</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B11" s="25">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>21639</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C11" s="25">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>22917</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D11" s="25">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>24270</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E11" s="25">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>25702</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F11" s="25">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>27220</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="28">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" s="28">
+        <f>B10+B11</f>
         <v>49825</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C12" s="28">
+        <f>C10+C11</f>
         <v>49825</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D12" s="28">
+        <f>D10+D11</f>
         <v>49825</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E12" s="28">
+        <f>E10+E11</f>
         <v>49825</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F12" s="28">
+        <f>F10+F11</f>
         <v>49825</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" s="33">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="33">
+        <f>MAX(0,B9-B11)</f>
         <v>478361</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C13" s="33">
+        <f>MAX(0,C9-C11)</f>
         <v>455444</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D13" s="33">
+        <f>MAX(0,D9-D11)</f>
         <v>431175</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E13" s="33">
+        <f>MAX(0,E9-E11)</f>
         <v>405473</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F13" s="33">
+        <f>MAX(0,F9-F11)</f>
         <v>378253</v>
       </c>
     </row>
@@ -4771,7 +4877,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4784,24 +4890,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4811,27 +4917,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="35">
+        <v>328</v>
+      </c>
+      <c r="B5" s="38">
         <v>-190250</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="38">
         <v>128096</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="38">
         <v>1434716</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="38">
         <v>3552210</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="38">
         <v>5999341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -4851,7 +4957,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B7" s="25">
         <v>0</v>
@@ -4871,7 +4977,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -4891,7 +4997,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B9" s="30">
         <v>-190250</v>
@@ -4911,7 +5017,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4921,7 +5027,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4941,7 +5047,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B13" s="25">
         <v>478361</v>
@@ -4961,7 +5067,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B14" s="30">
         <v>478361</v>
@@ -4981,7 +5087,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4991,7 +5097,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B17" s="26">
         <v>-668611</v>
@@ -5011,21 +5117,21 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B19" s="36">
+        <v>339</v>
+      </c>
+      <c r="B19" s="39">
         <v>0</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="39">
         <v>0</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="39">
         <v>0</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="40">
         <v>-1</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="40">
         <v>-1</v>
       </c>
     </row>
@@ -5055,7 +5161,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5068,24 +5174,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5095,7 +5201,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B5" s="25">
         <v>1288333</v>
@@ -5115,7 +5221,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B6" s="25">
         <v>1026431</v>
@@ -5135,7 +5241,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B7" s="25">
         <v>545000</v>
@@ -5155,7 +5261,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
@@ -5180,7 +5286,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B9" s="25">
         <v>49825</v>
@@ -5200,32 +5306,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="38">
+        <v>344</v>
+      </c>
+      <c r="B10" s="41">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-5.68</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="41">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>8.19</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="41">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>28.03</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="41">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>44</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="41">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>50.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5235,7 +5341,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B13" s="25">
         <v>-190250</v>
@@ -5255,7 +5361,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5280,7 +5386,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5305,7 +5411,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B16" s="24">
         <v>0.3</v>
@@ -5325,7 +5431,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5335,7 +5441,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B19" s="25">
         <v>10736</v>
@@ -5355,7 +5461,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B20" s="25">
         <v>1076256</v>
@@ -5375,7 +5481,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B21" s="25">
         <v>4542</v>
@@ -5395,27 +5501,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B22" s="39">
+        <v>352</v>
+      </c>
+      <c r="B22" s="42">
         <v>174</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="42">
         <v>158</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="42">
         <v>151</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="42">
         <v>148</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="42">
         <v>148</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5425,102 +5531,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>345</v>
+        <v>357</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="F26" s="44" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>344</v>
+        <v>358</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="E28" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>345</v>
+        <v>359</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="E29" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="F29" s="41" t="s">
-        <v>345</v>
+        <v>360</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5560,28 +5666,28 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>100</v>
+      <c r="A3" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B4" s="25">
         <v>500000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E4" s="25">
         <v>400000</v>
@@ -5589,13 +5695,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B5" s="25">
         <v>100000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E5" s="25">
         <v>75000</v>
@@ -5603,13 +5709,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B6" s="25">
         <v>50000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E6" s="25">
         <v>40000</v>
@@ -5617,7 +5723,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="E7" s="25">
         <v>60000</v>
@@ -5625,7 +5731,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E8" s="25">
         <v>75000</v>
@@ -5633,13 +5739,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B10" s="26">
         <v>650000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="E10" s="26">
         <v>650000</v>
@@ -5647,9 +5753,9 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B11" s="36">
+        <v>371</v>
+      </c>
+      <c r="B11" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5670,7 +5776,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5774,22 +5880,57 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>79</v>
+      <c r="B23" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5815,7 +5956,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5825,7 +5966,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5835,7 +5976,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5843,24 +5984,24 @@
         <v>67</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B6" s="25">
         <v>1288333</v>
@@ -5880,7 +6021,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B7" s="25">
         <v>1621256</v>
@@ -5900,7 +6041,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B8" s="26">
         <v>-332923</v>
@@ -5920,7 +6061,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B9" s="24">
         <v>-0.2584133416981985</v>
@@ -5940,27 +6081,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="43">
+        <v>344</v>
+      </c>
+      <c r="B10" s="46">
         <v>-5.68</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="46">
         <v>8.19</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="46">
         <v>28.03</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="46">
         <v>44</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="46">
         <v>50.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B11" s="22">
         <v>174</v>
@@ -5980,7 +6121,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5990,7 +6131,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5998,24 +6139,24 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B16" s="25">
         <v>966250</v>
@@ -6035,7 +6176,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B17" s="25">
         <v>1621256</v>
@@ -6055,7 +6196,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B18" s="26">
         <v>-655006</v>
@@ -6075,7 +6216,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B19" s="24">
         <v>-0.677884455597598</v>
@@ -6095,27 +6236,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B20" s="43">
+        <v>344</v>
+      </c>
+      <c r="B20" s="46">
         <v>-12.15</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="46">
         <v>-4.68</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="46">
         <v>8.49</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="46">
         <v>19.03</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="46">
         <v>23.13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B21" s="22">
         <v>230</v>
@@ -6135,7 +6276,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6145,7 +6286,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,24 +6294,24 @@
         <v>67</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B26" s="25">
         <v>1223917</v>
@@ -6190,7 +6331,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B27" s="25">
         <v>1621256</v>
@@ -6210,7 +6351,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B28" s="26">
         <v>-397339</v>
@@ -6230,7 +6371,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B29" s="24">
         <v>-0.3246456228402091</v>
@@ -6250,27 +6391,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B30" s="43">
+        <v>344</v>
+      </c>
+      <c r="B30" s="46">
         <v>-6.97</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="46">
         <v>5.62</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="46">
         <v>24.12</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="46">
         <v>39.01</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="46">
         <v>45.04</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B31" s="22">
         <v>191</v>
@@ -6290,7 +6431,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6300,7 +6441,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6308,24 +6449,24 @@
         <v>67</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B36" s="25">
         <v>1288333</v>
@@ -6345,7 +6486,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B37" s="25">
         <v>1667756</v>
@@ -6365,7 +6506,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B38" s="26">
         <v>-379423</v>
@@ -6385,7 +6526,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B39" s="24">
         <v>-0.2945064852945763</v>
@@ -6405,27 +6546,27 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B40" s="43">
+        <v>344</v>
+      </c>
+      <c r="B40" s="46">
         <v>-6.62</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="46">
         <v>6.39</v>
       </c>
-      <c r="D40" s="43">
+      <c r="D40" s="46">
         <v>25.34</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="46">
         <v>40.6</v>
       </c>
-      <c r="F40" s="43">
+      <c r="F40" s="46">
         <v>46.79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B41" s="22">
         <v>186</v>
@@ -6471,7 +6612,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6483,7 +6624,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6497,7 +6638,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6505,7 +6646,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6529,7 +6670,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6537,7 +6678,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6557,25 +6698,25 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>94</v>
+      <c r="D12" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D13" s="25">
         <v>1288333</v>
@@ -6595,7 +6736,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D14" s="25">
         <v>1621256</v>
@@ -6615,7 +6756,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D15" s="25">
         <v>-447923</v>
@@ -6635,7 +6776,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D16" s="25">
         <v>-190250</v>
@@ -6655,7 +6796,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D17" s="25">
         <v>478361</v>
@@ -6675,7 +6816,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6695,25 +6836,25 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>94</v>
+      <c r="D20" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D21" s="24">
         <v>-0.34767595489354136</v>
@@ -6733,27 +6874,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D22" s="43">
+        <v>344</v>
+      </c>
+      <c r="D22" s="46">
         <v>-5.68</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="46">
         <v>8.19</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="46">
         <v>28.03</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="46">
         <v>44</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="46">
         <v>50.52</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D23" s="24">
         <v>0.3</v>
@@ -6773,7 +6914,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D24" s="22">
         <v>120</v>
@@ -6793,7 +6934,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6831,7 +6972,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6842,12 +6983,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6890,10 +7031,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6914,7 +7055,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -6922,7 +7063,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="14">
         <v>400</v>
@@ -6930,7 +7071,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6944,24 +7085,24 @@
         <v>67</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" s="16">
         <v>120</v>
@@ -6981,7 +7122,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6992,30 +7133,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>9500</v>
@@ -7026,13 +7167,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>800</v>
@@ -7043,13 +7184,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>1200</v>
@@ -7060,13 +7201,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D24" s="17">
         <v>100000</v>
@@ -7077,13 +7218,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D25" s="17">
         <v>30000</v>
@@ -7094,13 +7235,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D26" s="17">
         <v>300</v>
@@ -7111,7 +7252,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7122,36 +7263,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -7168,13 +7309,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -7191,13 +7332,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D32" s="19">
         <v>1</v>
@@ -7214,13 +7355,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D33" s="19">
         <v>6</v>
@@ -7237,13 +7378,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
@@ -7260,13 +7401,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="D35" s="19">
         <v>3</v>
@@ -7283,13 +7424,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D36" s="19">
         <v>1</v>
@@ -7306,13 +7447,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D37" s="19">
         <v>2</v>
@@ -7329,13 +7470,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D38" s="19">
         <v>1</v>
@@ -7352,7 +7493,7 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -7363,30 +7504,30 @@
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D42" s="17">
         <v>18000</v>
@@ -7397,13 +7538,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D43" s="17">
         <v>2500</v>
@@ -7414,13 +7555,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D44" s="17">
         <v>18000</v>
@@ -7431,13 +7572,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D45" s="17">
         <v>1500</v>
@@ -7448,13 +7589,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D46" s="17">
         <v>700</v>
@@ -7465,13 +7606,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D47" s="17">
         <v>500</v>
@@ -7482,13 +7623,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D48" s="17">
         <v>25000</v>
@@ -7499,13 +7640,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D49" s="17">
         <v>15000</v>
@@ -7516,13 +7657,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D50" s="17">
         <v>20000</v>
@@ -7533,13 +7674,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D51" s="17">
         <v>800</v>
@@ -7550,13 +7691,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D52" s="17">
         <v>600</v>
@@ -7567,7 +7708,7 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -7578,27 +7719,27 @@
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C55" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>117</v>
-      </c>
       <c r="E55" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C56" s="17">
         <v>500000</v>
@@ -7612,10 +7753,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C57" s="17">
         <v>75000</v>
@@ -7629,10 +7770,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C58" s="17">
         <v>40000</v>
@@ -7646,7 +7787,7 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -7657,29 +7798,29 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B61" s="18">
         <v>0.03</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B62" s="18">
         <v>0.03</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B63" s="19">
         <v>0.8333333333333334</v>
@@ -7687,7 +7828,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B64" s="17">
         <v>0</v>
@@ -7695,10 +7836,10 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -7733,10 +7874,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7757,10 +7898,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7773,7 +7914,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7781,66 +7922,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -7883,24 +8024,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7910,7 +8051,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B6" s="21">
         <v>120</v>
@@ -7930,7 +8071,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B7" s="22">
         <v>400</v>
@@ -7938,7 +8079,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B8" s="23">
         <v>0.3</v>
@@ -7958,10 +8099,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C10" s="24">
         <v>0.6666666666666666</v>
@@ -8002,7 +8143,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8015,24 +8156,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8042,7 +8183,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B5" s="25">
         <v>1140000</v>
@@ -8062,7 +8203,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B6" s="25">
         <v>96000</v>
@@ -8082,7 +8223,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B7" s="25">
         <v>144000</v>
@@ -8102,7 +8243,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B8" s="25">
         <v>100000</v>
@@ -8122,7 +8263,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B9" s="25">
         <v>30000</v>
@@ -8142,7 +8283,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B10" s="25">
         <v>36000</v>
@@ -8162,7 +8303,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B11" s="26">
         <f>SUM(B5:B10)</f>
@@ -8226,33 +8367,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C4" s="27">
         <v>1</v>
@@ -8272,10 +8413,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
@@ -8295,10 +8436,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C6" s="27">
         <v>1</v>
@@ -8318,10 +8459,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C7" s="27">
         <v>6</v>
@@ -8341,10 +8482,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C8" s="27">
         <v>1</v>
@@ -8364,10 +8505,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C9" s="27">
         <v>3</v>
@@ -8387,10 +8528,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C10" s="27">
         <v>1</v>
@@ -8410,10 +8551,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C11" s="27">
         <v>2</v>
@@ -8433,10 +8574,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C12" s="27">
         <v>1</v>
@@ -8456,7 +8597,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -8470,24 +8611,24 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B16" s="26">
         <v>1026431</v>
@@ -8507,7 +8648,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B17" s="24">
         <v>0.6639270698576973</v>
@@ -8527,7 +8668,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B18" s="29">
         <v>7.1</v>
@@ -8571,7 +8712,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8584,24 +8725,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8611,7 +8752,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B5" s="25">
         <v>84000</v>
@@ -8631,7 +8772,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -8656,7 +8797,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8666,7 +8807,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B8" s="25">
         <v>60000</v>
@@ -8686,7 +8827,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -8711,7 +8852,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8721,7 +8862,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B11" s="25">
         <v>216000</v>
@@ -8741,7 +8882,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B12" s="25">
         <v>30000</v>
@@ -8761,7 +8902,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B13" s="25">
         <v>18000</v>
@@ -8781,7 +8922,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B14" s="25">
         <v>18000</v>
@@ -8801,7 +8942,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B15" s="30">
         <f>SUM(B11:B14)</f>
@@ -8826,7 +8967,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -8836,7 +8977,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B17" s="25">
         <v>25000</v>
@@ -8856,7 +8997,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B18" s="25">
         <v>15000</v>
@@ -8876,7 +9017,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B19" s="25">
         <v>20000</v>
@@ -8896,7 +9037,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B20" s="25">
         <v>96000</v>
@@ -8916,7 +9057,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B21" s="25">
         <v>72000</v>
@@ -8936,7 +9077,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B17:B21)</f>
@@ -8961,7 +9102,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B24" s="26">
         <f>B6+B9+B15+B22</f>
@@ -9011,7 +9152,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -9021,30 +9162,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>117</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C4" s="17">
         <v>500000</v>
@@ -9061,10 +9202,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C5" s="17">
         <v>75000</v>
@@ -9081,10 +9222,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C6" s="17">
         <v>40000</v>
@@ -9101,7 +9242,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F8" s="26">
         <v>49825</v>
@@ -9109,7 +9250,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F9" s="30">
         <v>500000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -4044,6 +4044,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="30">
+        <f>SUM(B4:M4)</f>
         <v>1546000</v>
       </c>
     </row>
@@ -4106,6 +4107,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="25">
+        <f>SUM(B7:M7)</f>
         <v>1026431</v>
       </c>
     </row>
@@ -4150,6 +4152,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="25">
+        <f>SUM(B8:M8)</f>
         <v>545000</v>
       </c>
     </row>
@@ -4194,6 +4197,7 @@
         <v>13735</v>
       </c>
       <c r="N9" s="25">
+        <f>SUM(B9:M9)</f>
         <v>164825</v>
       </c>
     </row>
@@ -4220,42 +4224,55 @@
         <v>283</v>
       </c>
       <c r="B12" s="28">
+        <f>B7+B8+B9</f>
         <v>170878</v>
       </c>
       <c r="C12" s="28">
+        <f>C7+C8+C9</f>
         <v>170878</v>
       </c>
       <c r="D12" s="28">
+        <f>D7+D8+D9</f>
         <v>170878</v>
       </c>
       <c r="E12" s="28">
+        <f>E7+E8+E9</f>
         <v>170878</v>
       </c>
       <c r="F12" s="28">
+        <f>F7+F8+F9</f>
         <v>170878</v>
       </c>
       <c r="G12" s="28">
+        <f>G7+G8+G9</f>
         <v>170878</v>
       </c>
       <c r="H12" s="28">
+        <f>H7+H8+H9</f>
         <v>170878</v>
       </c>
       <c r="I12" s="28">
+        <f>I7+I8+I9</f>
         <v>170878</v>
       </c>
       <c r="J12" s="28">
+        <f>J7+J8+J9</f>
         <v>170878</v>
       </c>
       <c r="K12" s="28">
+        <f>K7+K8+K9</f>
         <v>170878</v>
       </c>
       <c r="L12" s="28">
+        <f>L7+L8+L9</f>
         <v>13735</v>
       </c>
       <c r="M12" s="28">
+        <f>M7+M8+M9</f>
         <v>13735</v>
       </c>
       <c r="N12" s="28">
+        <f>SUM(B12:M12)</f>
         <v>1736250</v>
       </c>
     </row>
@@ -4264,42 +4281,55 @@
         <v>308</v>
       </c>
       <c r="B13" s="28">
+        <f>B4-B12</f>
         <v>-16278</v>
       </c>
       <c r="C13" s="28">
+        <f>C4-C12</f>
         <v>-16278</v>
       </c>
       <c r="D13" s="28">
+        <f>D4-D12</f>
         <v>-16278</v>
       </c>
       <c r="E13" s="28">
+        <f>E4-E12</f>
         <v>-16278</v>
       </c>
       <c r="F13" s="28">
+        <f>F4-F12</f>
         <v>-16278</v>
       </c>
       <c r="G13" s="28">
+        <f>G4-G12</f>
         <v>-16278</v>
       </c>
       <c r="H13" s="28">
+        <f>H4-H12</f>
         <v>-16278</v>
       </c>
       <c r="I13" s="28">
+        <f>I4-I12</f>
         <v>-16278</v>
       </c>
       <c r="J13" s="28">
+        <f>J4-J12</f>
         <v>-16278</v>
       </c>
       <c r="K13" s="28">
+        <f>K4-K12</f>
         <v>-16278</v>
       </c>
       <c r="L13" s="28">
+        <f>L4-L12</f>
         <v>-13735</v>
       </c>
       <c r="M13" s="28">
+        <f>M4-M12</f>
         <v>-13735</v>
       </c>
       <c r="N13" s="28">
+        <f>SUM(B13:M13)</f>
         <v>-190250</v>
       </c>
     </row>
@@ -4308,42 +4338,55 @@
         <v>309</v>
       </c>
       <c r="B14" s="33">
+        <f>B17+B13</f>
         <v>-16278</v>
       </c>
       <c r="C14" s="33">
+        <f>B14+C13</f>
         <v>-32556</v>
       </c>
       <c r="D14" s="33">
+        <f>C14+D13</f>
         <v>-48834</v>
       </c>
       <c r="E14" s="33">
+        <f>D14+E13</f>
         <v>-65112</v>
       </c>
       <c r="F14" s="33">
+        <f>E14+F13</f>
         <v>-81390</v>
       </c>
       <c r="G14" s="33">
+        <f>F14+G13</f>
         <v>-97668</v>
       </c>
       <c r="H14" s="33">
+        <f>G14+H13</f>
         <v>-113946</v>
       </c>
       <c r="I14" s="33">
+        <f>H14+I13</f>
         <v>-130224</v>
       </c>
       <c r="J14" s="33">
+        <f>I14+J13</f>
         <v>-146502</v>
       </c>
       <c r="K14" s="33">
+        <f>J14+K13</f>
         <v>-162780</v>
       </c>
       <c r="L14" s="33">
+        <f>K14+L13</f>
         <v>-176515</v>
       </c>
       <c r="M14" s="33">
+        <f>L14+M13</f>
         <v>-190250</v>
       </c>
       <c r="N14" s="26">
+        <f>M14</f>
         <v>-190250</v>
       </c>
     </row>
@@ -4358,7 +4401,7 @@
       <c r="A17" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="17">
         <v>0</v>
       </c>
     </row>
@@ -4367,6 +4410,7 @@
         <v>311</v>
       </c>
       <c r="B18" s="33">
+        <f>M14</f>
         <v>-190250</v>
       </c>
     </row>
@@ -4375,6 +4419,7 @@
         <v>312</v>
       </c>
       <c r="B19" s="25">
+        <f>MIN(B14:M14)</f>
         <v>-190250</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -4965,18 +4965,23 @@
         <v>328</v>
       </c>
       <c r="B5" s="38">
+        <f>'Monthly Cash Flow Y1'!M14</f>
         <v>-190250</v>
       </c>
       <c r="C5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>128096</v>
       </c>
       <c r="D5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1434716</v>
       </c>
       <c r="E5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>3552210</v>
       </c>
       <c r="F5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>5999341</v>
       </c>
     </row>
@@ -5045,18 +5050,23 @@
         <v>332</v>
       </c>
       <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
         <v>-190250</v>
       </c>
       <c r="C9" s="30">
+        <f>SUM(C5:C8)</f>
         <v>128096</v>
       </c>
       <c r="D9" s="30">
+        <f>SUM(D5:D8)</f>
         <v>1434716</v>
       </c>
       <c r="E9" s="30">
+        <f>SUM(E5:E8)</f>
         <v>3552210</v>
       </c>
       <c r="F9" s="30">
+        <f>SUM(F5:F8)</f>
         <v>5999341</v>
       </c>
     </row>
@@ -5095,18 +5105,23 @@
         <v>335</v>
       </c>
       <c r="B13" s="25">
+        <f>'Debt Schedule'!B13</f>
         <v>478361</v>
       </c>
       <c r="C13" s="25">
+        <f>'Debt Schedule'!C13</f>
         <v>455444</v>
       </c>
       <c r="D13" s="25">
+        <f>'Debt Schedule'!D13</f>
         <v>431175</v>
       </c>
       <c r="E13" s="25">
+        <f>'Debt Schedule'!E13</f>
         <v>405473</v>
       </c>
       <c r="F13" s="25">
+        <f>'Debt Schedule'!F13</f>
         <v>378253</v>
       </c>
     </row>
@@ -5115,18 +5130,23 @@
         <v>336</v>
       </c>
       <c r="B14" s="30">
+        <f>SUM(B12:B13)</f>
         <v>478361</v>
       </c>
       <c r="C14" s="30">
+        <f>SUM(C12:C13)</f>
         <v>455444</v>
       </c>
       <c r="D14" s="30">
+        <f>SUM(D12:D13)</f>
         <v>431175</v>
       </c>
       <c r="E14" s="30">
+        <f>SUM(E12:E13)</f>
         <v>405473</v>
       </c>
       <c r="F14" s="30">
+        <f>SUM(F12:F13)</f>
         <v>378253</v>
       </c>
     </row>
@@ -5145,18 +5165,23 @@
         <v>338</v>
       </c>
       <c r="B17" s="26">
+        <f>B9-B14</f>
         <v>-668611</v>
       </c>
       <c r="C17" s="26">
+        <f>C9-C14</f>
         <v>-327348</v>
       </c>
       <c r="D17" s="26">
+        <f>D9-D14</f>
         <v>1003541</v>
       </c>
       <c r="E17" s="26">
+        <f>E9-E14</f>
         <v>3146738</v>
       </c>
       <c r="F17" s="26">
+        <f>F9-F14</f>
         <v>5621089</v>
       </c>
     </row>
@@ -5164,19 +5189,24 @@
       <c r="A19" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="39" t="str">
+        <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="39" t="str">
+        <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="39" t="str">
+        <f>D9-D14-D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="40">
+        <f>E9-E14-E17</f>
         <v>-1</v>
       </c>
       <c r="F19" s="40">
+        <f>F9-F14-F17</f>
         <v>-1</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -25,13 +25,14 @@
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="429">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -72,7 +73,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -216,6 +217,12 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>Financial Health</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -225,7 +232,7 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
   </si>
   <si>
     <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
@@ -255,37 +262,28 @@
     <t>Tabs 14-17: Financial statements</t>
   </si>
   <si>
-    <t>Tabs 18-21: Analysis &amp; underwriting</t>
+    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
   </si>
   <si>
     <t>Debt Service Convention</t>
   </si>
   <si>
-    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+    <t>operating expense on the Operating Statement. This is a standard</t>
   </si>
   <si>
     <t>simplification used in school financial underwriting that ensures internal</t>
   </si>
   <si>
-    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
-  </si>
-  <si>
-    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
-  </si>
-  <si>
-    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+    <t>consistency across all tabs.</t>
   </si>
   <si>
     <t>Tips</t>
   </si>
   <si>
-    <t>Review the Budget Summary for a high-level view.</t>
-  </si>
-  <si>
-    <t>Check DSCR &amp; Covenants for lender readiness.</t>
-  </si>
-  <si>
-    <t>The Underwriting Snapshot provides a one-page summary.</t>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -300,7 +298,7 @@
     <t>Civic Scholars Charter - Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1204,6 +1202,123 @@
   </si>
   <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 25% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 50.52x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>24.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1332,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1283,6 +1398,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -1306,8 +1426,32 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1321,7 +1465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1332,6 +1476,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1377,7 +1526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1398,15 +1547,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1425,19 +1574,56 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1782,7 +1968,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C42"/>
+  <dimension ref="B3:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2040,18 +2226,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Cover'!A1"/>
@@ -2075,6 +2269,7 @@
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2098,7 +2293,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2108,27 +2303,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="31">
         <v>120</v>
@@ -2148,7 +2343,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2158,7 +2353,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="25">
         <v>1140000</v>
@@ -2178,7 +2373,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="25">
         <v>96000</v>
@@ -2198,7 +2393,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="25">
         <v>144000</v>
@@ -2218,7 +2413,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="25">
         <v>100000</v>
@@ -2238,7 +2433,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="25">
         <v>30000</v>
@@ -2258,7 +2453,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12" s="25">
         <v>36000</v>
@@ -2278,7 +2473,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B13" s="26">
         <f>SUM(B7:B12)</f>
@@ -2303,7 +2498,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" s="25">
         <v>12883</v>
@@ -2347,7 +2542,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2357,27 +2552,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2387,7 +2582,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B5" s="25">
         <v>352690</v>
@@ -2407,7 +2602,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B6" s="25">
         <v>62173</v>
@@ -2427,7 +2622,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="25">
         <v>95738</v>
@@ -2447,7 +2642,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -2472,7 +2667,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2482,7 +2677,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B10" s="25">
         <v>124346</v>
@@ -2502,7 +2697,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B11" s="25">
         <v>101738</v>
@@ -2522,7 +2717,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B12" s="25">
         <v>81390</v>
@@ -2542,7 +2737,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
@@ -2567,7 +2762,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2577,7 +2772,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B15" s="25">
         <v>62173</v>
@@ -2597,7 +2792,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
@@ -2622,7 +2817,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2632,7 +2827,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -2652,7 +2847,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
@@ -2677,7 +2872,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2687,7 +2882,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -2707,7 +2902,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B21:B21)</f>
@@ -2732,7 +2927,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" s="26">
         <f>B8+B13+B16+B19+B22</f>
@@ -2781,7 +2976,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2791,27 +2986,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2821,7 +3016,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B5" s="25">
         <v>950000</v>
@@ -2841,7 +3036,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B6" s="25">
         <v>80000</v>
@@ -2861,7 +3056,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B7" s="25">
         <v>120000</v>
@@ -2881,7 +3076,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B8" s="25">
         <v>83333</v>
@@ -2901,7 +3096,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B9" s="25">
         <v>25000</v>
@@ -2921,7 +3116,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B10" s="25">
         <v>30000</v>
@@ -2941,7 +3136,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
@@ -2966,7 +3161,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2976,7 +3171,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B14" s="25">
         <v>124346</v>
@@ -2996,7 +3191,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B15" s="25">
         <v>101738</v>
@@ -3016,7 +3211,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B16" s="25">
         <v>81390</v>
@@ -3036,7 +3231,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B17" s="25">
         <v>352690</v>
@@ -3056,7 +3251,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B18" s="25">
         <v>62173</v>
@@ -3076,7 +3271,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B19" s="25">
         <v>95738</v>
@@ -3096,7 +3291,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B20" s="25">
         <v>62173</v>
@@ -3116,7 +3311,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B21" s="25">
         <v>84012</v>
@@ -3136,7 +3331,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" s="25">
         <v>62173</v>
@@ -3156,7 +3351,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" s="30">
         <f>SUM(B14:B22)</f>
@@ -3181,7 +3376,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -3191,12 +3386,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B27" s="25">
         <v>70000</v>
@@ -3216,12 +3411,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B29" s="25">
         <v>50000</v>
@@ -3241,12 +3436,12 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B31" s="25">
         <v>180000</v>
@@ -3266,7 +3461,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" s="25">
         <v>25000</v>
@@ -3286,7 +3481,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B33" s="25">
         <v>15000</v>
@@ -3306,7 +3501,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B34" s="25">
         <v>15000</v>
@@ -3326,7 +3521,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B35" s="30">
         <f>SUM(B31:B34)</f>
@@ -3351,12 +3546,12 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B37" s="25">
         <v>20833</v>
@@ -3376,7 +3571,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B38" s="25">
         <v>12500</v>
@@ -3396,7 +3591,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B39" s="25">
         <v>16667</v>
@@ -3416,7 +3611,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B40" s="25">
         <v>80000</v>
@@ -3436,7 +3631,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B41" s="25">
         <v>60000</v>
@@ -3456,7 +3651,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B42" s="30">
         <f>SUM(B37:B41)</f>
@@ -3481,7 +3676,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B43" s="30">
         <f>B27+B29+B35+B42</f>
@@ -3506,7 +3701,7 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -3516,7 +3711,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B46" s="25">
         <v>49825</v>
@@ -3536,7 +3731,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B47" s="25">
         <v>75000</v>
@@ -3556,7 +3751,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B48" s="25">
         <v>40000</v>
@@ -3576,7 +3771,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B49" s="30">
         <f>SUM(B46:B48)</f>
@@ -3625,7 +3820,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3635,27 +3830,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="28">
         <f>'Budget Detail'!B11</f>
@@ -3680,7 +3875,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="28">
         <f>'Budget Detail'!B23</f>
@@ -3705,7 +3900,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B6" s="28">
         <f>'Budget Detail'!B43</f>
@@ -3730,7 +3925,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7" s="28">
         <f>'Budget Detail'!B49</f>
@@ -3755,7 +3950,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -3780,7 +3975,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3790,7 +3985,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
@@ -3815,7 +4010,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3840,7 +4035,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B13" s="25">
         <v>-447923</v>
@@ -3860,7 +4055,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B14" s="25">
         <v>10736</v>
@@ -3880,7 +4075,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B15" s="25">
         <v>14469</v>
@@ -3925,7 +4120,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3943,51 +4138,51 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4005,7 +4200,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="30">
         <v>154600</v>
@@ -4050,7 +4245,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4068,7 +4263,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B7" s="25">
         <v>102643</v>
@@ -4113,7 +4308,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B8" s="25">
         <v>54500</v>
@@ -4158,7 +4353,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B9" s="25">
         <v>13735</v>
@@ -4203,7 +4398,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4221,7 +4416,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B12" s="28">
         <f>B7+B8+B9</f>
@@ -4278,7 +4473,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B13" s="28">
         <f>B4-B12</f>
@@ -4335,7 +4530,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B14" s="33">
         <f>B17+B13</f>
@@ -4392,14 +4587,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B17" s="17">
         <v>0</v>
@@ -4407,7 +4602,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B18" s="33">
         <f>M14</f>
@@ -4416,7 +4611,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B19" s="25">
         <f>MIN(B14:M14)</f>
@@ -4449,7 +4644,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4459,27 +4654,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4489,7 +4684,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -4509,7 +4704,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4519,7 +4714,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B8" s="28">
         <v>1026431</v>
@@ -4539,7 +4734,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B9" s="28">
         <v>545000</v>
@@ -4559,7 +4754,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B10" s="28">
         <v>164825</v>
@@ -4579,7 +4774,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -4604,7 +4799,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4614,7 +4809,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
@@ -4639,7 +4834,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4698,27 +4893,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4728,24 +4923,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>319</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B6" s="17">
         <v>500000</v>
@@ -4763,7 +4958,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -4773,7 +4968,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B9" s="25">
         <f>B6</f>
@@ -4798,7 +4993,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B10" s="25">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4823,7 +5018,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B11" s="25">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4848,7 +5043,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B12" s="28">
         <f>B10+B11</f>
@@ -4873,7 +5068,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B13" s="33">
         <f>MAX(0,B9-B11)</f>
@@ -4922,7 +5117,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4932,27 +5127,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4962,7 +5157,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B5" s="38">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4987,7 +5182,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -5007,7 +5202,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B7" s="25">
         <v>0</v>
@@ -5027,7 +5222,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -5047,7 +5242,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
@@ -5072,7 +5267,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5082,7 +5277,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -5102,7 +5297,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B13" s="25">
         <f>'Debt Schedule'!B13</f>
@@ -5127,7 +5322,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B14" s="30">
         <f>SUM(B12:B13)</f>
@@ -5152,7 +5347,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -5162,7 +5357,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B17" s="26">
         <f>B9-B14</f>
@@ -5187,7 +5382,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" s="39" t="str">
         <f>B9-B14-B17</f>
@@ -5236,7 +5431,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5246,27 +5441,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5276,7 +5471,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B5" s="25">
         <v>1288333</v>
@@ -5296,7 +5491,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B6" s="25">
         <v>1026431</v>
@@ -5316,7 +5511,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B7" s="25">
         <v>545000</v>
@@ -5336,7 +5531,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
@@ -5361,7 +5556,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B9" s="25">
         <v>49825</v>
@@ -5381,7 +5576,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B10" s="41">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5406,7 +5601,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5416,7 +5611,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B13" s="25">
         <v>-190250</v>
@@ -5436,7 +5631,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5461,7 +5656,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5486,7 +5681,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B16" s="24">
         <v>0.3</v>
@@ -5506,7 +5701,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5516,7 +5711,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="25">
         <v>10736</v>
@@ -5536,7 +5731,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B20" s="25">
         <v>1076256</v>
@@ -5556,7 +5751,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B21" s="25">
         <v>4542</v>
@@ -5576,7 +5771,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B22" s="42">
         <v>174</v>
@@ -5596,7 +5791,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5606,102 +5801,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B25" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="C25" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C25" s="44" t="s">
-        <v>356</v>
-      </c>
       <c r="D25" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B26" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C26" s="44" t="s">
-        <v>356</v>
-      </c>
       <c r="D26" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B28" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="D28" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="E28" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="D28" s="44" t="s">
-        <v>356</v>
-      </c>
-      <c r="E28" s="44" t="s">
-        <v>356</v>
-      </c>
       <c r="F28" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B29" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="D29" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="E29" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="D29" s="44" t="s">
-        <v>356</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>356</v>
-      </c>
       <c r="F29" s="44" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -5742,27 +5937,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="45" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>362</v>
-      </c>
       <c r="E3" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B4" s="25">
         <v>500000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E4" s="25">
         <v>400000</v>
@@ -5770,13 +5965,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" s="25">
         <v>100000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E5" s="25">
         <v>75000</v>
@@ -5784,13 +5979,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B6" s="25">
         <v>50000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E6" s="25">
         <v>40000</v>
@@ -5798,7 +5993,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E7" s="25">
         <v>60000</v>
@@ -5806,7 +6001,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E8" s="25">
         <v>75000</v>
@@ -5814,13 +6009,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B10" s="26">
         <v>650000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E10" s="26">
         <v>650000</v>
@@ -5828,7 +6023,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B11" s="39">
         <v>0</v>
@@ -5851,7 +6046,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5860,152 +6055,137 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>80</v>
+      <c r="B23" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>81</v>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>83</v>
+      <c r="B27" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -6031,7 +6211,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6041,7 +6221,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -6051,32 +6231,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B6" s="25">
         <v>1288333</v>
@@ -6096,7 +6276,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B7" s="25">
         <v>1621256</v>
@@ -6116,7 +6296,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B8" s="26">
         <v>-332923</v>
@@ -6136,7 +6316,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B9" s="24">
         <v>-0.2584133416981985</v>
@@ -6156,7 +6336,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B10" s="46">
         <v>-5.68</v>
@@ -6176,7 +6356,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B11" s="22">
         <v>174</v>
@@ -6196,7 +6376,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -6206,32 +6386,32 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B16" s="25">
         <v>966250</v>
@@ -6251,7 +6431,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B17" s="25">
         <v>1621256</v>
@@ -6271,7 +6451,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B18" s="26">
         <v>-655006</v>
@@ -6291,7 +6471,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B19" s="24">
         <v>-0.677884455597598</v>
@@ -6311,7 +6491,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B20" s="46">
         <v>-12.15</v>
@@ -6331,7 +6511,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B21" s="22">
         <v>230</v>
@@ -6351,7 +6531,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6361,32 +6541,32 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B26" s="25">
         <v>1223917</v>
@@ -6406,7 +6586,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B27" s="25">
         <v>1621256</v>
@@ -6426,7 +6606,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B28" s="26">
         <v>-397339</v>
@@ -6446,7 +6626,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B29" s="24">
         <v>-0.3246456228402091</v>
@@ -6466,7 +6646,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B30" s="46">
         <v>-6.97</v>
@@ -6486,7 +6666,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B31" s="22">
         <v>191</v>
@@ -6506,7 +6686,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6516,32 +6696,32 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="D35" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="E35" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="F35" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B36" s="25">
         <v>1288333</v>
@@ -6561,7 +6741,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B37" s="25">
         <v>1667756</v>
@@ -6581,7 +6761,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B38" s="26">
         <v>-379423</v>
@@ -6601,7 +6781,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B39" s="24">
         <v>-0.2945064852945763</v>
@@ -6621,7 +6801,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" s="46">
         <v>-6.62</v>
@@ -6641,7 +6821,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B41" s="22">
         <v>186</v>
@@ -6687,7 +6867,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6699,7 +6879,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6713,7 +6893,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6721,7 +6901,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6745,7 +6925,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6753,7 +6933,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6765,33 +6945,33 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="F12" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D13" s="25">
         <v>1288333</v>
@@ -6811,7 +6991,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D14" s="25">
         <v>1621256</v>
@@ -6831,7 +7011,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D15" s="25">
         <v>-447923</v>
@@ -6851,7 +7031,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D16" s="25">
         <v>-190250</v>
@@ -6871,7 +7051,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D17" s="25">
         <v>478361</v>
@@ -6891,7 +7071,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6903,33 +7083,33 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="F20" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="G20" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="H20" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D21" s="24">
         <v>-0.34767595489354136</v>
@@ -6949,7 +7129,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D22" s="46">
         <v>-5.68</v>
@@ -6969,7 +7149,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="24">
         <v>0.3</v>
@@ -6989,7 +7169,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D24" s="22">
         <v>120</v>
@@ -7009,7 +7189,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7023,6 +7203,399 @@
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="48" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>395</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="G5" s="49" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C6" s="50">
+        <v>120</v>
+      </c>
+      <c r="D6" s="50">
+        <v>200</v>
+      </c>
+      <c r="E6" s="50">
+        <v>300</v>
+      </c>
+      <c r="F6" s="50">
+        <v>375</v>
+      </c>
+      <c r="G6" s="50">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C7" s="51">
+        <v>1288333.3333333335</v>
+      </c>
+      <c r="D7" s="51">
+        <v>2564700</v>
+      </c>
+      <c r="E7" s="51">
+        <v>3893503</v>
+      </c>
+      <c r="F7" s="51">
+        <v>4977371.484999999</v>
+      </c>
+      <c r="G7" s="51">
+        <v>5458717.7285</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="51">
+        <v>1026431.25</v>
+      </c>
+      <c r="D8" s="51">
+        <v>1268669.0250000001</v>
+      </c>
+      <c r="E8" s="51">
+        <v>1306729.0957499999</v>
+      </c>
+      <c r="F8" s="51">
+        <v>1345930.9686225</v>
+      </c>
+      <c r="G8" s="51">
+        <v>1386308.8976811753</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="51">
+        <v>545000</v>
+      </c>
+      <c r="D9" s="51">
+        <v>887860</v>
+      </c>
+      <c r="E9" s="51">
+        <v>1190329.8</v>
+      </c>
+      <c r="F9" s="51">
+        <v>1439121.459</v>
+      </c>
+      <c r="G9" s="51">
+        <v>1555453.1754200002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="51">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="D10" s="51">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="E10" s="51">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="F10" s="51">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="G10" s="51">
+        <v>49824.605221179416</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C11" s="52">
+        <v>-447922.5218878458</v>
+      </c>
+      <c r="D11" s="53">
+        <v>318346.3697788203</v>
+      </c>
+      <c r="E11" s="53">
+        <v>1306619.4990288205</v>
+      </c>
+      <c r="F11" s="53">
+        <v>2117494.45215632</v>
+      </c>
+      <c r="G11" s="53">
+        <v>2447131.0501776454</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="52">
+        <v>-190250</v>
+      </c>
+      <c r="D12" s="53">
+        <v>128096.36977882031</v>
+      </c>
+      <c r="E12" s="53">
+        <v>1434715.8688076409</v>
+      </c>
+      <c r="F12" s="53">
+        <v>3552210.320963961</v>
+      </c>
+      <c r="G12" s="53">
+        <v>5999341.371141607</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13" s="54">
+        <v>-0.34767595489354136</v>
+      </c>
+      <c r="D13" s="55">
+        <v>0.12412616281780338</v>
+      </c>
+      <c r="E13" s="55">
+        <v>0.33558969879535744</v>
+      </c>
+      <c r="F13" s="55">
+        <v>0.42542423416409325</v>
+      </c>
+      <c r="G13" s="55">
+        <v>0.44829778198663</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>405</v>
+      </c>
+      <c r="E16" s="57"/>
+      <c r="F16" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="G16" s="58"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="35" t="s">
+        <v>407</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>408</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>409</v>
+      </c>
+      <c r="E17" s="57"/>
+      <c r="F17" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="G17" s="58"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="E18" s="57"/>
+      <c r="F18" s="58" t="s">
+        <v>413</v>
+      </c>
+      <c r="G18" s="58"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>415</v>
+      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="58" t="s">
+        <v>416</v>
+      </c>
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="35" t="s">
+        <v>417</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>418</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="G20" s="58"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>421</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="58" t="s">
+        <v>422</v>
+      </c>
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>424</v>
+      </c>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58" t="s">
+        <v>425</v>
+      </c>
+      <c r="G22" s="58"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="60" t="s">
+        <v>428</v>
+      </c>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -7047,7 +7620,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7058,12 +7631,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7106,10 +7679,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7130,7 +7703,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -7138,7 +7711,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="14">
         <v>400</v>
@@ -7146,7 +7719,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7157,27 +7730,27 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>120</v>
@@ -7197,7 +7770,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -7208,30 +7781,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>9500</v>
@@ -7242,13 +7815,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>800</v>
@@ -7259,13 +7832,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>1200</v>
@@ -7276,13 +7849,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="D24" s="17">
         <v>100000</v>
@@ -7293,13 +7866,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="D25" s="17">
         <v>30000</v>
@@ -7310,13 +7883,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="17">
         <v>300</v>
@@ -7327,7 +7900,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -7338,36 +7911,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="F29" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="G29" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -7384,13 +7957,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -7407,13 +7980,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D32" s="19">
         <v>1</v>
@@ -7430,13 +8003,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="C33" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" s="19">
         <v>6</v>
@@ -7453,13 +8026,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
@@ -7476,13 +8049,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D35" s="19">
         <v>3</v>
@@ -7499,13 +8072,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" s="19">
         <v>1</v>
@@ -7522,13 +8095,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="C37" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D37" s="19">
         <v>2</v>
@@ -7545,13 +8118,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="C38" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D38" s="19">
         <v>1</v>
@@ -7568,7 +8141,7 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -7579,30 +8152,30 @@
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="C41" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="E41" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="D42" s="17">
         <v>18000</v>
@@ -7613,13 +8186,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="D43" s="17">
         <v>2500</v>
@@ -7630,13 +8203,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D44" s="17">
         <v>18000</v>
@@ -7647,13 +8220,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="D45" s="17">
         <v>1500</v>
@@ -7664,13 +8237,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="C46" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D46" s="17">
         <v>700</v>
@@ -7681,13 +8254,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="C47" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D47" s="17">
         <v>500</v>
@@ -7698,13 +8271,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="C48" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48" s="17">
         <v>25000</v>
@@ -7715,13 +8288,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D49" s="17">
         <v>15000</v>
@@ -7732,13 +8305,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D50" s="17">
         <v>20000</v>
@@ -7749,13 +8322,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D51" s="17">
         <v>800</v>
@@ -7766,13 +8339,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D52" s="17">
         <v>600</v>
@@ -7783,7 +8356,7 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -7794,27 +8367,27 @@
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="C56" s="17">
         <v>500000</v>
@@ -7828,10 +8401,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="C57" s="17">
         <v>75000</v>
@@ -7845,10 +8418,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C58" s="17">
         <v>40000</v>
@@ -7862,7 +8435,7 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -7873,29 +8446,29 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B61" s="18">
         <v>0.03</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B62" s="18">
         <v>0.03</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B63" s="19">
         <v>0.8333333333333334</v>
@@ -7903,7 +8476,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B64" s="17">
         <v>0</v>
@@ -7911,10 +8484,10 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B65" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -7949,10 +8522,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7973,10 +8546,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7989,7 +8562,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7997,66 +8570,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -8096,27 +8669,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -8126,7 +8699,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="21">
         <v>120</v>
@@ -8146,7 +8719,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="22">
         <v>400</v>
@@ -8154,7 +8727,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" s="23">
         <v>0.3</v>
@@ -8174,10 +8747,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="C10" s="24">
         <v>0.6666666666666666</v>
@@ -8218,7 +8791,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8228,27 +8801,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8258,7 +8831,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="25">
         <v>1140000</v>
@@ -8278,7 +8851,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B6" s="25">
         <v>96000</v>
@@ -8298,7 +8871,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B7" s="25">
         <v>144000</v>
@@ -8318,7 +8891,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8" s="25">
         <v>100000</v>
@@ -8338,7 +8911,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B9" s="25">
         <v>30000</v>
@@ -8358,7 +8931,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B10" s="25">
         <v>36000</v>
@@ -8378,7 +8951,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B11" s="26">
         <f>SUM(B5:B10)</f>
@@ -8442,33 +9015,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>205</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="27">
         <v>1</v>
@@ -8488,10 +9061,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
@@ -8511,10 +9084,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="27">
         <v>1</v>
@@ -8534,10 +9107,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="C7" s="27">
         <v>6</v>
@@ -8557,10 +9130,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="27">
         <v>1</v>
@@ -8580,10 +9153,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="27">
         <v>3</v>
@@ -8603,10 +9176,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="C10" s="27">
         <v>1</v>
@@ -8626,10 +9199,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="C11" s="27">
         <v>2</v>
@@ -8649,10 +9222,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="C12" s="27">
         <v>1</v>
@@ -8672,7 +9245,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -8683,27 +9256,27 @@
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B16" s="26">
         <v>1026431</v>
@@ -8723,7 +9296,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B17" s="24">
         <v>0.6639270698576973</v>
@@ -8743,7 +9316,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B18" s="29">
         <v>7.1</v>
@@ -8787,7 +9360,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8797,27 +9370,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8827,7 +9400,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B5" s="25">
         <v>84000</v>
@@ -8847,7 +9420,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -8872,7 +9445,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8882,7 +9455,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" s="25">
         <v>60000</v>
@@ -8902,7 +9475,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -8927,7 +9500,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8937,7 +9510,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="25">
         <v>216000</v>
@@ -8957,7 +9530,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" s="25">
         <v>30000</v>
@@ -8977,7 +9550,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" s="25">
         <v>18000</v>
@@ -8997,7 +9570,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="25">
         <v>18000</v>
@@ -9017,7 +9590,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" s="30">
         <f>SUM(B11:B14)</f>
@@ -9042,7 +9615,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -9052,7 +9625,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="25">
         <v>25000</v>
@@ -9072,7 +9645,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" s="25">
         <v>15000</v>
@@ -9092,7 +9665,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B19" s="25">
         <v>20000</v>
@@ -9112,7 +9685,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" s="25">
         <v>96000</v>
@@ -9132,7 +9705,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B21" s="25">
         <v>72000</v>
@@ -9152,7 +9725,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" s="30">
         <f>SUM(B17:B21)</f>
@@ -9177,7 +9750,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B24" s="26">
         <f>B6+B9+B15+B22</f>
@@ -9227,7 +9800,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -9237,30 +9810,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="C4" s="17">
         <v>500000</v>
@@ -9277,10 +9850,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="17">
         <v>75000</v>
@@ -9297,10 +9870,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="17">
         <v>40000</v>
@@ -9317,7 +9890,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F8" s="26">
         <v>49825</v>
@@ -9325,7 +9898,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F9" s="30">
         <v>500000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="435">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1229,6 +1229,24 @@
   </si>
   <si>
     <t>Net Income</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1526,7 +1544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1611,6 +1629,14 @@
     <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7217,7 +7243,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7426,176 +7452,302 @@
         <v>0.44829778198663</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="51">
+        <v>10736.111111111113</v>
+      </c>
+      <c r="D14" s="51">
+        <v>12823.5</v>
+      </c>
+      <c r="E14" s="51">
+        <v>12978.343333333334</v>
+      </c>
+      <c r="F14" s="51">
+        <v>13272.990626666666</v>
+      </c>
+      <c r="G14" s="51">
+        <v>13646.794321250001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="54">
+        <v>0.7967124838292367</v>
+      </c>
+      <c r="D15" s="55">
+        <v>0.49466566265060247</v>
+      </c>
+      <c r="E15" s="55">
+        <v>0.3356178474114441</v>
+      </c>
+      <c r="F15" s="55">
+        <v>0.27040998902305163</v>
+      </c>
+      <c r="G15" s="55">
+        <v>0.25396237113402065</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="C16" s="55">
+        <v>0.12690815006468303</v>
+      </c>
+      <c r="D16" s="55">
+        <v>0.10385542168674698</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0.09171662125340599</v>
+      </c>
+      <c r="F16" s="55">
+        <v>0.08673984632272229</v>
+      </c>
+      <c r="G16" s="55">
+        <v>0.08548453608247424</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
+      <c r="C17" s="54">
+        <v>-0.21973965071151344</v>
+      </c>
+      <c r="D17" s="55">
+        <v>0.15914959839357423</v>
+      </c>
+      <c r="E17" s="55">
+        <v>0.3586600817438692</v>
+      </c>
+      <c r="F17" s="55">
+        <v>0.4404571899012074</v>
+      </c>
+      <c r="G17" s="55">
+        <v>0.4610891752577319</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C18" s="56">
+        <v>-5.681889809461599</v>
+      </c>
+      <c r="D18" s="57">
+        <v>8.192156730355682</v>
+      </c>
+      <c r="E18" s="57">
+        <v>28.027198570886025</v>
+      </c>
+      <c r="F18" s="57">
+        <v>44.00073111759629</v>
+      </c>
+      <c r="G18" s="57">
+        <v>50.51631908021458</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
+      <c r="C19" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C20" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="E16" s="57"/>
-      <c r="F16" s="58" t="s">
+      <c r="C22" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="G16" s="58"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
+      <c r="D22" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="35" t="s">
         <v>409</v>
       </c>
-      <c r="E17" s="57"/>
-      <c r="F17" s="58" t="s">
+      <c r="C23" s="60" t="s">
         <v>410</v>
       </c>
-      <c r="G17" s="58"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+      <c r="D23" s="61" t="s">
         <v>411</v>
       </c>
-      <c r="C18" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D18" s="57" t="s">
+      <c r="E23" s="61"/>
+      <c r="F23" s="62" t="s">
         <v>412</v>
       </c>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58" t="s">
+      <c r="G23" s="62"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="35" t="s">
         <v>413</v>
       </c>
-      <c r="G18" s="58"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="35" t="s">
+      <c r="C24" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="C19" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D19" s="57" t="s">
+      <c r="D24" s="61" t="s">
         <v>415</v>
       </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="58" t="s">
+      <c r="E24" s="61"/>
+      <c r="F24" s="62" t="s">
         <v>416</v>
       </c>
-      <c r="G19" s="58"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="35" t="s">
+      <c r="G24" s="62"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="35" t="s">
         <v>417</v>
       </c>
-      <c r="C20" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D20" s="57" t="s">
+      <c r="C25" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="D25" s="61" t="s">
         <v>418</v>
       </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58" t="s">
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
         <v>419</v>
       </c>
-      <c r="G20" s="58"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
+      <c r="G25" s="62"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="35" t="s">
         <v>420</v>
       </c>
-      <c r="C21" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D21" s="57" t="s">
+      <c r="C26" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="D26" s="61" t="s">
         <v>421</v>
       </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="58" t="s">
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>422</v>
       </c>
-      <c r="G21" s="58"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
+      <c r="G26" s="62"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="C22" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D22" s="57" t="s">
+      <c r="C27" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="D27" s="61" t="s">
         <v>424</v>
       </c>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58" t="s">
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
         <v>425</v>
       </c>
-      <c r="G22" s="58"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="35" t="s">
+      <c r="G27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C28" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="61" t="s">
         <v>427</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="60" t="s">
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
         <v>428</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
+      <c r="G28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="35" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
+        <v>431</v>
+      </c>
+      <c r="G29" s="62"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="441">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1573,7 +1573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1596,6 +1596,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2390,22 +2391,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2413,49 +2414,49 @@
       <c r="A4" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>120</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>200</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>300</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>375</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>400</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>1140000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>1957000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>3023565</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>3892840</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>4276933</v>
       </c>
     </row>
@@ -2463,19 +2464,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>96000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>164800</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>254616</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>327818</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>360163</v>
       </c>
     </row>
@@ -2483,19 +2484,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>144000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>247200</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>381924</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>491727</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>540244</v>
       </c>
     </row>
@@ -2503,19 +2504,19 @@
       <c r="A10" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>100000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>103000</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>106090</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>109273</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>112551</v>
       </c>
     </row>
@@ -2523,19 +2524,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>31827</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>32782</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -2543,43 +2544,43 @@
       <c r="A12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>36000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>61800</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>95481</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>122932</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>SUM(B7:B12)</f>
         <v>1546000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUM(C7:C12)</f>
         <v>2564700</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUM(D7:D12)</f>
         <v>3893503</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUM(E7:E12)</f>
         <v>4977371</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>SUM(F7:F12)</f>
         <v>5458718</v>
       </c>
@@ -2588,19 +2589,19 @@
       <c r="A15" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>12883</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>12824</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>12978</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>13273</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>13647</v>
       </c>
     </row>
@@ -2639,52 +2640,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>352690</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>435925</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>449003</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>462473</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>476347</v>
       </c>
     </row>
@@ -2692,19 +2693,19 @@
       <c r="A6" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>62173</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>76846</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>79151</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>81526</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -2712,19 +2713,19 @@
       <c r="A7" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>95738</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>118332</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>121881</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>125538</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>129304</v>
       </c>
     </row>
@@ -2732,54 +2733,54 @@
       <c r="A8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>SUM(B5:B7)</f>
         <v>510600</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>SUM(C5:C7)</f>
         <v>631102</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <f>SUM(D5:D7)</f>
         <v>650035</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <f>SUM(E5:E7)</f>
         <v>669536</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>SUM(F5:F7)</f>
         <v>689622</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>124346</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>153691</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>158302</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>163051</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>167943</v>
       </c>
     </row>
@@ -2787,19 +2788,19 @@
       <c r="A11" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>101738</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>125748</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>129520</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>133406</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>137408</v>
       </c>
     </row>
@@ -2807,19 +2808,19 @@
       <c r="A12" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>81390</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>100598</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>103616</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>106724</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>109926</v>
       </c>
     </row>
@@ -2827,54 +2828,54 @@
       <c r="A13" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="35">
         <f>SUM(B10:B12)</f>
         <v>307473</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="35">
         <f>SUM(C10:C12)</f>
         <v>380037</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="35">
         <f>SUM(D10:D12)</f>
         <v>391438</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="35">
         <f>SUM(E10:E12)</f>
         <v>403181</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>SUM(F10:F12)</f>
         <v>415277</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>62173</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>76846</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>79151</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>81526</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -2882,54 +2883,54 @@
       <c r="A16" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>SUM(B15:B15)</f>
         <v>62173</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>SUM(C15:C15)</f>
         <v>76846</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <f>SUM(D15:D15)</f>
         <v>79151</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>SUM(E15:E15)</f>
         <v>81526</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>SUM(F15:F15)</f>
         <v>83971</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>62173</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>76846</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>79151</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>81526</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -2937,54 +2938,54 @@
       <c r="A19" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="35">
         <f>SUM(B18:B18)</f>
         <v>62173</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <f>SUM(C18:C18)</f>
         <v>76846</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="35">
         <f>SUM(D18:D18)</f>
         <v>79151</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="35">
         <f>SUM(E18:E18)</f>
         <v>81526</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="35">
         <f>SUM(F18:F18)</f>
         <v>83971</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>84012</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>103838</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>106954</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>110162</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>113467</v>
       </c>
     </row>
@@ -2992,48 +2993,48 @@
       <c r="A22" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B22" s="34">
+      <c r="B22" s="35">
         <f>SUM(B21:B21)</f>
         <v>84012</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="35">
         <f>SUM(C21:C21)</f>
         <v>103838</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="35">
         <f>SUM(D21:D21)</f>
         <v>106954</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="35">
         <f>SUM(E21:E21)</f>
         <v>110162</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="35">
         <f>SUM(F21:F21)</f>
         <v>113467</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>B8+B13+B16+B19+B22</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>C8+C13+C16+C19+C22</f>
         <v>1268669</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>D8+D13+D16+D19+D22</f>
         <v>1306729</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>E8+E13+E16+E19+E22</f>
         <v>1345931</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <f>F8+F13+F16+F19+F22</f>
         <v>1386309</v>
       </c>
@@ -3073,52 +3074,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>950000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>1957000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3023565</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>3892840</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>4276933</v>
       </c>
     </row>
@@ -3126,19 +3127,19 @@
       <c r="A6" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>80000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>164800</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>254616</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>360163</v>
       </c>
     </row>
@@ -3146,19 +3147,19 @@
       <c r="A7" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>120000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>247200</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>381924</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>491727</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>540244</v>
       </c>
     </row>
@@ -3166,19 +3167,19 @@
       <c r="A8" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>83333</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>103000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>106090</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>109273</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>112551</v>
       </c>
     </row>
@@ -3186,19 +3187,19 @@
       <c r="A9" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>25000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>30900</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>31827</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>32782</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -3206,19 +3207,19 @@
       <c r="A10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>30000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>61800</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>95481</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>122932</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>135061</v>
       </c>
     </row>
@@ -3226,54 +3227,54 @@
       <c r="A11" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>1288333</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>124346</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>153691</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>158302</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>163051</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>167943</v>
       </c>
     </row>
@@ -3281,19 +3282,19 @@
       <c r="A15" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>101738</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>125748</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>129520</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>133406</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>137408</v>
       </c>
     </row>
@@ -3301,19 +3302,19 @@
       <c r="A16" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>81390</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>100598</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>103616</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>106724</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>109926</v>
       </c>
     </row>
@@ -3321,19 +3322,19 @@
       <c r="A17" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>352690</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>435925</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>449003</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>462473</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>476347</v>
       </c>
     </row>
@@ -3341,19 +3342,19 @@
       <c r="A18" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>62173</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>76846</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>79151</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>81526</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -3361,19 +3362,19 @@
       <c r="A19" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>95738</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>118332</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>121881</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>125538</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>129304</v>
       </c>
     </row>
@@ -3381,19 +3382,19 @@
       <c r="A20" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>62173</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>76846</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>79151</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>81526</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -3401,19 +3402,19 @@
       <c r="A21" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>84012</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>103838</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>106954</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>110162</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>113467</v>
       </c>
     </row>
@@ -3421,19 +3422,19 @@
       <c r="A22" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <v>62173</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>76846</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>79151</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>81526</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>83971</v>
       </c>
     </row>
@@ -3441,39 +3442,39 @@
       <c r="A23" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>SUM(B14:B22)</f>
         <v>1026431</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>SUM(C14:C22)</f>
         <v>1268669</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>SUM(D14:D22)</f>
         <v>1306729</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="35">
         <f>SUM(E14:E22)</f>
         <v>1345931</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="35">
         <f>SUM(F14:F22)</f>
         <v>1386309</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="37" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3481,24 +3482,24 @@
       <c r="A27" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <v>70000</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>144200</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>222789</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>286841</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>315142</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3506,24 +3507,24 @@
       <c r="A29" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <v>50000</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>103000</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>159135</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>204886</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>225102</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="37" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3531,19 +3532,19 @@
       <c r="A31" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="30">
         <v>180000</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <v>222480</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <v>229154</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <v>236029</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="30">
         <v>243110</v>
       </c>
     </row>
@@ -3551,19 +3552,19 @@
       <c r="A32" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="30">
         <v>25000</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <v>30900</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <v>31827</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <v>32782</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -3571,19 +3572,19 @@
       <c r="A33" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <v>15000</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <v>18540</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <v>19096</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <v>19669</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="30">
         <v>20259</v>
       </c>
     </row>
@@ -3591,19 +3592,19 @@
       <c r="A34" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="30">
         <v>15000</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <v>18540</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <v>19096</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="30">
         <v>19669</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="30">
         <v>20259</v>
       </c>
     </row>
@@ -3611,29 +3612,29 @@
       <c r="A35" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="35">
         <f>SUM(B31:B34)</f>
         <v>235000</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <f>SUM(C31:C34)</f>
         <v>290460</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <f>SUM(D31:D34)</f>
         <v>299174</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <f>SUM(E31:E34)</f>
         <v>308149</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <f>SUM(F31:F34)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="37" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3641,19 +3642,19 @@
       <c r="A37" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <v>20833</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>25750</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>26523</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <v>27318</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <v>28138</v>
       </c>
     </row>
@@ -3661,19 +3662,19 @@
       <c r="A38" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="30">
         <v>12500</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <v>15450</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <v>15914</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <v>16391</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="30">
         <v>16883</v>
       </c>
     </row>
@@ -3681,19 +3682,19 @@
       <c r="A39" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <v>16667</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <v>20600</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <v>21218</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <v>21855</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="30">
         <v>22510</v>
       </c>
     </row>
@@ -3701,19 +3702,19 @@
       <c r="A40" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <v>80000</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <v>164800</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <v>254616</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="30">
         <v>327818</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="30">
         <v>360163</v>
       </c>
     </row>
@@ -3721,19 +3722,19 @@
       <c r="A41" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <v>60000</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <v>123600</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>190962</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <v>245864</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <v>270122</v>
       </c>
     </row>
@@ -3741,23 +3742,23 @@
       <c r="A42" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="35">
         <f>SUM(B37:B41)</f>
         <v>190000</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <f>SUM(C37:C41)</f>
         <v>350200</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <f>SUM(D37:D41)</f>
         <v>509232</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="35">
         <f>SUM(E37:E41)</f>
         <v>639245</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <f>SUM(F37:F41)</f>
         <v>697815</v>
       </c>
@@ -3766,54 +3767,54 @@
       <c r="A43" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="35">
         <f>B27+B29+B35+B42</f>
         <v>545000</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="35">
         <f>C27+C29+C35+C42</f>
         <v>887860</v>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="35">
         <f>D27+D29+D35+D42</f>
         <v>1190330</v>
       </c>
-      <c r="E43" s="34">
+      <c r="E43" s="35">
         <f>E27+E29+E35+E42</f>
         <v>1439121</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="35">
         <f>F27+F29+F35+F42</f>
         <v>1555453</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="30">
         <v>49825</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <v>49825</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="30">
         <v>49825</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="30">
         <v>49825</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="30">
         <v>49825</v>
       </c>
     </row>
@@ -3821,19 +3822,19 @@
       <c r="A47" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="30">
         <v>75000</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <v>25000</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <v>30000</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="30">
         <v>15000</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="30">
         <v>10000</v>
       </c>
     </row>
@@ -3841,19 +3842,19 @@
       <c r="A48" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="30">
         <v>40000</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="30">
         <v>15000</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="30">
         <v>10000</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="30">
         <v>10000</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <v>10000</v>
       </c>
     </row>
@@ -3861,23 +3862,23 @@
       <c r="A49" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B49" s="34">
+      <c r="B49" s="35">
         <f>SUM(B46:B48)</f>
         <v>164825</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="35">
         <f>SUM(C46:C48)</f>
         <v>89825</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="35">
         <f>SUM(D46:D48)</f>
         <v>89825</v>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="35">
         <f>SUM(E46:E48)</f>
         <v>74825</v>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="35">
         <f>SUM(F46:F48)</f>
         <v>69825</v>
       </c>
@@ -3917,22 +3918,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3940,23 +3941,23 @@
       <c r="A4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="33">
         <f>'Budget Detail'!B11</f>
         <v>1288333</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <f>'Budget Detail'!C11</f>
         <v>2564700</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="33">
         <f>'Budget Detail'!D11</f>
         <v>3893503</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="33">
         <f>'Budget Detail'!E11</f>
         <v>4977371</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="33">
         <f>'Budget Detail'!F11</f>
         <v>5458718</v>
       </c>
@@ -3965,23 +3966,23 @@
       <c r="A5" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="33">
         <f>'Budget Detail'!B23</f>
         <v>1026431</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <f>'Budget Detail'!C23</f>
         <v>1268669</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="33">
         <f>'Budget Detail'!D23</f>
         <v>1306729</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="33">
         <f>'Budget Detail'!E23</f>
         <v>1345931</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <f>'Budget Detail'!F23</f>
         <v>1386309</v>
       </c>
@@ -3990,23 +3991,23 @@
       <c r="A6" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="33">
         <f>'Budget Detail'!B43</f>
         <v>545000</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>'Budget Detail'!C43</f>
         <v>887860</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="33">
         <f>'Budget Detail'!D43</f>
         <v>1190330</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="33">
         <f>'Budget Detail'!E43</f>
         <v>1439121</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="33">
         <f>'Budget Detail'!F43</f>
         <v>1555453</v>
       </c>
@@ -4015,23 +4016,23 @@
       <c r="A7" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="33">
         <f>'Budget Detail'!B49</f>
         <v>164825</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>'Budget Detail'!C49</f>
         <v>89825</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
         <f>'Budget Detail'!D49</f>
         <v>89825</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>'Budget Detail'!E49</f>
         <v>74825</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>'Budget Detail'!F49</f>
         <v>69825</v>
       </c>
@@ -4040,58 +4041,58 @@
       <c r="A8" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>SUM(B5:B7)</f>
         <v>1736256</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>SUM(C5:C7)</f>
         <v>2246354</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <f>SUM(D5:D7)</f>
         <v>2586884</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <f>SUM(E5:E7)</f>
         <v>2859877</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>SUM(F5:F7)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B4-B8</f>
         <v>-447923</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>C4-C8</f>
         <v>318346</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>D4-D8</f>
         <v>1306619</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>E4-E8</f>
         <v>2117494</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>F4-F8</f>
         <v>2447131</v>
       </c>
@@ -4100,23 +4101,23 @@
       <c r="A12" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.44829778</v>
       </c>
@@ -4125,19 +4126,19 @@
       <c r="A13" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>-447923</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>-129576</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>1177043</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>3294538</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>5741669</v>
       </c>
     </row>
@@ -4145,19 +4146,19 @@
       <c r="A14" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>10736</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>12824</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>12978</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>13273</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>13647</v>
       </c>
     </row>
@@ -4165,19 +4166,19 @@
       <c r="A15" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>14469</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>11232</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>8623</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>7626</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>7529</v>
       </c>
     </row>
@@ -4225,171 +4226,171 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="35">
         <v>154600</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <v>154600</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="35">
         <v>154600</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="35">
         <v>154600</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="35">
         <v>154600</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="35">
         <v>154600</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="35">
         <v>154600</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="35">
         <v>154600</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="35">
         <v>154600</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="35">
         <v>154600</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="35">
         <v>0</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="35">
         <v>0</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <f>SUM(B4:M4)</f>
         <v>1546000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>102643</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>102643</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>102643</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>102643</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>102643</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>102643</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <v>102643</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <v>102643</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="30">
         <v>102643</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="30">
         <v>102643</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="30">
         <v>0</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="30">
         <v>0</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>1026431</v>
       </c>
@@ -4398,43 +4399,43 @@
       <c r="A8" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>54500</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>54500</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>54500</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>54500</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>54500</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <v>54500</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <v>54500</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="30">
         <v>54500</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="30">
         <v>54500</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="30">
         <v>54500</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="30">
         <v>0</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="30">
         <v>0</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>545000</v>
       </c>
@@ -4443,118 +4444,118 @@
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>13735</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>13735</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>13735</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>13735</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>13735</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <v>13735</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <v>13735</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <v>13735</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="30">
         <v>13735</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="30">
         <v>13735</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="30">
         <v>13735</v>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="30">
         <v>13735</v>
       </c>
-      <c r="N9" s="29">
+      <c r="N9" s="30">
         <f>SUM(B9:M9)</f>
         <v>164825</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>B7+B8+B9</f>
         <v>170878</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>C7+C8+C9</f>
         <v>170878</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>D7+D8+D9</f>
         <v>170878</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E7+E8+E9</f>
         <v>170878</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>F7+F8+F9</f>
         <v>170878</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <f>G7+G8+G9</f>
         <v>170878</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>H7+H8+H9</f>
         <v>170878</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="33">
         <f>I7+I8+I9</f>
         <v>170878</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="33">
         <f>J7+J8+J9</f>
         <v>170878</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="33">
         <f>K7+K8+K9</f>
         <v>170878</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="33">
         <f>L7+L8+L9</f>
         <v>13735</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="33">
         <f>M7+M8+M9</f>
         <v>13735</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="33">
         <f>SUM(B12:M12)</f>
         <v>1736250</v>
       </c>
@@ -4563,55 +4564,55 @@
       <c r="A13" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>B4-B12</f>
         <v>-16278</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>C4-C12</f>
         <v>-16278</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>D4-D12</f>
         <v>-16278</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E4-E12</f>
         <v>-16278</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>F4-F12</f>
         <v>-16278</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>G4-G12</f>
         <v>-16278</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>H4-H12</f>
         <v>-16278</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="33">
         <f>I4-I12</f>
         <v>-16278</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="33">
         <f>J4-J12</f>
         <v>-16278</v>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="33">
         <f>K4-K12</f>
         <v>-16278</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="33">
         <f>L4-L12</f>
         <v>-13735</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="33">
         <f>M4-M12</f>
         <v>-13735</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="33">
         <f>SUM(B13:M13)</f>
         <v>-190250</v>
       </c>
@@ -4620,71 +4621,71 @@
       <c r="A14" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>B17+B13</f>
         <v>-16278</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>B14+C13</f>
         <v>-32556</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>C14+D13</f>
         <v>-48834</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>D14+E13</f>
         <v>-65112</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>E14+F13</f>
         <v>-81390</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>F14+G13</f>
         <v>-97668</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>G14+H13</f>
         <v>-113946</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>H14+I13</f>
         <v>-130224</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="38">
         <f>I14+J13</f>
         <v>-146502</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>-162780</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>-176515</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>-190250</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="31">
         <f>M14</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4692,7 +4693,7 @@
       <c r="A18" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>M14</f>
         <v>-190250</v>
       </c>
@@ -4701,7 +4702,7 @@
       <c r="A19" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>-190250</v>
       </c>
@@ -4741,82 +4742,82 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <v>1288333</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>2564700</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>3893503</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>4977371</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>5458718</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <v>1026431</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>1268669</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>1306729</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>1345931</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>1386309</v>
       </c>
     </row>
@@ -4824,19 +4825,19 @@
       <c r="A9" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <v>545000</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>887860</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>1190330</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>1439121</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>1555453</v>
       </c>
     </row>
@@ -4844,78 +4845,78 @@
       <c r="A10" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <v>164825</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <v>89825</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <v>89825</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <v>74825</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <v>69825</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>SUM(B8:B10)</f>
         <v>1736256</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>SUM(C8:C10)</f>
         <v>2246354</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <f>SUM(D8:D10)</f>
         <v>2586884</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>SUM(E8:E10)</f>
         <v>2859877</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>SUM(F8:F10)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B5-B11</f>
         <v>-447923</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>C5-C11</f>
         <v>318346</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>D5-D11</f>
         <v>1306619</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E5-E11</f>
         <v>2117494</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F5-F11</f>
         <v>2447131</v>
       </c>
@@ -4924,23 +4925,23 @@
       <c r="A15" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.44829778</v>
       </c>
@@ -4980,101 +4981,101 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>322</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="41" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <v>500000</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <v>0.0575</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>15</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>49825</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6</f>
         <v>500000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>B13</f>
         <v>478361</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>C13</f>
         <v>455444</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>D13</f>
         <v>431175</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>E13</f>
         <v>405473</v>
       </c>
@@ -5083,23 +5084,23 @@
       <c r="A10" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>28186</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>26908</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>25555</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>24122</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>22605</v>
       </c>
@@ -5108,23 +5109,23 @@
       <c r="A11" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>21639</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>22917</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>24270</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>25702</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>27220</v>
       </c>
@@ -5133,23 +5134,23 @@
       <c r="A12" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>B10+B11</f>
         <v>49825</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>C10+C11</f>
         <v>49825</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>D10+D11</f>
         <v>49825</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E10+E11</f>
         <v>49825</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>F10+F11</f>
         <v>49825</v>
       </c>
@@ -5158,23 +5159,23 @@
       <c r="A13" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
         <v>478361</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="38">
         <f>MAX(0,C9-C11)</f>
         <v>455444</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="38">
         <f>MAX(0,D9-D11)</f>
         <v>431175</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <f>MAX(0,E9-E11)</f>
         <v>405473</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="38">
         <f>MAX(0,F9-F11)</f>
         <v>378253</v>
       </c>
@@ -5214,56 +5215,56 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>-190250</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>128096</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1434716</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>3552210</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>5999341</v>
       </c>
@@ -5272,19 +5273,19 @@
       <c r="A6" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>0</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>0</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>0</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>0</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5292,19 +5293,19 @@
       <c r="A7" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>0</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>0</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>0</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>0</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5312,19 +5313,19 @@
       <c r="A8" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>0</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>0</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>0</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>0</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5332,54 +5333,54 @@
       <c r="A9" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>-190250</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>SUM(C5:C8)</f>
         <v>128096</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>SUM(D5:D8)</f>
         <v>1434716</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <f>SUM(E5:E8)</f>
         <v>3552210</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>SUM(F5:F8)</f>
         <v>5999341</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>0</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>0</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>0</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>0</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5387,23 +5388,23 @@
       <c r="A13" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
         <v>478361</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>'Debt Schedule'!C13</f>
         <v>455444</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>'Debt Schedule'!D13</f>
         <v>431175</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>'Debt Schedule'!E13</f>
         <v>405473</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>'Debt Schedule'!F13</f>
         <v>378253</v>
       </c>
@@ -5412,58 +5413,58 @@
       <c r="A14" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>SUM(B12:B13)</f>
         <v>478361</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>SUM(C12:C13)</f>
         <v>455444</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>SUM(D12:D13)</f>
         <v>431175</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>SUM(E12:E13)</f>
         <v>405473</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>SUM(F12:F13)</f>
         <v>378253</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>B9-B14</f>
         <v>-668611</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C9-C14</f>
         <v>-327348</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D9-D14</f>
         <v>1003541</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E9-E14</f>
         <v>3146738</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F9-F14</f>
         <v>5621089</v>
       </c>
@@ -5472,23 +5473,23 @@
       <c r="A19" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="43" t="str">
+      <c r="C19" s="44" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="43" t="str">
+      <c r="D19" s="44" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="45">
         <f>E9-E14-E17</f>
         <v>-1</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="45">
         <f>F9-F14-F17</f>
         <v>-1</v>
       </c>
@@ -5528,52 +5529,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>1288333</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>2564700</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3893503</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>4977371</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>5458718</v>
       </c>
     </row>
@@ -5581,19 +5582,19 @@
       <c r="A6" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>1026431</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>1268669</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>1306729</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>1345931</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>1386309</v>
       </c>
     </row>
@@ -5601,19 +5602,19 @@
       <c r="A7" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>545000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>887860</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>1190330</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>1439121</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>1555453</v>
       </c>
     </row>
@@ -5621,23 +5622,23 @@
       <c r="A8" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <f>B5-B6-B7</f>
         <v>-283098</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>C5-C6-C7</f>
         <v>408171</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <f>D5-D6-D7</f>
         <v>1396444</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <f>E5-E6-E7</f>
         <v>2192319</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <f>F5-F6-F7</f>
         <v>2516956</v>
       </c>
@@ -5646,19 +5647,19 @@
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>49825</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>49825</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>49825</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>49825</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>49825</v>
       </c>
     </row>
@@ -5666,54 +5667,54 @@
       <c r="A10" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="46">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-5.68</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="46">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>8.19</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="46">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>28.03</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="46">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>44</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="46">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>50.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>-190250</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>128096</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>1434716</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>3552210</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>5999341</v>
       </c>
     </row>
@@ -5721,23 +5722,23 @@
       <c r="A14" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>-43</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>21</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>206</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>457</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>732</v>
       </c>
@@ -5746,23 +5747,23 @@
       <c r="A15" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>-1.4</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>0.7</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>6.8</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>15</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>24.1</v>
       </c>
@@ -5771,49 +5772,49 @@
       <c r="A16" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <v>0.3</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <v>0.5</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>0.75</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>0.9375</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>10736</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>12824</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>12978</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>13273</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>13647</v>
       </c>
     </row>
@@ -5821,19 +5822,19 @@
       <c r="A20" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>1076256</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>1318494</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>1356554</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>1395756</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>1436134</v>
       </c>
     </row>
@@ -5841,19 +5842,19 @@
       <c r="A21" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>4542</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>4439</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>3968</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>3838</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>3889</v>
       </c>
     </row>
@@ -5861,49 +5862,49 @@
       <c r="A22" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="47">
         <v>174</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="47">
         <v>158</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="47">
         <v>151</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="47">
         <v>148</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="47">
         <v>148</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="49" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5911,19 +5912,19 @@
       <c r="A26" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="E26" s="48" t="s">
+      <c r="E26" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="49" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5931,19 +5932,19 @@
       <c r="A27" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="48" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5951,19 +5952,19 @@
       <c r="A28" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="49" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5971,19 +5972,19 @@
       <c r="A29" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="49" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6024,16 +6025,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="50" t="s">
         <v>367</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>111</v>
       </c>
     </row>
@@ -6041,13 +6042,13 @@
       <c r="A4" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>400000</v>
       </c>
     </row>
@@ -6055,13 +6056,13 @@
       <c r="A5" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>75000</v>
       </c>
     </row>
@@ -6069,13 +6070,13 @@
       <c r="A6" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>40000</v>
       </c>
     </row>
@@ -6083,7 +6084,7 @@
       <c r="D7" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>60000</v>
       </c>
     </row>
@@ -6091,7 +6092,7 @@
       <c r="D8" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>75000</v>
       </c>
     </row>
@@ -6099,13 +6100,13 @@
       <c r="A10" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>650000</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>650000</v>
       </c>
     </row>
@@ -6113,7 +6114,7 @@
       <c r="A11" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="44">
         <v>0</v>
       </c>
     </row>
@@ -6468,37 +6469,37 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6506,19 +6507,19 @@
       <c r="A6" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>1288333</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>2564700</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>3893503</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>4977371</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>5458718</v>
       </c>
     </row>
@@ -6526,19 +6527,19 @@
       <c r="A7" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>1621256</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>2206354</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>2546884</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>2834877</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>2991587</v>
       </c>
     </row>
@@ -6546,19 +6547,19 @@
       <c r="A8" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>-332923</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>358346</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>1346619</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>2142494</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>2467131</v>
       </c>
     </row>
@@ -6566,19 +6567,19 @@
       <c r="A9" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <v>-0.2584133416981985</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>0.1397225288645145</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>0.3458632236905482</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>0.43044696555461553</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>0.4519616461017463</v>
       </c>
     </row>
@@ -6586,19 +6587,19 @@
       <c r="A10" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="51">
         <v>-5.68</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="51">
         <v>8.19</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="51">
         <v>28.03</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="51">
         <v>44</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="51">
         <v>50.52</v>
       </c>
     </row>
@@ -6606,54 +6607,54 @@
       <c r="A11" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>174</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>158</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <v>151</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>148</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <v>148</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6661,19 +6662,19 @@
       <c r="A16" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>966250</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>1923525</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>2920127</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>3733029</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>4094038</v>
       </c>
     </row>
@@ -6681,19 +6682,19 @@
       <c r="A17" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>1621256</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>2206354</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>2546884</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>2834877</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>2991587</v>
       </c>
     </row>
@@ -6701,19 +6702,19 @@
       <c r="A18" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>-655006</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>-282829</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>373244</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>898152</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>1102452</v>
       </c>
     </row>
@@ -6721,19 +6722,19 @@
       <c r="A19" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <v>-0.677884455597598</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <v>-0.14703662818064733</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <v>0.12781763158739762</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <v>0.2405959540728207</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <v>0.26928219480232835</v>
       </c>
     </row>
@@ -6741,19 +6742,19 @@
       <c r="A20" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="51">
         <v>-12.15</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="51">
         <v>-4.68</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="51">
         <v>8.49</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="51">
         <v>19.03</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="51">
         <v>23.13</v>
       </c>
     </row>
@@ -6761,54 +6762,54 @@
       <c r="A21" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <v>230</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <v>191</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <v>177</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <v>171</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <v>170</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6816,19 +6817,19 @@
       <c r="A26" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <v>1223917</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>2436465</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>3698828</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <v>4728503</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <v>5185782</v>
       </c>
     </row>
@@ -6836,19 +6837,19 @@
       <c r="A27" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <v>1621256</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>2206354</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>2546884</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>2834877</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>2991587</v>
       </c>
     </row>
@@ -6856,19 +6857,19 @@
       <c r="A28" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <v>-397339</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>230111</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>1151944</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>1893626</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>2194195</v>
       </c>
     </row>
@@ -6876,19 +6877,19 @@
       <c r="A29" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="29">
         <v>-0.3246456228402091</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <v>0.09444476722580472</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="29">
         <v>0.31143497230584016</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="29">
         <v>0.40047049005748997</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="29">
         <v>0.4231175222123644</v>
       </c>
     </row>
@@ -6896,19 +6897,19 @@
       <c r="A30" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="51">
         <v>-6.97</v>
       </c>
-      <c r="C30" s="50">
+      <c r="C30" s="51">
         <v>5.62</v>
       </c>
-      <c r="D30" s="50">
+      <c r="D30" s="51">
         <v>24.12</v>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="51">
         <v>39.01</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="51">
         <v>45.04</v>
       </c>
     </row>
@@ -6916,54 +6917,54 @@
       <c r="A31" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="27">
         <v>191</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <v>171</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="27">
         <v>163</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="27">
         <v>160</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="27">
         <v>159</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="17" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6971,19 +6972,19 @@
       <c r="A36" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <v>1288333</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <v>2564700</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <v>3893503</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <v>4977371</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="30">
         <v>5458718</v>
       </c>
     </row>
@@ -6991,19 +6992,19 @@
       <c r="A37" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <v>1667756</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>2295964</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>2680557</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <v>3004523</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <v>3177296</v>
       </c>
     </row>
@@ -7011,19 +7012,19 @@
       <c r="A38" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="31">
         <v>-379423</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <v>268736</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <v>1212946</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <v>1972849</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <v>2281422</v>
       </c>
     </row>
@@ -7031,19 +7032,19 @@
       <c r="A39" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <v>-0.2945064852945763</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="29">
         <v>0.10478276982836991</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="29">
         <v>0.31153079862242844</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="29">
         <v>0.3963635407467121</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="29">
         <v>0.4179410275450453</v>
       </c>
     </row>
@@ -7051,19 +7052,19 @@
       <c r="A40" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B40" s="50">
+      <c r="B40" s="51">
         <v>-6.62</v>
       </c>
-      <c r="C40" s="50">
+      <c r="C40" s="51">
         <v>6.39</v>
       </c>
-      <c r="D40" s="50">
+      <c r="D40" s="51">
         <v>25.34</v>
       </c>
-      <c r="E40" s="50">
+      <c r="E40" s="51">
         <v>40.6</v>
       </c>
-      <c r="F40" s="50">
+      <c r="F40" s="51">
         <v>46.79</v>
       </c>
     </row>
@@ -7071,19 +7072,19 @@
       <c r="A41" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="27">
         <v>186</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="27">
         <v>167</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="27">
         <v>159</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="27">
         <v>156</v>
       </c>
-      <c r="F41" s="26">
+      <c r="F41" s="27">
         <v>155</v>
       </c>
     </row>
@@ -7126,10 +7127,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -7180,16 +7181,16 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -7201,19 +7202,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7221,19 +7222,19 @@
       <c r="A13" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>1288333</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>2564700</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>3893503</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <v>4977371</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <v>5458718</v>
       </c>
     </row>
@@ -7241,19 +7242,19 @@
       <c r="A14" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>1621256</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>2206354</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>2546884</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <v>2834877</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>2991587</v>
       </c>
     </row>
@@ -7261,19 +7262,19 @@
       <c r="A15" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>-447923</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>318346</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>1306619</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <v>2117494</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <v>2447131</v>
       </c>
     </row>
@@ -7281,19 +7282,19 @@
       <c r="A16" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>-190250</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>128096</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>1434716</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <v>3552210</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <v>5999341</v>
       </c>
     </row>
@@ -7301,33 +7302,33 @@
       <c r="A17" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>478361</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>455444</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>431175</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <v>405473</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="30">
         <v>378253</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -7339,19 +7340,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H20" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7359,19 +7360,19 @@
       <c r="A21" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <v>0.12412616281780338</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <v>0.33558969879535744</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>0.42542423416409325</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>0.44829778198663</v>
       </c>
     </row>
@@ -7379,19 +7380,19 @@
       <c r="A22" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="51">
         <v>-5.68</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="51">
         <v>8.19</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="51">
         <v>28.03</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="51">
         <v>44</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="51">
         <v>50.52</v>
       </c>
     </row>
@@ -7399,19 +7400,19 @@
       <c r="A23" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <v>0.3</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <v>0.5</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <v>0.75</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>0.9375</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
     </row>
@@ -7419,19 +7420,19 @@
       <c r="A24" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <v>120</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>200</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <v>300</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="27">
         <v>375</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="27">
         <v>400</v>
       </c>
     </row>
@@ -7486,32 +7487,32 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="54" t="s">
         <v>400</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="54" t="s">
         <v>401</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="54" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="54" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7519,19 +7520,19 @@
       <c r="B6" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="55">
         <v>120</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="55">
         <v>200</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="55">
         <v>300</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="55">
         <v>375</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="55">
         <v>400</v>
       </c>
     </row>
@@ -7539,19 +7540,19 @@
       <c r="B7" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <v>1288333.3333333335</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="56">
         <v>2564700</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="56">
         <v>3893503</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <v>4977371.484999999</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="56">
         <v>5458717.7285</v>
       </c>
     </row>
@@ -7559,19 +7560,19 @@
       <c r="B8" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="56">
         <v>1026431.25</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="56">
         <v>1268669.0250000001</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="56">
         <v>1306729.0957499999</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <v>1345930.9686225</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="56">
         <v>1386308.8976811753</v>
       </c>
     </row>
@@ -7579,19 +7580,19 @@
       <c r="B9" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <v>545000</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="56">
         <v>887860</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <v>1190329.8</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <v>1439121.459</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <v>1555453.1754200002</v>
       </c>
     </row>
@@ -7599,19 +7600,19 @@
       <c r="B10" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="56">
         <v>49824.605221179416</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="56">
         <v>49824.605221179416</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="56">
         <v>49824.605221179416</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="56">
         <v>49824.605221179416</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="56">
         <v>49824.605221179416</v>
       </c>
     </row>
@@ -7619,19 +7620,19 @@
       <c r="B11" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <v>-447922.5218878458</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="58">
         <v>318346.3697788203</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="58">
         <v>1306619.4990288205</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F11" s="58">
         <v>2117494.45215632</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G11" s="58">
         <v>2447131.0501776454</v>
       </c>
     </row>
@@ -7639,19 +7640,19 @@
       <c r="B12" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <v>-190250</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="58">
         <v>128096.36977882031</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="58">
         <v>1434715.8688076409</v>
       </c>
-      <c r="F12" s="57">
+      <c r="F12" s="58">
         <v>3552210.320963961</v>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="58">
         <v>5999341.371141607</v>
       </c>
     </row>
@@ -7659,19 +7660,19 @@
       <c r="B13" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C13" s="58">
+      <c r="C13" s="59">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="60">
         <v>0.12412616281780338</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="60">
         <v>0.33558969879535744</v>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="60">
         <v>0.42542423416409325</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="60">
         <v>0.44829778198663</v>
       </c>
     </row>
@@ -7679,19 +7680,19 @@
       <c r="B14" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="56">
         <v>10736.111111111113</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="56">
         <v>12823.5</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="56">
         <v>12978.343333333334</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <v>13272.990626666666</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="56">
         <v>13646.794321250001</v>
       </c>
     </row>
@@ -7699,19 +7700,19 @@
       <c r="B15" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C15" s="58">
+      <c r="C15" s="59">
         <v>0.7967124838292367</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="60">
         <v>0.49466566265060247</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="60">
         <v>0.3356178474114441</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="60">
         <v>0.27040998902305163</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="60">
         <v>0.25396237113402065</v>
       </c>
     </row>
@@ -7719,19 +7720,19 @@
       <c r="B16" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="60">
         <v>0.12690815006468303</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="60">
         <v>0.10385542168674698</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="60">
         <v>0.09171662125340599</v>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="60">
         <v>0.08673984632272229</v>
       </c>
-      <c r="G16" s="59">
+      <c r="G16" s="60">
         <v>0.08548453608247424</v>
       </c>
     </row>
@@ -7739,19 +7740,19 @@
       <c r="B17" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="59">
         <v>-0.21973965071151344</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="60">
         <v>0.15914959839357423</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="60">
         <v>0.3586600817438692</v>
       </c>
-      <c r="F17" s="59">
+      <c r="F17" s="60">
         <v>0.4404571899012074</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G17" s="60">
         <v>0.4610891752577319</v>
       </c>
     </row>
@@ -7759,19 +7760,19 @@
       <c r="B18" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="61">
         <v>-5.681889809461599</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="62">
         <v>8.192156730355682</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="62">
         <v>28.027198570886025</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="62">
         <v>44.00073111759629</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="62">
         <v>50.51631908021458</v>
       </c>
     </row>
@@ -7779,156 +7780,156 @@
       <c r="B19" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="63" t="s">
         <v>400</v>
       </c>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>412</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D23" s="65" t="s">
+      <c r="D23" s="66" t="s">
         <v>417</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="66" t="s">
+      <c r="E23" s="66"/>
+      <c r="F23" s="67" t="s">
         <v>418</v>
       </c>
-      <c r="G23" s="66"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>419</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="68" t="s">
         <v>420</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="66" t="s">
         <v>421</v>
       </c>
-      <c r="E24" s="65"/>
-      <c r="F24" s="66" t="s">
+      <c r="E24" s="66"/>
+      <c r="F24" s="67" t="s">
         <v>422</v>
       </c>
-      <c r="G24" s="66"/>
+      <c r="G24" s="67"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D25" s="65" t="s">
+      <c r="D25" s="66" t="s">
         <v>424</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66" t="s">
+      <c r="E25" s="66"/>
+      <c r="F25" s="67" t="s">
         <v>425</v>
       </c>
-      <c r="G25" s="66"/>
+      <c r="G25" s="67"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="40" t="s">
         <v>426</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="66" t="s">
         <v>427</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66" t="s">
+      <c r="E26" s="66"/>
+      <c r="F26" s="67" t="s">
         <v>428</v>
       </c>
-      <c r="G26" s="66"/>
+      <c r="G26" s="67"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D27" s="65" t="s">
+      <c r="D27" s="66" t="s">
         <v>430</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66" t="s">
+      <c r="E27" s="66"/>
+      <c r="F27" s="67" t="s">
         <v>431</v>
       </c>
-      <c r="G27" s="66"/>
+      <c r="G27" s="67"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="66" t="s">
         <v>433</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66" t="s">
+      <c r="E28" s="66"/>
+      <c r="F28" s="67" t="s">
         <v>434</v>
       </c>
-      <c r="G28" s="66"/>
+      <c r="G28" s="67"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="40" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="64" t="s">
+      <c r="C29" s="65" t="s">
         <v>416</v>
       </c>
-      <c r="D29" s="65" t="s">
+      <c r="D29" s="66" t="s">
         <v>436</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66" t="s">
+      <c r="E29" s="66"/>
+      <c r="F29" s="67" t="s">
         <v>437</v>
       </c>
-      <c r="G29" s="66"/>
+      <c r="G29" s="67"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="40" t="s">
         <v>438</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -7938,14 +7939,14 @@
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="69" t="s">
         <v>440</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -8081,27 +8082,30 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8109,7 +8113,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8117,7 +8121,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8125,7 +8129,7 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8133,7 +8137,7 @@
       <c r="A9" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8141,7 +8145,7 @@
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -8149,7 +8153,7 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -8157,7 +8161,7 @@
       <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>7</v>
       </c>
     </row>
@@ -8165,38 +8169,38 @@
       <c r="A13" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>400</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -8204,47 +8208,47 @@
       <c r="A17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="21">
         <v>120</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>200</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>300</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>375</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8258,10 +8262,10 @@
       <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>9500</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8275,10 +8279,10 @@
       <c r="C22" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <v>800</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8292,10 +8296,10 @@
       <c r="C23" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="22">
         <v>1200</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8309,10 +8313,10 @@
       <c r="C24" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <v>100000</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8326,10 +8330,10 @@
       <c r="C25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <v>30000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8343,44 +8347,44 @@
       <c r="C26" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="22">
         <v>300</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="20" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8394,16 +8398,16 @@
       <c r="C30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="24">
         <v>1</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="22">
         <v>110000</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="23">
         <v>0.28</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8417,16 +8421,16 @@
       <c r="C31" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <v>1</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>90000</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>0.28</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8440,16 +8444,16 @@
       <c r="C32" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="24">
         <v>1</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="22">
         <v>72000</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="23">
         <v>0.28</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8463,16 +8467,16 @@
       <c r="C33" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="24">
         <v>6</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <v>52000</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="23">
         <v>0.28</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8486,16 +8490,16 @@
       <c r="C34" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="24">
         <v>1</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="22">
         <v>55000</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="23">
         <v>0.28</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8509,16 +8513,16 @@
       <c r="C35" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="24">
         <v>3</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <v>30000</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>0.2</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8532,16 +8536,16 @@
       <c r="C36" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <v>1</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="22">
         <v>55000</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="23">
         <v>0.28</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8555,16 +8559,16 @@
       <c r="C37" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="24">
         <v>2</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="22">
         <v>38000</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="23">
         <v>0.25</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8578,44 +8582,44 @@
       <c r="C38" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="24">
         <v>1</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="22">
         <v>55000</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="23">
         <v>0.28</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="23">
         <v>0.0765</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8629,10 +8633,10 @@
       <c r="C42" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>18000</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>0.03</v>
       </c>
     </row>
@@ -8646,10 +8650,10 @@
       <c r="C43" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="22">
         <v>2500</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8663,10 +8667,10 @@
       <c r="C44" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="22">
         <v>18000</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8680,10 +8684,10 @@
       <c r="C45" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <v>1500</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8697,10 +8701,10 @@
       <c r="C46" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="22">
         <v>700</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8714,10 +8718,10 @@
       <c r="C47" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="22">
         <v>500</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8731,10 +8735,10 @@
       <c r="C48" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="22">
         <v>25000</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8748,10 +8752,10 @@
       <c r="C49" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="22">
         <v>15000</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8765,10 +8769,10 @@
       <c r="C50" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="22">
         <v>20000</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8782,10 +8786,10 @@
       <c r="C51" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="22">
         <v>800</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E51" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8799,38 +8803,38 @@
       <c r="C52" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="21">
+      <c r="D52" s="22">
         <v>600</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E52" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="20" t="s">
         <v>165</v>
       </c>
     </row>
@@ -8841,13 +8845,13 @@
       <c r="B56" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C56" s="21">
+      <c r="C56" s="22">
         <v>500000</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="23">
         <v>0.0575</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <v>15</v>
       </c>
     </row>
@@ -8858,13 +8862,13 @@
       <c r="B57" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C57" s="21">
+      <c r="C57" s="22">
         <v>75000</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="23">
         <v>0</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="21">
         <v>0</v>
       </c>
     </row>
@@ -8875,35 +8879,35 @@
       <c r="B58" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="21">
+      <c r="C58" s="22">
         <v>40000</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="23">
         <v>0</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B61" s="22">
+      <c r="B61" s="23">
         <v>0.03</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="25" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8911,10 +8915,10 @@
       <c r="A62" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B62" s="22">
+      <c r="B62" s="23">
         <v>0.03</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="25" t="s">
         <v>175</v>
       </c>
     </row>
@@ -8922,7 +8926,7 @@
       <c r="A63" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -8930,7 +8934,7 @@
       <c r="A64" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B64" s="21">
+      <c r="B64" s="22">
         <v>0</v>
       </c>
     </row>
@@ -8938,7 +8942,7 @@
       <c r="A65" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="19" t="s">
         <v>179</v>
       </c>
     </row>
@@ -9120,52 +9124,52 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>120</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>200</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>300</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>375</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>400</v>
       </c>
     </row>
@@ -9173,7 +9177,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <v>400</v>
       </c>
     </row>
@@ -9181,19 +9185,19 @@
       <c r="A8" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <v>0.3</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>0.5</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>0.75</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>0.9375</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>1</v>
       </c>
     </row>
@@ -9204,16 +9208,16 @@
       <c r="B10" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>0.5</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>0.25</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <v>0.06666666666666667</v>
       </c>
     </row>
@@ -9252,52 +9256,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>1140000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>1957000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3023565</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>3892840</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>4276933</v>
       </c>
     </row>
@@ -9305,19 +9309,19 @@
       <c r="A6" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>96000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>164800</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>254616</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>360163</v>
       </c>
     </row>
@@ -9325,19 +9329,19 @@
       <c r="A7" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>144000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>247200</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>381924</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>491727</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>540244</v>
       </c>
     </row>
@@ -9345,19 +9349,19 @@
       <c r="A8" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>100000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>103000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>106090</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>109273</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>112551</v>
       </c>
     </row>
@@ -9365,19 +9369,19 @@
       <c r="A9" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>30000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>30900</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>31827</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>32782</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -9385,43 +9389,43 @@
       <c r="A10" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>36000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>61800</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>95481</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>122932</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
         <v>1546000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
@@ -9466,25 +9470,25 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>211</v>
       </c>
     </row>
@@ -9495,19 +9499,19 @@
       <c r="B4" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>110000</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <v>0.28</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="33">
         <v>149215</v>
       </c>
     </row>
@@ -9518,19 +9522,19 @@
       <c r="B5" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>1</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>90000</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <v>0.28</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="33">
         <v>122085</v>
       </c>
     </row>
@@ -9541,19 +9545,19 @@
       <c r="B6" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <v>1</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>72000</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <v>0.28</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="33">
         <v>97668</v>
       </c>
     </row>
@@ -9564,19 +9568,19 @@
       <c r="B7" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <v>6</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>52000</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <v>0.28</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="33">
         <v>423228</v>
       </c>
     </row>
@@ -9587,19 +9591,19 @@
       <c r="B8" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <v>1</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>55000</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>0.28</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="33">
         <v>74608</v>
       </c>
     </row>
@@ -9610,19 +9614,19 @@
       <c r="B9" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <v>3</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>30000</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>0.2</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <v>114885</v>
       </c>
     </row>
@@ -9633,19 +9637,19 @@
       <c r="B10" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <v>1</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>55000</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>0.28</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="33">
         <v>74608</v>
       </c>
     </row>
@@ -9656,19 +9660,19 @@
       <c r="B11" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <v>2</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>38000</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <v>0.25</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="33">
         <v>100814</v>
       </c>
     </row>
@@ -9679,50 +9683,50 @@
       <c r="B12" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <v>1</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>55000</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <v>0.28</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <v>74608</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -9730,19 +9734,19 @@
       <c r="A16" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>1026431</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>1268669</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>1306729</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>1345931</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>1386309</v>
       </c>
     </row>
@@ -9750,19 +9754,19 @@
       <c r="A17" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="29">
         <v>0.6639270698576973</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <v>0.49466566265060247</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <v>0.3356178474114441</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="29">
         <v>0.27040998902305163</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <v>0.25396237113402065</v>
       </c>
     </row>
@@ -9770,19 +9774,19 @@
       <c r="A18" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="34">
         <v>7.1</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <v>11.8</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <v>17.6</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <v>22.1</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <v>23.5</v>
       </c>
     </row>
@@ -9821,52 +9825,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>84000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>144200</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>222789</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>286841</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>315142</v>
       </c>
     </row>
@@ -9874,54 +9878,54 @@
       <c r="A6" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <f>SUM(B5:B5)</f>
         <v>84000</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>SUM(C5:C5)</f>
         <v>144200</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <f>SUM(D5:D5)</f>
         <v>222789</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="35">
         <f>SUM(E5:E5)</f>
         <v>286841</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>SUM(F5:F5)</f>
         <v>315142</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>60000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>103000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>159135</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>204886</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>225102</v>
       </c>
     </row>
@@ -9929,54 +9933,54 @@
       <c r="A9" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>SUM(B8:B8)</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>SUM(C8:C8)</f>
         <v>103000</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>SUM(D8:D8)</f>
         <v>159135</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <f>SUM(E8:E8)</f>
         <v>204886</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>SUM(F8:F8)</f>
         <v>225102</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>216000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>222480</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>229154</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>236029</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>243110</v>
       </c>
     </row>
@@ -9984,19 +9988,19 @@
       <c r="A12" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>30000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>30900</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>31827</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>32782</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -10004,19 +10008,19 @@
       <c r="A13" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>18000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>18540</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>19096</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>19669</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>20259</v>
       </c>
     </row>
@@ -10024,19 +10028,19 @@
       <c r="A14" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>18000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18540</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19096</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19669</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20259</v>
       </c>
     </row>
@@ -10044,54 +10048,54 @@
       <c r="A15" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>SUM(B11:B14)</f>
         <v>282000</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>SUM(C11:C14)</f>
         <v>290460</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>SUM(D11:D14)</f>
         <v>299174</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>SUM(E11:E14)</f>
         <v>308149</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>SUM(F11:F14)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>25000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>25750</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>26523</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>27318</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>28138</v>
       </c>
     </row>
@@ -10099,19 +10103,19 @@
       <c r="A18" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>15000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>15450</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>15914</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>16391</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>16883</v>
       </c>
     </row>
@@ -10119,19 +10123,19 @@
       <c r="A19" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>20000</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>20600</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>21218</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>21855</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>22510</v>
       </c>
     </row>
@@ -10139,19 +10143,19 @@
       <c r="A20" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>96000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>164800</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>254616</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>327818</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>360163</v>
       </c>
     </row>
@@ -10159,19 +10163,19 @@
       <c r="A21" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>72000</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>123600</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>190962</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>245864</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>270122</v>
       </c>
     </row>
@@ -10179,48 +10183,48 @@
       <c r="A22" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B22" s="34">
+      <c r="B22" s="35">
         <f>SUM(B17:B21)</f>
         <v>228000</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="35">
         <f>SUM(C17:C21)</f>
         <v>350200</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="35">
         <f>SUM(D17:D21)</f>
         <v>509232</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="35">
         <f>SUM(E17:E21)</f>
         <v>639245</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="35">
         <f>SUM(F17:F21)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>B6+B9+B15+B22</f>
         <v>654000</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>C6+C9+C15+C22</f>
         <v>887860</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>D6+D9+D15+D22</f>
         <v>1190330</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>E6+E9+E15+E22</f>
         <v>1439121</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <f>F6+F9+F15+F22</f>
         <v>1555453</v>
       </c>
@@ -10261,22 +10265,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>234</v>
       </c>
     </row>
@@ -10287,16 +10291,16 @@
       <c r="B4" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="22">
         <v>500000</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>0.0575</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>15</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="33">
         <v>49825</v>
       </c>
     </row>
@@ -10307,16 +10311,16 @@
       <c r="B5" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <v>75000</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>0</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>0</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <v>75000</v>
       </c>
     </row>
@@ -10327,16 +10331,16 @@
       <c r="B6" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <v>40000</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>0</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>0</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="33">
         <v>40000</v>
       </c>
     </row>
@@ -10344,7 +10348,7 @@
       <c r="A8" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>49825</v>
       </c>
     </row>
@@ -10352,7 +10356,7 @@
       <c r="A9" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <v>500000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="441">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -640,118 +640,118 @@
     <t>Tuition &amp; Funding Drivers</t>
   </si>
   <si>
-    <t>REVENUE BY LINE ITEM</t>
-  </si>
-  <si>
-    <t>State Per-Pupil Funding (Public Funding)</t>
-  </si>
-  <si>
-    <t>Federal Title I (Public Funding)</t>
-  </si>
-  <si>
-    <t>Special Education Funding (Public Funding)</t>
-  </si>
-  <si>
-    <t>CSP Startup Grant (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Annual Fundraising (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Food Service Revenue (Other Revenue)</t>
+    <t>PUBLIC FUNDING</t>
+  </si>
+  <si>
+    <t>Total Public Funding</t>
+  </si>
+  <si>
+    <t>PHILANTHROPY</t>
+  </si>
+  <si>
+    <t>Total Philanthropy</t>
+  </si>
+  <si>
+    <t>OTHER REVENUE</t>
+  </si>
+  <si>
+    <t>Total Other Revenue</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t>Base Rate</t>
+  </si>
+  <si>
+    <t>Loaded Cost</t>
+  </si>
+  <si>
+    <t>5-YEAR TOTAL PERSONNEL COST</t>
+  </si>
+  <si>
+    <t>Total Personnel</t>
+  </si>
+  <si>
+    <t>Personnel as % of Revenue</t>
+  </si>
+  <si>
+    <t>Students per FTE</t>
+  </si>
+  <si>
+    <t>Operating Expense Drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Curriculum &amp; Textbooks</t>
+  </si>
+  <si>
+    <t>Total Instructional / Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Technology &amp; Devices</t>
+  </si>
+  <si>
+    <t>Total Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility Lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Janitorial</t>
+  </si>
+  <si>
+    <t>Total Occupancy / Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Marketing &amp; Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Professional Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Legal &amp; Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Food Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Transportation</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
+    <t>TOTAL OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t>Capital Stack &amp; Loan Terms</t>
+  </si>
+  <si>
+    <t>Annual Payment</t>
+  </si>
+  <si>
+    <t>Capital Expense</t>
+  </si>
+  <si>
+    <t>Total Annual Debt Service</t>
+  </si>
+  <si>
+    <t>Total Loan Principal</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Tuition Forecast</t>
+  </si>
+  <si>
+    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
-  </si>
-  <si>
-    <t>Base Rate</t>
-  </si>
-  <si>
-    <t>Loaded Cost</t>
-  </si>
-  <si>
-    <t>5-YEAR TOTAL PERSONNEL COST</t>
-  </si>
-  <si>
-    <t>Total Personnel</t>
-  </si>
-  <si>
-    <t>Personnel as % of Revenue</t>
-  </si>
-  <si>
-    <t>Students per FTE</t>
-  </si>
-  <si>
-    <t>Operating Expense Drivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Curriculum &amp; Textbooks</t>
-  </si>
-  <si>
-    <t>Total Instructional / Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Technology &amp; Devices</t>
-  </si>
-  <si>
-    <t>Total Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility Lease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Janitorial</t>
-  </si>
-  <si>
-    <t>Total Occupancy / Facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Marketing &amp; Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Professional Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Legal &amp; Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Food Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Transportation</t>
-  </si>
-  <si>
-    <t>Total Administrative / General</t>
-  </si>
-  <si>
-    <t>TOTAL OPERATING EXPENSES</t>
-  </si>
-  <si>
-    <t>Capital Stack &amp; Loan Terms</t>
-  </si>
-  <si>
-    <t>Annual Payment</t>
-  </si>
-  <si>
-    <t>Capital Expense</t>
-  </si>
-  <si>
-    <t>Total Annual Debt Service</t>
-  </si>
-  <si>
-    <t>Total Loan Principal</t>
-  </si>
-  <si>
-    <t>Enrollment &amp; Tuition Forecast</t>
-  </si>
-  <si>
-    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -1609,15 +1609,15 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2382,7 +2382,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2444,19 +2444,19 @@
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>1140000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>1957000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>3023565</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>3892840</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>4276933</v>
       </c>
     </row>
@@ -2464,19 +2464,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>96000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>164800</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>254616</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>327818</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>360163</v>
       </c>
     </row>
@@ -2484,19 +2484,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>144000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>247200</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>381924</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>491727</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>540244</v>
       </c>
     </row>
@@ -2504,19 +2504,19 @@
       <c r="A10" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>100000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <v>103000</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>106090</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>109273</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>112551</v>
       </c>
     </row>
@@ -2524,19 +2524,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>30000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>30900</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>31827</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>32782</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>33765</v>
       </c>
     </row>
@@ -2544,25 +2544,25 @@
       <c r="A12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>36000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>61800</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>95481</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>122932</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>135061</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B7:B12)</f>
@@ -2589,19 +2589,19 @@
       <c r="A15" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>12883</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>12824</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>12978</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>13273</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>13647</v>
       </c>
     </row>
@@ -2673,19 +2673,19 @@
       <c r="A5" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>352690</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>435925</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>449003</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>462473</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>476347</v>
       </c>
     </row>
@@ -2693,19 +2693,19 @@
       <c r="A6" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>62173</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>76846</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>79151</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>81526</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>83971</v>
       </c>
     </row>
@@ -2713,19 +2713,19 @@
       <c r="A7" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>95738</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>118332</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>121881</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>125538</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>129304</v>
       </c>
     </row>
@@ -2733,23 +2733,23 @@
       <c r="A8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>510600</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>631102</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>650035</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>669536</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>689622</v>
       </c>
@@ -2768,19 +2768,19 @@
       <c r="A10" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>124346</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <v>153691</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>158302</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>163051</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>167943</v>
       </c>
     </row>
@@ -2788,19 +2788,19 @@
       <c r="A11" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>101738</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>125748</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>129520</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>133406</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>137408</v>
       </c>
     </row>
@@ -2808,19 +2808,19 @@
       <c r="A12" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>81390</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>100598</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>103616</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>106724</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>109926</v>
       </c>
     </row>
@@ -2828,23 +2828,23 @@
       <c r="A13" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
         <v>307473</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="30">
         <f>SUM(C10:C12)</f>
         <v>380037</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="30">
         <f>SUM(D10:D12)</f>
         <v>391438</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="30">
         <f>SUM(E10:E12)</f>
         <v>403181</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="30">
         <f>SUM(F10:F12)</f>
         <v>415277</v>
       </c>
@@ -2863,19 +2863,19 @@
       <c r="A15" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>62173</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>76846</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>79151</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>81526</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>83971</v>
       </c>
     </row>
@@ -2883,23 +2883,23 @@
       <c r="A16" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="30">
         <f>SUM(B15:B15)</f>
         <v>62173</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="30">
         <f>SUM(C15:C15)</f>
         <v>76846</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="30">
         <f>SUM(D15:D15)</f>
         <v>79151</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="30">
         <f>SUM(E15:E15)</f>
         <v>81526</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="30">
         <f>SUM(F15:F15)</f>
         <v>83971</v>
       </c>
@@ -2918,19 +2918,19 @@
       <c r="A18" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>62173</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="29">
         <v>76846</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <v>79151</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>81526</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>83971</v>
       </c>
     </row>
@@ -2938,23 +2938,23 @@
       <c r="A19" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="30">
         <f>SUM(B18:B18)</f>
         <v>62173</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="30">
         <f>SUM(C18:C18)</f>
         <v>76846</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="30">
         <f>SUM(D18:D18)</f>
         <v>79151</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="30">
         <f>SUM(E18:E18)</f>
         <v>81526</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="30">
         <f>SUM(F18:F18)</f>
         <v>83971</v>
       </c>
@@ -2973,19 +2973,19 @@
       <c r="A21" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>84012</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>103838</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>106954</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>110162</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>113467</v>
       </c>
     </row>
@@ -2993,23 +2993,23 @@
       <c r="A22" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="30">
         <f>SUM(B21:B21)</f>
         <v>84012</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="30">
         <f>SUM(C21:C21)</f>
         <v>103838</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="30">
         <f>SUM(D21:D21)</f>
         <v>106954</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="30">
         <f>SUM(E21:E21)</f>
         <v>110162</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="30">
         <f>SUM(F21:F21)</f>
         <v>113467</v>
       </c>
@@ -3107,19 +3107,19 @@
       <c r="A5" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>950000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>1957000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>3023565</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>3892840</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>4276933</v>
       </c>
     </row>
@@ -3127,19 +3127,19 @@
       <c r="A6" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>80000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>164800</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>254616</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>360163</v>
       </c>
     </row>
@@ -3147,19 +3147,19 @@
       <c r="A7" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>120000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>247200</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>381924</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>491727</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>540244</v>
       </c>
     </row>
@@ -3167,19 +3167,19 @@
       <c r="A8" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>83333</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>103000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>106090</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>109273</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>112551</v>
       </c>
     </row>
@@ -3187,19 +3187,19 @@
       <c r="A9" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>25000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>30900</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>31827</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>32782</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>33765</v>
       </c>
     </row>
@@ -3207,19 +3207,19 @@
       <c r="A10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>30000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <v>61800</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>95481</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>122932</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>135061</v>
       </c>
     </row>
@@ -3227,23 +3227,23 @@
       <c r="A11" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1288333</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="30">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="30">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="30">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="30">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
@@ -3262,19 +3262,19 @@
       <c r="A14" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>124346</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>153691</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>158302</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>163051</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>167943</v>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
       <c r="A15" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>101738</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>125748</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>129520</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>133406</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>137408</v>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
       <c r="A16" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>81390</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>100598</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>103616</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>106724</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>109926</v>
       </c>
     </row>
@@ -3322,19 +3322,19 @@
       <c r="A17" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="29">
         <v>352690</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <v>435925</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>449003</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>462473</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>476347</v>
       </c>
     </row>
@@ -3342,19 +3342,19 @@
       <c r="A18" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>62173</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="29">
         <v>76846</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <v>79151</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>81526</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>83971</v>
       </c>
     </row>
@@ -3362,19 +3362,19 @@
       <c r="A19" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>95738</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>118332</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>121881</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>125538</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>129304</v>
       </c>
     </row>
@@ -3382,19 +3382,19 @@
       <c r="A20" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>62173</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>76846</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>79151</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>81526</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>83971</v>
       </c>
     </row>
@@ -3402,19 +3402,19 @@
       <c r="A21" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>84012</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>103838</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>106954</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>110162</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>113467</v>
       </c>
     </row>
@@ -3422,43 +3422,43 @@
       <c r="A22" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>62173</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="29">
         <v>76846</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <v>79151</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>81526</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="29">
         <v>83971</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="B23" s="35">
+        <v>212</v>
+      </c>
+      <c r="B23" s="30">
         <f>SUM(B14:B22)</f>
         <v>1026431</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="30">
         <f>SUM(C14:C22)</f>
         <v>1268669</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="30">
         <f>SUM(D14:D22)</f>
         <v>1306729</v>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="30">
         <f>SUM(E14:E22)</f>
         <v>1345931</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="30">
         <f>SUM(F14:F22)</f>
         <v>1386309</v>
       </c>
@@ -3482,19 +3482,19 @@
       <c r="A27" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>70000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="29">
         <v>144200</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <v>222789</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <v>286841</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="29">
         <v>315142</v>
       </c>
     </row>
@@ -3507,19 +3507,19 @@
       <c r="A29" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>50000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <v>103000</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>159135</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>204886</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>225102</v>
       </c>
     </row>
@@ -3532,19 +3532,19 @@
       <c r="A31" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>180000</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="29">
         <v>222480</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>229154</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="29">
         <v>236029</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="29">
         <v>243110</v>
       </c>
     </row>
@@ -3552,19 +3552,19 @@
       <c r="A32" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>25000</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="29">
         <v>30900</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <v>31827</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="29">
         <v>32782</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="29">
         <v>33765</v>
       </c>
     </row>
@@ -3572,19 +3572,19 @@
       <c r="A33" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>15000</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="29">
         <v>18540</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="29">
         <v>19096</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="29">
         <v>19669</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="29">
         <v>20259</v>
       </c>
     </row>
@@ -3592,19 +3592,19 @@
       <c r="A34" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>15000</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="29">
         <v>18540</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <v>19096</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="29">
         <v>19669</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="29">
         <v>20259</v>
       </c>
     </row>
@@ -3612,23 +3612,23 @@
       <c r="A35" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="30">
         <f>SUM(B31:B34)</f>
         <v>235000</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="30">
         <f>SUM(C31:C34)</f>
         <v>290460</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="30">
         <f>SUM(D31:D34)</f>
         <v>299174</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="30">
         <f>SUM(E31:E34)</f>
         <v>308149</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="30">
         <f>SUM(F31:F34)</f>
         <v>317393</v>
       </c>
@@ -3642,19 +3642,19 @@
       <c r="A37" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>20833</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="29">
         <v>25750</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <v>26523</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="29">
         <v>27318</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="29">
         <v>28138</v>
       </c>
     </row>
@@ -3662,19 +3662,19 @@
       <c r="A38" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="29">
         <v>12500</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="29">
         <v>15450</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="29">
         <v>15914</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="29">
         <v>16391</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="29">
         <v>16883</v>
       </c>
     </row>
@@ -3682,19 +3682,19 @@
       <c r="A39" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>16667</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="29">
         <v>20600</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="29">
         <v>21218</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="29">
         <v>21855</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="29">
         <v>22510</v>
       </c>
     </row>
@@ -3702,19 +3702,19 @@
       <c r="A40" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>80000</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="29">
         <v>164800</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="29">
         <v>254616</v>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="29">
         <v>327818</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="29">
         <v>360163</v>
       </c>
     </row>
@@ -3722,19 +3722,19 @@
       <c r="A41" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>60000</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="29">
         <v>123600</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <v>190962</v>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="29">
         <v>245864</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="29">
         <v>270122</v>
       </c>
     </row>
@@ -3742,23 +3742,23 @@
       <c r="A42" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="30">
         <f>SUM(B37:B41)</f>
         <v>190000</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="30">
         <f>SUM(C37:C41)</f>
         <v>350200</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="30">
         <f>SUM(D37:D41)</f>
         <v>509232</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="30">
         <f>SUM(E37:E41)</f>
         <v>639245</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="30">
         <f>SUM(F37:F41)</f>
         <v>697815</v>
       </c>
@@ -3767,23 +3767,23 @@
       <c r="A43" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="30">
         <f>B27+B29+B35+B42</f>
         <v>545000</v>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="30">
         <f>C27+C29+C35+C42</f>
         <v>887860</v>
       </c>
-      <c r="D43" s="35">
+      <c r="D43" s="30">
         <f>D27+D29+D35+D42</f>
         <v>1190330</v>
       </c>
-      <c r="E43" s="35">
+      <c r="E43" s="30">
         <f>E27+E29+E35+E42</f>
         <v>1439121</v>
       </c>
-      <c r="F43" s="35">
+      <c r="F43" s="30">
         <f>F27+F29+F35+F42</f>
         <v>1555453</v>
       </c>
@@ -3802,19 +3802,19 @@
       <c r="A46" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="29">
         <v>49825</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="29">
         <v>49825</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="29">
         <v>49825</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="29">
         <v>49825</v>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="29">
         <v>49825</v>
       </c>
     </row>
@@ -3822,19 +3822,19 @@
       <c r="A47" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="29">
         <v>75000</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="29">
         <v>25000</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="29">
         <v>30000</v>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="29">
         <v>15000</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -3842,19 +3842,19 @@
       <c r="A48" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="29">
         <v>40000</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="29">
         <v>15000</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="29">
         <v>10000</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="29">
         <v>10000</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -3862,23 +3862,23 @@
       <c r="A49" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B49" s="35">
+      <c r="B49" s="30">
         <f>SUM(B46:B48)</f>
         <v>164825</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="30">
         <f>SUM(C46:C48)</f>
         <v>89825</v>
       </c>
-      <c r="D49" s="35">
+      <c r="D49" s="30">
         <f>SUM(D46:D48)</f>
         <v>89825</v>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="30">
         <f>SUM(E46:E48)</f>
         <v>74825</v>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="30">
         <f>SUM(F46:F48)</f>
         <v>69825</v>
       </c>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B23</f>
@@ -4041,23 +4041,23 @@
       <c r="A8" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>1736256</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>2246354</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>2586884</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>2859877</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>3011587</v>
       </c>
@@ -4101,23 +4101,23 @@
       <c r="A12" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="28">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.44829778</v>
       </c>
@@ -4126,19 +4126,19 @@
       <c r="A13" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>-447923</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>-129576</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>1177043</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>3294538</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>5741669</v>
       </c>
     </row>
@@ -4146,19 +4146,19 @@
       <c r="A14" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>10736</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>12824</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>12978</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>13273</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>13647</v>
       </c>
     </row>
@@ -4166,19 +4166,19 @@
       <c r="A15" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>14469</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>11232</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>8623</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>7626</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>7529</v>
       </c>
     </row>
@@ -4291,43 +4291,43 @@
       <c r="A4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="30">
         <v>154600</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="30">
         <v>154600</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="30">
         <v>154600</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="30">
         <v>154600</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="30">
         <v>154600</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="30">
         <v>154600</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="30">
         <v>154600</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="30">
         <v>154600</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>154600</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="30">
         <v>154600</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="30">
         <v>0</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="30">
         <v>0</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="30">
         <f>SUM(B4:M4)</f>
         <v>1546000</v>
       </c>
@@ -4354,43 +4354,43 @@
       <c r="A7" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>102643</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>102643</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>102643</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>102643</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>102643</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="29">
         <v>102643</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="29">
         <v>102643</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <v>102643</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>102643</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="29">
         <v>102643</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="29">
         <v>0</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="29">
         <v>0</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>1026431</v>
       </c>
@@ -4399,43 +4399,43 @@
       <c r="A8" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>54500</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>54500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>54500</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>54500</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>54500</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="29">
         <v>54500</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="29">
         <v>54500</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <v>54500</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="29">
         <v>54500</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="29">
         <v>54500</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="29">
         <v>0</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="29">
         <v>0</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>545000</v>
       </c>
@@ -4444,43 +4444,43 @@
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>13735</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>13735</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>13735</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>13735</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>13735</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="29">
         <v>13735</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="29">
         <v>13735</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>13735</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>13735</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="29">
         <v>13735</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="29">
         <v>13735</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="29">
         <v>13735</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>164825</v>
       </c>
@@ -4702,7 +4702,7 @@
       <c r="A19" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <f>MIN(B14:M14)</f>
         <v>-190250</v>
       </c>
@@ -4775,19 +4775,19 @@
       <c r="A5" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="30">
         <v>1288333</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="30">
         <v>2564700</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="30">
         <v>3893503</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="30">
         <v>4977371</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="30">
         <v>5458718</v>
       </c>
     </row>
@@ -4865,23 +4865,23 @@
       <c r="A11" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
         <v>1736256</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="30">
         <f>SUM(C8:C10)</f>
         <v>2246354</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="30">
         <f>SUM(D8:D10)</f>
         <v>2586884</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="30">
         <f>SUM(E8:E10)</f>
         <v>2859877</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="30">
         <f>SUM(F8:F10)</f>
         <v>3011587</v>
       </c>
@@ -4925,23 +4925,23 @@
       <c r="A15" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="28">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="28">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.44829778</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>324</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
       <c r="D6" s="19">
         <v>15</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>49825</v>
       </c>
@@ -5059,23 +5059,23 @@
       <c r="A9" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>B6</f>
         <v>500000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <f>B13</f>
         <v>478361</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <f>C13</f>
         <v>455444</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <f>D13</f>
         <v>431175</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <f>E13</f>
         <v>405473</v>
       </c>
@@ -5084,23 +5084,23 @@
       <c r="A10" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>28186</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>26908</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>25555</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>24122</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>22605</v>
       </c>
@@ -5109,23 +5109,23 @@
       <c r="A11" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>21639</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>22917</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>24270</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>25702</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>27220</v>
       </c>
@@ -5273,19 +5273,19 @@
       <c r="A6" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>0</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>0</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>0</v>
       </c>
     </row>
@@ -5293,19 +5293,19 @@
       <c r="A7" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>0</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>0</v>
       </c>
     </row>
@@ -5313,19 +5313,19 @@
       <c r="A8" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>0</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>0</v>
       </c>
     </row>
@@ -5333,23 +5333,23 @@
       <c r="A9" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>-190250</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="30">
         <f>SUM(C5:C8)</f>
         <v>128096</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="30">
         <f>SUM(D5:D8)</f>
         <v>1434716</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="30">
         <f>SUM(E5:E8)</f>
         <v>3552210</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="30">
         <f>SUM(F5:F8)</f>
         <v>5999341</v>
       </c>
@@ -5368,19 +5368,19 @@
       <c r="A12" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>0</v>
       </c>
     </row>
@@ -5388,23 +5388,23 @@
       <c r="A13" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>'Debt Schedule'!B13</f>
         <v>478361</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <f>'Debt Schedule'!C13</f>
         <v>455444</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <f>'Debt Schedule'!D13</f>
         <v>431175</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <f>'Debt Schedule'!E13</f>
         <v>405473</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <f>'Debt Schedule'!F13</f>
         <v>378253</v>
       </c>
@@ -5413,23 +5413,23 @@
       <c r="A14" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="30">
         <f>SUM(B12:B13)</f>
         <v>478361</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="30">
         <f>SUM(C12:C13)</f>
         <v>455444</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="30">
         <f>SUM(D12:D13)</f>
         <v>431175</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="30">
         <f>SUM(E12:E13)</f>
         <v>405473</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="30">
         <f>SUM(F12:F13)</f>
         <v>378253</v>
       </c>
@@ -5562,19 +5562,19 @@
       <c r="A5" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>1288333</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>2564700</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>3893503</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>4977371</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>5458718</v>
       </c>
     </row>
@@ -5582,19 +5582,19 @@
       <c r="A6" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>1026431</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>1268669</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>1306729</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>1345931</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>1386309</v>
       </c>
     </row>
@@ -5602,19 +5602,19 @@
       <c r="A7" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>545000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>887860</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>1190330</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>1439121</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>1555453</v>
       </c>
     </row>
@@ -5647,19 +5647,19 @@
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>49825</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>49825</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>49825</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>49825</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>49825</v>
       </c>
     </row>
@@ -5702,19 +5702,19 @@
       <c r="A13" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>-190250</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>128096</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>1434716</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>3552210</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>5999341</v>
       </c>
     </row>
@@ -5722,23 +5722,23 @@
       <c r="A14" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="35">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>-43</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="35">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>21</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="35">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>206</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="35">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>457</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="35">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>732</v>
       </c>
@@ -5772,19 +5772,19 @@
       <c r="A16" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <v>0.3</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="28">
         <v>0.5</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <v>0.75</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="28">
         <v>0.9375</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5802,19 +5802,19 @@
       <c r="A19" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>10736</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>12824</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>12978</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>13273</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>13647</v>
       </c>
     </row>
@@ -5822,19 +5822,19 @@
       <c r="A20" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>1076256</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>1318494</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>1356554</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>1395756</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>1436134</v>
       </c>
     </row>
@@ -5842,19 +5842,19 @@
       <c r="A21" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>4542</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>4439</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>3968</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>3838</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>3889</v>
       </c>
     </row>
@@ -6042,13 +6042,13 @@
       <c r="A4" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="29">
         <v>400000</v>
       </c>
     </row>
@@ -6056,13 +6056,13 @@
       <c r="A5" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>75000</v>
       </c>
     </row>
@@ -6070,13 +6070,13 @@
       <c r="A6" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>40000</v>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       <c r="D7" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>60000</v>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       <c r="D8" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>75000</v>
       </c>
     </row>
@@ -6507,19 +6507,19 @@
       <c r="A6" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>1288333</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>2564700</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>3893503</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>4977371</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>5458718</v>
       </c>
     </row>
@@ -6527,19 +6527,19 @@
       <c r="A7" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>1621256</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>2206354</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>2546884</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>2834877</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>2991587</v>
       </c>
     </row>
@@ -6567,19 +6567,19 @@
       <c r="A9" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="28">
         <v>-0.2584133416981985</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <v>0.1397225288645145</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>0.3458632236905482</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>0.43044696555461553</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>0.4519616461017463</v>
       </c>
     </row>
@@ -6607,19 +6607,19 @@
       <c r="A11" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="35">
         <v>174</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="35">
         <v>158</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="35">
         <v>151</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="35">
         <v>148</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="35">
         <v>148</v>
       </c>
     </row>
@@ -6662,19 +6662,19 @@
       <c r="A16" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>966250</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>1923525</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>2920127</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>3733029</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>4094038</v>
       </c>
     </row>
@@ -6682,19 +6682,19 @@
       <c r="A17" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="29">
         <v>1621256</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <v>2206354</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>2546884</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>2834877</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>2991587</v>
       </c>
     </row>
@@ -6722,19 +6722,19 @@
       <c r="A19" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="28">
         <v>-0.677884455597598</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="28">
         <v>-0.14703662818064733</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <v>0.12781763158739762</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="28">
         <v>0.2405959540728207</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <v>0.26928219480232835</v>
       </c>
     </row>
@@ -6762,19 +6762,19 @@
       <c r="A21" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="35">
         <v>230</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="35">
         <v>191</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="35">
         <v>177</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="35">
         <v>171</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="35">
         <v>170</v>
       </c>
     </row>
@@ -6817,19 +6817,19 @@
       <c r="A26" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>1223917</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="29">
         <v>2436465</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <v>3698828</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <v>4728503</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <v>5185782</v>
       </c>
     </row>
@@ -6837,19 +6837,19 @@
       <c r="A27" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>1621256</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="29">
         <v>2206354</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <v>2546884</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <v>2834877</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="29">
         <v>2991587</v>
       </c>
     </row>
@@ -6877,19 +6877,19 @@
       <c r="A29" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <v>-0.3246456228402091</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="28">
         <v>0.09444476722580472</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="28">
         <v>0.31143497230584016</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="28">
         <v>0.40047049005748997</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="28">
         <v>0.4231175222123644</v>
       </c>
     </row>
@@ -6917,19 +6917,19 @@
       <c r="A31" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="35">
         <v>191</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="35">
         <v>171</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="35">
         <v>163</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="35">
         <v>160</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="35">
         <v>159</v>
       </c>
     </row>
@@ -6972,19 +6972,19 @@
       <c r="A36" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>1288333</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="29">
         <v>2564700</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>3893503</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="29">
         <v>4977371</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="29">
         <v>5458718</v>
       </c>
     </row>
@@ -6992,19 +6992,19 @@
       <c r="A37" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>1667756</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="29">
         <v>2295964</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <v>2680557</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="29">
         <v>3004523</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="29">
         <v>3177296</v>
       </c>
     </row>
@@ -7032,19 +7032,19 @@
       <c r="A39" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="28">
         <v>-0.2945064852945763</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="28">
         <v>0.10478276982836991</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="28">
         <v>0.31153079862242844</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="28">
         <v>0.3963635407467121</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="28">
         <v>0.4179410275450453</v>
       </c>
     </row>
@@ -7072,19 +7072,19 @@
       <c r="A41" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="35">
         <v>186</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="35">
         <v>167</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="35">
         <v>159</v>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="35">
         <v>156</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="35">
         <v>155</v>
       </c>
     </row>
@@ -7222,19 +7222,19 @@
       <c r="A13" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>1288333</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>2564700</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>3893503</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <v>4977371</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="29">
         <v>5458718</v>
       </c>
     </row>
@@ -7242,19 +7242,19 @@
       <c r="A14" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>1621256</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>2206354</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>2546884</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="29">
         <v>2834877</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="29">
         <v>2991587</v>
       </c>
     </row>
@@ -7262,19 +7262,19 @@
       <c r="A15" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>-447923</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>318346</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>1306619</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="29">
         <v>2117494</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="29">
         <v>2447131</v>
       </c>
     </row>
@@ -7282,19 +7282,19 @@
       <c r="A16" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>-190250</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>128096</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>1434716</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="29">
         <v>3552210</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="29">
         <v>5999341</v>
       </c>
     </row>
@@ -7302,19 +7302,19 @@
       <c r="A17" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>478361</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>455444</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>431175</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="29">
         <v>405473</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="29">
         <v>378253</v>
       </c>
     </row>
@@ -7360,19 +7360,19 @@
       <c r="A21" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="28">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="28">
         <v>0.12412616281780338</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>0.33558969879535744</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>0.42542423416409325</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <v>0.44829778198663</v>
       </c>
     </row>
@@ -7400,19 +7400,19 @@
       <c r="A23" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <v>0.3</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="28">
         <v>0.5</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <v>0.75</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28">
         <v>0.9375</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="28">
         <v>1</v>
       </c>
     </row>
@@ -7420,19 +7420,19 @@
       <c r="A24" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="35">
         <v>120</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="35">
         <v>200</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="35">
         <v>300</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="35">
         <v>375</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="35">
         <v>400</v>
       </c>
     </row>
@@ -9177,7 +9177,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="21">
         <v>400</v>
       </c>
     </row>
@@ -9185,19 +9185,24 @@
       <c r="A8" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
+        <f>B6/$B$7</f>
         <v>0.3</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
+        <f>C6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
+        <f>D6/$B$7</f>
         <v>0.75</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
+        <f>E6/$B$7</f>
         <v>0.9375</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
+        <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
@@ -9208,17 +9213,21 @@
       <c r="B10" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="29">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="D10" s="29">
+      <c r="C10" s="28">
+        <f>IF(B6=0,0,(C6-B6)/B6)</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="D10" s="28">
+        <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="28">
+        <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.25</v>
       </c>
-      <c r="F10" s="29">
-        <v>0.06666666666666667</v>
+      <c r="F10" s="28">
+        <f>IF(E6=0,0,(F6-E6)/E6)</f>
+        <v>0.06666667</v>
       </c>
     </row>
   </sheetData>
@@ -9238,10 +9247,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9287,146 +9296,241 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="30">
+        <v>113</v>
+      </c>
+      <c r="B5" s="29">
         <v>1140000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>1957000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>3023565</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>3892840</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>4276933</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="30">
+        <v>116</v>
+      </c>
+      <c r="B6" s="29">
         <v>96000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>164800</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>254616</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>360163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="30">
+        <v>117</v>
+      </c>
+      <c r="B7" s="29">
         <v>144000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>247200</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>381924</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>491727</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>540244</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>206</v>
+      <c r="A8" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="B8" s="30">
-        <v>100000</v>
+        <f>SUBTOTAL(9,B5:B7)</f>
+        <v>1380000</v>
       </c>
       <c r="C8" s="30">
-        <v>103000</v>
+        <f>SUBTOTAL(9,C5:C7)</f>
+        <v>2369000</v>
       </c>
       <c r="D8" s="30">
-        <v>106090</v>
+        <f>SUBTOTAL(9,D5:D7)</f>
+        <v>3660105</v>
       </c>
       <c r="E8" s="30">
-        <v>109273</v>
+        <f>SUBTOTAL(9,E5:E7)</f>
+        <v>4712385</v>
       </c>
       <c r="F8" s="30">
-        <v>112551</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="30">
-        <v>30000</v>
-      </c>
-      <c r="C9" s="30">
-        <v>30900</v>
-      </c>
-      <c r="D9" s="30">
-        <v>31827</v>
-      </c>
-      <c r="E9" s="30">
-        <v>32782</v>
-      </c>
-      <c r="F9" s="30">
-        <v>33765</v>
-      </c>
+        <f>SUBTOTAL(9,F5:F7)</f>
+        <v>5177341</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="22">
+        <v>100000</v>
+      </c>
+      <c r="C10" s="29">
+        <v>103000</v>
+      </c>
+      <c r="D10" s="29">
+        <v>106090</v>
+      </c>
+      <c r="E10" s="29">
+        <v>109273</v>
+      </c>
+      <c r="F10" s="29">
+        <v>112551</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="22">
+        <v>30000</v>
+      </c>
+      <c r="C11" s="29">
+        <v>30900</v>
+      </c>
+      <c r="D11" s="29">
+        <v>31827</v>
+      </c>
+      <c r="E11" s="29">
+        <v>32782</v>
+      </c>
+      <c r="F11" s="29">
+        <v>33765</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="30">
+        <f>SUBTOTAL(9,B10:B11)</f>
+        <v>130000</v>
+      </c>
+      <c r="C12" s="30">
+        <f>SUBTOTAL(9,C10:C11)</f>
+        <v>133900</v>
+      </c>
+      <c r="D12" s="30">
+        <f>SUBTOTAL(9,D10:D11)</f>
+        <v>137917</v>
+      </c>
+      <c r="E12" s="30">
+        <f>SUBTOTAL(9,E10:E11)</f>
+        <v>142055</v>
+      </c>
+      <c r="F12" s="30">
+        <f>SUBTOTAL(9,F10:F11)</f>
+        <v>146316</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="29">
+        <v>36000</v>
+      </c>
+      <c r="C14" s="29">
+        <v>61800</v>
+      </c>
+      <c r="D14" s="29">
+        <v>95481</v>
+      </c>
+      <c r="E14" s="29">
+        <v>122932</v>
+      </c>
+      <c r="F14" s="29">
+        <v>135061</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="30">
+        <f>SUBTOTAL(9,B14:B14)</f>
+        <v>36000</v>
+      </c>
+      <c r="C15" s="30">
+        <f>SUBTOTAL(9,C14:C14)</f>
+        <v>61800</v>
+      </c>
+      <c r="D15" s="30">
+        <f>SUBTOTAL(9,D14:D14)</f>
+        <v>95481</v>
+      </c>
+      <c r="E15" s="30">
+        <f>SUBTOTAL(9,E14:E14)</f>
+        <v>122932</v>
+      </c>
+      <c r="F15" s="30">
+        <f>SUBTOTAL(9,F14:F14)</f>
+        <v>135061</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="30">
-        <v>36000</v>
-      </c>
-      <c r="C10" s="30">
-        <v>61800</v>
-      </c>
-      <c r="D10" s="30">
-        <v>95481</v>
-      </c>
-      <c r="E10" s="30">
-        <v>122932</v>
-      </c>
-      <c r="F10" s="30">
-        <v>135061</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="31">
-        <f>SUM(B5:B10)</f>
+      <c r="B17" s="31">
+        <f>SUM(B8,B12,B15)</f>
         <v>1546000</v>
       </c>
-      <c r="C11" s="31">
-        <f>SUM(C5:C10)</f>
+      <c r="C17" s="31">
+        <f>SUM(C8,C12,C15)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="31">
-        <f>SUM(D5:D10)</f>
+      <c r="D17" s="31">
+        <f>SUM(D8,D12,D15)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="31">
-        <f>SUM(E5:E10)</f>
+      <c r="E17" s="31">
+        <f>SUM(E8,E12,E15)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="31">
-        <f>SUM(F5:F10)</f>
+      <c r="F17" s="31">
+        <f>SUM(F8,F12,F15)</f>
         <v>5458718</v>
       </c>
     </row>
@@ -9480,7 +9584,7 @@
         <v>127</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>129</v>
@@ -9489,7 +9593,7 @@
         <v>130</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9502,13 +9606,13 @@
       <c r="C4" s="32">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>110000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="28">
         <v>0.28</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <v>0.0765</v>
       </c>
       <c r="G4" s="33">
@@ -9525,13 +9629,13 @@
       <c r="C5" s="32">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>90000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="28">
         <v>0.28</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="28">
         <v>0.0765</v>
       </c>
       <c r="G5" s="33">
@@ -9548,13 +9652,13 @@
       <c r="C6" s="32">
         <v>1</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>72000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="28">
         <v>0.28</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="28">
         <v>0.0765</v>
       </c>
       <c r="G6" s="33">
@@ -9571,13 +9675,13 @@
       <c r="C7" s="32">
         <v>6</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>52000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <v>0.28</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <v>0.0765</v>
       </c>
       <c r="G7" s="33">
@@ -9594,13 +9698,13 @@
       <c r="C8" s="32">
         <v>1</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>55000</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
         <v>0.28</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <v>0.0765</v>
       </c>
       <c r="G8" s="33">
@@ -9617,13 +9721,13 @@
       <c r="C9" s="32">
         <v>3</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>30000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>0.2</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>0.0765</v>
       </c>
       <c r="G9" s="33">
@@ -9640,13 +9744,13 @@
       <c r="C10" s="32">
         <v>1</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>55000</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="28">
         <v>0.28</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="28">
         <v>0.0765</v>
       </c>
       <c r="G10" s="33">
@@ -9663,13 +9767,13 @@
       <c r="C11" s="32">
         <v>2</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>38000</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="28">
         <v>0.25</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>0.0765</v>
       </c>
       <c r="G11" s="33">
@@ -9686,13 +9790,13 @@
       <c r="C12" s="32">
         <v>1</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>55000</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="28">
         <v>0.28</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <v>0.0765</v>
       </c>
       <c r="G12" s="33">
@@ -9701,7 +9805,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -9732,7 +9836,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="31">
         <v>1026431</v>
@@ -9752,27 +9856,27 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" s="29">
+        <v>213</v>
+      </c>
+      <c r="B17" s="28">
         <v>0.6639270698576973</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="28">
         <v>0.49466566265060247</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="28">
         <v>0.3356178474114441</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="28">
         <v>0.27040998902305163</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <v>0.25396237113402065</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B18" s="34">
         <v>7.1</v>
@@ -9816,7 +9920,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9856,45 +9960,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="30">
+        <v>216</v>
+      </c>
+      <c r="B5" s="29">
         <v>84000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>144200</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>222789</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>286841</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>315142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="35">
+        <v>217</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
         <v>84000</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="30">
         <f>SUM(C5:C5)</f>
         <v>144200</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="30">
         <f>SUM(D5:D5)</f>
         <v>222789</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="30">
         <f>SUM(E5:E5)</f>
         <v>286841</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="30">
         <f>SUM(F5:F5)</f>
         <v>315142</v>
       </c>
@@ -9911,45 +10015,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="30">
+        <v>218</v>
+      </c>
+      <c r="B8" s="29">
         <v>60000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>103000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>159135</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>204886</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>225102</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="35">
+        <v>219</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>103000</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>159135</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>204886</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>225102</v>
       </c>
@@ -9966,105 +10070,105 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="30">
+        <v>220</v>
+      </c>
+      <c r="B11" s="29">
         <v>216000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>222480</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>229154</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>236029</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>243110</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="30">
+        <v>221</v>
+      </c>
+      <c r="B12" s="29">
         <v>30000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>30900</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>31827</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>32782</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" s="30">
+        <v>222</v>
+      </c>
+      <c r="B13" s="29">
         <v>18000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>18540</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>19096</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>19669</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>20259</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="30">
+        <v>223</v>
+      </c>
+      <c r="B14" s="29">
         <v>18000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>18540</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>19096</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>19669</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>20259</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" s="35">
+        <v>224</v>
+      </c>
+      <c r="B15" s="30">
         <f>SUM(B11:B14)</f>
         <v>282000</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="30">
         <f>SUM(C11:C14)</f>
         <v>290460</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="30">
         <f>SUM(D11:D14)</f>
         <v>299174</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="30">
         <f>SUM(E11:E14)</f>
         <v>308149</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="30">
         <f>SUM(F11:F14)</f>
         <v>317393</v>
       </c>
@@ -10081,132 +10185,132 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="30">
+        <v>225</v>
+      </c>
+      <c r="B17" s="29">
         <v>25000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <v>25750</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>26523</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>27318</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>28138</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="30">
+        <v>226</v>
+      </c>
+      <c r="B18" s="29">
         <v>15000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="29">
         <v>15450</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <v>15914</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>16391</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>16883</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B19" s="30">
+        <v>227</v>
+      </c>
+      <c r="B19" s="29">
         <v>20000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>20600</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>21218</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>21855</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>22510</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B20" s="30">
+        <v>228</v>
+      </c>
+      <c r="B20" s="29">
         <v>96000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>164800</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>254616</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>327818</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>360163</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="30">
+        <v>229</v>
+      </c>
+      <c r="B21" s="29">
         <v>72000</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>123600</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>190962</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>245864</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>270122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" s="35">
+        <v>230</v>
+      </c>
+      <c r="B22" s="30">
         <f>SUM(B17:B21)</f>
         <v>228000</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="30">
         <f>SUM(C17:C21)</f>
         <v>350200</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="30">
         <f>SUM(D17:D21)</f>
         <v>509232</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="30">
         <f>SUM(E17:E21)</f>
         <v>639245</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="30">
         <f>SUM(F17:F21)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" s="31">
         <f>B6+B9+B15+B22</f>
@@ -10256,7 +10360,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10281,7 +10385,7 @@
         <v>165</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10294,10 +10398,10 @@
       <c r="C4" s="22">
         <v>500000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="28">
         <v>0.0575</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="35">
         <v>15</v>
       </c>
       <c r="F4" s="33">
@@ -10309,15 +10413,15 @@
         <v>168</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="22">
         <v>75000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="28">
         <v>0</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="35">
         <v>0</v>
       </c>
       <c r="F5" s="33">
@@ -10329,15 +10433,15 @@
         <v>170</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="22">
         <v>40000</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="28">
         <v>0</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="35">
         <v>0</v>
       </c>
       <c r="F6" s="33">
@@ -10346,7 +10450,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F8" s="31">
         <v>49825</v>
@@ -10354,9 +10458,9 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" s="35">
+        <v>236</v>
+      </c>
+      <c r="F9" s="30">
         <v>500000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -9359,23 +9359,23 @@
         <v>203</v>
       </c>
       <c r="B8" s="30">
-        <f>SUBTOTAL(9,B5:B7)</f>
+        <f>SUM(B5,B6,B7)</f>
         <v>1380000</v>
       </c>
       <c r="C8" s="30">
-        <f>SUBTOTAL(9,C5:C7)</f>
+        <f>SUM(C5,C6,C7)</f>
         <v>2369000</v>
       </c>
       <c r="D8" s="30">
-        <f>SUBTOTAL(9,D5:D7)</f>
+        <f>SUM(D5,D6,D7)</f>
         <v>3660105</v>
       </c>
       <c r="E8" s="30">
-        <f>SUBTOTAL(9,E5:E7)</f>
+        <f>SUM(E5,E6,E7)</f>
         <v>4712385</v>
       </c>
       <c r="F8" s="30">
-        <f>SUBTOTAL(9,F5:F7)</f>
+        <f>SUM(F5,F6,F7)</f>
         <v>5177341</v>
       </c>
     </row>
@@ -9434,23 +9434,23 @@
         <v>205</v>
       </c>
       <c r="B12" s="30">
-        <f>SUBTOTAL(9,B10:B11)</f>
+        <f>SUM(B10,B11)</f>
         <v>130000</v>
       </c>
       <c r="C12" s="30">
-        <f>SUBTOTAL(9,C10:C11)</f>
+        <f>SUM(C10,C11)</f>
         <v>133900</v>
       </c>
       <c r="D12" s="30">
-        <f>SUBTOTAL(9,D10:D11)</f>
+        <f>SUM(D10,D11)</f>
         <v>137917</v>
       </c>
       <c r="E12" s="30">
-        <f>SUBTOTAL(9,E10:E11)</f>
+        <f>SUM(E10,E11)</f>
         <v>142055</v>
       </c>
       <c r="F12" s="30">
-        <f>SUBTOTAL(9,F10:F11)</f>
+        <f>SUM(F10,F11)</f>
         <v>146316</v>
       </c>
     </row>
@@ -9489,23 +9489,23 @@
         <v>207</v>
       </c>
       <c r="B15" s="30">
-        <f>SUBTOTAL(9,B14:B14)</f>
+        <f>SUM(B14)</f>
         <v>36000</v>
       </c>
       <c r="C15" s="30">
-        <f>SUBTOTAL(9,C14:C14)</f>
+        <f>SUM(C14)</f>
         <v>61800</v>
       </c>
       <c r="D15" s="30">
-        <f>SUBTOTAL(9,D14:D14)</f>
+        <f>SUM(D14)</f>
         <v>95481</v>
       </c>
       <c r="E15" s="30">
-        <f>SUBTOTAL(9,E14:E14)</f>
+        <f>SUM(E14)</f>
         <v>122932</v>
       </c>
       <c r="F15" s="30">
-        <f>SUBTOTAL(9,F14:F14)</f>
+        <f>SUM(F14)</f>
         <v>135061</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="442">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -316,7 +316,10 @@
     <t>Civic Scholars Charter - Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1498,7 +1501,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1517,6 +1520,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -1531,7 +1539,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1549,6 +1557,15 @@
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
@@ -1598,9 +1615,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1608,20 +1626,19 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1636,13 +1653,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1651,22 +1668,22 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2382,7 +2399,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2391,28 +2408,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="36">
         <v>120</v>
@@ -2431,177 +2448,177 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="29">
+        <v>114</v>
+      </c>
+      <c r="B7" s="30">
         <v>1140000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>1957000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>3023565</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>3892840</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>4276933</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="29">
+        <v>117</v>
+      </c>
+      <c r="B8" s="30">
         <v>96000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>164800</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>254616</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>327818</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>360163</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="29">
+        <v>118</v>
+      </c>
+      <c r="B9" s="30">
         <v>144000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>247200</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>381924</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>491727</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>540244</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="29">
+        <v>119</v>
+      </c>
+      <c r="B10" s="30">
         <v>100000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>103000</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>106090</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>109273</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>112551</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="29">
+        <v>122</v>
+      </c>
+      <c r="B11" s="30">
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>31827</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>32782</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="29">
+        <v>123</v>
+      </c>
+      <c r="B12" s="30">
         <v>36000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>61800</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>95481</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>122932</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B13" s="31">
+      <c r="A13" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" s="32">
         <f>SUM(B7:B12)</f>
         <v>1546000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C7:C12)</f>
         <v>2564700</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D7:D12)</f>
         <v>3893503</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E7:E12)</f>
         <v>4977371</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F7:F12)</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B15" s="29">
+        <v>241</v>
+      </c>
+      <c r="B15" s="30">
         <v>12883</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>12824</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>12978</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>13273</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>13647</v>
       </c>
     </row>
@@ -2631,7 +2648,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2640,401 +2657,401 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B5" s="29">
+        <v>243</v>
+      </c>
+      <c r="B5" s="30">
         <v>352690</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>435925</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>449003</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>462473</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>476347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="29">
+        <v>244</v>
+      </c>
+      <c r="B6" s="30">
         <v>62173</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>76846</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>79151</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>81526</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B7" s="29">
+        <v>245</v>
+      </c>
+      <c r="B7" s="30">
         <v>95738</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>118332</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>121881</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>125538</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>129304</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="30">
+        <v>246</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>510600</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>631102</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>650035</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>669536</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>689622</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="29">
+        <v>247</v>
+      </c>
+      <c r="B10" s="30">
         <v>124346</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>153691</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>158302</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>163051</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>167943</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="29">
+        <v>248</v>
+      </c>
+      <c r="B11" s="30">
         <v>101738</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>125748</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>129520</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>133406</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>137408</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B12" s="29">
+        <v>249</v>
+      </c>
+      <c r="B12" s="30">
         <v>81390</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>100598</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>103616</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>106724</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>109926</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" s="30">
+        <v>250</v>
+      </c>
+      <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
         <v>307473</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUM(C10:C12)</f>
         <v>380037</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUM(D10:D12)</f>
         <v>391438</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUM(E10:E12)</f>
         <v>403181</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>SUM(F10:F12)</f>
         <v>415277</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B15" s="29">
+        <v>251</v>
+      </c>
+      <c r="B15" s="30">
         <v>62173</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>76846</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>79151</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>81526</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B16" s="30">
+        <v>252</v>
+      </c>
+      <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
         <v>62173</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>SUM(C15:C15)</f>
         <v>76846</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>SUM(D15:D15)</f>
         <v>79151</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>SUM(E15:E15)</f>
         <v>81526</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>SUM(F15:F15)</f>
         <v>83971</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B18" s="29">
+        <v>253</v>
+      </c>
+      <c r="B18" s="30">
         <v>62173</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>76846</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>79151</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>81526</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="30">
+        <v>254</v>
+      </c>
+      <c r="B19" s="31">
         <f>SUM(B18:B18)</f>
         <v>62173</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>SUM(C18:C18)</f>
         <v>76846</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>SUM(D18:D18)</f>
         <v>79151</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>SUM(E18:E18)</f>
         <v>81526</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>SUM(F18:F18)</f>
         <v>83971</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B21" s="29">
+        <v>255</v>
+      </c>
+      <c r="B21" s="30">
         <v>84012</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>103838</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>106954</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>110162</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>113467</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="B22" s="30">
+        <v>256</v>
+      </c>
+      <c r="B22" s="31">
         <f>SUM(B21:B21)</f>
         <v>84012</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>SUM(C21:C21)</f>
         <v>103838</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>SUM(D21:D21)</f>
         <v>106954</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>SUM(E21:E21)</f>
         <v>110162</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>SUM(F21:F21)</f>
         <v>113467</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="32">
         <f>B8+B13+B16+B19+B22</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>C8+C13+C16+C19+C22</f>
         <v>1268669</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>D8+D13+D16+D19+D22</f>
         <v>1306729</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>E8+E13+E16+E19+E22</f>
         <v>1345931</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>F8+F13+F16+F19+F22</f>
         <v>1386309</v>
       </c>
@@ -3065,7 +3082,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3074,811 +3091,811 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="29">
+        <v>260</v>
+      </c>
+      <c r="B5" s="30">
         <v>950000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>1957000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3023565</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>3892840</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>4276933</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="29">
+        <v>261</v>
+      </c>
+      <c r="B6" s="30">
         <v>80000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>164800</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>254616</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>360163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="29">
+        <v>262</v>
+      </c>
+      <c r="B7" s="30">
         <v>120000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>247200</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>381924</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>491727</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>540244</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="29">
+        <v>263</v>
+      </c>
+      <c r="B8" s="30">
         <v>83333</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>103000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>106090</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>109273</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>112551</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="29">
+        <v>264</v>
+      </c>
+      <c r="B9" s="30">
         <v>25000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>30900</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>31827</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>32782</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="29">
+        <v>265</v>
+      </c>
+      <c r="B10" s="30">
         <v>30000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>61800</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>95481</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>122932</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="30">
+        <v>266</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
         <v>1288333</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C5:C10)</f>
         <v>2564700</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D5:D10)</f>
         <v>3893503</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E5:E10)</f>
         <v>4977371</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F5:F10)</f>
         <v>5458718</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="29">
+        <v>247</v>
+      </c>
+      <c r="B14" s="30">
         <v>124346</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>153691</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>158302</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>163051</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>167943</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" s="29">
+        <v>248</v>
+      </c>
+      <c r="B15" s="30">
         <v>101738</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>125748</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>129520</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>133406</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>137408</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B16" s="29">
+        <v>249</v>
+      </c>
+      <c r="B16" s="30">
         <v>81390</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>100598</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>103616</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>106724</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>109926</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B17" s="29">
+        <v>243</v>
+      </c>
+      <c r="B17" s="30">
         <v>352690</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>435925</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>449003</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>462473</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>476347</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="29">
+        <v>244</v>
+      </c>
+      <c r="B18" s="30">
         <v>62173</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>76846</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>79151</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>81526</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="29">
+        <v>245</v>
+      </c>
+      <c r="B19" s="30">
         <v>95738</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>118332</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>121881</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>125538</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>129304</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B20" s="29">
+        <v>253</v>
+      </c>
+      <c r="B20" s="30">
         <v>62173</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>76846</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>79151</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>81526</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B21" s="29">
+        <v>255</v>
+      </c>
+      <c r="B21" s="30">
         <v>84012</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>103838</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>106954</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>110162</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>113467</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B22" s="29">
+        <v>251</v>
+      </c>
+      <c r="B22" s="30">
         <v>62173</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>76846</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>79151</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>81526</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>83971</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="30">
+        <v>213</v>
+      </c>
+      <c r="B23" s="31">
         <f>SUM(B14:B22)</f>
         <v>1026431</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>SUM(C14:C22)</f>
         <v>1268669</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>SUM(D14:D22)</f>
         <v>1306729</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>SUM(E14:E22)</f>
         <v>1345931</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>SUM(F14:F22)</f>
         <v>1386309</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="A25" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B27" s="29">
+        <v>268</v>
+      </c>
+      <c r="B27" s="30">
         <v>70000</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>144200</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>222789</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>286841</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>315142</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B29" s="29">
+        <v>269</v>
+      </c>
+      <c r="B29" s="30">
         <v>50000</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>103000</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>159135</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>204886</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>225102</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B31" s="29">
+        <v>270</v>
+      </c>
+      <c r="B31" s="30">
         <v>180000</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <v>222480</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <v>229154</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <v>236029</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="30">
         <v>243110</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" s="29">
+        <v>271</v>
+      </c>
+      <c r="B32" s="30">
         <v>25000</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <v>30900</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <v>31827</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <v>32782</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B33" s="29">
+        <v>272</v>
+      </c>
+      <c r="B33" s="30">
         <v>15000</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <v>18540</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <v>19096</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <v>19669</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B34" s="29">
+        <v>273</v>
+      </c>
+      <c r="B34" s="30">
         <v>15000</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <v>18540</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <v>19096</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="30">
         <v>19669</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B35" s="30">
+        <v>274</v>
+      </c>
+      <c r="B35" s="31">
         <f>SUM(B31:B34)</f>
         <v>235000</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <f>SUM(C31:C34)</f>
         <v>290460</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <f>SUM(D31:D34)</f>
         <v>299174</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <f>SUM(E31:E34)</f>
         <v>308149</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <f>SUM(F31:F34)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B37" s="29">
+        <v>275</v>
+      </c>
+      <c r="B37" s="30">
         <v>20833</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>25750</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>26523</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <v>27318</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <v>28138</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B38" s="29">
+        <v>276</v>
+      </c>
+      <c r="B38" s="30">
         <v>12500</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <v>15450</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <v>15914</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <v>16391</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B39" s="29">
+        <v>277</v>
+      </c>
+      <c r="B39" s="30">
         <v>16667</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <v>20600</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <v>21218</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <v>21855</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="30">
         <v>22510</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B40" s="29">
+        <v>278</v>
+      </c>
+      <c r="B40" s="30">
         <v>80000</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <v>164800</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <v>254616</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="30">
         <v>327818</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="30">
         <v>360163</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="B41" s="29">
+        <v>279</v>
+      </c>
+      <c r="B41" s="30">
         <v>60000</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <v>123600</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>190962</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <v>245864</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <v>270122</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B42" s="30">
+        <v>280</v>
+      </c>
+      <c r="B42" s="31">
         <f>SUM(B37:B41)</f>
         <v>190000</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <f>SUM(C37:C41)</f>
         <v>350200</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <f>SUM(D37:D41)</f>
         <v>509232</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <f>SUM(E37:E41)</f>
         <v>639245</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <f>SUM(F37:F41)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="B43" s="30">
+        <v>281</v>
+      </c>
+      <c r="B43" s="31">
         <f>B27+B29+B35+B42</f>
         <v>545000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <f>C27+C29+C35+C42</f>
         <v>887860</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <f>D27+D29+D35+D42</f>
         <v>1190330</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <f>E27+E29+E35+E42</f>
         <v>1439121</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <f>F27+F29+F35+F42</f>
         <v>1555453</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
+      <c r="A45" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B46" s="29">
+        <v>283</v>
+      </c>
+      <c r="B46" s="30">
         <v>49825</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <v>49825</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="30">
         <v>49825</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="30">
         <v>49825</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="30">
         <v>49825</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="B47" s="29">
+        <v>284</v>
+      </c>
+      <c r="B47" s="30">
         <v>75000</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <v>25000</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <v>30000</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="30">
         <v>15000</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="B48" s="29">
+        <v>285</v>
+      </c>
+      <c r="B48" s="30">
         <v>40000</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="30">
         <v>15000</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="30">
         <v>10000</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="30">
         <v>10000</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="B49" s="30">
+        <v>286</v>
+      </c>
+      <c r="B49" s="31">
         <f>SUM(B46:B48)</f>
         <v>164825</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="31">
         <f>SUM(C46:C48)</f>
         <v>89825</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="31">
         <f>SUM(D46:D48)</f>
         <v>89825</v>
       </c>
-      <c r="E49" s="30">
+      <c r="E49" s="31">
         <f>SUM(E46:E48)</f>
         <v>74825</v>
       </c>
-      <c r="F49" s="30">
+      <c r="F49" s="31">
         <f>SUM(F46:F48)</f>
         <v>69825</v>
       </c>
@@ -3909,7 +3926,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3918,28 +3935,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B4" s="33">
         <f>'Budget Detail'!B11</f>
@@ -3964,7 +3981,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B23</f>
@@ -3989,7 +4006,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B43</f>
@@ -4014,7 +4031,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B7" s="33">
         <f>'Budget Detail'!B49</f>
@@ -4039,146 +4056,146 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="30">
+        <v>289</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>1736256</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>2246354</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>2586884</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>2859877</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B11" s="31">
+        <v>291</v>
+      </c>
+      <c r="B11" s="32">
         <f>B4-B8</f>
         <v>-447923</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>C4-C8</f>
         <v>318346</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>D4-D8</f>
         <v>1306619</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>E4-E8</f>
         <v>2117494</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>F4-F8</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="28">
+        <v>292</v>
+      </c>
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.44829778</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="29">
+        <v>293</v>
+      </c>
+      <c r="B13" s="30">
         <v>-447923</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>-129576</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>1177043</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>3294538</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>5741669</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="29">
+        <v>241</v>
+      </c>
+      <c r="B14" s="30">
         <v>10736</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>12824</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>12978</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>13273</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>13647</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B15" s="29">
+        <v>294</v>
+      </c>
+      <c r="B15" s="30">
         <v>14469</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>11232</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>8623</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>7626</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>7529</v>
       </c>
     </row>
@@ -4209,7 +4226,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4226,286 +4243,286 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>307</v>
       </c>
+      <c r="N2" s="21" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="30">
+        <v>266</v>
+      </c>
+      <c r="B4" s="31">
         <v>154600</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>154600</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>154600</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>154600</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>154600</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>154600</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>154600</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>154600</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="31">
         <v>154600</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>154600</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>0</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="31">
         <v>0</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="31">
         <f>SUM(B4:M4)</f>
         <v>1546000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B7" s="29">
+        <v>310</v>
+      </c>
+      <c r="B7" s="30">
         <v>102643</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>102643</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>102643</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>102643</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>102643</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>102643</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <v>102643</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <v>102643</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="30">
         <v>102643</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="30">
         <v>102643</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="30">
         <v>0</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="30">
         <v>0</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>1026431</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B8" s="29">
+        <v>311</v>
+      </c>
+      <c r="B8" s="30">
         <v>54500</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>54500</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>54500</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>54500</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>54500</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <v>54500</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <v>54500</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="30">
         <v>54500</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="30">
         <v>54500</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="30">
         <v>54500</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="30">
         <v>0</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="30">
         <v>0</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>545000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B9" s="29">
+        <v>312</v>
+      </c>
+      <c r="B9" s="30">
         <v>13735</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>13735</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>13735</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>13735</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>13735</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <v>13735</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <v>13735</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <v>13735</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="30">
         <v>13735</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="30">
         <v>13735</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="30">
         <v>13735</v>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="30">
         <v>13735</v>
       </c>
-      <c r="N9" s="29">
+      <c r="N9" s="30">
         <f>SUM(B9:M9)</f>
         <v>164825</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -4562,7 +4579,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -4619,7 +4636,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4669,29 +4686,29 @@
         <f>L14+M13</f>
         <v>-190250</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>M14</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="22">
+        <v>178</v>
+      </c>
+      <c r="B17" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -4700,9 +4717,9 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B19" s="29">
+        <v>318</v>
+      </c>
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>-190250</v>
       </c>
@@ -4733,7 +4750,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4742,68 +4759,68 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="30">
+        <v>266</v>
+      </c>
+      <c r="B5" s="31">
         <v>1288333</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2564700</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3893503</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>4977371</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>5458718</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B8" s="33">
         <v>1026431</v>
@@ -4823,7 +4840,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B9" s="33">
         <v>545000</v>
@@ -4843,7 +4860,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B10" s="33">
         <v>164825</v>
@@ -4863,85 +4880,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="30">
+        <v>289</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>1736256</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>2246354</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>2586884</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>2859877</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>3011587</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="B14" s="31">
+        <v>291</v>
+      </c>
+      <c r="B14" s="32">
         <f>B5-B11</f>
         <v>-447923</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C5-C11</f>
         <v>318346</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D5-D11</f>
         <v>1306619</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E5-E11</f>
         <v>2117494</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F5-F11</f>
         <v>2447131</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B15" s="28">
+        <v>292</v>
+      </c>
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.34767595</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.12412616</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.3355897</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.42542423</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.44829778</v>
       </c>
@@ -4981,158 +4998,158 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="23">
         <v>500000</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <v>0.0575</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>15</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>49825</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B9" s="29">
+        <v>327</v>
+      </c>
+      <c r="B9" s="30">
         <f>B6</f>
         <v>500000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>B13</f>
         <v>478361</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>C13</f>
         <v>455444</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>D13</f>
         <v>431175</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>E13</f>
         <v>405473</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B10" s="29">
+        <v>328</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>28186</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>26908</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>25555</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>24122</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>22605</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B11" s="29">
+        <v>329</v>
+      </c>
+      <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>21639</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>22917</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>24270</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>25702</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>27220</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B12" s="33">
         <f>B10+B11</f>
@@ -5157,7 +5174,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5206,7 +5223,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5215,38 +5232,38 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5271,207 +5288,207 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B6" s="29">
+        <v>335</v>
+      </c>
+      <c r="B6" s="30">
         <v>0</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>0</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>0</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>0</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B7" s="29">
+        <v>336</v>
+      </c>
+      <c r="B7" s="30">
         <v>0</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>0</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>0</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>0</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="29">
+        <v>337</v>
+      </c>
+      <c r="B8" s="30">
         <v>0</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>0</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>0</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>0</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B9" s="30">
+        <v>338</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
         <v>-190250</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
         <v>128096</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
         <v>1434716</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
         <v>3552210</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
         <v>5999341</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B12" s="29">
+        <v>340</v>
+      </c>
+      <c r="B12" s="30">
         <v>0</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>0</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>0</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>0</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="B13" s="29">
+        <v>341</v>
+      </c>
+      <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
         <v>478361</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>'Debt Schedule'!C13</f>
         <v>455444</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>'Debt Schedule'!D13</f>
         <v>431175</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>'Debt Schedule'!E13</f>
         <v>405473</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>'Debt Schedule'!F13</f>
         <v>378253</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="B14" s="30">
+        <v>342</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
         <v>478361</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C12:C13)</f>
         <v>455444</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D12:D13)</f>
         <v>431175</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E12:E13)</f>
         <v>405473</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F12:F13)</f>
         <v>378253</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="B17" s="31">
+        <v>344</v>
+      </c>
+      <c r="B17" s="32">
         <f>B9-B14</f>
         <v>-668611</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C9-C14</f>
         <v>-327348</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D9-D14</f>
         <v>1003541</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E9-E14</f>
         <v>3146738</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F9-F14</f>
         <v>5621089</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
@@ -5520,7 +5537,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5529,98 +5546,98 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B5" s="29">
+        <v>348</v>
+      </c>
+      <c r="B5" s="30">
         <v>1288333</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>2564700</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3893503</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>4977371</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>5458718</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B6" s="29">
+        <v>310</v>
+      </c>
+      <c r="B6" s="30">
         <v>1026431</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>1268669</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>1306729</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>1345931</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>1386309</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B7" s="29">
+        <v>311</v>
+      </c>
+      <c r="B7" s="30">
         <v>545000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>887860</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>1190330</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>1439121</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>1555453</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -5645,27 +5662,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B9" s="29">
+        <v>312</v>
+      </c>
+      <c r="B9" s="30">
         <v>49825</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>49825</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>49825</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>49825</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>49825</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B10" s="46">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5689,38 +5706,38 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B13" s="29">
+        <v>352</v>
+      </c>
+      <c r="B13" s="30">
         <v>-190250</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>128096</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>1434716</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>3552210</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>5999341</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14" s="35">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5745,7 +5762,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5770,97 +5787,97 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="28">
+        <v>199</v>
+      </c>
+      <c r="B16" s="29">
         <v>0.3</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <v>0.5</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>0.75</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>0.9375</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="29">
+        <v>241</v>
+      </c>
+      <c r="B19" s="30">
         <v>10736</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>12824</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>12978</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>13273</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>13647</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B20" s="29">
+        <v>356</v>
+      </c>
+      <c r="B20" s="30">
         <v>1076256</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>1318494</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>1356554</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>1395756</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>1436134</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="B21" s="29">
+        <v>357</v>
+      </c>
+      <c r="B21" s="30">
         <v>4542</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>4439</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>3968</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>3838</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>3889</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B22" s="47">
         <v>174</v>
@@ -5879,113 +5896,113 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>361</v>
+      </c>
+      <c r="C26" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>361</v>
-      </c>
       <c r="D26" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E26" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D27" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E28" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F28" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F29" s="49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -6026,93 +6043,93 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="29">
+        <v>167</v>
+      </c>
+      <c r="B4" s="30">
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="E4" s="29">
+        <v>369</v>
+      </c>
+      <c r="E4" s="30">
         <v>400000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="29">
+        <v>119</v>
+      </c>
+      <c r="B5" s="30">
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="E5" s="29">
+        <v>370</v>
+      </c>
+      <c r="E5" s="30">
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="B6" s="29">
+        <v>371</v>
+      </c>
+      <c r="B6" s="30">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="E6" s="29">
+        <v>372</v>
+      </c>
+      <c r="E6" s="30">
         <v>40000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="E7" s="29">
+        <v>373</v>
+      </c>
+      <c r="E7" s="30">
         <v>60000</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="29">
+        <v>374</v>
+      </c>
+      <c r="E8" s="30">
         <v>75000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B10" s="31">
+        <v>375</v>
+      </c>
+      <c r="B10" s="32">
         <v>650000</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="E10" s="31">
+        <v>376</v>
+      </c>
+      <c r="E10" s="32">
         <v>650000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B11" s="44">
         <v>0</v>
@@ -6460,7 +6477,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6469,123 +6486,123 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B6" s="29">
+        <v>348</v>
+      </c>
+      <c r="B6" s="30">
         <v>1288333</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>2564700</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>3893503</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>4977371</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>5458718</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="29">
+        <v>289</v>
+      </c>
+      <c r="B7" s="30">
         <v>1621256</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>2206354</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>2546884</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>2834877</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>2991587</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B8" s="31">
+        <v>291</v>
+      </c>
+      <c r="B8" s="32">
         <v>-332923</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <v>358346</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <v>1346619</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>2142494</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <v>2467131</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="28">
+        <v>292</v>
+      </c>
+      <c r="B9" s="29">
         <v>-0.2584133416981985</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>0.1397225288645145</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>0.3458632236905482</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>0.43044696555461553</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>0.4519616461017463</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B10" s="51">
         <v>-5.68</v>
@@ -6605,7 +6622,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B11" s="35">
         <v>174</v>
@@ -6624,123 +6641,123 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B16" s="29">
+        <v>348</v>
+      </c>
+      <c r="B16" s="30">
         <v>966250</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>1923525</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>2920127</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>3733029</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>4094038</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B17" s="29">
+        <v>289</v>
+      </c>
+      <c r="B17" s="30">
         <v>1621256</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>2206354</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>2546884</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>2834877</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>2991587</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B18" s="31">
+        <v>291</v>
+      </c>
+      <c r="B18" s="32">
         <v>-655006</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <v>-282829</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <v>373244</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <v>898152</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>1102452</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B19" s="28">
+        <v>292</v>
+      </c>
+      <c r="B19" s="29">
         <v>-0.677884455597598</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <v>-0.14703662818064733</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <v>0.12781763158739762</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <v>0.2405959540728207</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <v>0.26928219480232835</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B20" s="51">
         <v>-12.15</v>
@@ -6760,7 +6777,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B21" s="35">
         <v>230</v>
@@ -6779,123 +6796,123 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B26" s="29">
+        <v>348</v>
+      </c>
+      <c r="B26" s="30">
         <v>1223917</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>2436465</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>3698828</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <v>4728503</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <v>5185782</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B27" s="29">
+        <v>289</v>
+      </c>
+      <c r="B27" s="30">
         <v>1621256</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>2206354</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>2546884</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>2834877</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>2991587</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B28" s="31">
+        <v>291</v>
+      </c>
+      <c r="B28" s="32">
         <v>-397339</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>230111</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>1151944</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>1893626</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>2194195</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B29" s="28">
+        <v>292</v>
+      </c>
+      <c r="B29" s="29">
         <v>-0.3246456228402091</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <v>0.09444476722580472</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="29">
         <v>0.31143497230584016</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="29">
         <v>0.40047049005748997</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="29">
         <v>0.4231175222123644</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B30" s="51">
         <v>-6.97</v>
@@ -6915,7 +6932,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B31" s="35">
         <v>191</v>
@@ -6934,123 +6951,123 @@
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="A33" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="20" t="s">
+      <c r="B35" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="C35" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="D35" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="E35" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B36" s="29">
+        <v>348</v>
+      </c>
+      <c r="B36" s="30">
         <v>1288333</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <v>2564700</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <v>3893503</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <v>4977371</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="30">
         <v>5458718</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B37" s="29">
+        <v>289</v>
+      </c>
+      <c r="B37" s="30">
         <v>1667756</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>2295964</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>2680557</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <v>3004523</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <v>3177296</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B38" s="31">
+        <v>291</v>
+      </c>
+      <c r="B38" s="32">
         <v>-379423</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>268736</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1212946</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>1972849</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>2281422</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B39" s="28">
+        <v>292</v>
+      </c>
+      <c r="B39" s="29">
         <v>-0.2945064852945763</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="29">
         <v>0.10478276982836991</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="29">
         <v>0.31153079862242844</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="29">
         <v>0.3963635407467121</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="29">
         <v>0.4179410275450453</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B40" s="51">
         <v>-6.62</v>
@@ -7070,7 +7087,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" s="35">
         <v>186</v>
@@ -7116,7 +7133,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7127,10 +7144,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -7142,7 +7159,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -7150,7 +7167,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -7174,23 +7191,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -7203,132 +7220,132 @@
         <v>7</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D13" s="29">
+        <v>348</v>
+      </c>
+      <c r="D13" s="30">
         <v>1288333</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>2564700</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>3893503</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <v>4977371</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <v>5458718</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="D14" s="29">
+        <v>289</v>
+      </c>
+      <c r="D14" s="30">
         <v>1621256</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>2206354</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>2546884</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <v>2834877</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>2991587</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D15" s="29">
+        <v>291</v>
+      </c>
+      <c r="D15" s="30">
         <v>-447923</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>318346</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>1306619</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <v>2117494</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <v>2447131</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D16" s="29">
+        <v>391</v>
+      </c>
+      <c r="D16" s="30">
         <v>-190250</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>128096</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>1434716</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <v>3552210</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <v>5999341</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="D17" s="29">
+        <v>392</v>
+      </c>
+      <c r="D17" s="30">
         <v>478361</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>455444</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>431175</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <v>405473</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="30">
         <v>378253</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -7341,44 +7358,44 @@
         <v>7</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D21" s="28">
+        <v>394</v>
+      </c>
+      <c r="D21" s="29">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <v>0.12412616281780338</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <v>0.33558969879535744</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>0.42542423416409325</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>0.44829778198663</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D22" s="51">
         <v>-5.68</v>
@@ -7398,27 +7415,27 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D23" s="28">
+        <v>199</v>
+      </c>
+      <c r="D23" s="29">
         <v>0.3</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <v>0.5</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <v>0.75</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>0.9375</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D24" s="35">
         <v>120</v>
@@ -7438,7 +7455,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7478,7 +7495,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7488,7 +7505,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
@@ -7497,28 +7514,28 @@
       <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>398</v>
+      <c r="B5" s="19" t="s">
+        <v>399</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C6" s="55">
         <v>120</v>
@@ -7538,7 +7555,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C7" s="56">
         <v>1288333.3333333335</v>
@@ -7558,7 +7575,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C8" s="56">
         <v>1026431.25</v>
@@ -7578,7 +7595,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C9" s="56">
         <v>545000</v>
@@ -7598,7 +7615,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C10" s="56">
         <v>49824.605221179416</v>
@@ -7618,7 +7635,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C11" s="57">
         <v>-447922.5218878458</v>
@@ -7638,7 +7655,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C12" s="57">
         <v>-190250</v>
@@ -7658,7 +7675,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C13" s="59">
         <v>-0.34767595489354136</v>
@@ -7678,7 +7695,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C14" s="56">
         <v>10736.111111111113</v>
@@ -7698,7 +7715,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C15" s="59">
         <v>0.7967124838292367</v>
@@ -7718,7 +7735,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C16" s="60">
         <v>0.12690815006468303</v>
@@ -7738,7 +7755,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C17" s="59">
         <v>-0.21973965071151344</v>
@@ -7758,7 +7775,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C18" s="61">
         <v>-5.681889809461599</v>
@@ -7778,10 +7795,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D19" s="63"/>
       <c r="E19" s="63"/>
@@ -7790,10 +7807,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
@@ -7801,146 +7818,146 @@
       <c r="G20" s="64"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E23" s="66"/>
       <c r="F23" s="67" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G23" s="67"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E24" s="66"/>
       <c r="F24" s="67" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G24" s="67"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E25" s="66"/>
       <c r="F25" s="67" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G25" s="67"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E26" s="66"/>
       <c r="F26" s="67" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G26" s="67"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E27" s="66"/>
       <c r="F27" s="67" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G27" s="67"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C28" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E28" s="66"/>
       <c r="F28" s="67" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G28" s="67"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D29" s="66" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E29" s="66"/>
       <c r="F29" s="67" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G29" s="67"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="69" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C33" s="69"/>
       <c r="D33" s="69"/>
@@ -8082,30 +8099,36 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
+      <c r="D2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8113,7 +8136,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8121,7 +8144,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -8129,23 +8152,23 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="19" t="s">
         <v>97</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -8153,797 +8176,797 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="19">
+        <v>99</v>
+      </c>
+      <c r="B12" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="19">
+        <v>100</v>
+      </c>
+      <c r="B13" s="20">
         <v>400</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="21">
+        <v>107</v>
+      </c>
+      <c r="B17" s="22">
         <v>120</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>200</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <v>300</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>375</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="22">
+        <v>116</v>
+      </c>
+      <c r="D21" s="23">
         <v>9500</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <v>800</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="22">
+        <v>116</v>
+      </c>
+      <c r="D23" s="23">
         <v>1200</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="22">
+        <v>121</v>
+      </c>
+      <c r="D24" s="23">
         <v>100000</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <v>30000</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="22">
+        <v>116</v>
+      </c>
+      <c r="D26" s="23">
         <v>300</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="A28" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="B29" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="D29" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="F29" s="21" t="s">
         <v>130</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="24">
+        <v>134</v>
+      </c>
+      <c r="D30" s="25">
         <v>1</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="23">
         <v>110000</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="24">
         <v>0.28</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>1</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>90000</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="24">
         <v>0.28</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="24">
+        <v>134</v>
+      </c>
+      <c r="D32" s="25">
         <v>1</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <v>72000</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="24">
         <v>0.28</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" s="24">
+        <v>134</v>
+      </c>
+      <c r="D33" s="25">
         <v>6</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="23">
         <v>52000</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="24">
         <v>0.28</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="24">
+        <v>134</v>
+      </c>
+      <c r="D34" s="25">
         <v>1</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="23">
         <v>55000</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="24">
         <v>0.28</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="24">
+        <v>134</v>
+      </c>
+      <c r="D35" s="25">
         <v>3</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>30000</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="24">
         <v>0.2</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="24">
+        <v>134</v>
+      </c>
+      <c r="D36" s="25">
         <v>1</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>55000</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="24">
         <v>0.28</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="24">
+        <v>134</v>
+      </c>
+      <c r="D37" s="25">
         <v>2</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="23">
         <v>38000</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="24">
         <v>0.25</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="24">
+        <v>134</v>
+      </c>
+      <c r="D38" s="25">
         <v>1</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="23">
         <v>55000</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="24">
         <v>0.28</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
+      <c r="A40" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="20" t="s">
+      <c r="A41" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="C41" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="D41" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D42" s="22">
+        <v>150</v>
+      </c>
+      <c r="D42" s="23">
         <v>18000</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="24">
         <v>0.03</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D43" s="22">
+      <c r="D43" s="23">
         <v>2500</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="22">
+        <v>121</v>
+      </c>
+      <c r="D44" s="23">
         <v>18000</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D45" s="22">
+        <v>150</v>
+      </c>
+      <c r="D45" s="23">
         <v>1500</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" s="22">
+        <v>116</v>
+      </c>
+      <c r="D46" s="23">
         <v>700</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" s="22">
+        <v>116</v>
+      </c>
+      <c r="D47" s="23">
         <v>500</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="22">
+        <v>121</v>
+      </c>
+      <c r="D48" s="23">
         <v>25000</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="C49" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" s="22">
+        <v>121</v>
+      </c>
+      <c r="D49" s="23">
         <v>15000</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="22">
+        <v>121</v>
+      </c>
+      <c r="D50" s="23">
         <v>20000</v>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" s="22">
+        <v>116</v>
+      </c>
+      <c r="D51" s="23">
         <v>800</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" s="22">
+        <v>116</v>
+      </c>
+      <c r="D52" s="23">
         <v>600</v>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
+      <c r="A54" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" s="20" t="s">
+      <c r="A55" s="21" t="s">
         <v>165</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C56" s="22">
+        <v>168</v>
+      </c>
+      <c r="C56" s="23">
         <v>500000</v>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="24">
         <v>0.0575</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="22">
         <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" s="22">
+        <v>170</v>
+      </c>
+      <c r="C57" s="23">
         <v>75000</v>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="24">
         <v>0</v>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C58" s="22">
+      <c r="C58" s="23">
         <v>40000</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="24">
         <v>0</v>
       </c>
-      <c r="E58" s="21">
+      <c r="E58" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
+      <c r="A60" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" s="23">
+        <v>173</v>
+      </c>
+      <c r="B61" s="24">
         <v>0.03</v>
       </c>
-      <c r="C61" s="25" t="s">
-        <v>173</v>
+      <c r="C61" s="26" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" s="23">
+        <v>175</v>
+      </c>
+      <c r="B62" s="24">
         <v>0.03</v>
       </c>
-      <c r="C62" s="25" t="s">
-        <v>175</v>
+      <c r="C62" s="26" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B63" s="24">
+        <v>177</v>
+      </c>
+      <c r="B63" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B64" s="22">
+        <v>178</v>
+      </c>
+      <c r="B64" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B65" s="19" t="s">
         <v>179</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -8978,10 +9001,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -9002,10 +9025,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -9018,7 +9041,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -9026,66 +9049,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -9124,108 +9147,108 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="26">
+        <v>107</v>
+      </c>
+      <c r="B6" s="27">
         <v>120</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>200</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>300</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>375</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="21">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="27">
+        <v>199</v>
+      </c>
+      <c r="B8" s="28">
         <f>B6/$B$7</f>
         <v>0.3</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>C6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>D6/$B$7</f>
         <v>0.75</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>E6/$B$7</f>
         <v>0.9375</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="28">
+        <v>201</v>
+      </c>
+      <c r="C10" s="29">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.66666667</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.25</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0.06666667</v>
       </c>
@@ -9256,7 +9279,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9265,271 +9288,271 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="29">
+        <v>114</v>
+      </c>
+      <c r="B5" s="30">
         <v>1140000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>1957000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3023565</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>3892840</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>4276933</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="29">
+        <v>117</v>
+      </c>
+      <c r="B6" s="30">
         <v>96000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>164800</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>254616</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>360163</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="29">
+        <v>118</v>
+      </c>
+      <c r="B7" s="30">
         <v>144000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>247200</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>381924</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>491727</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>540244</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="30">
+        <v>204</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5,B6,B7)</f>
         <v>1380000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5,C6,C7)</f>
         <v>2369000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5,D6,D7)</f>
         <v>3660105</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5,E6,E7)</f>
         <v>4712385</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5,F6,F7)</f>
         <v>5177341</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="22">
+        <v>119</v>
+      </c>
+      <c r="B10" s="23">
         <v>100000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>103000</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>106090</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>109273</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>112551</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="22">
+        <v>122</v>
+      </c>
+      <c r="B11" s="23">
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>31827</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>32782</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="30">
+        <v>206</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B10,B11)</f>
         <v>130000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C10,C11)</f>
         <v>133900</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D10,D11)</f>
         <v>137917</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E10,E11)</f>
         <v>142055</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F10,F11)</f>
         <v>146316</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="29">
+        <v>123</v>
+      </c>
+      <c r="B14" s="30">
         <v>36000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>61800</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>95481</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>122932</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="30">
+        <v>208</v>
+      </c>
+      <c r="B15" s="31">
         <f>SUM(B14)</f>
         <v>36000</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>SUM(C14)</f>
         <v>61800</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>SUM(D14)</f>
         <v>95481</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>SUM(E14)</f>
         <v>122932</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>SUM(F14)</f>
         <v>135061</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" s="31">
+      <c r="A17" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="32">
         <f>SUM(B8,B12,B15)</f>
         <v>1546000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C8,C12,C15)</f>
         <v>2564700</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D8,D12,D15)</f>
         <v>3893503</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E8,E12,E15)</f>
         <v>4977371</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F8,F12,F15)</f>
         <v>5458718</v>
       </c>
@@ -9574,45 +9597,45 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="A3" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>210</v>
+      <c r="F3" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="32">
+        <v>133</v>
+      </c>
+      <c r="C4" s="25">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="23">
         <v>110000</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="24">
         <v>0.28</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
       <c r="G4" s="33">
@@ -9621,21 +9644,21 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="32">
+        <v>133</v>
+      </c>
+      <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="23">
         <v>90000</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="24">
         <v>0.28</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
       <c r="G5" s="33">
@@ -9644,21 +9667,21 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="32">
+        <v>133</v>
+      </c>
+      <c r="C6" s="25">
         <v>1</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="23">
         <v>72000</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="24">
         <v>0.28</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
       <c r="G6" s="33">
@@ -9667,21 +9690,21 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="32">
+        <v>138</v>
+      </c>
+      <c r="C7" s="25">
         <v>6</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="23">
         <v>52000</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="24">
         <v>0.28</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="24">
         <v>0.0765</v>
       </c>
       <c r="G7" s="33">
@@ -9690,21 +9713,21 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="32">
+      <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="23">
         <v>55000</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="24">
         <v>0.28</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="24">
         <v>0.0765</v>
       </c>
       <c r="G8" s="33">
@@ -9713,21 +9736,21 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="32">
+        <v>138</v>
+      </c>
+      <c r="C9" s="25">
         <v>3</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="23">
         <v>30000</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="24">
         <v>0.2</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="24">
         <v>0.0765</v>
       </c>
       <c r="G9" s="33">
@@ -9736,21 +9759,21 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="32">
+        <v>142</v>
+      </c>
+      <c r="C10" s="25">
         <v>1</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="23">
         <v>55000</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="24">
         <v>0.28</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="24">
         <v>0.0765</v>
       </c>
       <c r="G10" s="33">
@@ -9759,21 +9782,21 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="32">
+        <v>144</v>
+      </c>
+      <c r="C11" s="25">
         <v>2</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="23">
         <v>38000</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="24">
         <v>0.25</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="24">
         <v>0.0765</v>
       </c>
       <c r="G11" s="33">
@@ -9782,21 +9805,21 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="32">
+        <v>146</v>
+      </c>
+      <c r="C12" s="25">
         <v>1</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="23">
         <v>55000</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="24">
         <v>0.28</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="24">
         <v>0.0765</v>
       </c>
       <c r="G12" s="33">
@@ -9804,79 +9827,79 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
+      <c r="A14" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="31">
+        <v>213</v>
+      </c>
+      <c r="B16" s="32">
         <v>1026431</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <v>1268669</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <v>1306729</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <v>1345931</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <v>1386309</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="28">
+        <v>214</v>
+      </c>
+      <c r="B17" s="29">
         <v>0.6639270698576973</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <v>0.49466566265060247</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <v>0.3356178474114441</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="29">
         <v>0.27040998902305163</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <v>0.25396237113402065</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" s="34">
         <v>7.1</v>
@@ -9920,7 +9943,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9929,406 +9952,406 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="29">
+        <v>217</v>
+      </c>
+      <c r="B5" s="30">
         <v>84000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>144200</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>222789</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>286841</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>315142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6" s="30">
+        <v>218</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>84000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>144200</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>222789</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>286841</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>315142</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B8" s="29">
+        <v>219</v>
+      </c>
+      <c r="B8" s="30">
         <v>60000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>103000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>159135</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>204886</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>225102</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="30">
+        <v>220</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>103000</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>159135</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>204886</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>225102</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="29">
+        <v>221</v>
+      </c>
+      <c r="B11" s="30">
         <v>216000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>222480</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>229154</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>236029</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>243110</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B12" s="29">
+        <v>222</v>
+      </c>
+      <c r="B12" s="30">
         <v>30000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>30900</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>31827</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>32782</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="29">
+        <v>223</v>
+      </c>
+      <c r="B13" s="30">
         <v>18000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>18540</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>19096</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>19669</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="29">
+        <v>224</v>
+      </c>
+      <c r="B14" s="30">
         <v>18000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18540</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19096</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19669</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="30">
+        <v>225</v>
+      </c>
+      <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
         <v>282000</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>SUM(C11:C14)</f>
         <v>290460</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>SUM(D11:D14)</f>
         <v>299174</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>SUM(E11:E14)</f>
         <v>308149</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>SUM(F11:F14)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="29">
+        <v>226</v>
+      </c>
+      <c r="B17" s="30">
         <v>25000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>25750</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>26523</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>27318</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>28138</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B18" s="29">
+        <v>227</v>
+      </c>
+      <c r="B18" s="30">
         <v>15000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>15450</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>15914</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>16391</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="29">
+        <v>228</v>
+      </c>
+      <c r="B19" s="30">
         <v>20000</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>20600</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>21218</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>21855</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>22510</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" s="29">
+        <v>229</v>
+      </c>
+      <c r="B20" s="30">
         <v>96000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>164800</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>254616</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>327818</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>360163</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B21" s="29">
+        <v>230</v>
+      </c>
+      <c r="B21" s="30">
         <v>72000</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>123600</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>190962</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>245864</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>270122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" s="30">
+        <v>231</v>
+      </c>
+      <c r="B22" s="31">
         <f>SUM(B17:B21)</f>
         <v>228000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>SUM(C17:C21)</f>
         <v>350200</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>SUM(D17:D21)</f>
         <v>509232</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>SUM(E17:E21)</f>
         <v>639245</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>SUM(F17:F21)</f>
         <v>697815</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="32">
         <f>B6+B9+B15+B22</f>
         <v>654000</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>C6+C9+C15+C22</f>
         <v>887860</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>D6+D9+D15+D22</f>
         <v>1190330</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>E6+E9+E15+E22</f>
         <v>1439121</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>F6+F9+F15+F22</f>
         <v>1555453</v>
       </c>
@@ -10360,7 +10383,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10369,39 +10392,39 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>233</v>
+      <c r="B3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="22">
+        <v>168</v>
+      </c>
+      <c r="C4" s="23">
         <v>500000</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <v>0.0575</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="22">
         <v>15</v>
       </c>
       <c r="F4" s="33">
@@ -10410,15 +10433,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="22">
+        <v>235</v>
+      </c>
+      <c r="C5" s="23">
         <v>75000</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>0</v>
       </c>
       <c r="E5" s="35">
@@ -10430,15 +10453,15 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="22">
+        <v>235</v>
+      </c>
+      <c r="C6" s="23">
         <v>40000</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>0</v>
       </c>
       <c r="E6" s="35">
@@ -10450,17 +10473,17 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="31">
+        <v>236</v>
+      </c>
+      <c r="F8" s="32">
         <v>49825</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F9" s="30">
+        <v>237</v>
+      </c>
+      <c r="F9" s="31">
         <v>500000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="454">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1231,6 +1231,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -1249,18 +1258,42 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Net Income</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -1268,6 +1301,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1371,7 +1407,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1490,6 +1526,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1590,7 +1632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1659,6 +1701,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1680,6 +1725,11 @@
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1687,7 +1737,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1697,17 +1747,38 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7481,19 +7552,20 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>397</v>
       </c>
@@ -7502,8 +7574,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
         <v>398</v>
       </c>
@@ -7512,559 +7585,632 @@
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="H3" s="53"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="D4" s="55" t="s">
         <v>400</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="F4" s="56" t="s">
         <v>401</v>
       </c>
-      <c r="E5" s="54" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="C6" s="57" t="s">
         <v>403</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="D6" s="57" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="C6" s="55">
-        <v>120</v>
-      </c>
-      <c r="D6" s="55">
-        <v>200</v>
-      </c>
-      <c r="E6" s="55">
-        <v>300</v>
-      </c>
-      <c r="F6" s="55">
-        <v>375</v>
-      </c>
-      <c r="G6" s="55">
-        <v>400</v>
+      <c r="E6" s="57" t="s">
+        <v>405</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>406</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" s="56">
-        <v>1288333.3333333335</v>
-      </c>
-      <c r="D7" s="56">
-        <v>2564700</v>
-      </c>
-      <c r="E7" s="56">
-        <v>3893503</v>
-      </c>
-      <c r="F7" s="56">
-        <v>4977371.484999999</v>
-      </c>
-      <c r="G7" s="56">
-        <v>5458717.7285</v>
+        <v>395</v>
+      </c>
+      <c r="C7" s="58">
+        <v>120</v>
+      </c>
+      <c r="D7" s="58">
+        <v>200</v>
+      </c>
+      <c r="E7" s="58">
+        <v>300</v>
+      </c>
+      <c r="F7" s="58">
+        <v>375</v>
+      </c>
+      <c r="G7" s="58">
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="C8" s="56">
-        <v>1026431.25</v>
-      </c>
-      <c r="D8" s="56">
-        <v>1268669.0250000001</v>
-      </c>
-      <c r="E8" s="56">
-        <v>1306729.0957499999</v>
-      </c>
-      <c r="F8" s="56">
-        <v>1345930.9686225</v>
-      </c>
-      <c r="G8" s="56">
-        <v>1386308.8976811753</v>
+        <v>348</v>
+      </c>
+      <c r="C8" s="59">
+        <v>1288333.3333333335</v>
+      </c>
+      <c r="D8" s="59">
+        <v>2564700</v>
+      </c>
+      <c r="E8" s="59">
+        <v>3893503</v>
+      </c>
+      <c r="F8" s="59">
+        <v>4977371.484999999</v>
+      </c>
+      <c r="G8" s="59">
+        <v>5458717.7285</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="C9" s="56">
-        <v>545000</v>
-      </c>
-      <c r="D9" s="56">
-        <v>887860</v>
-      </c>
-      <c r="E9" s="56">
-        <v>1190329.8</v>
-      </c>
-      <c r="F9" s="56">
-        <v>1439121.459</v>
-      </c>
-      <c r="G9" s="56">
-        <v>1555453.1754200002</v>
+        <v>310</v>
+      </c>
+      <c r="C9" s="59">
+        <v>1026431.25</v>
+      </c>
+      <c r="D9" s="59">
+        <v>1268669.0250000001</v>
+      </c>
+      <c r="E9" s="59">
+        <v>1306729.0957499999</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1345930.9686225</v>
+      </c>
+      <c r="G9" s="59">
+        <v>1386308.8976811753</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="59">
+        <v>545000</v>
+      </c>
+      <c r="D10" s="59">
+        <v>887860</v>
+      </c>
+      <c r="E10" s="59">
+        <v>1190329.8</v>
+      </c>
+      <c r="F10" s="59">
+        <v>1439121.459</v>
+      </c>
+      <c r="G10" s="59">
+        <v>1555453.1754200002</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C11" s="59">
         <v>49824.605221179416</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D11" s="59">
         <v>49824.605221179416</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E11" s="59">
         <v>49824.605221179416</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F11" s="59">
         <v>49824.605221179416</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G11" s="59">
         <v>49824.605221179416</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="C11" s="57">
-        <v>-447922.5218878458</v>
-      </c>
-      <c r="D11" s="58">
-        <v>318346.3697788203</v>
-      </c>
-      <c r="E11" s="58">
-        <v>1306619.4990288205</v>
-      </c>
-      <c r="F11" s="58">
-        <v>2117494.45215632</v>
-      </c>
-      <c r="G11" s="58">
-        <v>2447131.0501776454</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="C12" s="57">
-        <v>-190250</v>
-      </c>
-      <c r="D12" s="58">
-        <v>128096.36977882031</v>
-      </c>
-      <c r="E12" s="58">
-        <v>1434715.8688076409</v>
-      </c>
-      <c r="F12" s="58">
-        <v>3552210.320963961</v>
-      </c>
-      <c r="G12" s="58">
-        <v>5999341.371141607</v>
+        <v>409</v>
+      </c>
+      <c r="C12" s="60">
+        <v>-447922.5218878458</v>
+      </c>
+      <c r="D12" s="61">
+        <v>318346.3697788203</v>
+      </c>
+      <c r="E12" s="61">
+        <v>1306619.4990288205</v>
+      </c>
+      <c r="F12" s="61">
+        <v>2117494.45215632</v>
+      </c>
+      <c r="G12" s="61">
+        <v>2447131.0501776454</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C13" s="59">
-        <v>-0.34767595489354136</v>
-      </c>
-      <c r="D13" s="60">
-        <v>0.12412616281780338</v>
-      </c>
-      <c r="E13" s="60">
-        <v>0.33558969879535744</v>
-      </c>
-      <c r="F13" s="60">
-        <v>0.42542423416409325</v>
-      </c>
-      <c r="G13" s="60">
-        <v>0.44829778198663</v>
+        <v>352</v>
+      </c>
+      <c r="C13" s="60">
+        <v>-190250</v>
+      </c>
+      <c r="D13" s="61">
+        <v>128096.36977882031</v>
+      </c>
+      <c r="E13" s="61">
+        <v>1434715.8688076409</v>
+      </c>
+      <c r="F13" s="61">
+        <v>3552210.320963961</v>
+      </c>
+      <c r="G13" s="61">
+        <v>5999341.371141607</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="62">
+        <v>-0.34767595489354136</v>
+      </c>
+      <c r="D14" s="63">
+        <v>0.12412616281780338</v>
+      </c>
+      <c r="E14" s="63">
+        <v>0.33558969879535744</v>
+      </c>
+      <c r="F14" s="63">
+        <v>0.42542423416409325</v>
+      </c>
+      <c r="G14" s="63">
+        <v>0.44829778198663</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C15" s="64">
         <v>10736.111111111113</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D15" s="64">
         <v>12823.5</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E15" s="64">
         <v>12978.343333333334</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F15" s="64">
         <v>13272.990626666666</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G15" s="64">
         <v>13646.794321250001</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="C15" s="59">
+      <c r="H15" s="65" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="62">
         <v>0.7967124838292367</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D16" s="63">
         <v>0.49466566265060247</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E16" s="63">
         <v>0.3356178474114441</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F16" s="63">
         <v>0.27040998902305163</v>
       </c>
-      <c r="G15" s="60">
+      <c r="G16" s="63">
         <v>0.25396237113402065</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C16" s="60">
+      <c r="H16" s="65" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="63">
         <v>0.12690815006468303</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D17" s="63">
         <v>0.10385542168674698</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E17" s="63">
         <v>0.09171662125340599</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F17" s="63">
         <v>0.08673984632272229</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G17" s="63">
         <v>0.08548453608247424</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="C17" s="59">
+      <c r="H17" s="65" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C18" s="62">
         <v>-0.21973965071151344</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D18" s="63">
         <v>0.15914959839357423</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E18" s="63">
         <v>0.3586600817438692</v>
       </c>
-      <c r="F17" s="60">
+      <c r="F18" s="63">
         <v>0.4404571899012074</v>
       </c>
-      <c r="G17" s="60">
+      <c r="G18" s="63">
         <v>0.4610891752577319</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="H18" s="65" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C19" s="66">
+        <v>1</v>
+      </c>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="65" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="C18" s="61">
+      <c r="C20" s="67">
         <v>-5.681889809461599</v>
       </c>
-      <c r="D18" s="62">
+      <c r="D20" s="68">
         <v>8.192156730355682</v>
       </c>
-      <c r="E18" s="62">
+      <c r="E20" s="68">
         <v>28.027198570886025</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F20" s="68">
         <v>44.00073111759629</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G20" s="68">
         <v>50.51631908021458</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>401</v>
-      </c>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>416</v>
-      </c>
-      <c r="C23" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D23" s="66" t="s">
-        <v>418</v>
-      </c>
-      <c r="E23" s="66"/>
-      <c r="F23" s="67" t="s">
+      <c r="H20" s="65" t="s">
         <v>419</v>
       </c>
-      <c r="G23" s="67"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C21" s="69" t="s">
+        <v>404</v>
+      </c>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="65" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="C22" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67" t="s">
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="65" t="s">
         <v>423</v>
       </c>
-      <c r="G24" s="67"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>424</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D25" s="66" t="s">
-        <v>425</v>
-      </c>
-      <c r="E25" s="66"/>
-      <c r="F25" s="67" t="s">
-        <v>426</v>
-      </c>
-      <c r="G25" s="67"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+      <c r="C25" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="D25" s="72" t="s">
+        <v>430</v>
+      </c>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
+        <v>431</v>
+      </c>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D26" s="66" t="s">
-        <v>428</v>
-      </c>
-      <c r="E26" s="66"/>
-      <c r="F26" s="67" t="s">
+        <v>432</v>
+      </c>
+      <c r="C26" s="74" t="s">
+        <v>433</v>
+      </c>
+      <c r="D26" s="72" t="s">
+        <v>434</v>
+      </c>
+      <c r="E26" s="72"/>
+      <c r="F26" s="73" t="s">
+        <v>435</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="40" t="s">
+        <v>436</v>
+      </c>
+      <c r="C27" s="71" t="s">
         <v>429</v>
       </c>
-      <c r="G26" s="67"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>430</v>
-      </c>
-      <c r="C27" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D27" s="66" t="s">
-        <v>431</v>
-      </c>
-      <c r="E27" s="66"/>
-      <c r="F27" s="67" t="s">
-        <v>432</v>
-      </c>
-      <c r="G27" s="67"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D27" s="72" t="s">
+        <v>437</v>
+      </c>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
+        <v>438</v>
+      </c>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="C28" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D28" s="66" t="s">
-        <v>434</v>
-      </c>
-      <c r="E28" s="66"/>
-      <c r="F28" s="67" t="s">
-        <v>435</v>
-      </c>
-      <c r="G28" s="67"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="C28" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="D28" s="72" t="s">
+        <v>440</v>
+      </c>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
+        <v>441</v>
+      </c>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
-        <v>436</v>
-      </c>
-      <c r="C29" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D29" s="66" t="s">
-        <v>437</v>
-      </c>
-      <c r="E29" s="66"/>
-      <c r="F29" s="67" t="s">
-        <v>438</v>
-      </c>
-      <c r="G29" s="67"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="D29" s="72" t="s">
+        <v>443</v>
+      </c>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
+        <v>444</v>
+      </c>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="40" t="s">
+        <v>445</v>
+      </c>
+      <c r="C30" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="D30" s="72" t="s">
+        <v>446</v>
+      </c>
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
+        <v>447</v>
+      </c>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
-        <v>439</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
-        <v>441</v>
-      </c>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
+        <v>448</v>
+      </c>
+      <c r="C31" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="D31" s="72" t="s">
+        <v>449</v>
+      </c>
+      <c r="E31" s="72"/>
+      <c r="F31" s="73" t="s">
+        <v>450</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="40" t="s">
+        <v>451</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
+        <v>453</v>
+      </c>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="458">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1000,6 +1000,15 @@
     <t>BOTTOM LINE</t>
   </si>
   <si>
+    <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
+  </si>
+  <si>
     <t>LOAN TERMS</t>
   </si>
   <si>
@@ -1321,30 +1330,33 @@
     <t>Viability</t>
   </si>
   <si>
+    <t>◐ Watch closely</t>
+  </si>
+  <si>
+    <t>The model reaches break-even by Year 3, but margins remain thin. A revenue shortfall could push it negative.</t>
+  </si>
+  <si>
+    <t>Track monthly revenue vs. budget and have a contingency plan if you miss targets.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
     <t>● Healthy</t>
   </si>
   <si>
-    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
-  </si>
-  <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
-  </si>
-  <si>
-    <t>Liquidity</t>
-  </si>
-  <si>
-    <t>○ Needs attention</t>
-  </si>
-  <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
-  </si>
-  <si>
-    <t>Secure a line of credit or bridge funding before operations begin.</t>
-  </si>
-  <si>
-    <t>Staffing Burden</t>
-  </si>
-  <si>
     <t>Staffing at 25% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
@@ -1390,7 +1402,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+    <t>5 Healthy  |  1 Watch  |  1 Needs Attention</t>
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1502,6 +1514,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF328555"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1515,12 +1533,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1632,7 +1644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1681,18 +1693,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1700,8 +1718,8 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1728,23 +1746,23 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4812,7 +4830,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5032,6 +5050,51 @@
       <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.44829778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="33">
+        <f>B14</f>
+        <v>-447923</v>
+      </c>
+      <c r="C16" s="33">
+        <f>B16+C14</f>
+        <v>-129576</v>
+      </c>
+      <c r="D16" s="33">
+        <f>C16+D14</f>
+        <v>1177043</v>
+      </c>
+      <c r="E16" s="33">
+        <f>D16+E14</f>
+        <v>3294538</v>
+      </c>
+      <c r="F16" s="33">
+        <f>E16+F14</f>
+        <v>5741669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5090,7 +5153,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5099,19 +5162,19 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>323</v>
-      </c>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>325</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="C5" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>234</v>
       </c>
     </row>
@@ -5135,7 +5198,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5145,7 +5208,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B9" s="30">
         <f>B6</f>
@@ -5170,7 +5233,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5195,7 +5258,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5220,7 +5283,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B12" s="33">
         <f>B10+B11</f>
@@ -5245,7 +5308,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5294,7 +5357,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5324,7 +5387,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5334,32 +5397,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B5" s="43">
+        <v>337</v>
+      </c>
+      <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>-190250</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>128096</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1434716</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>3552210</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>5999341</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B6" s="30">
         <v>0</v>
@@ -5379,7 +5442,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B7" s="30">
         <v>0</v>
@@ -5399,7 +5462,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -5419,7 +5482,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
@@ -5444,7 +5507,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5454,7 +5517,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -5474,7 +5537,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
@@ -5499,7 +5562,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
@@ -5524,7 +5587,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5534,7 +5597,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
@@ -5559,25 +5622,25 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="B19" s="44" t="str">
+        <v>348</v>
+      </c>
+      <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="44" t="str">
+      <c r="C19" s="46" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="44" t="str">
+      <c r="D19" s="46" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="47">
         <f>E9-E14-E17</f>
         <v>-1</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="47">
         <f>F9-F14-F17</f>
         <v>-1</v>
       </c>
@@ -5608,7 +5671,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5638,7 +5701,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5648,7 +5711,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -5708,7 +5771,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -5753,32 +5816,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B10" s="46">
+        <v>353</v>
+      </c>
+      <c r="B10" s="48">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-5.68</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="48">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>8.19</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>28.03</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="48">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>44</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="48">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>50.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5788,7 +5851,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B13" s="30">
         <v>-190250</v>
@@ -5808,7 +5871,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B14" s="35">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5833,7 +5896,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5878,7 +5941,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5908,7 +5971,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B20" s="30">
         <v>1076256</v>
@@ -5928,7 +5991,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B21" s="30">
         <v>4542</v>
@@ -5948,27 +6011,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B22" s="47">
+        <v>361</v>
+      </c>
+      <c r="B22" s="49">
         <v>174</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="49">
         <v>158</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="49">
         <v>151</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="49">
         <v>148</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="49">
         <v>148</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5978,102 +6041,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>362</v>
+        <v>363</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>362</v>
+        <v>366</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B27" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="B27" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="D27" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="E27" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="F27" s="48" t="s">
-        <v>361</v>
+      <c r="C27" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="B28" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="E28" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="F28" s="49" t="s">
-        <v>362</v>
+      <c r="E28" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="D29" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>362</v>
-      </c>
-      <c r="F29" s="49" t="s">
-        <v>362</v>
+        <v>369</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>364</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6113,16 +6176,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>367</v>
-      </c>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>368</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6134,7 +6197,7 @@
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E4" s="30">
         <v>400000</v>
@@ -6148,7 +6211,7 @@
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E5" s="30">
         <v>75000</v>
@@ -6156,13 +6219,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B6" s="30">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E6" s="30">
         <v>40000</v>
@@ -6170,7 +6233,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E7" s="30">
         <v>60000</v>
@@ -6178,7 +6241,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E8" s="30">
         <v>75000</v>
@@ -6186,13 +6249,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B10" s="32">
         <v>650000</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E10" s="32">
         <v>650000</v>
@@ -6200,9 +6263,9 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="B11" s="44">
+        <v>380</v>
+      </c>
+      <c r="B11" s="46">
         <v>0</v>
       </c>
     </row>
@@ -6548,7 +6611,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6558,7 +6621,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6568,7 +6631,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,7 +6656,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B6" s="30">
         <v>1288333</v>
@@ -6673,27 +6736,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B10" s="51">
+        <v>353</v>
+      </c>
+      <c r="B10" s="53">
         <v>-5.68</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="53">
         <v>8.19</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="53">
         <v>28.03</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="53">
         <v>44</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="53">
         <v>50.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B11" s="35">
         <v>174</v>
@@ -6713,7 +6776,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6723,7 +6786,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6748,7 +6811,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B16" s="30">
         <v>966250</v>
@@ -6828,27 +6891,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B20" s="51">
+        <v>353</v>
+      </c>
+      <c r="B20" s="53">
         <v>-12.15</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="53">
         <v>-4.68</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="53">
         <v>8.49</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="53">
         <v>19.03</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="53">
         <v>23.13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B21" s="35">
         <v>230</v>
@@ -6868,7 +6931,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6878,7 +6941,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6903,7 +6966,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B26" s="30">
         <v>1223917</v>
@@ -6983,27 +7046,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B30" s="51">
+        <v>353</v>
+      </c>
+      <c r="B30" s="53">
         <v>-6.97</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="53">
         <v>5.62</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="53">
         <v>24.12</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="53">
         <v>39.01</v>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="53">
         <v>45.04</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B31" s="35">
         <v>191</v>
@@ -7023,7 +7086,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -7033,7 +7096,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,7 +7121,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B36" s="30">
         <v>1288333</v>
@@ -7138,27 +7201,27 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B40" s="51">
+        <v>353</v>
+      </c>
+      <c r="B40" s="53">
         <v>-6.62</v>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="53">
         <v>6.39</v>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="53">
         <v>25.34</v>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="53">
         <v>40.6</v>
       </c>
-      <c r="F40" s="51">
+      <c r="F40" s="53">
         <v>46.79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B41" s="35">
         <v>186</v>
@@ -7204,7 +7267,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7238,7 +7301,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -7262,7 +7325,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -7270,7 +7333,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7290,25 +7353,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D13" s="30">
         <v>1288333</v>
@@ -7368,7 +7431,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D16" s="30">
         <v>-190250</v>
@@ -7388,7 +7451,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D17" s="30">
         <v>478361</v>
@@ -7408,7 +7471,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7428,25 +7491,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D21" s="29">
         <v>-0.34767595489354136</v>
@@ -7466,21 +7529,21 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D22" s="51">
+        <v>353</v>
+      </c>
+      <c r="D22" s="53">
         <v>-5.68</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="53">
         <v>8.19</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="53">
         <v>28.03</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="53">
         <v>44</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="53">
         <v>50.52</v>
       </c>
     </row>
@@ -7506,7 +7569,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D24" s="35">
         <v>120</v>
@@ -7526,7 +7589,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7567,7 +7630,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7577,87 +7640,87 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
-        <v>398</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="B3" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>400</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>401</v>
+      <c r="B4" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>404</v>
-      </c>
-      <c r="E6" s="57" t="s">
         <v>405</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="C6" s="59" t="s">
         <v>406</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="D6" s="59" t="s">
         <v>407</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="59" t="s">
         <v>408</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>410</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="C7" s="58">
+        <v>398</v>
+      </c>
+      <c r="C7" s="60">
         <v>120</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="60">
         <v>200</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="60">
         <v>300</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="60">
         <v>375</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="60">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="59">
+        <v>351</v>
+      </c>
+      <c r="C8" s="61">
         <v>1288333.3333333335</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="61">
         <v>2564700</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="61">
         <v>3893503</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="61">
         <v>4977371.484999999</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="61">
         <v>5458717.7285</v>
       </c>
     </row>
@@ -7665,19 +7728,19 @@
       <c r="B9" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="61">
         <v>1026431.25</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="61">
         <v>1268669.0250000001</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="61">
         <v>1306729.0957499999</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="61">
         <v>1345930.9686225</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="61">
         <v>1386308.8976811753</v>
       </c>
     </row>
@@ -7685,19 +7748,19 @@
       <c r="B10" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="61">
         <v>545000</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="61">
         <v>887860</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="61">
         <v>1190329.8</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="61">
         <v>1439121.459</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="61">
         <v>1555453.1754200002</v>
       </c>
     </row>
@@ -7705,79 +7768,79 @@
       <c r="B11" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="61">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="61">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="61">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="61">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="61">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C12" s="60">
+        <v>412</v>
+      </c>
+      <c r="C12" s="62">
         <v>-447922.5218878458</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="63">
         <v>318346.3697788203</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="63">
         <v>1306619.4990288205</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="63">
         <v>2117494.45215632</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="63">
         <v>2447131.0501776454</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="C13" s="60">
+        <v>355</v>
+      </c>
+      <c r="C13" s="62">
         <v>-190250</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="63">
         <v>128096.36977882031</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="63">
         <v>1434715.8688076409</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="63">
         <v>3552210.320963961</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="63">
         <v>5999341.371141607</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C14" s="62">
+        <v>397</v>
+      </c>
+      <c r="C14" s="64">
         <v>-0.34767595489354136</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="65">
         <v>0.12412616281780338</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="65">
         <v>0.33558969879535744</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="65">
         <v>0.42542423416409325</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="65">
         <v>0.44829778198663</v>
       </c>
     </row>
@@ -7785,319 +7848,319 @@
       <c r="B15" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="64">
+      <c r="C15" s="66">
         <v>10736.111111111113</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="66">
         <v>12823.5</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="66">
         <v>12978.343333333334</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="66">
         <v>13272.990626666666</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="66">
         <v>13646.794321250001</v>
       </c>
-      <c r="H15" s="65" t="s">
-        <v>410</v>
+      <c r="H15" s="67" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C16" s="62">
+        <v>414</v>
+      </c>
+      <c r="C16" s="64">
         <v>0.7967124838292367</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="65">
         <v>0.49466566265060247</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="65">
         <v>0.3356178474114441</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="65">
         <v>0.27040998902305163</v>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="65">
         <v>0.25396237113402065</v>
       </c>
-      <c r="H16" s="65" t="s">
-        <v>412</v>
+      <c r="H16" s="67" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="C17" s="63">
+        <v>416</v>
+      </c>
+      <c r="C17" s="65">
         <v>0.12690815006468303</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="65">
         <v>0.10385542168674698</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="65">
         <v>0.09171662125340599</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="65">
         <v>0.08673984632272229</v>
       </c>
-      <c r="G17" s="63">
+      <c r="G17" s="65">
         <v>0.08548453608247424</v>
       </c>
-      <c r="H17" s="65" t="s">
-        <v>414</v>
+      <c r="H17" s="67" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="C18" s="62">
+        <v>418</v>
+      </c>
+      <c r="C18" s="64">
         <v>-0.21973965071151344</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="65">
         <v>0.15914959839357423</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="65">
         <v>0.3586600817438692</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="65">
         <v>0.4404571899012074</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G18" s="65">
         <v>0.4610891752577319</v>
       </c>
-      <c r="H18" s="65" t="s">
-        <v>416</v>
+      <c r="H18" s="67" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="C19" s="66">
-        <v>1</v>
-      </c>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="65" t="s">
-        <v>418</v>
+        <v>420</v>
+      </c>
+      <c r="C19" s="68">
+        <v>3</v>
+      </c>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="67" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C20" s="67">
+        <v>353</v>
+      </c>
+      <c r="C20" s="69">
         <v>-5.681889809461599</v>
       </c>
-      <c r="D20" s="68">
+      <c r="D20" s="70">
         <v>8.192156730355682</v>
       </c>
-      <c r="E20" s="68">
+      <c r="E20" s="70">
         <v>28.027198570886025</v>
       </c>
-      <c r="F20" s="68">
+      <c r="F20" s="70">
         <v>44.00073111759629</v>
       </c>
-      <c r="G20" s="68">
+      <c r="G20" s="70">
         <v>50.51631908021458</v>
       </c>
-      <c r="H20" s="65" t="s">
-        <v>419</v>
+      <c r="H20" s="67" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>404</v>
-      </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="65" t="s">
-        <v>403</v>
+        <v>423</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>408</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="67" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>422</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="65" t="s">
-        <v>423</v>
+        <v>424</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>425</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="67" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="C25" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>430</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
+      <c r="B25" s="42" t="s">
         <v>431</v>
       </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
+      <c r="C25" s="73" t="s">
+        <v>432</v>
+      </c>
+      <c r="D25" s="74" t="s">
+        <v>433</v>
+      </c>
+      <c r="E25" s="74"/>
+      <c r="F25" s="75" t="s">
+        <v>434</v>
+      </c>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
-        <v>432</v>
-      </c>
-      <c r="C26" s="74" t="s">
-        <v>433</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>434</v>
-      </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
+      <c r="B26" s="42" t="s">
         <v>435</v>
       </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
+      <c r="C26" s="76" t="s">
+        <v>436</v>
+      </c>
+      <c r="D26" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="E26" s="74"/>
+      <c r="F26" s="75" t="s">
+        <v>438</v>
+      </c>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>436</v>
-      </c>
-      <c r="C27" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D27" s="72" t="s">
-        <v>437</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
-        <v>438</v>
-      </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
+      <c r="B27" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>440</v>
+      </c>
+      <c r="D27" s="74" t="s">
+        <v>441</v>
+      </c>
+      <c r="E27" s="74"/>
+      <c r="F27" s="75" t="s">
+        <v>442</v>
+      </c>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
-        <v>439</v>
-      </c>
-      <c r="C28" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D28" s="72" t="s">
+      <c r="B28" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="C28" s="41" t="s">
         <v>440</v>
       </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
-        <v>441</v>
-      </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
+      <c r="D28" s="74" t="s">
+        <v>444</v>
+      </c>
+      <c r="E28" s="74"/>
+      <c r="F28" s="75" t="s">
+        <v>445</v>
+      </c>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
-        <v>442</v>
-      </c>
-      <c r="C29" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>443</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
-        <v>444</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="B29" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>440</v>
+      </c>
+      <c r="D29" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="E29" s="74"/>
+      <c r="F29" s="75" t="s">
+        <v>448</v>
+      </c>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="40" t="s">
-        <v>445</v>
-      </c>
-      <c r="C30" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>446</v>
-      </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
-        <v>447</v>
-      </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+      <c r="B30" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>440</v>
+      </c>
+      <c r="D30" s="74" t="s">
+        <v>450</v>
+      </c>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
+        <v>451</v>
+      </c>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="C31" s="71" t="s">
-        <v>429</v>
-      </c>
-      <c r="D31" s="72" t="s">
-        <v>449</v>
-      </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73" t="s">
-        <v>450</v>
-      </c>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
+      <c r="B31" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>440</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
+        <v>454</v>
+      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="40" t="s">
-        <v>451</v>
+      <c r="B33" s="42" t="s">
+        <v>455</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
-        <v>453</v>
-      </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="B35" s="77" t="s">
+        <v>457</v>
+      </c>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -8270,10 +8270,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="458">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1754,7 +1754,9 @@
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7978,13 +7980,26 @@
       <c r="B21" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="C21" s="71" t="s">
-        <v>408</v>
-      </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
+      <c r="C21" s="71" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="71" t="str">
+        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="41" t="str">
+        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="F21" s="71" t="str">
+        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="71" t="str">
+        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="67" t="s">
         <v>406</v>
       </c>
@@ -8163,11 +8178,10 @@
       <c r="H35" s="77"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -8248,10 +8262,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="457">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1306,13 +1306,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1555,7 +1552,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1590,6 +1587,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1644,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1747,7 +1749,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1757,7 +1761,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7945,10 +7954,18 @@
       <c r="C19" s="68">
         <v>3</v>
       </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
+      <c r="D19" s="68">
+        <v>3</v>
+      </c>
+      <c r="E19" s="68">
+        <v>3</v>
+      </c>
+      <c r="F19" s="68">
+        <v>3</v>
+      </c>
+      <c r="G19" s="68">
+        <v>3</v>
+      </c>
       <c r="H19" s="67" t="s">
         <v>421</v>
       </c>
@@ -7985,19 +8002,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="71" t="str">
-        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="41" t="str">
-        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="F21" s="71" t="str">
-        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="71" t="str">
-        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="67" t="s">
@@ -8008,181 +8025,187 @@
       <c r="B22" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="72">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="72">
+        <v>1</v>
+      </c>
+      <c r="E22" s="72">
+        <v>7</v>
+      </c>
+      <c r="F22" s="73">
+        <v>15</v>
+      </c>
+      <c r="G22" s="68">
+        <v>24</v>
+      </c>
+      <c r="H22" s="67" t="s">
         <v>425</v>
-      </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="67" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="19" t="s">
         <v>428</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>429</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="C25" s="74" t="s">
         <v>431</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="D25" s="75" t="s">
         <v>432</v>
       </c>
-      <c r="D25" s="74" t="s">
+      <c r="E25" s="75"/>
+      <c r="F25" s="76" t="s">
         <v>433</v>
       </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="75" t="s">
-        <v>434</v>
-      </c>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="C26" s="77" t="s">
         <v>435</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="D26" s="75" t="s">
         <v>436</v>
       </c>
-      <c r="D26" s="74" t="s">
+      <c r="E26" s="75"/>
+      <c r="F26" s="76" t="s">
         <v>437</v>
       </c>
-      <c r="E26" s="74"/>
-      <c r="F26" s="75" t="s">
-        <v>438</v>
-      </c>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="C27" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="D27" s="75" t="s">
         <v>440</v>
       </c>
-      <c r="D27" s="74" t="s">
+      <c r="E27" s="75"/>
+      <c r="F27" s="76" t="s">
         <v>441</v>
       </c>
-      <c r="E27" s="74"/>
-      <c r="F27" s="75" t="s">
-        <v>442</v>
-      </c>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D28" s="75" t="s">
         <v>443</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="D28" s="74" t="s">
+      <c r="E28" s="75"/>
+      <c r="F28" s="76" t="s">
         <v>444</v>
       </c>
-      <c r="E28" s="74"/>
-      <c r="F28" s="75" t="s">
-        <v>445</v>
-      </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D29" s="75" t="s">
         <v>446</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="D29" s="74" t="s">
+      <c r="E29" s="75"/>
+      <c r="F29" s="76" t="s">
         <v>447</v>
       </c>
-      <c r="E29" s="74"/>
-      <c r="F29" s="75" t="s">
-        <v>448</v>
-      </c>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D30" s="75" t="s">
         <v>449</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="D30" s="74" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
         <v>450</v>
       </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75" t="s">
-        <v>451</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D31" s="75" t="s">
         <v>452</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="D31" s="74" t="s">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
         <v>453</v>
       </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75" t="s">
-        <v>454</v>
-      </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>455</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>456</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="77" t="s">
-        <v>457</v>
-      </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="B35" s="78" t="s">
+        <v>456</v>
+      </c>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -1363,7 +1363,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -1646,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1749,6 +1749,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7905,20 +7908,20 @@
       <c r="B17" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="C17" s="65">
-        <v>0.12690815006468303</v>
+      <c r="C17" s="68">
+        <v>0.2188874514877102</v>
       </c>
       <c r="D17" s="65">
-        <v>0.10385542168674698</v>
+        <v>0.11325301204819277</v>
       </c>
       <c r="E17" s="65">
-        <v>0.09171662125340599</v>
+        <v>0.07683923705722072</v>
       </c>
       <c r="F17" s="65">
-        <v>0.08673984632272229</v>
+        <v>0.0619099890230516</v>
       </c>
       <c r="G17" s="65">
-        <v>0.08548453608247424</v>
+        <v>0.05814432989690721</v>
       </c>
       <c r="H17" s="67" t="s">
         <v>417</v>
@@ -7951,19 +7954,19 @@
       <c r="B19" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="C19" s="68">
+      <c r="C19" s="69">
         <v>3</v>
       </c>
-      <c r="D19" s="68">
+      <c r="D19" s="69">
         <v>3</v>
       </c>
-      <c r="E19" s="68">
+      <c r="E19" s="69">
         <v>3</v>
       </c>
-      <c r="F19" s="68">
+      <c r="F19" s="69">
         <v>3</v>
       </c>
-      <c r="G19" s="68">
+      <c r="G19" s="69">
         <v>3</v>
       </c>
       <c r="H19" s="67" t="s">
@@ -7974,19 +7977,19 @@
       <c r="B20" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="70">
         <v>-5.681889809461599</v>
       </c>
-      <c r="D20" s="70">
+      <c r="D20" s="71">
         <v>8.192156730355682</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="71">
         <v>28.027198570886025</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="71">
         <v>44.00073111759629</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="71">
         <v>50.51631908021458</v>
       </c>
       <c r="H20" s="67" t="s">
@@ -7997,11 +8000,11 @@
       <c r="B21" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="C21" s="71" t="str">
+      <c r="C21" s="72" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="71" t="str">
+      <c r="D21" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -8009,11 +8012,11 @@
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="71" t="str">
+      <c r="F21" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="71" t="str">
+      <c r="G21" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -8025,19 +8028,19 @@
       <c r="B22" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="73">
         <v>-1</v>
       </c>
-      <c r="D22" s="72">
+      <c r="D22" s="73">
         <v>1</v>
       </c>
-      <c r="E22" s="72">
+      <c r="E22" s="73">
         <v>7</v>
       </c>
-      <c r="F22" s="73">
+      <c r="F22" s="74">
         <v>15</v>
       </c>
-      <c r="G22" s="68">
+      <c r="G22" s="69">
         <v>24</v>
       </c>
       <c r="H22" s="67" t="s">
@@ -8065,35 +8068,35 @@
       <c r="B25" s="42" t="s">
         <v>430</v>
       </c>
-      <c r="C25" s="74" t="s">
+      <c r="C25" s="75" t="s">
         <v>431</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="76" t="s">
         <v>432</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76" t="s">
+      <c r="E25" s="76"/>
+      <c r="F25" s="77" t="s">
         <v>433</v>
       </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
         <v>434</v>
       </c>
-      <c r="C26" s="77" t="s">
+      <c r="C26" s="78" t="s">
         <v>435</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="76" t="s">
         <v>436</v>
       </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76" t="s">
+      <c r="E26" s="76"/>
+      <c r="F26" s="77" t="s">
         <v>437</v>
       </c>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
@@ -8102,15 +8105,15 @@
       <c r="C27" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="76" t="s">
         <v>440</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76" t="s">
+      <c r="E27" s="76"/>
+      <c r="F27" s="77" t="s">
         <v>441</v>
       </c>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
@@ -8119,15 +8122,15 @@
       <c r="C28" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="D28" s="75" t="s">
+      <c r="D28" s="76" t="s">
         <v>443</v>
       </c>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76" t="s">
+      <c r="E28" s="76"/>
+      <c r="F28" s="77" t="s">
         <v>444</v>
       </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
@@ -8136,15 +8139,15 @@
       <c r="C29" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="76" t="s">
         <v>446</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76" t="s">
+      <c r="E29" s="76"/>
+      <c r="F29" s="77" t="s">
         <v>447</v>
       </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
@@ -8153,15 +8156,15 @@
       <c r="C30" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="76" t="s">
         <v>449</v>
       </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>450</v>
       </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -8170,15 +8173,15 @@
       <c r="C31" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="D31" s="75" t="s">
+      <c r="D31" s="76" t="s">
         <v>452</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>453</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
@@ -8192,15 +8195,15 @@
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
+      <c r="B35" s="79" t="s">
         <v>456</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -40,7 +40,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +160,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1237,7 +1237,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="466">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -763,6 +763,90 @@
     <t>Staffing Costs Forecast</t>
   </si>
   <si>
+    <t xml:space="preserve">  Core Teachers [1:22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Special Education Teacher [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional Aides [3 FTE]</t>
+  </si>
+  <si>
+    <t>Total Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Executive Director [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Principal [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dean of Students [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total School Leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  School Counselor [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total Student Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Operations Manager [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Office Staff [2 FTE]</t>
+  </si>
+  <si>
+    <t>Total Administrative</t>
+  </si>
+  <si>
+    <t>TOTAL PERSONNEL</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter - Budget Detail</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  State Per-Pupil Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Federal Title I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Special Education Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CSP Startup Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Annual Fundraising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Food Service Revenue</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PERSONNEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Executive Director</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dean of Students</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Core Teachers</t>
   </si>
   <si>
@@ -772,72 +856,15 @@
     <t xml:space="preserve">  Instructional Aides</t>
   </si>
   <si>
-    <t>Total Instructional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Executive Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Principal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dean of Students</t>
-  </si>
-  <si>
-    <t>Total School Leadership</t>
+    <t xml:space="preserve">  Operations Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Office Staff</t>
   </si>
   <si>
     <t xml:space="preserve">  School Counselor</t>
   </si>
   <si>
-    <t>Total Student Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Operations Manager</t>
-  </si>
-  <si>
-    <t>Total Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Office Staff</t>
-  </si>
-  <si>
-    <t>Total Administrative</t>
-  </si>
-  <si>
-    <t>TOTAL PERSONNEL</t>
-  </si>
-  <si>
-    <t>Civic Scholars Charter - Budget Detail</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  State Per-Pupil Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Federal Title I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Special Education Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  CSP Startup Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Annual Fundraising</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Food Service Revenue</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>PERSONNEL</t>
-  </si>
-  <si>
     <t xml:space="preserve">    Curriculum &amp; Textbooks</t>
   </si>
   <si>
@@ -1354,7 +1381,7 @@
     <t>● Healthy</t>
   </si>
   <si>
-    <t>Staffing at 25% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 44% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1372,7 +1399,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 50.52x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 30.60x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1390,7 +1417,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>24.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>9.9 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1646,7 +1673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1742,6 +1769,9 @@
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1749,9 +1779,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1765,9 +1792,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2794,19 +2818,19 @@
         <v>243</v>
       </c>
       <c r="B5" s="30">
-        <v>352690</v>
+        <v>323299</v>
       </c>
       <c r="C5" s="30">
-        <v>435925</v>
+        <v>690214</v>
       </c>
       <c r="D5" s="30">
-        <v>449003</v>
+        <v>1047673</v>
       </c>
       <c r="E5" s="30">
-        <v>462473</v>
+        <v>1348879</v>
       </c>
       <c r="F5" s="30">
-        <v>476347</v>
+        <v>1468736</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,23 +2879,23 @@
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
-        <v>510600</v>
+        <v>481210</v>
       </c>
       <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
-        <v>631102</v>
+        <v>885392</v>
       </c>
       <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
-        <v>650035</v>
+        <v>1248705</v>
       </c>
       <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
-        <v>669536</v>
+        <v>1555942</v>
       </c>
       <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
-        <v>689622</v>
+        <v>1682012</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,23 +3164,23 @@
       </c>
       <c r="B24" s="32">
         <f>B8+B13+B16+B19+B22</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C24" s="32">
         <f>C8+C13+C16+C19+C22</f>
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D24" s="32">
         <f>D8+D13+D16+D19+D22</f>
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E24" s="32">
         <f>E8+E13+E16+E19+E22</f>
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F24" s="32">
         <f>F8+F13+F16+F19+F22</f>
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
   </sheetData>
@@ -3380,7 +3404,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B14" s="30">
         <v>124346</v>
@@ -3400,7 +3424,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="B15" s="30">
         <v>101738</v>
@@ -3420,7 +3444,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B16" s="30">
         <v>81390</v>
@@ -3440,27 +3464,27 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="B17" s="30">
-        <v>352690</v>
+        <v>323299</v>
       </c>
       <c r="C17" s="30">
-        <v>435925</v>
+        <v>690214</v>
       </c>
       <c r="D17" s="30">
-        <v>449003</v>
+        <v>1047673</v>
       </c>
       <c r="E17" s="30">
-        <v>462473</v>
+        <v>1348879</v>
       </c>
       <c r="F17" s="30">
-        <v>476347</v>
+        <v>1468736</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="B18" s="30">
         <v>62173</v>
@@ -3480,7 +3504,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="B19" s="30">
         <v>95738</v>
@@ -3500,7 +3524,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B20" s="30">
         <v>62173</v>
@@ -3520,7 +3544,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B21" s="30">
         <v>84012</v>
@@ -3540,7 +3564,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B22" s="30">
         <v>62173</v>
@@ -3564,23 +3588,23 @@
       </c>
       <c r="B23" s="31">
         <f>SUM(B14:B22)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C23" s="31">
         <f>SUM(C14:C22)</f>
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D23" s="31">
         <f>SUM(D14:D22)</f>
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E23" s="31">
         <f>SUM(E14:E22)</f>
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F23" s="31">
         <f>SUM(F14:F22)</f>
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3600,7 +3624,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B27" s="30">
         <v>70000</v>
@@ -3625,7 +3649,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B29" s="30">
         <v>50000</v>
@@ -3650,7 +3674,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B31" s="30">
         <v>180000</v>
@@ -3670,7 +3694,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B32" s="30">
         <v>25000</v>
@@ -3690,7 +3714,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B33" s="30">
         <v>15000</v>
@@ -3710,7 +3734,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B34" s="30">
         <v>15000</v>
@@ -3730,7 +3754,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B35" s="31">
         <f>SUM(B31:B34)</f>
@@ -3760,7 +3784,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B37" s="30">
         <v>20833</v>
@@ -3780,7 +3804,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B38" s="30">
         <v>12500</v>
@@ -3800,7 +3824,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B39" s="30">
         <v>16667</v>
@@ -3820,7 +3844,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B40" s="30">
         <v>80000</v>
@@ -3840,7 +3864,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B41" s="30">
         <v>60000</v>
@@ -3860,7 +3884,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B42" s="31">
         <f>SUM(B37:B41)</f>
@@ -3885,7 +3909,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B43" s="31">
         <f>B27+B29+B35+B42</f>
@@ -3910,7 +3934,7 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -3920,7 +3944,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B46" s="30">
         <v>49825</v>
@@ -3940,7 +3964,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B47" s="30">
         <v>75000</v>
@@ -3960,7 +3984,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B48" s="30">
         <v>40000</v>
@@ -3980,7 +4004,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B49" s="31">
         <f>SUM(B46:B48)</f>
@@ -4029,7 +4053,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4088,28 +4112,28 @@
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B23</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C5" s="33">
         <f>'Budget Detail'!C23</f>
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D5" s="33">
         <f>'Budget Detail'!D23</f>
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E5" s="33">
         <f>'Budget Detail'!E23</f>
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F5" s="33">
         <f>'Budget Detail'!F23</f>
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B43</f>
@@ -4134,7 +4158,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B7" s="33">
         <f>'Budget Detail'!B49</f>
@@ -4159,32 +4183,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
-        <v>2246354</v>
+        <v>2500643</v>
       </c>
       <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
-        <v>2586884</v>
+        <v>3185554</v>
       </c>
       <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
-        <v>2859877</v>
+        <v>3746283</v>
       </c>
       <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
-        <v>3011587</v>
+        <v>4003976</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4194,72 +4218,72 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C11" s="32">
         <f>C4-C8</f>
-        <v>318346</v>
+        <v>64057</v>
       </c>
       <c r="D11" s="32">
         <f>D4-D8</f>
-        <v>1306619</v>
+        <v>707949</v>
       </c>
       <c r="E11" s="32">
         <f>E4-E8</f>
-        <v>2117494</v>
+        <v>1231089</v>
       </c>
       <c r="F11" s="32">
         <f>F4-F8</f>
-        <v>2447131</v>
+        <v>1454742</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
-        <v>-0.34767595</v>
+        <v>-0.32486289</v>
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.12412616</v>
+        <v>0.02497636</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.3355897</v>
+        <v>0.18182839</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.42542423</v>
+        <v>0.24733708</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.44829778</v>
+        <v>0.26649881</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B13" s="30">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C13" s="30">
-        <v>-129576</v>
+        <v>-354475</v>
       </c>
       <c r="D13" s="30">
-        <v>1177043</v>
+        <v>353475</v>
       </c>
       <c r="E13" s="30">
-        <v>3294538</v>
+        <v>1584563</v>
       </c>
       <c r="F13" s="30">
-        <v>5741669</v>
+        <v>3039305</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4284,22 +4308,22 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B15" s="30">
-        <v>14469</v>
+        <v>14224</v>
       </c>
       <c r="C15" s="30">
-        <v>11232</v>
+        <v>12503</v>
       </c>
       <c r="D15" s="30">
-        <v>8623</v>
+        <v>10619</v>
       </c>
       <c r="E15" s="30">
-        <v>7626</v>
+        <v>9990</v>
       </c>
       <c r="F15" s="30">
-        <v>7529</v>
+        <v>10010</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4353,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4350,43 +4374,43 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4454,7 +4478,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4472,37 +4496,37 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="C7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="D7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="E7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="F7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="G7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="H7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="I7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="J7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="K7" s="30">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="L7" s="30">
         <v>0</v>
@@ -4512,12 +4536,12 @@
       </c>
       <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B8" s="30">
         <v>54500</v>
@@ -4562,7 +4586,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B9" s="30">
         <v>13735</v>
@@ -4607,7 +4631,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4625,47 +4649,47 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="C12" s="33">
         <f>C7+C8+C9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="D12" s="33">
         <f>D7+D8+D9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="E12" s="33">
         <f>E7+E8+E9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="F12" s="33">
         <f>F7+F8+F9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="G12" s="33">
         <f>G7+G8+G9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="H12" s="33">
         <f>H7+H8+H9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="I12" s="33">
         <f>I7+I8+I9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="J12" s="33">
         <f>J7+J8+J9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="K12" s="33">
         <f>K7+K8+K9</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="L12" s="33">
         <f>L7+L8+L9</f>
@@ -4677,52 +4701,52 @@
       </c>
       <c r="N12" s="33">
         <f>SUM(B12:M12)</f>
-        <v>1736250</v>
+        <v>1706860</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C13" s="33">
         <f>C4-C12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="D13" s="33">
         <f>D4-D12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="E13" s="33">
         <f>E4-E12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="F13" s="33">
         <f>F4-F12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="G13" s="33">
         <f>G4-G12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="H13" s="33">
         <f>H4-H12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="I13" s="33">
         <f>I4-I12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="J13" s="33">
         <f>J4-J12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="K13" s="33">
         <f>K4-K12</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="L13" s="33">
         <f>L4-L12</f>
@@ -4734,69 +4758,69 @@
       </c>
       <c r="N13" s="33">
         <f>SUM(B13:M13)</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C14" s="38">
         <f>B14+C13</f>
-        <v>-32556</v>
+        <v>-26678</v>
       </c>
       <c r="D14" s="38">
         <f>C14+D13</f>
-        <v>-48834</v>
+        <v>-40017</v>
       </c>
       <c r="E14" s="38">
         <f>D14+E13</f>
-        <v>-65112</v>
+        <v>-53356</v>
       </c>
       <c r="F14" s="38">
         <f>E14+F13</f>
-        <v>-81390</v>
+        <v>-66695</v>
       </c>
       <c r="G14" s="38">
         <f>F14+G13</f>
-        <v>-97668</v>
+        <v>-80034</v>
       </c>
       <c r="H14" s="38">
         <f>G14+H13</f>
-        <v>-113946</v>
+        <v>-93373</v>
       </c>
       <c r="I14" s="38">
         <f>H14+I13</f>
-        <v>-130224</v>
+        <v>-106712</v>
       </c>
       <c r="J14" s="38">
         <f>I14+J13</f>
-        <v>-146502</v>
+        <v>-120051</v>
       </c>
       <c r="K14" s="38">
         <f>J14+K13</f>
-        <v>-162780</v>
+        <v>-133390</v>
       </c>
       <c r="L14" s="38">
         <f>K14+L13</f>
-        <v>-176515</v>
+        <v>-147125</v>
       </c>
       <c r="M14" s="38">
         <f>L14+M13</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="N14" s="32">
         <f>M14</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4811,20 +4835,20 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
   </sheetData>
@@ -4853,7 +4877,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4913,7 +4937,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4923,27 +4947,27 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B8" s="33">
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C8" s="33">
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D8" s="33">
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E8" s="33">
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F8" s="33">
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B9" s="33">
         <v>545000</v>
@@ -4963,7 +4987,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B10" s="33">
         <v>164825</v>
@@ -4983,32 +5007,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
-        <v>2246354</v>
+        <v>2500643</v>
       </c>
       <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
-        <v>2586884</v>
+        <v>3185554</v>
       </c>
       <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
-        <v>2859877</v>
+        <v>3746283</v>
       </c>
       <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
-        <v>3011587</v>
+        <v>4003976</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5018,82 +5042,82 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B14" s="32">
         <f>B5-B11</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C14" s="32">
         <f>C5-C11</f>
-        <v>318346</v>
+        <v>64057</v>
       </c>
       <c r="D14" s="32">
         <f>D5-D11</f>
-        <v>1306619</v>
+        <v>707949</v>
       </c>
       <c r="E14" s="32">
         <f>E5-E11</f>
-        <v>2117494</v>
+        <v>1231089</v>
       </c>
       <c r="F14" s="32">
         <f>F5-F11</f>
-        <v>2447131</v>
+        <v>1454742</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
-        <v>-0.34767595</v>
+        <v>-0.32486289</v>
       </c>
       <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.12412616</v>
+        <v>0.02497636</v>
       </c>
       <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.3355897</v>
+        <v>0.18182839</v>
       </c>
       <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.42542423</v>
+        <v>0.24733708</v>
       </c>
       <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.44829778</v>
+        <v>0.26649881</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B16" s="33">
         <f>B14</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C16" s="33">
         <f>B16+C14</f>
-        <v>-129576</v>
+        <v>-354475</v>
       </c>
       <c r="D16" s="33">
         <f>C16+D14</f>
-        <v>1177043</v>
+        <v>353475</v>
       </c>
       <c r="E16" s="33">
         <f>D16+E14</f>
-        <v>3294538</v>
+        <v>1584563</v>
       </c>
       <c r="F16" s="33">
         <f>E16+F14</f>
-        <v>5741669</v>
+        <v>3039305</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B17" s="40" t="s">
         <v>7</v>
@@ -5102,7 +5126,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E17" s="40" t="s">
         <v>7</v>
@@ -5167,7 +5191,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5177,16 +5201,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>135</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>234</v>
@@ -5212,7 +5236,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5222,7 +5246,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B9" s="30">
         <f>B6</f>
@@ -5247,7 +5271,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5272,7 +5296,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5297,7 +5321,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B12" s="33">
         <f>B10+B11</f>
@@ -5322,7 +5346,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5371,7 +5395,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5401,7 +5425,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5411,32 +5435,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="C5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14</f>
-        <v>128096</v>
+        <v>-96803</v>
       </c>
       <c r="D5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
-        <v>1434716</v>
+        <v>611146</v>
       </c>
       <c r="E5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
-        <v>3552210</v>
+        <v>1842235</v>
       </c>
       <c r="F5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
-        <v>5999341</v>
+        <v>3296977</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B6" s="30">
         <v>0</v>
@@ -5456,7 +5480,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B7" s="30">
         <v>0</v>
@@ -5476,7 +5500,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -5496,32 +5520,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>128096</v>
+        <v>-96803</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>1434716</v>
+        <v>611146</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>3552210</v>
+        <v>1842235</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>5999341</v>
+        <v>3296977</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5531,7 +5555,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -5551,7 +5575,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
@@ -5576,7 +5600,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
@@ -5601,7 +5625,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5611,52 +5635,52 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
-        <v>-668611</v>
+        <v>-639221</v>
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>-327348</v>
+        <v>-552248</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>1003541</v>
+        <v>179971</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>3146738</v>
+        <v>1436762</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>5621089</v>
+        <v>2918724</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="str">
+      <c r="C19" s="47">
         <f>C9-C14-C17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="46" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="46" t="str">
         <f>E9-E14-E17</f>
-        <v>-1</v>
-      </c>
-      <c r="F19" s="47">
+        <v>0</v>
+      </c>
+      <c r="F19" s="46" t="str">
         <f>F9-F14-F17</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5685,7 +5709,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5715,7 +5739,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5725,7 +5749,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -5745,27 +5769,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B6" s="30">
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C6" s="30">
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D6" s="30">
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E6" s="30">
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F6" s="30">
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B7" s="30">
         <v>545000</v>
@@ -5785,32 +5809,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
-        <v>-283098</v>
+        <v>-253707</v>
       </c>
       <c r="C8" s="33">
         <f>C5-C6-C7</f>
-        <v>408171</v>
+        <v>153881</v>
       </c>
       <c r="D8" s="33">
         <f>D5-D6-D7</f>
-        <v>1396444</v>
+        <v>797774</v>
       </c>
       <c r="E8" s="33">
         <f>E5-E6-E7</f>
-        <v>2192319</v>
+        <v>1305913</v>
       </c>
       <c r="F8" s="33">
         <f>F5-F6-F7</f>
-        <v>2516956</v>
+        <v>1524566</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B9" s="30">
         <v>49825</v>
@@ -5830,32 +5854,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B10" s="48">
         <f>IF(B9=0,"N/A",B8/B9)</f>
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C10" s="48">
         <f>IF(C9=0,"N/A",C8/C9)</f>
-        <v>8.19</v>
+        <v>3.09</v>
       </c>
       <c r="D10" s="48">
         <f>IF(D9=0,"N/A",D8/D9)</f>
-        <v>28.03</v>
+        <v>16.01</v>
       </c>
       <c r="E10" s="48">
         <f>IF(E9=0,"N/A",E8/E9)</f>
-        <v>44</v>
+        <v>26.21</v>
       </c>
       <c r="F10" s="48">
         <f>IF(F9=0,"N/A",F8/F9)</f>
-        <v>50.52</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5865,72 +5889,72 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B13" s="30">
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="C13" s="30">
-        <v>128096</v>
+        <v>-96803</v>
       </c>
       <c r="D13" s="30">
-        <v>1434716</v>
+        <v>611146</v>
       </c>
       <c r="E13" s="30">
-        <v>3552210</v>
+        <v>1842235</v>
       </c>
       <c r="F13" s="30">
-        <v>5999341</v>
+        <v>3296977</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B14" s="35">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>-43</v>
+        <v>-37</v>
       </c>
       <c r="C14" s="35">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>21</v>
+        <v>-14</v>
       </c>
       <c r="D14" s="35">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>206</v>
+        <v>71</v>
       </c>
       <c r="E14" s="35">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>457</v>
+        <v>181</v>
       </c>
       <c r="F14" s="35">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>732</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="C15" s="34">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="D15" s="34">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="E15" s="34">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="F15" s="34">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>24.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5955,7 +5979,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5985,27 +6009,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B20" s="30">
-        <v>1076256</v>
+        <v>1046865</v>
       </c>
       <c r="C20" s="30">
-        <v>1318494</v>
+        <v>1572783</v>
       </c>
       <c r="D20" s="30">
-        <v>1356554</v>
+        <v>1955224</v>
       </c>
       <c r="E20" s="30">
-        <v>1395756</v>
+        <v>2282162</v>
       </c>
       <c r="F20" s="30">
-        <v>1436134</v>
+        <v>2428523</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B21" s="30">
         <v>4542</v>
@@ -6025,27 +6049,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B22" s="49">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C22" s="49">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="D22" s="49">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="E22" s="49">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="F22" s="49">
-        <v>148</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -6055,102 +6079,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -6191,13 +6215,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E3" s="52" t="s">
         <v>112</v>
@@ -6211,7 +6235,7 @@
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E4" s="30">
         <v>400000</v>
@@ -6225,7 +6249,7 @@
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E5" s="30">
         <v>75000</v>
@@ -6233,13 +6257,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B6" s="30">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="E6" s="30">
         <v>40000</v>
@@ -6247,7 +6271,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="E7" s="30">
         <v>60000</v>
@@ -6255,7 +6279,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E8" s="30">
         <v>75000</v>
@@ -6263,13 +6287,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B10" s="32">
         <v>650000</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="E10" s="32">
         <v>650000</v>
@@ -6277,7 +6301,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B11" s="46">
         <v>0</v>
@@ -6625,7 +6649,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6635,7 +6659,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6645,7 +6669,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6670,7 +6694,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B6" s="30">
         <v>1288333</v>
@@ -6690,107 +6714,107 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B7" s="30">
-        <v>1621256</v>
+        <v>1591865</v>
       </c>
       <c r="C7" s="30">
-        <v>2206354</v>
+        <v>2460643</v>
       </c>
       <c r="D7" s="30">
-        <v>2546884</v>
+        <v>3145554</v>
       </c>
       <c r="E7" s="30">
-        <v>2834877</v>
+        <v>3721283</v>
       </c>
       <c r="F7" s="30">
-        <v>2991587</v>
+        <v>3983976</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B8" s="32">
-        <v>-332923</v>
+        <v>-303532</v>
       </c>
       <c r="C8" s="32">
-        <v>358346</v>
+        <v>104057</v>
       </c>
       <c r="D8" s="32">
-        <v>1346619</v>
+        <v>747949</v>
       </c>
       <c r="E8" s="32">
-        <v>2142494</v>
+        <v>1256089</v>
       </c>
       <c r="F8" s="32">
-        <v>2467131</v>
+        <v>1474742</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B9" s="29">
-        <v>-0.2584133416981985</v>
+        <v>-0.2356002757214845</v>
       </c>
       <c r="C9" s="29">
-        <v>0.1397225288645145</v>
+        <v>0.04057272966772744</v>
       </c>
       <c r="D9" s="29">
-        <v>0.3458632236905482</v>
+        <v>0.19210191578864091</v>
       </c>
       <c r="E9" s="29">
-        <v>0.43044696555461553</v>
+        <v>0.2523598085842533</v>
       </c>
       <c r="F9" s="29">
-        <v>0.4519616461017463</v>
+        <v>0.2701626770295813</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B10" s="53">
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C10" s="53">
-        <v>8.19</v>
+        <v>3.09</v>
       </c>
       <c r="D10" s="53">
-        <v>28.03</v>
+        <v>16.01</v>
       </c>
       <c r="E10" s="53">
-        <v>44</v>
+        <v>26.21</v>
       </c>
       <c r="F10" s="53">
-        <v>50.52</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B11" s="35">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C11" s="35">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="D11" s="35">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="E11" s="35">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="F11" s="35">
-        <v>148</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6800,7 +6824,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6825,7 +6849,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B16" s="30">
         <v>966250</v>
@@ -6845,107 +6869,107 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B17" s="30">
-        <v>1621256</v>
+        <v>1591865</v>
       </c>
       <c r="C17" s="30">
-        <v>2206354</v>
+        <v>2460643</v>
       </c>
       <c r="D17" s="30">
-        <v>2546884</v>
+        <v>3145554</v>
       </c>
       <c r="E17" s="30">
-        <v>2834877</v>
+        <v>3721283</v>
       </c>
       <c r="F17" s="30">
-        <v>2991587</v>
+        <v>3983976</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B18" s="32">
-        <v>-655006</v>
+        <v>-625615</v>
       </c>
       <c r="C18" s="32">
-        <v>-282829</v>
+        <v>-537118</v>
       </c>
       <c r="D18" s="32">
-        <v>373244</v>
+        <v>-225426</v>
       </c>
       <c r="E18" s="32">
-        <v>898152</v>
+        <v>11746</v>
       </c>
       <c r="F18" s="32">
-        <v>1102452</v>
+        <v>110062</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B19" s="29">
-        <v>-0.677884455597598</v>
+        <v>-0.6474670342953127</v>
       </c>
       <c r="C19" s="29">
-        <v>-0.14703662818064733</v>
+        <v>-0.2792363604430301</v>
       </c>
       <c r="D19" s="29">
-        <v>0.12781763158739762</v>
+        <v>-0.07719744561514545</v>
       </c>
       <c r="E19" s="29">
-        <v>0.2405959540728207</v>
+        <v>0.0031464114456710686</v>
       </c>
       <c r="F19" s="29">
-        <v>0.26928219480232835</v>
+        <v>0.026883569372774998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B20" s="53">
-        <v>-12.15</v>
+        <v>-11.56</v>
       </c>
       <c r="C20" s="53">
-        <v>-4.68</v>
+        <v>-9.78</v>
       </c>
       <c r="D20" s="53">
-        <v>8.49</v>
+        <v>-3.52</v>
       </c>
       <c r="E20" s="53">
-        <v>19.03</v>
+        <v>1.24</v>
       </c>
       <c r="F20" s="53">
-        <v>23.13</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B21" s="35">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C21" s="35">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="D21" s="35">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="E21" s="35">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="F21" s="35">
-        <v>170</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6955,7 +6979,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6980,7 +7004,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B26" s="30">
         <v>1223917</v>
@@ -7000,107 +7024,107 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B27" s="30">
-        <v>1621256</v>
+        <v>1591865</v>
       </c>
       <c r="C27" s="30">
-        <v>2206354</v>
+        <v>2460643</v>
       </c>
       <c r="D27" s="30">
-        <v>2546884</v>
+        <v>3145554</v>
       </c>
       <c r="E27" s="30">
-        <v>2834877</v>
+        <v>3721283</v>
       </c>
       <c r="F27" s="30">
-        <v>2991587</v>
+        <v>3983976</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B28" s="32">
-        <v>-397339</v>
+        <v>-367948</v>
       </c>
       <c r="C28" s="32">
-        <v>230111</v>
+        <v>-24178</v>
       </c>
       <c r="D28" s="32">
-        <v>1151944</v>
+        <v>553274</v>
       </c>
       <c r="E28" s="32">
-        <v>1893626</v>
+        <v>1007220</v>
       </c>
       <c r="F28" s="32">
-        <v>2194195</v>
+        <v>1201806</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B29" s="29">
-        <v>-0.3246456228402091</v>
+        <v>-0.3006318691805101</v>
       </c>
       <c r="C29" s="29">
-        <v>0.09444476722580472</v>
+        <v>-0.00992344245502375</v>
       </c>
       <c r="D29" s="29">
-        <v>0.31143497230584016</v>
+        <v>0.14958096398804296</v>
       </c>
       <c r="E29" s="29">
-        <v>0.40047049005748997</v>
+        <v>0.2130103248255297</v>
       </c>
       <c r="F29" s="29">
-        <v>0.4231175222123644</v>
+        <v>0.2317501863469276</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B30" s="53">
-        <v>-6.97</v>
+        <v>-6.38</v>
       </c>
       <c r="C30" s="53">
-        <v>5.62</v>
+        <v>0.51</v>
       </c>
       <c r="D30" s="53">
-        <v>24.12</v>
+        <v>12.1</v>
       </c>
       <c r="E30" s="53">
-        <v>39.01</v>
+        <v>21.22</v>
       </c>
       <c r="F30" s="53">
-        <v>45.04</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B31" s="35">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C31" s="35">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="D31" s="35">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="E31" s="35">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="F31" s="35">
-        <v>159</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -7110,7 +7134,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,7 +7159,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B36" s="30">
         <v>1288333</v>
@@ -7155,102 +7179,102 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B37" s="30">
-        <v>1667756</v>
+        <v>1638365</v>
       </c>
       <c r="C37" s="30">
-        <v>2295964</v>
+        <v>2550253</v>
       </c>
       <c r="D37" s="30">
-        <v>2680557</v>
+        <v>3279227</v>
       </c>
       <c r="E37" s="30">
-        <v>3004523</v>
+        <v>3890929</v>
       </c>
       <c r="F37" s="30">
-        <v>3177296</v>
+        <v>4169685</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B38" s="32">
-        <v>-379423</v>
+        <v>-350032</v>
       </c>
       <c r="C38" s="32">
-        <v>268736</v>
+        <v>14447</v>
       </c>
       <c r="D38" s="32">
-        <v>1212946</v>
+        <v>614276</v>
       </c>
       <c r="E38" s="32">
-        <v>1972849</v>
+        <v>1086443</v>
       </c>
       <c r="F38" s="32">
-        <v>2281422</v>
+        <v>1289033</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B39" s="29">
-        <v>-0.2945064852945763</v>
+        <v>-0.27169341931786223</v>
       </c>
       <c r="C39" s="29">
-        <v>0.10478276982836991</v>
+        <v>0.005632970631582858</v>
       </c>
       <c r="D39" s="29">
-        <v>0.31153079862242844</v>
+        <v>0.15776949072052104</v>
       </c>
       <c r="E39" s="29">
-        <v>0.3963635407467121</v>
+        <v>0.2182763837763499</v>
       </c>
       <c r="F39" s="29">
-        <v>0.4179410275450453</v>
+        <v>0.23614205847288033</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B40" s="53">
-        <v>-6.62</v>
+        <v>-6.03</v>
       </c>
       <c r="C40" s="53">
-        <v>6.39</v>
+        <v>1.29</v>
       </c>
       <c r="D40" s="53">
-        <v>25.34</v>
+        <v>13.33</v>
       </c>
       <c r="E40" s="53">
-        <v>40.6</v>
+        <v>22.81</v>
       </c>
       <c r="F40" s="53">
-        <v>46.79</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B41" s="35">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C41" s="35">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="D41" s="35">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="E41" s="35">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="F41" s="35">
-        <v>155</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -7281,7 +7305,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7315,7 +7339,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -7339,7 +7363,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -7347,7 +7371,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7385,7 +7409,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D13" s="30">
         <v>1288333</v>
@@ -7405,67 +7429,67 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D14" s="30">
-        <v>1621256</v>
+        <v>1591865</v>
       </c>
       <c r="E14" s="30">
-        <v>2206354</v>
+        <v>2460643</v>
       </c>
       <c r="F14" s="30">
-        <v>2546884</v>
+        <v>3145554</v>
       </c>
       <c r="G14" s="30">
-        <v>2834877</v>
+        <v>3721283</v>
       </c>
       <c r="H14" s="30">
-        <v>2991587</v>
+        <v>3983976</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D15" s="30">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="E15" s="30">
-        <v>318346</v>
+        <v>64057</v>
       </c>
       <c r="F15" s="30">
-        <v>1306619</v>
+        <v>707949</v>
       </c>
       <c r="G15" s="30">
-        <v>2117494</v>
+        <v>1231089</v>
       </c>
       <c r="H15" s="30">
-        <v>2447131</v>
+        <v>1454742</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D16" s="30">
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="E16" s="30">
-        <v>128096</v>
+        <v>-96803</v>
       </c>
       <c r="F16" s="30">
-        <v>1434716</v>
+        <v>611146</v>
       </c>
       <c r="G16" s="30">
-        <v>3552210</v>
+        <v>1842235</v>
       </c>
       <c r="H16" s="30">
-        <v>5999341</v>
+        <v>3296977</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D17" s="30">
         <v>478361</v>
@@ -7485,7 +7509,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7523,42 +7547,42 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D21" s="29">
-        <v>-0.34767595489354136</v>
+        <v>-0.3248628889168275</v>
       </c>
       <c r="E21" s="29">
-        <v>0.12412616281780338</v>
+        <v>0.02497636362101632</v>
       </c>
       <c r="F21" s="29">
-        <v>0.33558969879535744</v>
+        <v>0.18182839089345013</v>
       </c>
       <c r="G21" s="29">
-        <v>0.42542423416409325</v>
+        <v>0.24733707719373102</v>
       </c>
       <c r="H21" s="29">
-        <v>0.44829778198663</v>
+        <v>0.26649881291446503</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D22" s="53">
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="E22" s="53">
-        <v>8.19</v>
+        <v>3.09</v>
       </c>
       <c r="F22" s="53">
-        <v>28.03</v>
+        <v>16.01</v>
       </c>
       <c r="G22" s="53">
-        <v>44</v>
+        <v>26.21</v>
       </c>
       <c r="H22" s="53">
-        <v>50.52</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7583,7 +7607,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="D24" s="35">
         <v>120</v>
@@ -7603,7 +7627,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7644,7 +7668,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7655,7 +7679,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
@@ -7666,41 +7690,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="56" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C7" s="60">
         <v>120</v>
@@ -7720,7 +7744,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C8" s="61">
         <v>1288333.3333333335</v>
@@ -7740,27 +7764,27 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C9" s="61">
-        <v>1026431.25</v>
+        <v>997040.4166666667</v>
       </c>
       <c r="D9" s="61">
-        <v>1268669.0250000001</v>
+        <v>1522958.5150000001</v>
       </c>
       <c r="E9" s="61">
-        <v>1306729.0957499999</v>
+        <v>1905399.20935</v>
       </c>
       <c r="F9" s="61">
-        <v>1345930.9686225</v>
+        <v>2232336.9055715</v>
       </c>
       <c r="G9" s="61">
-        <v>1386308.8976811753</v>
+        <v>2378698.1531784255</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C10" s="61">
         <v>545000</v>
@@ -7780,7 +7804,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C11" s="61">
         <v>49824.605221179416</v>
@@ -7800,159 +7824,159 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C12" s="62">
-        <v>-447922.5218878458</v>
+        <v>-418531.6885545128</v>
       </c>
       <c r="D12" s="63">
-        <v>318346.3697788203</v>
+        <v>64056.879778820556</v>
       </c>
       <c r="E12" s="63">
-        <v>1306619.4990288205</v>
+        <v>707949.3854288207</v>
       </c>
       <c r="F12" s="63">
-        <v>2117494.45215632</v>
+        <v>1231088.5152073205</v>
       </c>
       <c r="G12" s="63">
-        <v>2447131.0501776454</v>
+        <v>1454741.7946803952</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C13" s="62">
-        <v>-190250</v>
-      </c>
-      <c r="D13" s="63">
-        <v>128096.36977882031</v>
+        <v>-160860</v>
+      </c>
+      <c r="D13" s="62">
+        <v>-96803.12022117944</v>
       </c>
       <c r="E13" s="63">
-        <v>1434715.8688076409</v>
+        <v>611146.2652076413</v>
       </c>
       <c r="F13" s="63">
-        <v>3552210.320963961</v>
+        <v>1842234.7804149617</v>
       </c>
       <c r="G13" s="63">
-        <v>5999341.371141607</v>
+        <v>3296976.575095357</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C14" s="64">
-        <v>-0.34767595489354136</v>
+        <v>-0.3248628889168275</v>
       </c>
       <c r="D14" s="65">
-        <v>0.12412616281780338</v>
-      </c>
-      <c r="E14" s="65">
-        <v>0.33558969879535744</v>
-      </c>
-      <c r="F14" s="65">
-        <v>0.42542423416409325</v>
-      </c>
-      <c r="G14" s="65">
-        <v>0.44829778198663</v>
+        <v>0.02497636362101632</v>
+      </c>
+      <c r="E14" s="66">
+        <v>0.18182839089345013</v>
+      </c>
+      <c r="F14" s="66">
+        <v>0.24733707719373102</v>
+      </c>
+      <c r="G14" s="66">
+        <v>0.26649881291446503</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="66">
+      <c r="C15" s="67">
         <v>10736.111111111113</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="67">
         <v>12823.5</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="67">
         <v>12978.343333333334</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="67">
         <v>13272.990626666666</v>
       </c>
-      <c r="G15" s="66">
+      <c r="G15" s="67">
         <v>13646.794321250001</v>
       </c>
-      <c r="H15" s="67" t="s">
-        <v>413</v>
+      <c r="H15" s="68" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C16" s="64">
-        <v>0.7967124838292367</v>
+        <v>0.7738994178525226</v>
       </c>
       <c r="D16" s="65">
-        <v>0.49466566265060247</v>
-      </c>
-      <c r="E16" s="65">
-        <v>0.3356178474114441</v>
-      </c>
-      <c r="F16" s="65">
-        <v>0.27040998902305163</v>
-      </c>
-      <c r="G16" s="65">
-        <v>0.25396237113402065</v>
-      </c>
-      <c r="H16" s="67" t="s">
-        <v>415</v>
+        <v>0.5938154618473896</v>
+      </c>
+      <c r="E16" s="66">
+        <v>0.48937915531335147</v>
+      </c>
+      <c r="F16" s="66">
+        <v>0.44849714599341384</v>
+      </c>
+      <c r="G16" s="66">
+        <v>0.4357613402061856</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="68">
+        <v>425</v>
+      </c>
+      <c r="C17" s="65">
         <v>0.2188874514877102</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="66">
         <v>0.11325301204819277</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="66">
         <v>0.07683923705722072</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="66">
         <v>0.0619099890230516</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="66">
         <v>0.05814432989690721</v>
       </c>
-      <c r="H17" s="67" t="s">
-        <v>417</v>
+      <c r="H17" s="68" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C18" s="64">
-        <v>-0.21973965071151344</v>
+        <v>-0.1969265847347994</v>
       </c>
       <c r="D18" s="65">
-        <v>0.15914959839357423</v>
-      </c>
-      <c r="E18" s="65">
-        <v>0.3586600817438692</v>
-      </c>
-      <c r="F18" s="65">
-        <v>0.4404571899012074</v>
-      </c>
-      <c r="G18" s="65">
-        <v>0.4610891752577319</v>
-      </c>
-      <c r="H18" s="67" t="s">
-        <v>419</v>
+        <v>0.0599997991967871</v>
+      </c>
+      <c r="E18" s="66">
+        <v>0.20489877384196187</v>
+      </c>
+      <c r="F18" s="66">
+        <v>0.26237003293084515</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.2792902061855669</v>
+      </c>
+      <c r="H18" s="68" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C19" s="69">
         <v>3</v>
@@ -7969,36 +7993,36 @@
       <c r="G19" s="69">
         <v>3</v>
       </c>
-      <c r="H19" s="67" t="s">
-        <v>421</v>
+      <c r="H19" s="68" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C20" s="70">
-        <v>-5.681889809461599</v>
+        <v>-5.092003884568414</v>
       </c>
       <c r="D20" s="71">
-        <v>8.192156730355682</v>
+        <v>3.0884637081798294</v>
       </c>
       <c r="E20" s="71">
-        <v>28.027198570886025</v>
+        <v>16.01164699867773</v>
       </c>
       <c r="F20" s="71">
-        <v>44.00073111759629</v>
+        <v>26.21020507099538</v>
       </c>
       <c r="G20" s="71">
-        <v>50.51631908021458</v>
-      </c>
-      <c r="H20" s="67" t="s">
-        <v>422</v>
+        <v>30.598664919346167</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C21" s="72" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
@@ -8020,190 +8044,190 @@
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="67" t="s">
-        <v>406</v>
+      <c r="H21" s="68" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C22" s="73">
         <v>-1</v>
       </c>
       <c r="D22" s="73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="73">
-        <v>7</v>
-      </c>
-      <c r="F22" s="74">
-        <v>15</v>
-      </c>
-      <c r="G22" s="69">
-        <v>24</v>
-      </c>
-      <c r="H22" s="67" t="s">
-        <v>425</v>
+        <v>2</v>
+      </c>
+      <c r="F22" s="73">
+        <v>6</v>
+      </c>
+      <c r="G22" s="73">
+        <v>10</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>430</v>
-      </c>
-      <c r="C25" s="75" t="s">
-        <v>431</v>
-      </c>
-      <c r="D25" s="76" t="s">
-        <v>432</v>
-      </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77" t="s">
-        <v>433</v>
-      </c>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
+        <v>439</v>
+      </c>
+      <c r="C25" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76" t="s">
+        <v>442</v>
+      </c>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>434</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>435</v>
-      </c>
-      <c r="D26" s="76" t="s">
-        <v>436</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77" t="s">
-        <v>437</v>
-      </c>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
+        <v>443</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>444</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>445</v>
+      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76" t="s">
+        <v>446</v>
+      </c>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>440</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77" t="s">
-        <v>441</v>
-      </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
+        <v>448</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>449</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76" t="s">
+        <v>450</v>
+      </c>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>443</v>
-      </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77" t="s">
-        <v>444</v>
-      </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
+        <v>448</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>452</v>
+      </c>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77" t="s">
-        <v>447</v>
-      </c>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+        <v>448</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>455</v>
+      </c>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="C30" s="41" t="s">
         <v>448</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>449</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>450</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+      <c r="D30" s="75" t="s">
+        <v>458</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>459</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>452</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
-        <v>453</v>
-      </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+        <v>448</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>461</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>462</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
-        <v>456</v>
-      </c>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="B35" s="78" t="s">
+        <v>465</v>
+      </c>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -9957,7 +9981,7 @@
         <v>0.0765</v>
       </c>
       <c r="G7" s="33">
-        <v>423228</v>
+        <v>387959</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10111,19 +10135,19 @@
         <v>213</v>
       </c>
       <c r="B16" s="32">
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C16" s="32">
-        <v>1268669</v>
+        <v>1522959</v>
       </c>
       <c r="D16" s="32">
-        <v>1306729</v>
+        <v>1905399</v>
       </c>
       <c r="E16" s="32">
-        <v>1345931</v>
+        <v>2232337</v>
       </c>
       <c r="F16" s="32">
-        <v>1386309</v>
+        <v>2378698</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -10131,19 +10155,19 @@
         <v>214</v>
       </c>
       <c r="B17" s="29">
-        <v>0.6639270698576973</v>
+        <v>0.644916181543769</v>
       </c>
       <c r="C17" s="29">
-        <v>0.49466566265060247</v>
+        <v>0.5938154618473896</v>
       </c>
       <c r="D17" s="29">
-        <v>0.3356178474114441</v>
+        <v>0.48937915531335147</v>
       </c>
       <c r="E17" s="29">
-        <v>0.27040998902305163</v>
+        <v>0.44849714599341384</v>
       </c>
       <c r="F17" s="29">
-        <v>0.25396237113402065</v>
+        <v>0.4357613402061856</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="467">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1337,6 +1337,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1673,7 +1676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1792,6 +1795,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7656,7 +7662,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -8071,170 +8077,191 @@
         <v>434</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23" s="73">
+        <v>0</v>
+      </c>
+      <c r="D23" s="73">
+        <v>0</v>
+      </c>
+      <c r="E23" s="74">
+        <v>71</v>
+      </c>
+      <c r="F23" s="69">
+        <v>181</v>
+      </c>
+      <c r="G23" s="69">
+        <v>302</v>
+      </c>
+      <c r="H23" s="68" t="s">
         <v>435</v>
       </c>
-      <c r="C24" s="19" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+      <c r="E25" s="19"/>
+      <c r="F25" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="C25" s="74" t="s">
-        <v>440</v>
-      </c>
-      <c r="D25" s="75" t="s">
-        <v>441</v>
-      </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76" t="s">
-        <v>442</v>
-      </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="C26" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>442</v>
+      </c>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77" t="s">
         <v>443</v>
       </c>
-      <c r="C26" s="77" t="s">
-        <v>444</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>445</v>
-      </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>445</v>
+      </c>
+      <c r="D27" s="76" t="s">
+        <v>446</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D27" s="75" t="s">
-        <v>449</v>
-      </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76" t="s">
-        <v>450</v>
-      </c>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>450</v>
+      </c>
+      <c r="E28" s="76"/>
+      <c r="F28" s="77" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>452</v>
-      </c>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76" t="s">
-        <v>453</v>
-      </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D29" s="76" t="s">
+        <v>453</v>
+      </c>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77" t="s">
         <v>454</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D29" s="75" t="s">
-        <v>455</v>
-      </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76" t="s">
-        <v>456</v>
-      </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D30" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>457</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>458</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>459</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>459</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>460</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D31" s="75" t="s">
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
         <v>461</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
+      <c r="C32" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D32" s="76" t="s">
         <v>462</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
         <v>463</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
         <v>464</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
+      <c r="C34" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="79" t="s">
+        <v>466</v>
+      </c>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -8249,8 +8276,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="471">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1301,6 +1301,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1676,7 +1688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1782,6 +1794,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7662,7 +7686,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7911,365 +7935,440 @@
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="69">
+        <v>13265.541849065385</v>
+      </c>
+      <c r="D16" s="69">
+        <v>12303.215601105898</v>
+      </c>
+      <c r="E16" s="69">
+        <v>10485.178715237264</v>
+      </c>
+      <c r="F16" s="69">
+        <v>9923.421252780478</v>
+      </c>
+      <c r="G16" s="69">
+        <v>9959.939834549012</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="C16" s="64">
-        <v>0.7738994178525226</v>
-      </c>
-      <c r="D16" s="65">
-        <v>0.5938154618473896</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.48937915531335147</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.44849714599341384</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.4357613402061856</v>
-      </c>
-      <c r="H16" s="68" t="s">
+      <c r="C17" s="61">
+        <v>700</v>
+      </c>
+      <c r="D17" s="61">
+        <v>721</v>
+      </c>
+      <c r="E17" s="61">
+        <v>742.63</v>
+      </c>
+      <c r="F17" s="61">
+        <v>764.9089</v>
+      </c>
+      <c r="G17" s="61">
+        <v>787.8561670000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="70">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="67">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="67">
+        <v>997.2460000000002</v>
+      </c>
+      <c r="F18" s="67">
+        <v>821.7307040000001</v>
+      </c>
+      <c r="G18" s="67">
+        <v>793.48371105</v>
+      </c>
+      <c r="H18" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="C17" s="65">
-        <v>0.2188874514877102</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0.11325301204819277</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0.07683923705722072</v>
-      </c>
-      <c r="F17" s="66">
-        <v>0.0619099890230516</v>
-      </c>
-      <c r="G17" s="66">
-        <v>0.05814432989690721</v>
-      </c>
-      <c r="H17" s="68" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="C18" s="64">
-        <v>-0.1969265847347994</v>
-      </c>
-      <c r="D18" s="65">
-        <v>0.0599997991967871</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.20489877384196187</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.26237003293084515</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.2792902061855669</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="C19" s="69">
-        <v>3</v>
-      </c>
-      <c r="D19" s="69">
-        <v>3</v>
-      </c>
-      <c r="E19" s="69">
-        <v>3</v>
-      </c>
-      <c r="F19" s="69">
-        <v>3</v>
-      </c>
-      <c r="G19" s="69">
-        <v>3</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>430</v>
+      <c r="C19" s="71">
+        <v>-3487.764071287607</v>
+      </c>
+      <c r="D19" s="72">
+        <v>320.28439889410276</v>
+      </c>
+      <c r="E19" s="72">
+        <v>2359.831284762736</v>
+      </c>
+      <c r="F19" s="72">
+        <v>3282.9027072195213</v>
+      </c>
+      <c r="G19" s="72">
+        <v>3636.8544867009878</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C20" s="70">
-        <v>-5.092003884568414</v>
-      </c>
-      <c r="D20" s="71">
-        <v>3.0884637081798294</v>
-      </c>
-      <c r="E20" s="71">
-        <v>16.01164699867773</v>
-      </c>
-      <c r="F20" s="71">
-        <v>26.21020507099538</v>
-      </c>
-      <c r="G20" s="71">
-        <v>30.598664919346167</v>
+        <v>427</v>
+      </c>
+      <c r="C20" s="64">
+        <v>0.7738994178525226</v>
+      </c>
+      <c r="D20" s="65">
+        <v>0.5938154618473896</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.48937915531335147</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.44849714599341384</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.4357613402061856</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0.2188874514877102</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.11325301204819277</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.07683923705722072</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.0619099890230516</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.05814432989690721</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C22" s="64">
+        <v>-0.1969265847347994</v>
+      </c>
+      <c r="D22" s="65">
+        <v>0.0599997991967871</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.20489877384196187</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.26237003293084515</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.2792902061855669</v>
+      </c>
+      <c r="H22" s="68" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="72" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="73">
+        <v>3</v>
+      </c>
+      <c r="D23" s="73">
+        <v>3</v>
+      </c>
+      <c r="E23" s="73">
+        <v>3</v>
+      </c>
+      <c r="F23" s="73">
+        <v>3</v>
+      </c>
+      <c r="G23" s="73">
+        <v>3</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24" s="74">
+        <v>-5.092003884568414</v>
+      </c>
+      <c r="D24" s="75">
+        <v>3.0884637081798294</v>
+      </c>
+      <c r="E24" s="75">
+        <v>16.01164699867773</v>
+      </c>
+      <c r="F24" s="75">
+        <v>26.21020507099538</v>
+      </c>
+      <c r="G24" s="75">
+        <v>30.598664919346167</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C25" s="76" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="72" t="str">
+      <c r="D25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="41" t="str">
+      <c r="E25" s="41" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="72" t="str">
+      <c r="F25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="72" t="str">
+      <c r="G25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H25" s="68" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C22" s="73">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C26" s="77">
         <v>-1</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D26" s="77">
         <v>0</v>
       </c>
-      <c r="E22" s="73">
+      <c r="E26" s="77">
         <v>2</v>
       </c>
-      <c r="F22" s="73">
+      <c r="F26" s="77">
         <v>6</v>
       </c>
-      <c r="G22" s="73">
+      <c r="G26" s="77">
         <v>10</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="H26" s="68" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="C23" s="73">
+      <c r="C27" s="77">
         <v>0</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D27" s="77">
         <v>0</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E27" s="78">
         <v>71</v>
       </c>
-      <c r="F23" s="69">
+      <c r="F27" s="73">
         <v>181</v>
       </c>
-      <c r="G23" s="69">
+      <c r="G27" s="73">
         <v>302</v>
       </c>
-      <c r="H23" s="68" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
+      <c r="H27" s="68" t="s">
         <v>439</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="C26" s="75" t="s">
+      <c r="C29" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D29" s="19" t="s">
         <v>442</v>
       </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="C27" s="78" t="s">
-        <v>445</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77" t="s">
-        <v>447</v>
-      </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>450</v>
-      </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77" t="s">
-        <v>451</v>
-      </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>453</v>
-      </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77" t="s">
-        <v>454</v>
-      </c>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>455</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>456</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>457</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+        <v>444</v>
+      </c>
+      <c r="C30" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="D30" s="80" t="s">
+        <v>446</v>
+      </c>
+      <c r="E30" s="80"/>
+      <c r="F30" s="81" t="s">
+        <v>447</v>
+      </c>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>458</v>
-      </c>
-      <c r="C31" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="C31" s="82" t="s">
         <v>449</v>
       </c>
-      <c r="D31" s="76" t="s">
-        <v>459</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
-        <v>460</v>
-      </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+      <c r="D31" s="80" t="s">
+        <v>450</v>
+      </c>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81" t="s">
+        <v>451</v>
+      </c>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D32" s="80" t="s">
+        <v>454</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="F32" s="81" t="s">
+        <v>455</v>
+      </c>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D33" s="80" t="s">
+        <v>457</v>
+      </c>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81" t="s">
+        <v>458</v>
+      </c>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D34" s="80" t="s">
+        <v>460</v>
+      </c>
+      <c r="E34" s="80"/>
+      <c r="F34" s="81" t="s">
         <v>461</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D32" s="76" t="s">
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77" t="s">
+      <c r="C35" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D35" s="80" t="s">
         <v>463</v>
       </c>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
+      <c r="E35" s="80"/>
+      <c r="F35" s="81" t="s">
         <v>464</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="42" t="s">
         <v>465</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="79" t="s">
+      <c r="C36" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D36" s="80" t="s">
         <v>466</v>
       </c>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="81" t="s">
+        <v>467</v>
+      </c>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="83" t="s">
+        <v>470</v>
+      </c>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -8278,8 +8377,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8325,48 +8432,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="466">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1303,18 +1303,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1349,9 +1337,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1688,7 +1673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1794,18 +1779,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1819,9 +1792,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7686,7 +7656,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7935,458 +7905,352 @@
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="69">
-        <v>13265.541849065385</v>
-      </c>
-      <c r="D16" s="69">
-        <v>12303.215601105898</v>
-      </c>
-      <c r="E16" s="69">
-        <v>10485.178715237264</v>
-      </c>
-      <c r="F16" s="69">
-        <v>9923.421252780478</v>
-      </c>
-      <c r="G16" s="69">
-        <v>9959.939834549012</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="C17" s="61">
-        <v>700</v>
-      </c>
-      <c r="D17" s="61">
-        <v>721</v>
-      </c>
-      <c r="E17" s="61">
-        <v>742.63</v>
-      </c>
-      <c r="F17" s="61">
-        <v>764.9089</v>
-      </c>
-      <c r="G17" s="61">
-        <v>787.8561670000001</v>
+      <c r="C16" s="64">
+        <v>0.7738994178525226</v>
+      </c>
+      <c r="D16" s="65">
+        <v>0.5938154618473896</v>
+      </c>
+      <c r="E16" s="66">
+        <v>0.48937915531335147</v>
+      </c>
+      <c r="F16" s="66">
+        <v>0.44849714599341384</v>
+      </c>
+      <c r="G16" s="66">
+        <v>0.4357613402061856</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C17" s="65">
+        <v>0.2188874514877102</v>
+      </c>
+      <c r="D17" s="66">
+        <v>0.11325301204819277</v>
+      </c>
+      <c r="E17" s="66">
+        <v>0.07683923705722072</v>
+      </c>
+      <c r="F17" s="66">
+        <v>0.0619099890230516</v>
+      </c>
+      <c r="G17" s="66">
+        <v>0.05814432989690721</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="C18" s="70">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="67">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="67">
-        <v>997.2460000000002</v>
-      </c>
-      <c r="F18" s="67">
-        <v>821.7307040000001</v>
-      </c>
-      <c r="G18" s="67">
-        <v>793.48371105</v>
+      <c r="B18" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="C18" s="64">
+        <v>-0.1969265847347994</v>
+      </c>
+      <c r="D18" s="65">
+        <v>0.0599997991967871</v>
+      </c>
+      <c r="E18" s="66">
+        <v>0.20489877384196187</v>
+      </c>
+      <c r="F18" s="66">
+        <v>0.26237003293084515</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.2792902061855669</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C19" s="71">
-        <v>-3487.764071287607</v>
-      </c>
-      <c r="D19" s="72">
-        <v>320.28439889410276</v>
-      </c>
-      <c r="E19" s="72">
-        <v>2359.831284762736</v>
-      </c>
-      <c r="F19" s="72">
-        <v>3282.9027072195213</v>
-      </c>
-      <c r="G19" s="72">
-        <v>3636.8544867009878</v>
+        <v>429</v>
+      </c>
+      <c r="C19" s="69">
+        <v>3</v>
+      </c>
+      <c r="D19" s="69">
+        <v>3</v>
+      </c>
+      <c r="E19" s="69">
+        <v>3</v>
+      </c>
+      <c r="F19" s="69">
+        <v>3</v>
+      </c>
+      <c r="G19" s="69">
+        <v>3</v>
+      </c>
+      <c r="H19" s="68" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="64">
-        <v>0.7738994178525226</v>
-      </c>
-      <c r="D20" s="65">
-        <v>0.5938154618473896</v>
-      </c>
-      <c r="E20" s="66">
-        <v>0.48937915531335147</v>
-      </c>
-      <c r="F20" s="66">
-        <v>0.44849714599341384</v>
-      </c>
-      <c r="G20" s="66">
-        <v>0.4357613402061856</v>
+        <v>362</v>
+      </c>
+      <c r="C20" s="70">
+        <v>-5.092003884568414</v>
+      </c>
+      <c r="D20" s="71">
+        <v>3.0884637081798294</v>
+      </c>
+      <c r="E20" s="71">
+        <v>16.01164699867773</v>
+      </c>
+      <c r="F20" s="71">
+        <v>26.21020507099538</v>
+      </c>
+      <c r="G20" s="71">
+        <v>30.598664919346167</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="C21" s="65">
-        <v>0.2188874514877102</v>
-      </c>
-      <c r="D21" s="66">
-        <v>0.11325301204819277</v>
-      </c>
-      <c r="E21" s="66">
-        <v>0.07683923705722072</v>
-      </c>
-      <c r="F21" s="66">
-        <v>0.0619099890230516</v>
-      </c>
-      <c r="G21" s="66">
-        <v>0.05814432989690721</v>
+        <v>432</v>
+      </c>
+      <c r="C21" s="72" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="41" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="F21" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="68" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="C22" s="64">
-        <v>-0.1969265847347994</v>
-      </c>
-      <c r="D22" s="65">
-        <v>0.0599997991967871</v>
-      </c>
-      <c r="E22" s="66">
-        <v>0.20489877384196187</v>
-      </c>
-      <c r="F22" s="66">
-        <v>0.26237003293084515</v>
-      </c>
-      <c r="G22" s="66">
-        <v>0.2792902061855669</v>
+        <v>433</v>
+      </c>
+      <c r="C22" s="73">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="73">
+        <v>0</v>
+      </c>
+      <c r="E22" s="73">
+        <v>2</v>
+      </c>
+      <c r="F22" s="73">
+        <v>6</v>
+      </c>
+      <c r="G22" s="73">
+        <v>10</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C23" s="73">
-        <v>3</v>
-      </c>
-      <c r="D23" s="73">
-        <v>3</v>
-      </c>
-      <c r="E23" s="73">
-        <v>3</v>
-      </c>
-      <c r="F23" s="73">
-        <v>3</v>
-      </c>
-      <c r="G23" s="73">
-        <v>3</v>
-      </c>
-      <c r="H23" s="68" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C24" s="74">
-        <v>-5.092003884568414</v>
-      </c>
-      <c r="D24" s="75">
-        <v>3.0884637081798294</v>
-      </c>
-      <c r="E24" s="75">
-        <v>16.01164699867773</v>
-      </c>
-      <c r="F24" s="75">
-        <v>26.21020507099538</v>
-      </c>
-      <c r="G24" s="75">
-        <v>30.598664919346167</v>
-      </c>
-      <c r="H24" s="68" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+      <c r="C24" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="C25" s="76" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="41" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="F25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="68" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="D24" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="C26" s="77">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="77">
-        <v>0</v>
-      </c>
-      <c r="E26" s="77">
-        <v>2</v>
-      </c>
-      <c r="F26" s="77">
-        <v>6</v>
-      </c>
-      <c r="G26" s="77">
-        <v>10</v>
-      </c>
-      <c r="H26" s="68" t="s">
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="C27" s="77">
-        <v>0</v>
-      </c>
-      <c r="D27" s="77">
-        <v>0</v>
-      </c>
-      <c r="E27" s="78">
-        <v>71</v>
-      </c>
-      <c r="F27" s="73">
-        <v>181</v>
-      </c>
-      <c r="G27" s="73">
-        <v>302</v>
-      </c>
-      <c r="H27" s="68" t="s">
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="42" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+      <c r="C25" s="74" t="s">
         <v>440</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="D25" s="75" t="s">
         <v>441</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="E25" s="75"/>
+      <c r="F25" s="76" t="s">
         <v>442</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="42" t="s">
         <v>443</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+      <c r="C26" s="77" t="s">
+        <v>444</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>445</v>
+      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76" t="s">
+        <v>446</v>
+      </c>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>449</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76" t="s">
+        <v>450</v>
+      </c>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>452</v>
+      </c>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>455</v>
+      </c>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="C30" s="79" t="s">
-        <v>445</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>446</v>
-      </c>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81" t="s">
-        <v>447</v>
-      </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
+        <v>457</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>458</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>459</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>460</v>
+      </c>
+      <c r="C31" s="41" t="s">
         <v>448</v>
       </c>
-      <c r="C31" s="82" t="s">
-        <v>449</v>
-      </c>
-      <c r="D31" s="80" t="s">
-        <v>450</v>
-      </c>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81" t="s">
-        <v>451</v>
-      </c>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D32" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81" t="s">
-        <v>455</v>
-      </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D31" s="75" t="s">
+        <v>461</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>462</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D33" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="E33" s="80"/>
-      <c r="F33" s="81" t="s">
-        <v>458</v>
-      </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>459</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D34" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="E34" s="80"/>
-      <c r="F34" s="81" t="s">
-        <v>461</v>
-      </c>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>462</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D35" s="80" t="s">
         <v>463</v>
       </c>
-      <c r="E35" s="80"/>
-      <c r="F35" s="81" t="s">
+      <c r="C33" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="42" t="s">
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="78" t="s">
         <v>465</v>
       </c>
-      <c r="C36" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D36" s="80" t="s">
-        <v>466</v>
-      </c>
-      <c r="E36" s="80"/>
-      <c r="F36" s="81" t="s">
-        <v>467</v>
-      </c>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="42" t="s">
-        <v>468</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="83" t="s">
-        <v>470</v>
-      </c>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8432,48 +8296,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="471">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1303,6 +1303,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1337,6 +1349,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1673,7 +1688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1779,6 +1794,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1792,6 +1819,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7656,7 +7686,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7905,352 +7935,458 @@
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="69">
+        <v>13265.541849065385</v>
+      </c>
+      <c r="D16" s="69">
+        <v>12303.215601105898</v>
+      </c>
+      <c r="E16" s="69">
+        <v>10485.178715237264</v>
+      </c>
+      <c r="F16" s="69">
+        <v>9923.421252780478</v>
+      </c>
+      <c r="G16" s="69">
+        <v>9959.939834549012</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="C16" s="64">
-        <v>0.7738994178525226</v>
-      </c>
-      <c r="D16" s="65">
-        <v>0.5938154618473896</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.48937915531335147</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.44849714599341384</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.4357613402061856</v>
-      </c>
-      <c r="H16" s="68" t="s">
+      <c r="C17" s="61">
+        <v>700</v>
+      </c>
+      <c r="D17" s="61">
+        <v>721</v>
+      </c>
+      <c r="E17" s="61">
+        <v>742.63</v>
+      </c>
+      <c r="F17" s="61">
+        <v>764.9089</v>
+      </c>
+      <c r="G17" s="61">
+        <v>787.8561670000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="70">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="67">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="67">
+        <v>997.2460000000002</v>
+      </c>
+      <c r="F18" s="67">
+        <v>821.7307040000001</v>
+      </c>
+      <c r="G18" s="67">
+        <v>793.48371105</v>
+      </c>
+      <c r="H18" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="C17" s="65">
-        <v>0.2188874514877102</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0.11325301204819277</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0.07683923705722072</v>
-      </c>
-      <c r="F17" s="66">
-        <v>0.0619099890230516</v>
-      </c>
-      <c r="G17" s="66">
-        <v>0.05814432989690721</v>
-      </c>
-      <c r="H17" s="68" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="C18" s="64">
-        <v>-0.1969265847347994</v>
-      </c>
-      <c r="D18" s="65">
-        <v>0.0599997991967871</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.20489877384196187</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.26237003293084515</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.2792902061855669</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="C19" s="69">
-        <v>3</v>
-      </c>
-      <c r="D19" s="69">
-        <v>3</v>
-      </c>
-      <c r="E19" s="69">
-        <v>3</v>
-      </c>
-      <c r="F19" s="69">
-        <v>3</v>
-      </c>
-      <c r="G19" s="69">
-        <v>3</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>430</v>
+      <c r="C19" s="71">
+        <v>-3487.764071287607</v>
+      </c>
+      <c r="D19" s="72">
+        <v>320.28439889410276</v>
+      </c>
+      <c r="E19" s="72">
+        <v>2359.831284762736</v>
+      </c>
+      <c r="F19" s="72">
+        <v>3282.9027072195213</v>
+      </c>
+      <c r="G19" s="72">
+        <v>3636.8544867009878</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C20" s="70">
-        <v>-5.092003884568414</v>
-      </c>
-      <c r="D20" s="71">
-        <v>3.0884637081798294</v>
-      </c>
-      <c r="E20" s="71">
-        <v>16.01164699867773</v>
-      </c>
-      <c r="F20" s="71">
-        <v>26.21020507099538</v>
-      </c>
-      <c r="G20" s="71">
-        <v>30.598664919346167</v>
+        <v>427</v>
+      </c>
+      <c r="C20" s="64">
+        <v>0.7738994178525226</v>
+      </c>
+      <c r="D20" s="65">
+        <v>0.5938154618473896</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.48937915531335147</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.44849714599341384</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.4357613402061856</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0.2188874514877102</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.11325301204819277</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.07683923705722072</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.0619099890230516</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.05814432989690721</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C22" s="64">
+        <v>-0.1969265847347994</v>
+      </c>
+      <c r="D22" s="65">
+        <v>0.0599997991967871</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.20489877384196187</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.26237003293084515</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.2792902061855669</v>
+      </c>
+      <c r="H22" s="68" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="72" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="73">
+        <v>3</v>
+      </c>
+      <c r="D23" s="73">
+        <v>3</v>
+      </c>
+      <c r="E23" s="73">
+        <v>3</v>
+      </c>
+      <c r="F23" s="73">
+        <v>3</v>
+      </c>
+      <c r="G23" s="73">
+        <v>3</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24" s="74">
+        <v>-5.092003884568414</v>
+      </c>
+      <c r="D24" s="75">
+        <v>3.0884637081798294</v>
+      </c>
+      <c r="E24" s="75">
+        <v>16.01164699867773</v>
+      </c>
+      <c r="F24" s="75">
+        <v>26.21020507099538</v>
+      </c>
+      <c r="G24" s="75">
+        <v>30.598664919346167</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C25" s="76" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="72" t="str">
+      <c r="D25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="41" t="str">
+      <c r="E25" s="41" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="72" t="str">
+      <c r="F25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="72" t="str">
+      <c r="G25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H25" s="68" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C22" s="73">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C26" s="77">
         <v>-1</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D26" s="77">
         <v>0</v>
       </c>
-      <c r="E22" s="73">
+      <c r="E26" s="77">
         <v>2</v>
       </c>
-      <c r="F22" s="73">
+      <c r="F26" s="77">
         <v>6</v>
       </c>
-      <c r="G22" s="73">
+      <c r="G26" s="77">
         <v>10</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="H26" s="68" t="s">
         <v>438</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C27" s="77">
+        <v>0</v>
+      </c>
+      <c r="D27" s="77">
+        <v>0</v>
+      </c>
+      <c r="E27" s="78">
+        <v>71</v>
+      </c>
+      <c r="F27" s="73">
+        <v>181</v>
+      </c>
+      <c r="G27" s="73">
+        <v>302</v>
+      </c>
+      <c r="H27" s="68" t="s">
         <v>439</v>
       </c>
-      <c r="C25" s="74" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="C29" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76" t="s">
+      <c r="D29" s="19" t="s">
         <v>442</v>
       </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="C26" s="77" t="s">
-        <v>444</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>445</v>
-      </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>447</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D27" s="75" t="s">
-        <v>449</v>
-      </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76" t="s">
-        <v>450</v>
-      </c>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>452</v>
-      </c>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76" t="s">
-        <v>453</v>
-      </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>454</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D29" s="75" t="s">
-        <v>455</v>
-      </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76" t="s">
-        <v>456</v>
-      </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>457</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>458</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>459</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+        <v>444</v>
+      </c>
+      <c r="C30" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="D30" s="80" t="s">
+        <v>446</v>
+      </c>
+      <c r="E30" s="80"/>
+      <c r="F30" s="81" t="s">
+        <v>447</v>
+      </c>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="C31" s="82" t="s">
+        <v>449</v>
+      </c>
+      <c r="D31" s="80" t="s">
+        <v>450</v>
+      </c>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81" t="s">
+        <v>451</v>
+      </c>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D32" s="80" t="s">
+        <v>454</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="F32" s="81" t="s">
+        <v>455</v>
+      </c>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D33" s="80" t="s">
+        <v>457</v>
+      </c>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81" t="s">
+        <v>458</v>
+      </c>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D34" s="80" t="s">
         <v>460</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="D31" s="75" t="s">
+      <c r="E34" s="80"/>
+      <c r="F34" s="81" t="s">
         <v>461</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
+      <c r="C35" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D35" s="80" t="s">
         <v>463</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="E35" s="80"/>
+      <c r="F35" s="81" t="s">
         <v>464</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="42" t="s">
         <v>465</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="C36" s="41" t="s">
+        <v>453</v>
+      </c>
+      <c r="D36" s="80" t="s">
+        <v>466</v>
+      </c>
+      <c r="E36" s="80"/>
+      <c r="F36" s="81" t="s">
+        <v>467</v>
+      </c>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="83" t="s">
+        <v>470</v>
+      </c>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8296,48 +8432,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -26,13 +26,15 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="509">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -40,7 +42,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +162,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -310,6 +312,12 @@
     <t>Financial Health</t>
   </si>
   <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>Budget Narrative</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -376,6 +384,9 @@
     <t>Escalation %</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>State Per-Pupil Funding</t>
   </si>
   <si>
@@ -385,6 +396,9 @@
     <t>Per Student</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
     <t>Federal Title I</t>
   </si>
   <si>
@@ -577,6 +591,48 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Enrollment Growth Rate</t>
+  </si>
+  <si>
+    <t>Rent Escalation Rate</t>
+  </si>
+  <si>
+    <t>Tuition Escalation Rate</t>
+  </si>
+  <si>
+    <t>Default Benefits Rate</t>
+  </si>
+  <si>
+    <t>Default Payroll Tax Rate</t>
+  </si>
+  <si>
+    <t>Student Retention Rate</t>
+  </si>
+  <si>
+    <t>REVENUE COLLECTION DEFAULTS</t>
+  </si>
+  <si>
+    <t>Default Billing Months</t>
+  </si>
+  <si>
+    <t>10 months (Aug-May)</t>
+  </si>
+  <si>
+    <t>Default Collection Method</t>
+  </si>
+  <si>
+    <t>Autopay</t>
+  </si>
+  <si>
+    <t>Default Collection Rate</t>
+  </si>
+  <si>
+    <t>Default Collection Delay</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
     <t>School Model</t>
   </si>
   <si>
@@ -634,9 +690,6 @@
     <t>Capacity Utilization</t>
   </si>
   <si>
-    <t>Enrollment Growth Rate</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -670,6 +723,9 @@
     <t>Loaded Cost</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>5-YEAR TOTAL PERSONNEL COST</t>
   </si>
   <si>
@@ -1018,12 +1074,24 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
+    <t>Cash Trough: June (Month 12)</t>
+  </si>
+  <si>
+    <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
+  </si>
+  <si>
     <t>Civic Scholars Charter - 5-Year Operating Statement</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
     <t>BOTTOM LINE</t>
   </si>
   <si>
@@ -1078,7 +1146,7 @@
     <t>Accounts Receivable</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
+    <t>Fixed Assets (Net of Depreciation)</t>
   </si>
   <si>
     <t>Other Assets</t>
@@ -1117,7 +1185,16 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>CFADS (Rev - Pers - OpEx)</t>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>Debt Service (Loan)</t>
+  </si>
+  <si>
+    <t>CFADS (NI + Depr + DS)</t>
   </si>
   <si>
     <t>DSCR</t>
@@ -1162,6 +1239,9 @@
     <t>Positive Net Income</t>
   </si>
   <si>
+    <t>Current Ratio ≥ 1.1x</t>
+  </si>
+  <si>
     <t>Capacity ≥ 7000%</t>
   </si>
   <si>
@@ -1264,7 +1344,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1297,9 +1377,6 @@
     <t>Benchmark</t>
   </si>
   <si>
-    <t>Net Income</t>
-  </si>
-  <si>
     <t>≥ $10,000</t>
   </si>
   <si>
@@ -1384,7 +1461,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -1445,6 +1522,45 @@
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Enrollment Strategy</t>
+  </si>
+  <si>
+    <t>(Not provided)</t>
+  </si>
+  <si>
+    <t>Retention Plan</t>
+  </si>
+  <si>
+    <t>Risk Mitigation</t>
+  </si>
+  <si>
+    <t>Mission &amp; Vision</t>
+  </si>
+  <si>
+    <t>Revenue Assumptions</t>
+  </si>
+  <si>
+    <t>Staffing Philosophy</t>
+  </si>
+  <si>
+    <t>Expense Assumptions</t>
+  </si>
+  <si>
+    <t>Growth Strategy</t>
+  </si>
+  <si>
+    <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1574,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1552,6 +1668,23 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF16A34A"/>
       <sz val="11"/>
@@ -1594,7 +1727,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1624,6 +1757,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1688,7 +1826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1736,25 +1874,28 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1762,10 +1903,10 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1775,16 +1916,16 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1793,14 +1934,14 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1809,7 +1950,7 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1818,26 +1959,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2556,7 +2706,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2569,24 +2719,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="36">
         <v>120</v>
@@ -2606,7 +2756,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2616,7 +2766,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="30">
         <v>1140000</v>
@@ -2636,7 +2786,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="30">
         <v>96000</v>
@@ -2656,7 +2806,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="30">
         <v>144000</v>
@@ -2676,7 +2826,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B10" s="30">
         <v>100000</v>
@@ -2696,7 +2846,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B11" s="30">
         <v>30000</v>
@@ -2716,7 +2866,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B12" s="30">
         <v>36000</v>
@@ -2736,7 +2886,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B13" s="32">
         <f>SUM(B7:B12)</f>
@@ -2761,7 +2911,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B15" s="30">
         <v>12883</v>
@@ -2805,7 +2955,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2818,24 +2968,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2845,7 +2995,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B5" s="30">
         <v>323299</v>
@@ -2865,7 +3015,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B6" s="30">
         <v>62173</v>
@@ -2885,7 +3035,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B7" s="30">
         <v>95738</v>
@@ -2905,7 +3055,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -2930,7 +3080,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -2940,7 +3090,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B10" s="30">
         <v>124346</v>
@@ -2960,7 +3110,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B11" s="30">
         <v>101738</v>
@@ -2980,7 +3130,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B12" s="30">
         <v>81390</v>
@@ -3000,7 +3150,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -3025,7 +3175,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -3035,7 +3185,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B15" s="30">
         <v>62173</v>
@@ -3055,7 +3205,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B15:B15)</f>
@@ -3080,7 +3230,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -3090,7 +3240,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B18" s="30">
         <v>62173</v>
@@ -3110,7 +3260,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B18:B18)</f>
@@ -3135,7 +3285,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -3145,7 +3295,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B21" s="30">
         <v>84012</v>
@@ -3165,7 +3315,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B22" s="31">
         <f>SUM(B21:B21)</f>
@@ -3190,7 +3340,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B24" s="32">
         <f>B8+B13+B16+B19+B22</f>
@@ -3239,7 +3389,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3252,24 +3402,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3279,7 +3429,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B5" s="30">
         <v>950000</v>
@@ -3299,7 +3449,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B6" s="30">
         <v>80000</v>
@@ -3319,7 +3469,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B7" s="30">
         <v>120000</v>
@@ -3339,7 +3489,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B8" s="30">
         <v>83333</v>
@@ -3359,7 +3509,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B9" s="30">
         <v>25000</v>
@@ -3379,7 +3529,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B10" s="30">
         <v>30000</v>
@@ -3399,7 +3549,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
@@ -3424,7 +3574,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -3434,7 +3584,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B14" s="30">
         <v>124346</v>
@@ -3454,7 +3604,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B15" s="30">
         <v>101738</v>
@@ -3474,7 +3624,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B16" s="30">
         <v>81390</v>
@@ -3494,7 +3644,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B17" s="30">
         <v>323299</v>
@@ -3514,7 +3664,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B18" s="30">
         <v>62173</v>
@@ -3534,7 +3684,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B19" s="30">
         <v>95738</v>
@@ -3554,7 +3704,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B20" s="30">
         <v>62173</v>
@@ -3574,7 +3724,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B21" s="30">
         <v>84012</v>
@@ -3594,7 +3744,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B22" s="30">
         <v>62173</v>
@@ -3614,7 +3764,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B23" s="31">
         <f>SUM(B14:B22)</f>
@@ -3639,7 +3789,7 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -3649,12 +3799,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B27" s="30">
         <v>70000</v>
@@ -3674,12 +3824,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B29" s="30">
         <v>50000</v>
@@ -3699,12 +3849,12 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="37" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B31" s="30">
         <v>180000</v>
@@ -3724,7 +3874,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B32" s="30">
         <v>25000</v>
@@ -3744,7 +3894,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B33" s="30">
         <v>15000</v>
@@ -3764,7 +3914,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B34" s="30">
         <v>15000</v>
@@ -3784,7 +3934,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B35" s="31">
         <f>SUM(B31:B34)</f>
@@ -3809,12 +3959,12 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B37" s="30">
         <v>20833</v>
@@ -3834,7 +3984,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B38" s="30">
         <v>12500</v>
@@ -3854,7 +4004,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B39" s="30">
         <v>16667</v>
@@ -3874,7 +4024,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B40" s="30">
         <v>80000</v>
@@ -3894,7 +4044,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B41" s="30">
         <v>60000</v>
@@ -3914,7 +4064,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B42" s="31">
         <f>SUM(B37:B41)</f>
@@ -3939,7 +4089,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B43" s="31">
         <f>B27+B29+B35+B42</f>
@@ -3964,7 +4114,7 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -3974,7 +4124,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B46" s="30">
         <v>49825</v>
@@ -3994,7 +4144,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B47" s="30">
         <v>75000</v>
@@ -4014,7 +4164,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B48" s="30">
         <v>40000</v>
@@ -4034,7 +4184,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B49" s="31">
         <f>SUM(B46:B48)</f>
@@ -4083,7 +4233,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4096,24 +4246,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B4" s="33">
         <f>'Budget Detail'!B11</f>
@@ -4138,7 +4288,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B23</f>
@@ -4163,7 +4313,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B43</f>
@@ -4188,7 +4338,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B7" s="33">
         <f>'Budget Detail'!B49</f>
@@ -4213,7 +4363,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -4238,7 +4388,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4248,7 +4398,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
@@ -4273,7 +4423,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -4298,7 +4448,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B13" s="30">
         <v>-418532</v>
@@ -4318,7 +4468,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B14" s="30">
         <v>10736</v>
@@ -4338,7 +4488,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B15" s="30">
         <v>14224</v>
@@ -4373,7 +4523,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4383,7 +4533,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4404,48 +4554,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -4463,7 +4613,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B4" s="31">
         <v>154600</v>
@@ -4508,7 +4658,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4526,7 +4676,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B7" s="30">
         <v>99704</v>
@@ -4571,7 +4721,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B8" s="30">
         <v>54500</v>
@@ -4616,7 +4766,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B9" s="30">
         <v>13735</v>
@@ -4661,7 +4811,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4679,7 +4829,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -4736,7 +4886,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -4793,7 +4943,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4850,14 +5000,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4865,7 +5015,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -4874,16 +5024,40 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B19" s="30">
+        <v>345</v>
+      </c>
+      <c r="B19" s="39">
         <f>MIN(B14:M14)</f>
         <v>-160860</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4898,7 +5072,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4907,7 +5081,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4915,29 +5089,39 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+    </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4946,8 +5130,8 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>266</v>
+      <c r="A5" s="42" t="s">
+        <v>284</v>
       </c>
       <c r="B5" s="31">
         <v>1288333</v>
@@ -4967,7 +5151,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4977,7 +5161,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B8" s="33">
         <v>997040</v>
@@ -4997,7 +5181,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B9" s="33">
         <v>545000</v>
@@ -5017,7 +5201,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="B10" s="33">
         <v>164825</v>
@@ -5036,138 +5220,159 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11" s="31">
-        <f>SUM(B8:B10)</f>
+      <c r="A11" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="33">
+        <v>0</v>
+      </c>
+      <c r="C11" s="33">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="31">
+        <f>SUM(B8:B11)</f>
         <v>1706865</v>
       </c>
-      <c r="C11" s="31">
-        <f>SUM(C8:C10)</f>
+      <c r="C12" s="31">
+        <f>SUM(C8:C11)</f>
         <v>2500643</v>
       </c>
-      <c r="D11" s="31">
-        <f>SUM(D8:D10)</f>
+      <c r="D12" s="31">
+        <f>SUM(D8:D11)</f>
         <v>3185554</v>
       </c>
-      <c r="E11" s="31">
-        <f>SUM(E8:E10)</f>
+      <c r="E12" s="31">
+        <f>SUM(E8:E11)</f>
         <v>3746283</v>
       </c>
-      <c r="F11" s="31">
-        <f>SUM(F8:F10)</f>
+      <c r="F12" s="31">
+        <f>SUM(F8:F11)</f>
         <v>4003976</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="B14" s="32">
-        <f>B5-B11</f>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="B15" s="32">
+        <f>B5-B12</f>
         <v>-418532</v>
       </c>
-      <c r="C14" s="32">
-        <f>C5-C11</f>
+      <c r="C15" s="32">
+        <f>C5-C12</f>
         <v>64057</v>
       </c>
-      <c r="D14" s="32">
-        <f>D5-D11</f>
+      <c r="D15" s="32">
+        <f>D5-D12</f>
         <v>707949</v>
       </c>
-      <c r="E14" s="32">
-        <f>E5-E11</f>
+      <c r="E15" s="32">
+        <f>E5-E12</f>
         <v>1231089</v>
       </c>
-      <c r="F14" s="32">
-        <f>F5-F11</f>
+      <c r="F15" s="32">
+        <f>F5-F12</f>
         <v>1454742</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B15" s="29">
-        <f>IF(B5=0,0,B14/B5)</f>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="29">
+        <f>IF(B5=0,0,B15/B5)</f>
         <v>-0.32486289</v>
       </c>
-      <c r="C15" s="29">
-        <f>IF(C5=0,0,C14/C5)</f>
+      <c r="C16" s="29">
+        <f>IF(C5=0,0,C15/C5)</f>
         <v>0.02497636</v>
       </c>
-      <c r="D15" s="29">
-        <f>IF(D5=0,0,D14/D5)</f>
+      <c r="D16" s="29">
+        <f>IF(D5=0,0,D15/D5)</f>
         <v>0.18182839</v>
       </c>
-      <c r="E15" s="29">
-        <f>IF(E5=0,0,E14/E5)</f>
+      <c r="E16" s="29">
+        <f>IF(E5=0,0,E15/E5)</f>
         <v>0.24733708</v>
       </c>
-      <c r="F15" s="29">
-        <f>IF(F5=0,0,F14/F5)</f>
+      <c r="F16" s="29">
+        <f>IF(F5=0,0,F15/F5)</f>
         <v>0.26649881</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="33">
-        <f>B14</f>
-        <v>-418532</v>
-      </c>
-      <c r="C16" s="33">
-        <f>B16+C14</f>
-        <v>-354475</v>
-      </c>
-      <c r="D16" s="33">
-        <f>C16+D14</f>
-        <v>353475</v>
-      </c>
-      <c r="E16" s="33">
-        <f>D16+E14</f>
-        <v>1584563</v>
-      </c>
-      <c r="F16" s="33">
-        <f>E16+F14</f>
-        <v>3039305</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B17" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="33">
+        <f>B15</f>
+        <v>-418532</v>
+      </c>
+      <c r="C17" s="33">
+        <f>B17+C15</f>
+        <v>-354475</v>
+      </c>
+      <c r="D17" s="33">
+        <f>C17+D15</f>
+        <v>353475</v>
+      </c>
+      <c r="E17" s="33">
+        <f>D17+E15</f>
+        <v>1584563</v>
+      </c>
+      <c r="F17" s="33">
+        <f>E17+F15</f>
+        <v>3039305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="E17" s="40" t="s">
+      <c r="D18" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5204,24 +5409,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5230,25 +5435,25 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>336</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>337</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>234</v>
+      <c r="A5" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>358</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B6" s="23">
         <v>500000</v>
@@ -5266,7 +5471,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5276,7 +5481,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="B9" s="30">
         <f>B6</f>
@@ -5301,7 +5506,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5326,7 +5531,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5351,7 +5556,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B12" s="33">
         <f>B10+B11</f>
@@ -5376,7 +5581,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5425,7 +5630,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5438,24 +5643,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5465,52 +5670,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5" s="45">
+        <v>368</v>
+      </c>
+      <c r="B5" s="48">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>-160860</v>
       </c>
-      <c r="C5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
+      <c r="C5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15</f>
         <v>-96803</v>
       </c>
-      <c r="D5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
+      <c r="D5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
         <v>611146</v>
       </c>
-      <c r="E5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
+      <c r="E5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
         <v>1842235</v>
       </c>
-      <c r="F5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
+      <c r="F5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
         <v>3296977</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B6" s="30">
-        <v>0</v>
+        <v>74123</v>
       </c>
       <c r="C6" s="30">
-        <v>0</v>
+        <v>147558</v>
       </c>
       <c r="D6" s="30">
-        <v>0</v>
+        <v>224010</v>
       </c>
       <c r="E6" s="30">
-        <v>0</v>
+        <v>286369</v>
       </c>
       <c r="F6" s="30">
-        <v>0</v>
+        <v>314063</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B7" s="30">
         <v>0</v>
@@ -5530,7 +5735,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -5550,32 +5755,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
-        <v>-160860</v>
+        <v>-86737</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>-96803</v>
+        <v>50755</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>611146</v>
+        <v>835156</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>1842235</v>
+        <v>2128604</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>3296977</v>
+        <v>3611040</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5585,7 +5790,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -5605,7 +5810,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
@@ -5630,7 +5835,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
@@ -5655,7 +5860,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5665,50 +5870,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
-        <v>-639221</v>
+        <v>-565098</v>
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>-552248</v>
+        <v>-404690</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>179971</v>
+        <v>403981</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>1436762</v>
+        <v>1723132</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>2918724</v>
+        <v>3232787</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="B19" s="46" t="str">
+        <v>379</v>
+      </c>
+      <c r="B19" s="49" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="50">
         <f>C9-C14-C17</f>
         <v>1</v>
       </c>
-      <c r="D19" s="46" t="str">
+      <c r="D19" s="49" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="46" t="str">
+      <c r="E19" s="50">
         <f>E9-E14-E17</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="46" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="49" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5730,7 +5935,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5739,7 +5944,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5752,24 +5957,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5779,7 +5984,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B5" s="30">
         <v>1288333</v>
@@ -5799,7 +6004,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B6" s="30">
         <v>997040</v>
@@ -5819,7 +6024,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B7" s="30">
         <v>545000</v>
@@ -5839,372 +6044,432 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B8" s="33">
-        <f>B5-B6-B7</f>
-        <v>-253707</v>
+        <v>-418532</v>
       </c>
       <c r="C8" s="33">
-        <f>C5-C6-C7</f>
-        <v>153881</v>
+        <v>64057</v>
       </c>
       <c r="D8" s="33">
-        <f>D5-D6-D7</f>
-        <v>797774</v>
+        <v>707949</v>
       </c>
       <c r="E8" s="33">
-        <f>E5-E6-E7</f>
-        <v>1305913</v>
+        <v>1231089</v>
       </c>
       <c r="F8" s="33">
-        <f>F5-F6-F7</f>
-        <v>1524566</v>
+        <v>1454742</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B10" s="30">
         <v>49825</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="30">
         <v>49825</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D10" s="30">
         <v>49825</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E10" s="30">
         <v>49825</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F10" s="30">
         <v>49825</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="48">
-        <f>IF(B9=0,"N/A",B8/B9)</f>
-        <v>-5.09</v>
-      </c>
-      <c r="C10" s="48">
-        <f>IF(C9=0,"N/A",C8/C9)</f>
-        <v>3.09</v>
-      </c>
-      <c r="D10" s="48">
-        <f>IF(D9=0,"N/A",D8/D9)</f>
-        <v>16.01</v>
-      </c>
-      <c r="E10" s="48">
-        <f>IF(E9=0,"N/A",E8/E9)</f>
-        <v>26.21</v>
-      </c>
-      <c r="F10" s="48">
-        <f>IF(F9=0,"N/A",F8/F9)</f>
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="B13" s="30">
-        <v>-160860</v>
-      </c>
-      <c r="C13" s="30">
-        <v>-96803</v>
-      </c>
-      <c r="D13" s="30">
-        <v>611146</v>
-      </c>
-      <c r="E13" s="30">
-        <v>1842235</v>
-      </c>
-      <c r="F13" s="30">
-        <v>3296977</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B14" s="35">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>-37</v>
-      </c>
-      <c r="C14" s="35">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>-14</v>
-      </c>
-      <c r="D14" s="35">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>71</v>
-      </c>
-      <c r="E14" s="35">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>181</v>
-      </c>
-      <c r="F14" s="35">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>302</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B11" s="33">
+        <f>B8+B9+B10</f>
+        <v>-368707</v>
+      </c>
+      <c r="C11" s="33">
+        <f>C8+C9+C10</f>
+        <v>113881</v>
+      </c>
+      <c r="D11" s="33">
+        <f>D8+D9+D10</f>
+        <v>757774</v>
+      </c>
+      <c r="E11" s="33">
+        <f>E8+E9+E10</f>
+        <v>1280913</v>
+      </c>
+      <c r="F11" s="33">
+        <f>F8+F9+F10</f>
+        <v>1504566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B12" s="51">
+        <f>IF(B10=0,"N/A",B11/B10)</f>
+        <v>-7.4</v>
+      </c>
+      <c r="C12" s="51">
+        <f>IF(C10=0,"N/A",C11/C10)</f>
+        <v>2.29</v>
+      </c>
+      <c r="D12" s="51">
+        <f>IF(D10=0,"N/A",D11/D10)</f>
+        <v>15.21</v>
+      </c>
+      <c r="E12" s="51">
+        <f>IF(E10=0,"N/A",E11/E10)</f>
+        <v>25.71</v>
+      </c>
+      <c r="F12" s="51">
+        <f>IF(F10=0,"N/A",F11/F10)</f>
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="B15" s="34">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>-1.2</v>
-      </c>
-      <c r="C15" s="34">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>-0.5</v>
-      </c>
-      <c r="D15" s="34">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>2.3</v>
-      </c>
-      <c r="E15" s="34">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>5.9</v>
-      </c>
-      <c r="F15" s="34">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>9.9</v>
+        <v>389</v>
+      </c>
+      <c r="B15" s="30">
+        <v>-160860</v>
+      </c>
+      <c r="C15" s="30">
+        <v>-96803</v>
+      </c>
+      <c r="D15" s="30">
+        <v>611146</v>
+      </c>
+      <c r="E15" s="30">
+        <v>1842235</v>
+      </c>
+      <c r="F15" s="30">
+        <v>3296977</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" s="29">
+        <v>390</v>
+      </c>
+      <c r="B16" s="35">
+        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
+        <v>-34</v>
+      </c>
+      <c r="C16" s="35">
+        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
+        <v>-14</v>
+      </c>
+      <c r="D16" s="35">
+        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
+        <v>70</v>
+      </c>
+      <c r="E16" s="35">
+        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
+        <v>179</v>
+      </c>
+      <c r="F16" s="35">
+        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="B17" s="34">
+        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
+        <v>-1.1</v>
+      </c>
+      <c r="C17" s="34">
+        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D17" s="34">
+        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
+        <v>2.3</v>
+      </c>
+      <c r="E17" s="34">
+        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
+        <v>5.9</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="29">
         <v>0.3</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C18" s="29">
         <v>0.5</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D18" s="29">
         <v>0.75</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E18" s="29">
         <v>0.9375</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F18" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" s="30">
-        <v>10736</v>
-      </c>
-      <c r="C19" s="30">
-        <v>12824</v>
-      </c>
-      <c r="D19" s="30">
-        <v>12978</v>
-      </c>
-      <c r="E19" s="30">
-        <v>13273</v>
-      </c>
-      <c r="F19" s="30">
-        <v>13647</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="B20" s="30">
-        <v>1046865</v>
-      </c>
-      <c r="C20" s="30">
-        <v>1572783</v>
-      </c>
-      <c r="D20" s="30">
-        <v>1955224</v>
-      </c>
-      <c r="E20" s="30">
-        <v>2282162</v>
-      </c>
-      <c r="F20" s="30">
-        <v>2428523</v>
-      </c>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>369</v>
+        <v>259</v>
       </c>
       <c r="B21" s="30">
+        <v>10736</v>
+      </c>
+      <c r="C21" s="30">
+        <v>12824</v>
+      </c>
+      <c r="D21" s="30">
+        <v>12978</v>
+      </c>
+      <c r="E21" s="30">
+        <v>13273</v>
+      </c>
+      <c r="F21" s="30">
+        <v>13647</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B22" s="30">
+        <v>1046865</v>
+      </c>
+      <c r="C22" s="30">
+        <v>1572783</v>
+      </c>
+      <c r="D22" s="30">
+        <v>1955224</v>
+      </c>
+      <c r="E22" s="30">
+        <v>2282162</v>
+      </c>
+      <c r="F22" s="30">
+        <v>2428523</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B23" s="30">
         <v>4542</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C23" s="30">
         <v>4439</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D23" s="30">
         <v>3968</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E23" s="30">
         <v>3838</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F23" s="30">
         <v>3889</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="B22" s="49">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="52">
         <v>170</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C24" s="52">
         <v>188</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D24" s="52">
         <v>217</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E24" s="52">
         <v>242</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F24" s="52">
         <v>249</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>374</v>
-      </c>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>373</v>
+        <v>397</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>374</v>
+        <v>400</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>374</v>
+        <v>401</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -6244,28 +6509,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>379</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>112</v>
+      <c r="A3" s="55" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>406</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B4" s="30">
         <v>500000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="E4" s="30">
         <v>400000</v>
@@ -6273,13 +6538,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B5" s="30">
         <v>100000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="E5" s="30">
         <v>75000</v>
@@ -6287,13 +6552,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="B6" s="30">
         <v>50000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="E6" s="30">
         <v>40000</v>
@@ -6301,7 +6566,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="E7" s="30">
         <v>60000</v>
@@ -6309,7 +6574,7 @@
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="E8" s="30">
         <v>75000</v>
@@ -6317,13 +6582,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B10" s="32">
         <v>650000</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="E10" s="32">
         <v>650000</v>
@@ -6331,9 +6596,9 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="B11" s="46">
+        <v>415</v>
+      </c>
+      <c r="B11" s="49">
         <v>0</v>
       </c>
     </row>
@@ -6354,7 +6619,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C43"/>
+  <dimension ref="B3:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6620,18 +6885,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C41" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -6656,6 +6929,7 @@
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
+    <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6679,7 +6953,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6689,7 +6963,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6699,7 +6973,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6707,24 +6981,24 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B6" s="30">
         <v>1288333</v>
@@ -6744,7 +7018,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B7" s="30">
         <v>1591865</v>
@@ -6764,7 +7038,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B8" s="32">
         <v>-303532</v>
@@ -6784,7 +7058,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B9" s="29">
         <v>-0.2356002757214845</v>
@@ -6804,27 +7078,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="53">
+        <v>387</v>
+      </c>
+      <c r="B10" s="56">
         <v>-5.09</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="56">
         <v>3.09</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="56">
         <v>16.01</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="56">
         <v>26.21</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="56">
         <v>30.6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B11" s="35">
         <v>170</v>
@@ -6844,7 +7118,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6854,7 +7128,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,24 +7136,24 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B16" s="30">
         <v>966250</v>
@@ -6899,7 +7173,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B17" s="30">
         <v>1591865</v>
@@ -6919,7 +7193,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B18" s="32">
         <v>-625615</v>
@@ -6939,7 +7213,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B19" s="29">
         <v>-0.6474670342953127</v>
@@ -6959,27 +7233,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="B20" s="53">
+        <v>387</v>
+      </c>
+      <c r="B20" s="56">
         <v>-11.56</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="56">
         <v>-9.78</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="56">
         <v>-3.52</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="56">
         <v>1.24</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="56">
         <v>3.21</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B21" s="35">
         <v>224</v>
@@ -6999,7 +7273,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -7009,7 +7283,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,24 +7291,24 @@
         <v>7</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B26" s="30">
         <v>1223917</v>
@@ -7054,7 +7328,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B27" s="30">
         <v>1591865</v>
@@ -7074,7 +7348,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B28" s="32">
         <v>-367948</v>
@@ -7094,7 +7368,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B29" s="29">
         <v>-0.3006318691805101</v>
@@ -7114,27 +7388,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="B30" s="53">
+        <v>387</v>
+      </c>
+      <c r="B30" s="56">
         <v>-6.38</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="56">
         <v>0.51</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="56">
         <v>12.1</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="56">
         <v>21.22</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="56">
         <v>25.12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B31" s="35">
         <v>186</v>
@@ -7154,7 +7428,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -7164,7 +7438,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,24 +7446,24 @@
         <v>7</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B36" s="30">
         <v>1288333</v>
@@ -7209,7 +7483,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B37" s="30">
         <v>1638365</v>
@@ -7229,7 +7503,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B38" s="32">
         <v>-350032</v>
@@ -7249,7 +7523,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B39" s="29">
         <v>-0.27169341931786223</v>
@@ -7269,27 +7543,27 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="B40" s="53">
+        <v>387</v>
+      </c>
+      <c r="B40" s="56">
         <v>-6.03</v>
       </c>
-      <c r="C40" s="53">
+      <c r="C40" s="56">
         <v>1.29</v>
       </c>
-      <c r="D40" s="53">
+      <c r="D40" s="56">
         <v>13.33</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="56">
         <v>22.81</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="56">
         <v>26.87</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B41" s="35">
         <v>181</v>
@@ -7335,7 +7609,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7347,7 +7621,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -7361,7 +7635,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -7369,7 +7643,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -7393,7 +7667,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -7401,7 +7675,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7421,25 +7695,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="54" t="s">
+      <c r="D12" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="E12" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="F12" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="D13" s="30">
         <v>1288333</v>
@@ -7459,7 +7733,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D14" s="30">
         <v>1591865</v>
@@ -7479,7 +7753,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="D15" s="30">
         <v>-418532</v>
@@ -7499,7 +7773,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="D16" s="30">
         <v>-160860</v>
@@ -7519,7 +7793,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="D17" s="30">
         <v>478361</v>
@@ -7539,7 +7813,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7559,25 +7833,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="54" t="s">
+      <c r="D20" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="E20" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="F20" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D21" s="29">
         <v>-0.3248628889168275</v>
@@ -7597,27 +7871,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="D22" s="53">
-        <v>-5.09</v>
-      </c>
-      <c r="E22" s="53">
-        <v>3.09</v>
-      </c>
-      <c r="F22" s="53">
-        <v>16.01</v>
-      </c>
-      <c r="G22" s="53">
-        <v>26.21</v>
-      </c>
-      <c r="H22" s="53">
-        <v>30.6</v>
+        <v>387</v>
+      </c>
+      <c r="D22" s="56">
+        <v>-7.4</v>
+      </c>
+      <c r="E22" s="56">
+        <v>2.29</v>
+      </c>
+      <c r="F22" s="56">
+        <v>15.21</v>
+      </c>
+      <c r="G22" s="56">
+        <v>25.71</v>
+      </c>
+      <c r="H22" s="56">
+        <v>30.2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D23" s="29">
         <v>0.3</v>
@@ -7637,7 +7911,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="D24" s="35">
         <v>120</v>
@@ -7657,7 +7931,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7698,7 +7972,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7708,662 +7982,662 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="B3" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
-        <v>411</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>412</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>413</v>
+      <c r="B4" s="59" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>415</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>416</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>417</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>418</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>419</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>420</v>
+        <v>440</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>441</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>442</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>444</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>445</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="C7" s="60">
+        <v>433</v>
+      </c>
+      <c r="C7" s="63">
         <v>120</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="63">
         <v>200</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="63">
         <v>300</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="63">
         <v>375</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="63">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="C8" s="61">
+        <v>382</v>
+      </c>
+      <c r="C8" s="64">
         <v>1288333.3333333335</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="64">
         <v>2564700</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="64">
         <v>3893503</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="64">
         <v>4977371.484999999</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="64">
         <v>5458717.7285</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C9" s="61">
+        <v>337</v>
+      </c>
+      <c r="C9" s="64">
         <v>997040.4166666667</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="64">
         <v>1522958.5150000001</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="64">
         <v>1905399.20935</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="64">
         <v>2232336.9055715</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="64">
         <v>2378698.1531784255</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="C10" s="61">
+        <v>338</v>
+      </c>
+      <c r="C10" s="64">
         <v>545000</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="64">
         <v>887860</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="64">
         <v>1190329.8</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="64">
         <v>1439121.459</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="64">
         <v>1555453.1754200002</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C11" s="61">
+        <v>339</v>
+      </c>
+      <c r="C11" s="64">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="64">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="64">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="64">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="64">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C12" s="62">
+        <v>383</v>
+      </c>
+      <c r="C12" s="65">
         <v>-418531.6885545128</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="66">
         <v>64056.879778820556</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="66">
         <v>707949.3854288207</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="66">
         <v>1231088.5152073205</v>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="66">
         <v>1454741.7946803952</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="62">
+        <v>389</v>
+      </c>
+      <c r="C13" s="65">
         <v>-160860</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="65">
         <v>-96803.12022117944</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="66">
         <v>611146.2652076413</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="66">
         <v>1842234.7804149617</v>
       </c>
-      <c r="G13" s="63">
+      <c r="G13" s="66">
         <v>3296976.575095357</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="C14" s="64">
+        <v>432</v>
+      </c>
+      <c r="C14" s="67">
         <v>-0.3248628889168275</v>
       </c>
-      <c r="D14" s="65">
+      <c r="D14" s="68">
         <v>0.02497636362101632</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="69">
         <v>0.18182839089345013</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="69">
         <v>0.24733707719373102</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="69">
         <v>0.26649881291446503</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="67">
+        <v>259</v>
+      </c>
+      <c r="C15" s="70">
         <v>10736.111111111113</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="70">
         <v>12823.5</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="70">
         <v>12978.343333333334</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="70">
         <v>13272.990626666666</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="70">
         <v>13646.794321250001</v>
       </c>
-      <c r="H15" s="68" t="s">
-        <v>422</v>
+      <c r="H15" s="71" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="69">
+        <v>321</v>
+      </c>
+      <c r="C16" s="72">
         <v>13265.541849065385</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="72">
         <v>12303.215601105898</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="72">
         <v>10485.178715237264</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="72">
         <v>9923.421252780478</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="72">
         <v>9959.939834549012</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="C17" s="61">
+        <v>448</v>
+      </c>
+      <c r="C17" s="64">
         <v>700</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="64">
         <v>721</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="64">
         <v>742.63</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="64">
         <v>764.9089</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="64">
         <v>787.8561670000001</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="C18" s="70">
+        <v>449</v>
+      </c>
+      <c r="C18" s="73">
         <v>2350</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="70">
         <v>1452.3</v>
       </c>
-      <c r="E18" s="67">
+      <c r="E18" s="70">
         <v>997.2460000000002</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="70">
         <v>821.7307040000001</v>
       </c>
-      <c r="G18" s="67">
+      <c r="G18" s="70">
         <v>793.48371105</v>
       </c>
-      <c r="H18" s="68" t="s">
-        <v>425</v>
+      <c r="H18" s="71" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C19" s="71">
+        <v>451</v>
+      </c>
+      <c r="C19" s="74">
         <v>-3487.764071287607</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="75">
         <v>320.28439889410276</v>
       </c>
-      <c r="E19" s="72">
+      <c r="E19" s="75">
         <v>2359.831284762736</v>
       </c>
-      <c r="F19" s="72">
+      <c r="F19" s="75">
         <v>3282.9027072195213</v>
       </c>
-      <c r="G19" s="72">
+      <c r="G19" s="75">
         <v>3636.8544867009878</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="64">
+        <v>452</v>
+      </c>
+      <c r="C20" s="67">
         <v>0.7738994178525226</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="68">
         <v>0.5938154618473896</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="69">
         <v>0.48937915531335147</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="69">
         <v>0.44849714599341384</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="69">
         <v>0.4357613402061856</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>428</v>
+      <c r="H20" s="71" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="C21" s="65">
+        <v>454</v>
+      </c>
+      <c r="C21" s="68">
         <v>0.2188874514877102</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="69">
         <v>0.11325301204819277</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="69">
         <v>0.07683923705722072</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="69">
         <v>0.0619099890230516</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="69">
         <v>0.05814432989690721</v>
       </c>
-      <c r="H21" s="68" t="s">
-        <v>430</v>
+      <c r="H21" s="71" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="C22" s="64">
+        <v>456</v>
+      </c>
+      <c r="C22" s="67">
         <v>-0.1969265847347994</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="68">
         <v>0.0599997991967871</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="69">
         <v>0.20489877384196187</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="69">
         <v>0.26237003293084515</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="69">
         <v>0.2792902061855669</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>432</v>
+      <c r="H22" s="71" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C23" s="73">
+        <v>458</v>
+      </c>
+      <c r="C23" s="76">
         <v>3</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D23" s="76">
         <v>3</v>
       </c>
-      <c r="E23" s="73">
+      <c r="E23" s="76">
         <v>3</v>
       </c>
-      <c r="F23" s="73">
+      <c r="F23" s="76">
         <v>3</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="76">
         <v>3</v>
       </c>
-      <c r="H23" s="68" t="s">
-        <v>434</v>
+      <c r="H23" s="71" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C24" s="74">
+        <v>387</v>
+      </c>
+      <c r="C24" s="77">
         <v>-5.092003884568414</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="78">
         <v>3.0884637081798294</v>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="78">
         <v>16.01164699867773</v>
       </c>
-      <c r="F24" s="75">
+      <c r="F24" s="78">
         <v>26.21020507099538</v>
       </c>
-      <c r="G24" s="75">
+      <c r="G24" s="78">
         <v>30.598664919346167</v>
       </c>
-      <c r="H24" s="68" t="s">
-        <v>435</v>
+      <c r="H24" s="71" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="C25" s="76" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>461</v>
+      </c>
+      <c r="C25" s="79" t="str">
+        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+      <c r="D25" s="79" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="41" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+      <c r="E25" s="44" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+      <c r="F25" s="79" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+      <c r="G25" s="79" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="68" t="s">
-        <v>415</v>
+      <c r="H25" s="71" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="C26" s="77">
+        <v>462</v>
+      </c>
+      <c r="C26" s="80">
         <v>-1</v>
       </c>
-      <c r="D26" s="77">
+      <c r="D26" s="80">
         <v>0</v>
       </c>
-      <c r="E26" s="77">
+      <c r="E26" s="80">
         <v>2</v>
       </c>
-      <c r="F26" s="77">
+      <c r="F26" s="80">
         <v>6</v>
       </c>
-      <c r="G26" s="77">
+      <c r="G26" s="80">
         <v>10</v>
       </c>
-      <c r="H26" s="68" t="s">
-        <v>438</v>
+      <c r="H26" s="71" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="C27" s="77">
+        <v>390</v>
+      </c>
+      <c r="C27" s="80">
         <v>0</v>
       </c>
-      <c r="D27" s="77">
+      <c r="D27" s="80">
         <v>0</v>
       </c>
-      <c r="E27" s="78">
+      <c r="E27" s="81">
         <v>71</v>
       </c>
-      <c r="F27" s="73">
+      <c r="F27" s="76">
         <v>181</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="76">
         <v>302</v>
       </c>
-      <c r="H27" s="68" t="s">
-        <v>439</v>
+      <c r="H27" s="71" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="C30" s="79" t="s">
-        <v>445</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>446</v>
-      </c>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81" t="s">
-        <v>447</v>
-      </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
+      <c r="B30" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="C30" s="82" t="s">
+        <v>470</v>
+      </c>
+      <c r="D30" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="E30" s="83"/>
+      <c r="F30" s="84" t="s">
+        <v>472</v>
+      </c>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="C31" s="82" t="s">
-        <v>449</v>
-      </c>
-      <c r="D31" s="80" t="s">
-        <v>450</v>
-      </c>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81" t="s">
-        <v>451</v>
-      </c>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
+      <c r="B31" s="45" t="s">
+        <v>473</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>474</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>475</v>
+      </c>
+      <c r="E31" s="83"/>
+      <c r="F31" s="84" t="s">
+        <v>476</v>
+      </c>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D32" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81" t="s">
-        <v>455</v>
-      </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
+      <c r="B32" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="D32" s="83" t="s">
+        <v>479</v>
+      </c>
+      <c r="E32" s="83"/>
+      <c r="F32" s="84" t="s">
+        <v>480</v>
+      </c>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D33" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="E33" s="80"/>
-      <c r="F33" s="81" t="s">
-        <v>458</v>
-      </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
+      <c r="B33" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="D33" s="83" t="s">
+        <v>482</v>
+      </c>
+      <c r="E33" s="83"/>
+      <c r="F33" s="84" t="s">
+        <v>483</v>
+      </c>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>459</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D34" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="E34" s="80"/>
-      <c r="F34" s="81" t="s">
-        <v>461</v>
-      </c>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
+      <c r="B34" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="D34" s="83" t="s">
+        <v>485</v>
+      </c>
+      <c r="E34" s="83"/>
+      <c r="F34" s="84" t="s">
+        <v>486</v>
+      </c>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>462</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D35" s="80" t="s">
-        <v>463</v>
-      </c>
-      <c r="E35" s="80"/>
-      <c r="F35" s="81" t="s">
-        <v>464</v>
-      </c>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
+      <c r="B35" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="D35" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="E35" s="83"/>
+      <c r="F35" s="84" t="s">
+        <v>489</v>
+      </c>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="42" t="s">
-        <v>465</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D36" s="80" t="s">
-        <v>466</v>
-      </c>
-      <c r="E36" s="80"/>
-      <c r="F36" s="81" t="s">
-        <v>467</v>
-      </c>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
+      <c r="B36" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="D36" s="83" t="s">
+        <v>491</v>
+      </c>
+      <c r="E36" s="83"/>
+      <c r="F36" s="84" t="s">
+        <v>492</v>
+      </c>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="42" t="s">
-        <v>468</v>
+      <c r="B38" s="45" t="s">
+        <v>493</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="83" t="s">
-        <v>470</v>
-      </c>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
+      <c r="B40" s="86" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -8470,12 +8744,225 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" s="87"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B7" s="87"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B10" s="87"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B13" s="87"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B16" s="87"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B19" s="87"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B22" s="87"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B25" s="87"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B28" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="88" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="89" t="s">
+        <v>508</v>
+      </c>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -8489,7 +8976,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -8499,7 +8986,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8513,18 +9000,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8567,10 +9054,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -8591,7 +9078,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -8599,7 +9086,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="20">
         <v>400</v>
@@ -8607,7 +9094,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8621,24 +9108,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="22">
         <v>120</v>
@@ -8658,7 +9145,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -8667,32 +9154,35 @@
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="23">
         <v>9500</v>
@@ -8700,16 +9190,19 @@
       <c r="E21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>800</v>
@@ -8717,16 +9210,19 @@
       <c r="E22" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>115</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" s="23">
         <v>1200</v>
@@ -8734,16 +9230,19 @@
       <c r="E23" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D24" s="23">
         <v>100000</v>
@@ -8751,16 +9250,19 @@
       <c r="E24" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D25" s="23">
         <v>30000</v>
@@ -8768,16 +9270,19 @@
       <c r="E25" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D26" s="23">
         <v>300</v>
@@ -8785,10 +9290,13 @@
       <c r="E26" s="24">
         <v>0</v>
       </c>
+      <c r="F26" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -8799,36 +9307,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D30" s="25">
         <v>1</v>
@@ -8845,13 +9353,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D31" s="25">
         <v>1</v>
@@ -8868,13 +9376,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D32" s="25">
         <v>1</v>
@@ -8891,13 +9399,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="D33" s="25">
         <v>6</v>
@@ -8914,13 +9422,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="D34" s="25">
         <v>1</v>
@@ -8937,13 +9445,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B35" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="D35" s="25">
         <v>3</v>
@@ -8960,13 +9468,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D36" s="25">
         <v>1</v>
@@ -8983,13 +9491,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D37" s="25">
         <v>2</v>
@@ -9006,13 +9514,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D38" s="25">
         <v>1</v>
@@ -9029,7 +9537,7 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
@@ -9040,30 +9548,30 @@
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D42" s="23">
         <v>18000</v>
@@ -9074,13 +9582,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D43" s="23">
         <v>2500</v>
@@ -9091,13 +9599,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D44" s="23">
         <v>18000</v>
@@ -9108,13 +9616,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>149</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D45" s="23">
         <v>1500</v>
@@ -9125,13 +9633,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D46" s="23">
         <v>700</v>
@@ -9142,13 +9650,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D47" s="23">
         <v>500</v>
@@ -9159,13 +9667,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D48" s="23">
         <v>25000</v>
@@ -9176,13 +9684,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D49" s="23">
         <v>15000</v>
@@ -9193,13 +9701,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D50" s="23">
         <v>20000</v>
@@ -9210,13 +9718,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D51" s="23">
         <v>800</v>
@@ -9227,13 +9735,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>159</v>
-      </c>
       <c r="C52" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D52" s="23">
         <v>600</v>
@@ -9244,7 +9752,7 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -9255,27 +9763,27 @@
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C56" s="23">
         <v>500000</v>
@@ -9289,10 +9797,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C57" s="23">
         <v>75000</v>
@@ -9306,10 +9814,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C58" s="23">
         <v>40000</v>
@@ -9323,7 +9831,7 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -9334,29 +9842,29 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B61" s="24">
         <v>0.03</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B62" s="24">
         <v>0.03</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B63" s="25">
         <v>0.8333333333333334</v>
@@ -9364,7 +9872,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B64" s="23">
         <v>0</v>
@@ -9372,10 +9880,101 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>180</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -9410,10 +10009,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -9434,10 +10033,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -9450,7 +10049,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -9458,66 +10057,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -9560,24 +10159,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -9587,7 +10186,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="27">
         <v>120</v>
@@ -9607,7 +10206,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="22">
         <v>400</v>
@@ -9615,7 +10214,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B8" s="28">
         <f>B6/$B$7</f>
@@ -9640,10 +10239,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C10" s="29">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
@@ -9688,7 +10287,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9701,24 +10300,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9728,7 +10327,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="30">
         <v>1140000</v>
@@ -9748,7 +10347,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="30">
         <v>96000</v>
@@ -9768,7 +10367,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B7" s="30">
         <v>144000</v>
@@ -9788,7 +10387,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5,B6,B7)</f>
@@ -9813,7 +10412,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -9823,7 +10422,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B10" s="23">
         <v>100000</v>
@@ -9843,7 +10442,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B11" s="23">
         <v>30000</v>
@@ -9863,7 +10462,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B10,B11)</f>
@@ -9888,7 +10487,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -9898,7 +10497,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B14" s="30">
         <v>36000</v>
@@ -9918,7 +10517,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B14)</f>
@@ -9943,7 +10542,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B17" s="32">
         <f>SUM(B8,B12,B15)</f>
@@ -9983,7 +10582,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -9992,9 +10591,10 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
@@ -10004,36 +10604,40 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C4" s="25">
         <v>1</v>
@@ -10050,13 +10654,16 @@
       <c r="G4" s="33">
         <v>149215</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C5" s="25">
         <v>1</v>
@@ -10073,13 +10680,16 @@
       <c r="G5" s="33">
         <v>122085</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C6" s="25">
         <v>1</v>
@@ -10096,13 +10706,16 @@
       <c r="G6" s="33">
         <v>97668</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" s="25">
         <v>6</v>
@@ -10119,13 +10732,16 @@
       <c r="G7" s="33">
         <v>387959</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C8" s="25">
         <v>1</v>
@@ -10142,13 +10758,16 @@
       <c r="G8" s="33">
         <v>74608</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C9" s="25">
         <v>3</v>
@@ -10165,13 +10784,16 @@
       <c r="G9" s="33">
         <v>114885</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C10" s="25">
         <v>1</v>
@@ -10188,13 +10810,16 @@
       <c r="G10" s="33">
         <v>74608</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="25">
         <v>2</v>
@@ -10211,13 +10836,16 @@
       <c r="G11" s="33">
         <v>100814</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C12" s="25">
         <v>1</v>
@@ -10234,10 +10862,13 @@
       <c r="G12" s="33">
         <v>74608</v>
       </c>
+      <c r="H12" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -10251,24 +10882,24 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B16" s="32">
         <v>997040</v>
@@ -10288,7 +10919,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B17" s="29">
         <v>0.644916181543769</v>
@@ -10308,7 +10939,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B18" s="34">
         <v>7.1</v>
@@ -10328,7 +10959,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -10352,7 +10983,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10365,24 +10996,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -10392,7 +11023,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B5" s="30">
         <v>84000</v>
@@ -10412,7 +11043,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -10437,7 +11068,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -10447,7 +11078,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B8" s="30">
         <v>60000</v>
@@ -10467,7 +11098,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -10492,7 +11123,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -10502,7 +11133,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B11" s="30">
         <v>216000</v>
@@ -10522,7 +11153,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B12" s="30">
         <v>30000</v>
@@ -10542,7 +11173,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B13" s="30">
         <v>18000</v>
@@ -10562,7 +11193,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B14" s="30">
         <v>18000</v>
@@ -10582,7 +11213,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
@@ -10607,7 +11238,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -10617,7 +11248,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B17" s="30">
         <v>25000</v>
@@ -10637,7 +11268,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B18" s="30">
         <v>15000</v>
@@ -10657,7 +11288,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B19" s="30">
         <v>20000</v>
@@ -10677,7 +11308,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B20" s="30">
         <v>96000</v>
@@ -10697,7 +11328,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B21" s="30">
         <v>72000</v>
@@ -10717,7 +11348,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B22" s="31">
         <f>SUM(B17:B21)</f>
@@ -10742,7 +11373,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B24" s="32">
         <f>B6+B9+B15+B22</f>
@@ -10792,7 +11423,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10802,30 +11433,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C4" s="23">
         <v>500000</v>
@@ -10842,10 +11473,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C5" s="23">
         <v>75000</v>
@@ -10862,10 +11493,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C6" s="23">
         <v>40000</v>
@@ -10882,7 +11513,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F8" s="32">
         <v>49825</v>
@@ -10890,7 +11521,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F9" s="31">
         <v>500000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="512">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1344,7 +1345,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1552,6 +1553,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1574,7 +1584,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1726,6 +1736,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1826,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1983,6 +1998,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -8908,6 +8927,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="88" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
+        <v>508</v>
+      </c>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8926,7 +8993,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -8936,26 +9003,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
-        <v>507</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
+      <c r="B2" s="90" t="s">
+        <v>510</v>
+      </c>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="89" t="s">
-        <v>508</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
+      <c r="B4" s="91" t="s">
+        <v>511</v>
+      </c>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_Public_Funding.xlsx
@@ -43,7 +43,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1345,7 +1345,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1474,7 +1474,7 @@
     <t>● Healthy</t>
   </si>
   <si>
-    <t>Staffing at 44% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 46% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1492,7 +1492,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 30.60x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 25.09x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1510,7 +1510,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>9.9 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>8.0 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1841,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1904,7 +1904,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3576,19 +3575,19 @@
       </c>
       <c r="C11" s="31">
         <f>SUM(C5:C10)</f>
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D11" s="31">
         <f>SUM(D5:D10)</f>
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E11" s="31">
         <f>SUM(E5:E10)</f>
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F11" s="31">
         <f>SUM(F5:F10)</f>
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,19 +4289,19 @@
       </c>
       <c r="C4" s="33">
         <f>'Budget Detail'!C11</f>
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D4" s="33">
         <f>'Budget Detail'!D11</f>
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E4" s="33">
         <f>'Budget Detail'!E11</f>
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F4" s="33">
         <f>'Budget Detail'!F11</f>
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4425,19 +4424,19 @@
       </c>
       <c r="C11" s="32">
         <f>C4-C8</f>
-        <v>64057</v>
+        <v>22157</v>
       </c>
       <c r="D11" s="32">
         <f>D4-D8</f>
-        <v>707949</v>
+        <v>599046</v>
       </c>
       <c r="E11" s="32">
         <f>E4-E8</f>
-        <v>1231089</v>
+        <v>1012842</v>
       </c>
       <c r="F11" s="32">
         <f>F4-F8</f>
-        <v>1454742</v>
+        <v>1180424</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4450,19 +4449,19 @@
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.02497636</v>
+        <v>0.00878265</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.18182839</v>
+        <v>0.15828526</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.24733708</v>
+        <v>0.21282106</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.26649881</v>
+        <v>0.22768769</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,16 +4472,16 @@
         <v>-418532</v>
       </c>
       <c r="C13" s="30">
-        <v>-354475</v>
+        <v>-396375</v>
       </c>
       <c r="D13" s="30">
-        <v>353475</v>
+        <v>202672</v>
       </c>
       <c r="E13" s="30">
-        <v>1584563</v>
+        <v>1215514</v>
       </c>
       <c r="F13" s="30">
-        <v>3039305</v>
+        <v>2395938</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,16 +4492,16 @@
         <v>10736</v>
       </c>
       <c r="C14" s="30">
-        <v>12824</v>
+        <v>12614</v>
       </c>
       <c r="D14" s="30">
-        <v>12978</v>
+        <v>12615</v>
       </c>
       <c r="E14" s="30">
-        <v>13273</v>
+        <v>12691</v>
       </c>
       <c r="F14" s="30">
-        <v>13647</v>
+        <v>12961</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5156,16 +5155,16 @@
         <v>1288333</v>
       </c>
       <c r="C5" s="31">
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D5" s="31">
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E5" s="31">
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F5" s="31">
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5303,19 +5302,19 @@
       </c>
       <c r="C15" s="32">
         <f>C5-C12</f>
-        <v>64057</v>
+        <v>22157</v>
       </c>
       <c r="D15" s="32">
         <f>D5-D12</f>
-        <v>707949</v>
+        <v>599046</v>
       </c>
       <c r="E15" s="32">
         <f>E5-E12</f>
-        <v>1231089</v>
+        <v>1012842</v>
       </c>
       <c r="F15" s="32">
         <f>F5-F12</f>
-        <v>1454742</v>
+        <v>1180424</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5328,19 +5327,19 @@
       </c>
       <c r="C16" s="29">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.02497636</v>
+        <v>0.00878265</v>
       </c>
       <c r="D16" s="29">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.18182839</v>
+        <v>0.15828526</v>
       </c>
       <c r="E16" s="29">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.24733708</v>
+        <v>0.21282106</v>
       </c>
       <c r="F16" s="29">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.26649881</v>
+        <v>0.22768769</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,19 +5352,19 @@
       </c>
       <c r="C17" s="33">
         <f>B17+C15</f>
-        <v>-354475</v>
+        <v>-396375</v>
       </c>
       <c r="D17" s="33">
         <f>C17+D15</f>
-        <v>353475</v>
+        <v>202672</v>
       </c>
       <c r="E17" s="33">
         <f>D17+E15</f>
-        <v>1584563</v>
+        <v>1215514</v>
       </c>
       <c r="F17" s="33">
         <f>E17+F15</f>
-        <v>3039305</v>
+        <v>2395938</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5697,19 +5696,19 @@
       </c>
       <c r="C5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>-96803</v>
+        <v>-138703</v>
       </c>
       <c r="D5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>611146</v>
+        <v>460343</v>
       </c>
       <c r="E5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>1842235</v>
+        <v>1473185</v>
       </c>
       <c r="F5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>3296977</v>
+        <v>2653609</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5720,16 +5719,16 @@
         <v>74123</v>
       </c>
       <c r="C6" s="30">
-        <v>147558</v>
+        <v>145147</v>
       </c>
       <c r="D6" s="30">
-        <v>224010</v>
+        <v>217744</v>
       </c>
       <c r="E6" s="30">
-        <v>286369</v>
+        <v>273813</v>
       </c>
       <c r="F6" s="30">
-        <v>314063</v>
+        <v>298281</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5782,19 +5781,19 @@
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>50755</v>
+        <v>6444</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>835156</v>
+        <v>678087</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>2128604</v>
+        <v>1746998</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>3611040</v>
+        <v>2951890</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5897,19 +5896,19 @@
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>-404690</v>
+        <v>-449000</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>403981</v>
+        <v>246912</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>1723132</v>
+        <v>1341525</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>3232787</v>
+        <v>2573637</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5920,17 +5919,17 @@
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="49" t="str">
         <f>C9-C14-C17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="49" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="49" t="str">
         <f>E9-E14-E17</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="49" t="str">
         <f>F9-F14-F17</f>
@@ -6009,16 +6008,16 @@
         <v>1288333</v>
       </c>
       <c r="C5" s="30">
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D5" s="30">
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E5" s="30">
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F5" s="30">
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6069,16 +6068,16 @@
         <v>-418532</v>
       </c>
       <c r="C8" s="33">
-        <v>64057</v>
+        <v>22157</v>
       </c>
       <c r="D8" s="33">
-        <v>707949</v>
+        <v>599046</v>
       </c>
       <c r="E8" s="33">
-        <v>1231089</v>
+        <v>1012842</v>
       </c>
       <c r="F8" s="33">
-        <v>1454742</v>
+        <v>1180424</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6131,44 +6130,44 @@
       </c>
       <c r="C11" s="33">
         <f>C8+C9+C10</f>
-        <v>113881</v>
+        <v>71981</v>
       </c>
       <c r="D11" s="33">
         <f>D8+D9+D10</f>
-        <v>757774</v>
+        <v>648871</v>
       </c>
       <c r="E11" s="33">
         <f>E8+E9+E10</f>
-        <v>1280913</v>
+        <v>1062667</v>
       </c>
       <c r="F11" s="33">
         <f>F8+F9+F10</f>
-        <v>1504566</v>
+        <v>1230249</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>IF(B10=0,"N/A",B11/B10)</f>
         <v>-7.4</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>IF(C10=0,"N/A",C11/C10)</f>
-        <v>2.29</v>
-      </c>
-      <c r="D12" s="51">
+        <v>1.44</v>
+      </c>
+      <c r="D12" s="50">
         <f>IF(D10=0,"N/A",D11/D10)</f>
-        <v>15.21</v>
-      </c>
-      <c r="E12" s="51">
+        <v>13.02</v>
+      </c>
+      <c r="E12" s="50">
         <f>IF(E10=0,"N/A",E11/E10)</f>
-        <v>25.71</v>
-      </c>
-      <c r="F12" s="51">
+        <v>21.33</v>
+      </c>
+      <c r="F12" s="50">
         <f>IF(F10=0,"N/A",F11/F10)</f>
-        <v>30.2</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6189,16 +6188,16 @@
         <v>-160860</v>
       </c>
       <c r="C15" s="30">
-        <v>-96803</v>
+        <v>-138703</v>
       </c>
       <c r="D15" s="30">
-        <v>611146</v>
+        <v>460343</v>
       </c>
       <c r="E15" s="30">
-        <v>1842235</v>
+        <v>1473185</v>
       </c>
       <c r="F15" s="30">
-        <v>3296977</v>
+        <v>2653609</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6211,19 +6210,19 @@
       </c>
       <c r="C16" s="35">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>-14</v>
+        <v>-20</v>
       </c>
       <c r="D16" s="35">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E16" s="35">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="F16" s="35">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>301</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,19 +6235,19 @@
       </c>
       <c r="C17" s="34">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="D17" s="34">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="E17" s="34">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="F17" s="34">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>9.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6289,16 +6288,16 @@
         <v>10736</v>
       </c>
       <c r="C21" s="30">
-        <v>12824</v>
+        <v>12614</v>
       </c>
       <c r="D21" s="30">
-        <v>12978</v>
+        <v>12615</v>
       </c>
       <c r="E21" s="30">
-        <v>13273</v>
+        <v>12691</v>
       </c>
       <c r="F21" s="30">
-        <v>13647</v>
+        <v>12961</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6345,20 +6344,20 @@
       <c r="A24" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="51">
         <v>170</v>
       </c>
-      <c r="C24" s="52">
-        <v>188</v>
-      </c>
-      <c r="D24" s="52">
-        <v>217</v>
-      </c>
-      <c r="E24" s="52">
-        <v>242</v>
-      </c>
-      <c r="F24" s="52">
-        <v>249</v>
+      <c r="C24" s="51">
+        <v>193</v>
+      </c>
+      <c r="D24" s="51">
+        <v>227</v>
+      </c>
+      <c r="E24" s="51">
+        <v>258</v>
+      </c>
+      <c r="F24" s="51">
+        <v>268</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,19 +6374,19 @@
       <c r="A27" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E27" s="54" t="s">
+      <c r="E27" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="F27" s="54" t="s">
+      <c r="F27" s="53" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6395,19 +6394,19 @@
       <c r="A28" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C28" s="54" t="s">
+      <c r="C28" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="D28" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E28" s="54" t="s">
+      <c r="E28" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="F28" s="54" t="s">
+      <c r="F28" s="53" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6415,19 +6414,19 @@
       <c r="A29" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="D29" s="54" t="s">
+      <c r="D29" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="E29" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="F29" s="54" t="s">
+      <c r="F29" s="53" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6435,19 +6434,19 @@
       <c r="A30" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="52" t="s">
         <v>398</v>
       </c>
     </row>
@@ -6455,19 +6454,19 @@
       <c r="A31" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="52" t="s">
+        <v>398</v>
+      </c>
+      <c r="E31" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E31" s="54" t="s">
-        <v>399</v>
-      </c>
-      <c r="F31" s="54" t="s">
+      <c r="F31" s="53" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6475,19 +6474,19 @@
       <c r="A32" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="E32" s="54" t="s">
+      <c r="E32" s="53" t="s">
         <v>399</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="53" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6528,16 +6527,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>405</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="54" t="s">
         <v>406</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="54" t="s">
         <v>114</v>
       </c>
     </row>
@@ -7023,16 +7022,16 @@
         <v>1288333</v>
       </c>
       <c r="C6" s="30">
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D6" s="30">
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E6" s="30">
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F6" s="30">
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,16 +7062,16 @@
         <v>-303532</v>
       </c>
       <c r="C8" s="32">
-        <v>104057</v>
+        <v>62157</v>
       </c>
       <c r="D8" s="32">
-        <v>747949</v>
+        <v>639046</v>
       </c>
       <c r="E8" s="32">
-        <v>1256089</v>
+        <v>1037842</v>
       </c>
       <c r="F8" s="32">
-        <v>1474742</v>
+        <v>1200424</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -7080,39 +7079,39 @@
         <v>319</v>
       </c>
       <c r="B9" s="29">
-        <v>-0.2356002757214845</v>
+        <v>-0.23560027572148473</v>
       </c>
       <c r="C9" s="29">
-        <v>0.04057272966772744</v>
+        <v>0.024638052869359477</v>
       </c>
       <c r="D9" s="29">
-        <v>0.19210191578864091</v>
+        <v>0.16885440612715233</v>
       </c>
       <c r="E9" s="29">
-        <v>0.2523598085842533</v>
+        <v>0.21807412711524074</v>
       </c>
       <c r="F9" s="29">
-        <v>0.2701626770295813</v>
+        <v>0.23154541821240557</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="55">
         <v>-5.09</v>
       </c>
-      <c r="C10" s="56">
-        <v>3.09</v>
-      </c>
-      <c r="D10" s="56">
-        <v>16.01</v>
-      </c>
-      <c r="E10" s="56">
-        <v>26.21</v>
-      </c>
-      <c r="F10" s="56">
-        <v>30.6</v>
+      <c r="C10" s="55">
+        <v>2.25</v>
+      </c>
+      <c r="D10" s="55">
+        <v>13.83</v>
+      </c>
+      <c r="E10" s="55">
+        <v>21.83</v>
+      </c>
+      <c r="F10" s="55">
+        <v>25.09</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7123,16 +7122,16 @@
         <v>170</v>
       </c>
       <c r="C11" s="35">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D11" s="35">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E11" s="35">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="F11" s="35">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7178,16 +7177,16 @@
         <v>966250</v>
       </c>
       <c r="C16" s="30">
-        <v>1923525</v>
+        <v>1892100</v>
       </c>
       <c r="D16" s="30">
-        <v>2920127</v>
+        <v>2838450</v>
       </c>
       <c r="E16" s="30">
-        <v>3733029</v>
+        <v>3569344</v>
       </c>
       <c r="F16" s="30">
-        <v>4094038</v>
+        <v>3888300</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -7218,16 +7217,16 @@
         <v>-625615</v>
       </c>
       <c r="C18" s="32">
-        <v>-537118</v>
+        <v>-568543</v>
       </c>
       <c r="D18" s="32">
-        <v>-225426</v>
+        <v>-307104</v>
       </c>
       <c r="E18" s="32">
-        <v>11746</v>
+        <v>-151939</v>
       </c>
       <c r="F18" s="32">
-        <v>110062</v>
+        <v>-95676</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,39 +7234,39 @@
         <v>319</v>
       </c>
       <c r="B19" s="29">
-        <v>-0.6474670342953127</v>
+        <v>-0.6474670342953128</v>
       </c>
       <c r="C19" s="29">
-        <v>-0.2792363604430301</v>
+        <v>-0.3004825961741874</v>
       </c>
       <c r="D19" s="29">
-        <v>-0.07719744561514545</v>
+        <v>-0.10819412516379688</v>
       </c>
       <c r="E19" s="29">
-        <v>0.0031464114456710686</v>
+        <v>-0.042567830513012335</v>
       </c>
       <c r="F19" s="29">
-        <v>0.026883569372774998</v>
+        <v>-0.024606109050125908</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B20" s="56">
+      <c r="B20" s="55">
         <v>-11.56</v>
       </c>
-      <c r="C20" s="56">
-        <v>-9.78</v>
-      </c>
-      <c r="D20" s="56">
-        <v>-3.52</v>
-      </c>
-      <c r="E20" s="56">
-        <v>1.24</v>
-      </c>
-      <c r="F20" s="56">
-        <v>3.21</v>
+      <c r="C20" s="55">
+        <v>-10.41</v>
+      </c>
+      <c r="D20" s="55">
+        <v>-5.16</v>
+      </c>
+      <c r="E20" s="55">
+        <v>-2.05</v>
+      </c>
+      <c r="F20" s="55">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -7278,16 +7277,16 @@
         <v>224</v>
       </c>
       <c r="C21" s="35">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D21" s="35">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E21" s="35">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="F21" s="35">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7333,16 +7332,16 @@
         <v>1223917</v>
       </c>
       <c r="C26" s="30">
-        <v>2436465</v>
+        <v>2396660</v>
       </c>
       <c r="D26" s="30">
-        <v>3698828</v>
+        <v>3595370</v>
       </c>
       <c r="E26" s="30">
-        <v>4728503</v>
+        <v>4521169</v>
       </c>
       <c r="F26" s="30">
-        <v>5185782</v>
+        <v>4925180</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -7373,16 +7372,16 @@
         <v>-367948</v>
       </c>
       <c r="C28" s="32">
-        <v>-24178</v>
+        <v>-63983</v>
       </c>
       <c r="D28" s="32">
-        <v>553274</v>
+        <v>449816</v>
       </c>
       <c r="E28" s="32">
-        <v>1007220</v>
+        <v>799886</v>
       </c>
       <c r="F28" s="32">
-        <v>1201806</v>
+        <v>941204</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -7390,39 +7389,39 @@
         <v>319</v>
       </c>
       <c r="B29" s="29">
-        <v>-0.3006318691805101</v>
+        <v>-0.3006318691805103</v>
       </c>
       <c r="C29" s="29">
-        <v>-0.00992344245502375</v>
+        <v>-0.026696786453305813</v>
       </c>
       <c r="D29" s="29">
-        <v>0.14958096398804296</v>
+        <v>0.12510990118647614</v>
       </c>
       <c r="E29" s="29">
-        <v>0.2130103248255297</v>
+        <v>0.17692013380551658</v>
       </c>
       <c r="F29" s="29">
-        <v>0.2317501863469276</v>
+        <v>0.1911004402235848</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="56">
+      <c r="B30" s="55">
         <v>-6.38</v>
       </c>
-      <c r="C30" s="56">
-        <v>0.51</v>
-      </c>
-      <c r="D30" s="56">
-        <v>12.1</v>
-      </c>
-      <c r="E30" s="56">
-        <v>21.22</v>
-      </c>
-      <c r="F30" s="56">
-        <v>25.12</v>
+      <c r="C30" s="55">
+        <v>-0.28</v>
+      </c>
+      <c r="D30" s="55">
+        <v>10.03</v>
+      </c>
+      <c r="E30" s="55">
+        <v>17.05</v>
+      </c>
+      <c r="F30" s="55">
+        <v>19.89</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -7433,16 +7432,16 @@
         <v>186</v>
       </c>
       <c r="C31" s="35">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D31" s="35">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E31" s="35">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="F31" s="35">
-        <v>268</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7488,16 +7487,16 @@
         <v>1288333</v>
       </c>
       <c r="C36" s="30">
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="D36" s="30">
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="E36" s="30">
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="F36" s="30">
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -7528,16 +7527,16 @@
         <v>-350032</v>
       </c>
       <c r="C38" s="32">
-        <v>14447</v>
+        <v>-27453</v>
       </c>
       <c r="D38" s="32">
-        <v>614276</v>
+        <v>505373</v>
       </c>
       <c r="E38" s="32">
-        <v>1086443</v>
+        <v>868196</v>
       </c>
       <c r="F38" s="32">
-        <v>1289033</v>
+        <v>1014715</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -7545,39 +7544,39 @@
         <v>319</v>
       </c>
       <c r="B39" s="29">
-        <v>-0.27169341931786223</v>
+        <v>-0.27169341931786245</v>
       </c>
       <c r="C39" s="29">
-        <v>0.005632970631582858</v>
+        <v>-0.01088200421007607</v>
       </c>
       <c r="D39" s="29">
-        <v>0.15776949072052104</v>
+        <v>0.1335340552314169</v>
       </c>
       <c r="E39" s="29">
-        <v>0.2182763837763499</v>
+        <v>0.1824276864880247</v>
       </c>
       <c r="F39" s="29">
-        <v>0.23614205847288033</v>
+        <v>0.19572469572764367</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B40" s="56">
+      <c r="B40" s="55">
         <v>-6.03</v>
       </c>
-      <c r="C40" s="56">
-        <v>1.29</v>
-      </c>
-      <c r="D40" s="56">
-        <v>13.33</v>
-      </c>
-      <c r="E40" s="56">
-        <v>22.81</v>
-      </c>
-      <c r="F40" s="56">
-        <v>26.87</v>
+      <c r="C40" s="55">
+        <v>0.45</v>
+      </c>
+      <c r="D40" s="55">
+        <v>11.14</v>
+      </c>
+      <c r="E40" s="55">
+        <v>18.43</v>
+      </c>
+      <c r="F40" s="55">
+        <v>21.37</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -7588,16 +7587,16 @@
         <v>181</v>
       </c>
       <c r="C41" s="35">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D41" s="35">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E41" s="35">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="F41" s="35">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -7714,19 +7713,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="F12" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="57" t="s">
+      <c r="G12" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="56" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7738,16 +7737,16 @@
         <v>1288333</v>
       </c>
       <c r="E13" s="30">
-        <v>2564700</v>
+        <v>2522800</v>
       </c>
       <c r="F13" s="30">
-        <v>3893503</v>
+        <v>3784600</v>
       </c>
       <c r="G13" s="30">
-        <v>4977371</v>
+        <v>4759125</v>
       </c>
       <c r="H13" s="30">
-        <v>5458718</v>
+        <v>5184400</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -7778,16 +7777,16 @@
         <v>-418532</v>
       </c>
       <c r="E15" s="30">
-        <v>64057</v>
+        <v>22157</v>
       </c>
       <c r="F15" s="30">
-        <v>707949</v>
+        <v>599046</v>
       </c>
       <c r="G15" s="30">
-        <v>1231089</v>
+        <v>1012842</v>
       </c>
       <c r="H15" s="30">
-        <v>1454742</v>
+        <v>1180424</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -7798,16 +7797,16 @@
         <v>-160860</v>
       </c>
       <c r="E16" s="30">
-        <v>-96803</v>
+        <v>-138703</v>
       </c>
       <c r="F16" s="30">
-        <v>611146</v>
+        <v>460343</v>
       </c>
       <c r="G16" s="30">
-        <v>1842235</v>
+        <v>1473185</v>
       </c>
       <c r="H16" s="30">
-        <v>3296977</v>
+        <v>2653609</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7852,19 +7851,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="57" t="s">
+      <c r="F20" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="57" t="s">
+      <c r="G20" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="56" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7873,39 +7872,39 @@
         <v>432</v>
       </c>
       <c r="D21" s="29">
-        <v>-0.3248628889168275</v>
+        <v>-0.32486288891682774</v>
       </c>
       <c r="E21" s="29">
-        <v>0.02497636362101632</v>
+        <v>0.008782654106080581</v>
       </c>
       <c r="F21" s="29">
-        <v>0.18182839089345013</v>
+        <v>0.1582852574720765</v>
       </c>
       <c r="G21" s="29">
-        <v>0.24733707719373102</v>
+        <v>0.21282106063768447</v>
       </c>
       <c r="H21" s="29">
-        <v>0.26649881291446503</v>
+        <v>0.22768769118517002</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="55">
         <v>-7.4</v>
       </c>
-      <c r="E22" s="56">
-        <v>2.29</v>
-      </c>
-      <c r="F22" s="56">
-        <v>15.21</v>
-      </c>
-      <c r="G22" s="56">
-        <v>25.71</v>
-      </c>
-      <c r="H22" s="56">
-        <v>30.2</v>
+      <c r="E22" s="55">
+        <v>1.44</v>
+      </c>
+      <c r="F22" s="55">
+        <v>13.02</v>
+      </c>
+      <c r="G22" s="55">
+        <v>21.33</v>
+      </c>
+      <c r="H22" s="55">
+        <v>24.69</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7979,7 +7978,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7989,7 +7988,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>435</v>
       </c>
@@ -7999,26 +7998,28 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="59" t="s">
         <v>438</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="60" t="s">
         <v>439</v>
       </c>
     </row>
@@ -8026,22 +8027,22 @@
       <c r="B6" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>441</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="61" t="s">
         <v>443</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="61" t="s">
         <v>444</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="61" t="s">
         <v>445</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="61" t="s">
         <v>446</v>
       </c>
     </row>
@@ -8049,19 +8050,19 @@
       <c r="B7" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="62">
         <v>120</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="62">
         <v>200</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="62">
         <v>300</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="62">
         <v>375</v>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="62">
         <v>400</v>
       </c>
     </row>
@@ -8069,59 +8070,59 @@
       <c r="B8" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C8" s="64">
-        <v>1288333.3333333335</v>
-      </c>
-      <c r="D8" s="64">
-        <v>2564700</v>
-      </c>
-      <c r="E8" s="64">
-        <v>3893503</v>
-      </c>
-      <c r="F8" s="64">
-        <v>4977371.484999999</v>
-      </c>
-      <c r="G8" s="64">
-        <v>5458717.7285</v>
+      <c r="C8" s="63">
+        <v>1288333.3333333333</v>
+      </c>
+      <c r="D8" s="63">
+        <v>2522800</v>
+      </c>
+      <c r="E8" s="63">
+        <v>3784600</v>
+      </c>
+      <c r="F8" s="63">
+        <v>4759125</v>
+      </c>
+      <c r="G8" s="63">
+        <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="63">
         <v>997040.4166666667</v>
       </c>
-      <c r="D9" s="64">
-        <v>1522958.5150000001</v>
-      </c>
-      <c r="E9" s="64">
-        <v>1905399.20935</v>
-      </c>
-      <c r="F9" s="64">
-        <v>2232336.9055715</v>
-      </c>
-      <c r="G9" s="64">
-        <v>2378698.1531784255</v>
+      <c r="D9" s="63">
+        <v>1522958.5150000004</v>
+      </c>
+      <c r="E9" s="63">
+        <v>1905399.2093500001</v>
+      </c>
+      <c r="F9" s="63">
+        <v>2232336.9055715003</v>
+      </c>
+      <c r="G9" s="63">
+        <v>2378698.153178425</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="63">
         <v>545000</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="63">
         <v>887860</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="63">
         <v>1190329.8</v>
       </c>
-      <c r="F10" s="64">
+      <c r="F10" s="63">
         <v>1439121.459</v>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="63">
         <v>1555453.1754200002</v>
       </c>
     </row>
@@ -8129,19 +8130,19 @@
       <c r="B11" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="63">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="63">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="63">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="63">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="63">
         <v>49824.605221179416</v>
       </c>
     </row>
@@ -8149,82 +8150,82 @@
       <c r="B12" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="C12" s="65">
-        <v>-418531.6885545128</v>
-      </c>
-      <c r="D12" s="66">
-        <v>64056.879778820556</v>
-      </c>
-      <c r="E12" s="66">
-        <v>707949.3854288207</v>
-      </c>
-      <c r="F12" s="66">
-        <v>1231088.5152073205</v>
-      </c>
-      <c r="G12" s="66">
-        <v>1454741.7946803952</v>
+      <c r="C12" s="64">
+        <v>-418531.68855451304</v>
+      </c>
+      <c r="D12" s="65">
+        <v>22156.87977882009</v>
+      </c>
+      <c r="E12" s="65">
+        <v>599046.3854288207</v>
+      </c>
+      <c r="F12" s="65">
+        <v>1012842.0302073201</v>
+      </c>
+      <c r="G12" s="65">
+        <v>1180424.0661803954</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="64">
         <v>-160860</v>
       </c>
-      <c r="D13" s="65">
-        <v>-96803.12022117944</v>
-      </c>
-      <c r="E13" s="66">
-        <v>611146.2652076413</v>
-      </c>
-      <c r="F13" s="66">
-        <v>1842234.7804149617</v>
-      </c>
-      <c r="G13" s="66">
-        <v>3296976.575095357</v>
+      <c r="D13" s="64">
+        <v>-138703.1202211799</v>
+      </c>
+      <c r="E13" s="65">
+        <v>460343.2652076408</v>
+      </c>
+      <c r="F13" s="65">
+        <v>1473185.295414961</v>
+      </c>
+      <c r="G13" s="65">
+        <v>2653609.3615953564</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="C14" s="67">
-        <v>-0.3248628889168275</v>
-      </c>
-      <c r="D14" s="68">
-        <v>0.02497636362101632</v>
-      </c>
-      <c r="E14" s="69">
-        <v>0.18182839089345013</v>
-      </c>
-      <c r="F14" s="69">
-        <v>0.24733707719373102</v>
-      </c>
-      <c r="G14" s="69">
-        <v>0.26649881291446503</v>
+      <c r="C14" s="66">
+        <v>-0.32486288891682774</v>
+      </c>
+      <c r="D14" s="67">
+        <v>0.008782654106080581</v>
+      </c>
+      <c r="E14" s="68">
+        <v>0.1582852574720765</v>
+      </c>
+      <c r="F14" s="68">
+        <v>0.21282106063768447</v>
+      </c>
+      <c r="G14" s="68">
+        <v>0.22768769118517002</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C15" s="70">
-        <v>10736.111111111113</v>
-      </c>
-      <c r="D15" s="70">
-        <v>12823.5</v>
-      </c>
-      <c r="E15" s="70">
-        <v>12978.343333333334</v>
-      </c>
-      <c r="F15" s="70">
-        <v>13272.990626666666</v>
-      </c>
-      <c r="G15" s="70">
-        <v>13646.794321250001</v>
-      </c>
-      <c r="H15" s="71" t="s">
+      <c r="C15" s="69">
+        <v>10736.111111111111</v>
+      </c>
+      <c r="D15" s="69">
+        <v>12614</v>
+      </c>
+      <c r="E15" s="69">
+        <v>12615.333333333334</v>
+      </c>
+      <c r="F15" s="69">
+        <v>12691</v>
+      </c>
+      <c r="G15" s="69">
+        <v>12961</v>
+      </c>
+      <c r="H15" s="70" t="s">
         <v>447</v>
       </c>
     </row>
@@ -8232,19 +8233,19 @@
       <c r="B16" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="71">
         <v>13265.541849065385</v>
       </c>
-      <c r="D16" s="72">
-        <v>12303.215601105898</v>
-      </c>
-      <c r="E16" s="72">
+      <c r="D16" s="71">
+        <v>12303.2156011059</v>
+      </c>
+      <c r="E16" s="71">
         <v>10485.178715237264</v>
       </c>
-      <c r="F16" s="72">
-        <v>9923.421252780478</v>
-      </c>
-      <c r="G16" s="72">
+      <c r="F16" s="71">
+        <v>9923.42125278048</v>
+      </c>
+      <c r="G16" s="71">
         <v>9959.939834549012</v>
       </c>
     </row>
@@ -8252,19 +8253,19 @@
       <c r="B17" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="63">
         <v>700</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="63">
         <v>721</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="63">
         <v>742.63</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="63">
         <v>764.9089</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="63">
         <v>787.8561670000001</v>
       </c>
     </row>
@@ -8272,22 +8273,22 @@
       <c r="B18" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="C18" s="73">
+      <c r="C18" s="72">
         <v>2350</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="69">
         <v>1452.3</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="69">
         <v>997.2460000000002</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="69">
         <v>821.7307040000001</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="69">
         <v>793.48371105</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="70" t="s">
         <v>450</v>
       </c>
     </row>
@@ -8295,42 +8296,42 @@
       <c r="B19" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C19" s="74">
-        <v>-3487.764071287607</v>
-      </c>
-      <c r="D19" s="75">
-        <v>320.28439889410276</v>
-      </c>
-      <c r="E19" s="75">
-        <v>2359.831284762736</v>
-      </c>
-      <c r="F19" s="75">
-        <v>3282.9027072195213</v>
-      </c>
-      <c r="G19" s="75">
-        <v>3636.8544867009878</v>
+      <c r="C19" s="73">
+        <v>-3487.7640712876087</v>
+      </c>
+      <c r="D19" s="74">
+        <v>110.78439889410045</v>
+      </c>
+      <c r="E19" s="74">
+        <v>1996.8212847627358</v>
+      </c>
+      <c r="F19" s="74">
+        <v>2700.9120805528537</v>
+      </c>
+      <c r="G19" s="74">
+        <v>2951.0601654509887</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="C20" s="67">
-        <v>0.7738994178525226</v>
-      </c>
-      <c r="D20" s="68">
-        <v>0.5938154618473896</v>
-      </c>
-      <c r="E20" s="69">
-        <v>0.48937915531335147</v>
-      </c>
-      <c r="F20" s="69">
-        <v>0.44849714599341384</v>
-      </c>
-      <c r="G20" s="69">
-        <v>0.4357613402061856</v>
-      </c>
-      <c r="H20" s="71" t="s">
+      <c r="C20" s="66">
+        <v>0.7738994178525227</v>
+      </c>
+      <c r="D20" s="67">
+        <v>0.6036778638814018</v>
+      </c>
+      <c r="E20" s="68">
+        <v>0.5034611872721028</v>
+      </c>
+      <c r="F20" s="68">
+        <v>0.4690645666107741</v>
+      </c>
+      <c r="G20" s="68">
+        <v>0.45881840775758526</v>
+      </c>
+      <c r="H20" s="70" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8338,22 +8339,22 @@
       <c r="B21" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="C21" s="68">
-        <v>0.2188874514877102</v>
-      </c>
-      <c r="D21" s="69">
-        <v>0.11325301204819277</v>
-      </c>
-      <c r="E21" s="69">
-        <v>0.07683923705722072</v>
-      </c>
-      <c r="F21" s="69">
-        <v>0.0619099890230516</v>
-      </c>
-      <c r="G21" s="69">
-        <v>0.05814432989690721</v>
-      </c>
-      <c r="H21" s="71" t="s">
+      <c r="C21" s="67">
+        <v>0.21888745148771024</v>
+      </c>
+      <c r="D21" s="68">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="68">
+        <v>0.07905030914759817</v>
+      </c>
+      <c r="F21" s="68">
+        <v>0.06474909022141676</v>
+      </c>
+      <c r="G21" s="68">
+        <v>0.061220871155775014</v>
+      </c>
+      <c r="H21" s="70" t="s">
         <v>455</v>
       </c>
     </row>
@@ -8361,22 +8362,22 @@
       <c r="B22" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="C22" s="67">
-        <v>-0.1969265847347994</v>
-      </c>
-      <c r="D22" s="68">
-        <v>0.0599997991967871</v>
-      </c>
-      <c r="E22" s="69">
-        <v>0.20489877384196187</v>
-      </c>
-      <c r="F22" s="69">
-        <v>0.26237003293084515</v>
-      </c>
-      <c r="G22" s="69">
-        <v>0.2792902061855669</v>
-      </c>
-      <c r="H22" s="71" t="s">
+      <c r="C22" s="66">
+        <v>-0.19692658473479963</v>
+      </c>
+      <c r="D22" s="67">
+        <v>0.044387777469478217</v>
+      </c>
+      <c r="E22" s="68">
+        <v>0.18201949760873007</v>
+      </c>
+      <c r="F22" s="68">
+        <v>0.22854340565303488</v>
+      </c>
+      <c r="G22" s="68">
+        <v>0.24115590452155983</v>
+      </c>
+      <c r="H22" s="70" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8384,22 +8385,22 @@
       <c r="B23" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <v>3</v>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="75">
         <v>3</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="75">
         <v>3</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="75">
         <v>3</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="75">
         <v>3</v>
       </c>
-      <c r="H23" s="71" t="s">
+      <c r="H23" s="70" t="s">
         <v>459</v>
       </c>
     </row>
@@ -8407,22 +8408,22 @@
       <c r="B24" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="C24" s="77">
-        <v>-5.092003884568414</v>
-      </c>
-      <c r="D24" s="78">
-        <v>3.0884637081798294</v>
-      </c>
-      <c r="E24" s="78">
-        <v>16.01164699867773</v>
-      </c>
-      <c r="F24" s="78">
-        <v>26.21020507099538</v>
-      </c>
-      <c r="G24" s="78">
-        <v>30.598664919346167</v>
-      </c>
-      <c r="H24" s="71" t="s">
+      <c r="C24" s="76">
+        <v>-5.092003884568419</v>
+      </c>
+      <c r="D24" s="77">
+        <v>2.2475137435188066</v>
+      </c>
+      <c r="E24" s="77">
+        <v>13.825919695539804</v>
+      </c>
+      <c r="F24" s="77">
+        <v>21.829909752423987</v>
+      </c>
+      <c r="G24" s="77">
+        <v>25.092997041351765</v>
+      </c>
+      <c r="H24" s="70" t="s">
         <v>460</v>
       </c>
     </row>
@@ -8430,11 +8431,11 @@
       <c r="B25" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="C25" s="79" t="str">
+      <c r="C25" s="78" t="str">
         <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="79" t="str">
+      <c r="D25" s="78" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -8442,15 +8443,15 @@
         <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F25" s="79" t="str">
+      <c r="F25" s="78" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="79" t="str">
+      <c r="G25" s="78" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="71" t="s">
+      <c r="H25" s="70" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8458,22 +8459,22 @@
       <c r="B26" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="C26" s="80">
+      <c r="C26" s="79">
         <v>-1</v>
       </c>
-      <c r="D26" s="80">
-        <v>0</v>
-      </c>
-      <c r="E26" s="80">
+      <c r="D26" s="79">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="79">
         <v>2</v>
       </c>
-      <c r="F26" s="80">
-        <v>6</v>
-      </c>
-      <c r="G26" s="80">
-        <v>10</v>
-      </c>
-      <c r="H26" s="71" t="s">
+      <c r="F26" s="79">
+        <v>5</v>
+      </c>
+      <c r="G26" s="79">
+        <v>8</v>
+      </c>
+      <c r="H26" s="70" t="s">
         <v>463</v>
       </c>
     </row>
@@ -8481,26 +8482,26 @@
       <c r="B27" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="C27" s="80">
+      <c r="C27" s="79">
         <v>0</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="79">
         <v>0</v>
       </c>
-      <c r="E27" s="81">
-        <v>71</v>
-      </c>
-      <c r="F27" s="76">
-        <v>181</v>
-      </c>
-      <c r="G27" s="76">
-        <v>302</v>
-      </c>
-      <c r="H27" s="71" t="s">
+      <c r="E27" s="80">
+        <v>53</v>
+      </c>
+      <c r="F27" s="75">
+        <v>144</v>
+      </c>
+      <c r="G27" s="75">
+        <v>243</v>
+      </c>
+      <c r="H27" s="70" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>465</v>
       </c>
@@ -8516,125 +8517,133 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="45" t="s">
         <v>469</v>
       </c>
-      <c r="C30" s="82" t="s">
+      <c r="C30" s="81" t="s">
         <v>470</v>
       </c>
-      <c r="D30" s="83" t="s">
+      <c r="D30" s="82" t="s">
         <v>471</v>
       </c>
-      <c r="E30" s="83"/>
-      <c r="F30" s="84" t="s">
+      <c r="E30" s="82"/>
+      <c r="F30" s="83" t="s">
         <v>472</v>
       </c>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
         <v>473</v>
       </c>
-      <c r="C31" s="85" t="s">
+      <c r="C31" s="84" t="s">
         <v>474</v>
       </c>
-      <c r="D31" s="83" t="s">
+      <c r="D31" s="82" t="s">
         <v>475</v>
       </c>
-      <c r="E31" s="83"/>
-      <c r="F31" s="84" t="s">
+      <c r="E31" s="82"/>
+      <c r="F31" s="83" t="s">
         <v>476</v>
       </c>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="45" t="s">
         <v>477</v>
       </c>
       <c r="C32" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D32" s="83" t="s">
+      <c r="D32" s="82" t="s">
         <v>479</v>
       </c>
-      <c r="E32" s="83"/>
-      <c r="F32" s="84" t="s">
+      <c r="E32" s="82"/>
+      <c r="F32" s="83" t="s">
         <v>480</v>
       </c>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="45" t="s">
         <v>481</v>
       </c>
       <c r="C33" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D33" s="83" t="s">
+      <c r="D33" s="82" t="s">
         <v>482</v>
       </c>
-      <c r="E33" s="83"/>
-      <c r="F33" s="84" t="s">
+      <c r="E33" s="82"/>
+      <c r="F33" s="83" t="s">
         <v>483</v>
       </c>
-      <c r="G33" s="84"/>
-      <c r="H33" s="84"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="45" t="s">
         <v>484</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D34" s="83" t="s">
+      <c r="D34" s="82" t="s">
         <v>485</v>
       </c>
-      <c r="E34" s="83"/>
-      <c r="F34" s="84" t="s">
+      <c r="E34" s="82"/>
+      <c r="F34" s="83" t="s">
         <v>486</v>
       </c>
-      <c r="G34" s="84"/>
-      <c r="H34" s="84"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="45" t="s">
         <v>487</v>
       </c>
       <c r="C35" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D35" s="83" t="s">
+      <c r="D35" s="82" t="s">
         <v>488</v>
       </c>
-      <c r="E35" s="83"/>
-      <c r="F35" s="84" t="s">
+      <c r="E35" s="82"/>
+      <c r="F35" s="83" t="s">
         <v>489</v>
       </c>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="45" t="s">
         <v>490</v>
       </c>
       <c r="C36" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="D36" s="83" t="s">
+      <c r="D36" s="82" t="s">
         <v>491</v>
       </c>
-      <c r="E36" s="83"/>
-      <c r="F36" s="84" t="s">
+      <c r="E36" s="82"/>
+      <c r="F36" s="83" t="s">
         <v>492</v>
       </c>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="45" t="s">
@@ -8647,39 +8656,40 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="86" t="s">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="85" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8802,10 +8812,10 @@
       <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B4" s="87"/>
+      <c r="B4" s="86"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
@@ -8814,10 +8824,10 @@
       <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B7" s="87"/>
+      <c r="B7" s="86"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
@@ -8826,10 +8836,10 @@
       <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B10" s="87"/>
+      <c r="B10" s="86"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
@@ -8838,10 +8848,10 @@
       <c r="B12" s="19"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B13" s="87"/>
+      <c r="B13" s="86"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
@@ -8850,10 +8860,10 @@
       <c r="B15" s="19"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B16" s="87"/>
+      <c r="B16" s="86"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
@@ -8862,10 +8872,10 @@
       <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B19" s="87"/>
+      <c r="B19" s="86"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
@@ -8874,10 +8884,10 @@
       <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B22" s="87"/>
+      <c r="B22" s="86"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
@@ -8886,10 +8896,10 @@
       <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B25" s="87"/>
+      <c r="B25" s="86"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
@@ -8898,10 +8908,10 @@
       <c r="B27" s="19"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="B28" s="87"/>
+      <c r="B28" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8945,18 +8955,18 @@
       <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="87" t="s">
         <v>507</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="88" t="s">
         <v>508</v>
       </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9003,26 +9013,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="90" t="s">
         <v>511</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9159,7 +9169,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -9168,7 +9178,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -10349,7 +10358,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10933,7 +10942,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>230</v>
       </c>
@@ -10942,7 +10951,6 @@
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
@@ -11045,7 +11053,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
